--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D95D93E-D539-42EE-8083-5DB0FAA2F6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2766265C-0C38-415A-A722-38C588AA0C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PRODUTOS B" sheetId="1" r:id="rId1"/>
@@ -5110,6 +5110,51 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5127,12 +5172,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5142,43 +5181,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5193,14 +5196,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5221,10 +5221,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5546,83 +5546,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="126"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="128"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="111"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="128"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="111"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="128"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="128"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="108"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="111"/>
+      <c r="A6" s="127"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="128"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="114"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="125"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="117"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="122" t="s">
+      <c r="A9" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="120"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -7308,20 +7308,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="121"/>
-      <c r="B109" s="109"/>
-      <c r="C109" s="109"/>
-      <c r="D109" s="110"/>
-      <c r="E109" s="117"/>
+      <c r="A109" s="102"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="103"/>
+      <c r="D109" s="104"/>
+      <c r="E109" s="105"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="122" t="s">
+      <c r="A110" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="119"/>
-      <c r="C110" s="119"/>
-      <c r="D110" s="119"/>
-      <c r="E110" s="120"/>
+      <c r="B110" s="112"/>
+      <c r="C110" s="112"/>
+      <c r="D110" s="112"/>
+      <c r="E110" s="113"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7613,20 +7613,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="121"/>
-      <c r="B128" s="109"/>
-      <c r="C128" s="109"/>
-      <c r="D128" s="110"/>
-      <c r="E128" s="117"/>
+      <c r="A128" s="102"/>
+      <c r="B128" s="103"/>
+      <c r="C128" s="103"/>
+      <c r="D128" s="104"/>
+      <c r="E128" s="105"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="122" t="s">
+      <c r="A129" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="119"/>
-      <c r="C129" s="119"/>
-      <c r="D129" s="119"/>
-      <c r="E129" s="120"/>
+      <c r="B129" s="112"/>
+      <c r="C129" s="112"/>
+      <c r="D129" s="112"/>
+      <c r="E129" s="113"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7782,20 +7782,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="121"/>
-      <c r="B139" s="109"/>
-      <c r="C139" s="109"/>
-      <c r="D139" s="110"/>
-      <c r="E139" s="117"/>
+      <c r="A139" s="102"/>
+      <c r="B139" s="103"/>
+      <c r="C139" s="103"/>
+      <c r="D139" s="104"/>
+      <c r="E139" s="105"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="126" t="s">
+      <c r="A140" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="119"/>
-      <c r="C140" s="119"/>
-      <c r="D140" s="119"/>
-      <c r="E140" s="127"/>
+      <c r="B140" s="112"/>
+      <c r="C140" s="112"/>
+      <c r="D140" s="112"/>
+      <c r="E140" s="120"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -9039,20 +9039,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="121"/>
-      <c r="B214" s="109"/>
-      <c r="C214" s="109"/>
-      <c r="D214" s="110"/>
-      <c r="E214" s="117"/>
+      <c r="A214" s="102"/>
+      <c r="B214" s="103"/>
+      <c r="C214" s="103"/>
+      <c r="D214" s="104"/>
+      <c r="E214" s="105"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="122" t="s">
+      <c r="A215" s="118" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="119"/>
-      <c r="C215" s="119"/>
-      <c r="D215" s="119"/>
-      <c r="E215" s="120"/>
+      <c r="B215" s="112"/>
+      <c r="C215" s="112"/>
+      <c r="D215" s="112"/>
+      <c r="E215" s="113"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -10260,20 +10260,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="116"/>
-      <c r="B287" s="109"/>
-      <c r="C287" s="109"/>
-      <c r="D287" s="110"/>
-      <c r="E287" s="117"/>
+      <c r="A287" s="114"/>
+      <c r="B287" s="103"/>
+      <c r="C287" s="103"/>
+      <c r="D287" s="104"/>
+      <c r="E287" s="105"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="122" t="s">
+      <c r="A288" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="119"/>
-      <c r="C288" s="119"/>
-      <c r="D288" s="119"/>
-      <c r="E288" s="120"/>
+      <c r="B288" s="112"/>
+      <c r="C288" s="112"/>
+      <c r="D288" s="112"/>
+      <c r="E288" s="113"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -10992,7 +10992,7 @@
         <v>211</v>
       </c>
       <c r="B331" s="69" t="s">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="C331" s="70">
         <v>3621</v>
@@ -11001,7 +11001,7 @@
         <v>84</v>
       </c>
       <c r="E331" s="40">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="332" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -11838,20 +11838,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="116"/>
-      <c r="B381" s="109"/>
-      <c r="C381" s="109"/>
-      <c r="D381" s="110"/>
-      <c r="E381" s="117"/>
+      <c r="A381" s="114"/>
+      <c r="B381" s="103"/>
+      <c r="C381" s="103"/>
+      <c r="D381" s="104"/>
+      <c r="E381" s="105"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="118" t="s">
+      <c r="A382" s="111" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="119"/>
-      <c r="C382" s="119"/>
-      <c r="D382" s="119"/>
-      <c r="E382" s="120"/>
+      <c r="B382" s="112"/>
+      <c r="C382" s="112"/>
+      <c r="D382" s="112"/>
+      <c r="E382" s="113"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12505,13 +12505,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="118" t="s">
+      <c r="A422" s="111" t="s">
         <v>1304</v>
       </c>
-      <c r="B422" s="119"/>
-      <c r="C422" s="119"/>
-      <c r="D422" s="119"/>
-      <c r="E422" s="120"/>
+      <c r="B422" s="112"/>
+      <c r="C422" s="112"/>
+      <c r="D422" s="112"/>
+      <c r="E422" s="113"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -14448,20 +14448,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="116"/>
-      <c r="B537" s="109"/>
-      <c r="C537" s="109"/>
-      <c r="D537" s="110"/>
-      <c r="E537" s="117"/>
+      <c r="A537" s="114"/>
+      <c r="B537" s="103"/>
+      <c r="C537" s="103"/>
+      <c r="D537" s="104"/>
+      <c r="E537" s="105"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="118" t="s">
+      <c r="A538" s="111" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="119"/>
-      <c r="C538" s="119"/>
-      <c r="D538" s="119"/>
-      <c r="E538" s="120"/>
+      <c r="B538" s="112"/>
+      <c r="C538" s="112"/>
+      <c r="D538" s="112"/>
+      <c r="E538" s="113"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14819,20 +14819,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="116"/>
-      <c r="B560" s="109"/>
-      <c r="C560" s="109"/>
-      <c r="D560" s="110"/>
-      <c r="E560" s="117"/>
+      <c r="A560" s="114"/>
+      <c r="B560" s="103"/>
+      <c r="C560" s="103"/>
+      <c r="D560" s="104"/>
+      <c r="E560" s="105"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="118" t="s">
+      <c r="A561" s="111" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="119"/>
-      <c r="C561" s="119"/>
-      <c r="D561" s="119"/>
-      <c r="E561" s="120"/>
+      <c r="B561" s="112"/>
+      <c r="C561" s="112"/>
+      <c r="D561" s="112"/>
+      <c r="E561" s="113"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15428,20 +15428,20 @@
       </c>
     </row>
     <row r="597" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="128"/>
-      <c r="B597" s="129"/>
-      <c r="C597" s="129"/>
-      <c r="D597" s="129"/>
-      <c r="E597" s="129"/>
+      <c r="A597" s="106"/>
+      <c r="B597" s="107"/>
+      <c r="C597" s="107"/>
+      <c r="D597" s="107"/>
+      <c r="E597" s="107"/>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="118" t="s">
+      <c r="A598" s="111" t="s">
         <v>370</v>
       </c>
-      <c r="B598" s="119"/>
-      <c r="C598" s="119"/>
-      <c r="D598" s="119"/>
-      <c r="E598" s="120"/>
+      <c r="B598" s="112"/>
+      <c r="C598" s="112"/>
+      <c r="D598" s="112"/>
+      <c r="E598" s="113"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="66" t="s">
@@ -17400,20 +17400,20 @@
       </c>
     </row>
     <row r="714" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A714" s="116"/>
-      <c r="B714" s="109"/>
-      <c r="C714" s="109"/>
-      <c r="D714" s="110"/>
-      <c r="E714" s="117"/>
+      <c r="A714" s="114"/>
+      <c r="B714" s="103"/>
+      <c r="C714" s="103"/>
+      <c r="D714" s="104"/>
+      <c r="E714" s="105"/>
     </row>
     <row r="715" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A715" s="118" t="s">
+      <c r="A715" s="111" t="s">
         <v>420</v>
       </c>
-      <c r="B715" s="119"/>
-      <c r="C715" s="119"/>
-      <c r="D715" s="119"/>
-      <c r="E715" s="120"/>
+      <c r="B715" s="112"/>
+      <c r="C715" s="112"/>
+      <c r="D715" s="112"/>
+      <c r="E715" s="113"/>
     </row>
     <row r="716" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="66" t="s">
@@ -17591,13 +17591,13 @@
       <c r="E726" s="61"/>
     </row>
     <row r="727" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A727" s="118" t="s">
+      <c r="A727" s="111" t="s">
         <v>1305</v>
       </c>
-      <c r="B727" s="119"/>
-      <c r="C727" s="119"/>
-      <c r="D727" s="119"/>
-      <c r="E727" s="120"/>
+      <c r="B727" s="112"/>
+      <c r="C727" s="112"/>
+      <c r="D727" s="112"/>
+      <c r="E727" s="113"/>
     </row>
     <row r="728" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A728" s="72" t="s">
@@ -17719,20 +17719,20 @@
       </c>
     </row>
     <row r="735" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A735" s="121"/>
-      <c r="B735" s="109"/>
-      <c r="C735" s="109"/>
-      <c r="D735" s="110"/>
-      <c r="E735" s="117"/>
+      <c r="A735" s="102"/>
+      <c r="B735" s="103"/>
+      <c r="C735" s="103"/>
+      <c r="D735" s="104"/>
+      <c r="E735" s="105"/>
     </row>
     <row r="736" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A736" s="118" t="s">
+      <c r="A736" s="111" t="s">
         <v>421</v>
       </c>
-      <c r="B736" s="119"/>
-      <c r="C736" s="119"/>
-      <c r="D736" s="119"/>
-      <c r="E736" s="120"/>
+      <c r="B736" s="112"/>
+      <c r="C736" s="112"/>
+      <c r="D736" s="112"/>
+      <c r="E736" s="113"/>
     </row>
     <row r="737" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A737" s="66" t="s">
@@ -17886,20 +17886,20 @@
       </c>
     </row>
     <row r="746" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A746" s="121"/>
-      <c r="B746" s="109"/>
-      <c r="C746" s="109"/>
-      <c r="D746" s="110"/>
-      <c r="E746" s="117"/>
+      <c r="A746" s="102"/>
+      <c r="B746" s="103"/>
+      <c r="C746" s="103"/>
+      <c r="D746" s="104"/>
+      <c r="E746" s="105"/>
     </row>
     <row r="747" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A747" s="118" t="s">
+      <c r="A747" s="111" t="s">
         <v>1303</v>
       </c>
-      <c r="B747" s="119"/>
-      <c r="C747" s="119"/>
-      <c r="D747" s="119"/>
-      <c r="E747" s="120"/>
+      <c r="B747" s="112"/>
+      <c r="C747" s="112"/>
+      <c r="D747" s="112"/>
+      <c r="E747" s="113"/>
     </row>
     <row r="748" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A748" s="66" t="s">
@@ -18329,13 +18329,13 @@
       <c r="E772" s="98"/>
     </row>
     <row r="773" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A773" s="130" t="s">
+      <c r="A773" s="108" t="s">
         <v>1289</v>
       </c>
-      <c r="B773" s="131"/>
-      <c r="C773" s="131"/>
-      <c r="D773" s="131"/>
-      <c r="E773" s="132"/>
+      <c r="B773" s="109"/>
+      <c r="C773" s="109"/>
+      <c r="D773" s="109"/>
+      <c r="E773" s="110"/>
     </row>
     <row r="774" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="66" t="s">
@@ -20280,13 +20280,13 @@
       <c r="E889" s="100"/>
     </row>
     <row r="890" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A890" s="102" t="s">
+      <c r="A890" s="121" t="s">
         <v>1290</v>
       </c>
-      <c r="B890" s="103"/>
-      <c r="C890" s="103"/>
-      <c r="D890" s="103"/>
-      <c r="E890" s="104"/>
+      <c r="B890" s="122"/>
+      <c r="C890" s="122"/>
+      <c r="D890" s="122"/>
+      <c r="E890" s="123"/>
     </row>
     <row r="891" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A891" s="87" t="s">
@@ -20559,27 +20559,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A735:E735"/>
-    <mergeCell ref="A597:E597"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A773:E773"/>
-    <mergeCell ref="A727:E727"/>
-    <mergeCell ref="A746:E746"/>
-    <mergeCell ref="A747:E747"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A538:E538"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A422:E422"/>
-    <mergeCell ref="A382:E382"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A381:E381"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A215:E215"/>
     <mergeCell ref="A890:E890"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
@@ -20596,6 +20575,27 @@
     <mergeCell ref="A560:E560"/>
     <mergeCell ref="A714:E714"/>
     <mergeCell ref="A288:E288"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A538:E538"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A422:E422"/>
+    <mergeCell ref="A382:E382"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A215:E215"/>
+    <mergeCell ref="A735:E735"/>
+    <mergeCell ref="A597:E597"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A773:E773"/>
+    <mergeCell ref="A727:E727"/>
+    <mergeCell ref="A746:E746"/>
+    <mergeCell ref="A747:E747"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20635,78 +20635,78 @@
       <c r="A2" s="148" t="s">
         <v>486</v>
       </c>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="138"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="139"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="150" t="s">
         <v>487</v>
       </c>
-      <c r="B3" s="134"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="138"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="139"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="149" t="s">
+      <c r="A4" s="138" t="s">
         <v>488</v>
       </c>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="138"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="139"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="150" t="s">
         <v>489</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="138"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="139"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="134"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="138"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="139"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>490</v>
       </c>
-      <c r="B7" s="134"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="138"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="139"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="138"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="139"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="138"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="139"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="150" t="s">
+      <c r="A10" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22429,19 +22429,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="133"/>
-      <c r="B112" s="134"/>
-      <c r="C112" s="135"/>
-      <c r="D112" s="136"/>
+      <c r="A112" s="134"/>
+      <c r="B112" s="135"/>
+      <c r="C112" s="136"/>
+      <c r="D112" s="137"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="140" t="s">
+      <c r="A113" s="149" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="119"/>
-      <c r="C113" s="119"/>
-      <c r="D113" s="127"/>
+      <c r="B113" s="112"/>
+      <c r="C113" s="112"/>
+      <c r="D113" s="120"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22734,19 +22734,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="133"/>
-      <c r="B131" s="134"/>
-      <c r="C131" s="135"/>
-      <c r="D131" s="136"/>
+      <c r="A131" s="134"/>
+      <c r="B131" s="135"/>
+      <c r="C131" s="136"/>
+      <c r="D131" s="137"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="140" t="s">
+      <c r="A132" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="119"/>
-      <c r="C132" s="119"/>
-      <c r="D132" s="127"/>
+      <c r="B132" s="112"/>
+      <c r="C132" s="112"/>
+      <c r="D132" s="120"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22920,19 +22920,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="133"/>
-      <c r="B143" s="134"/>
-      <c r="C143" s="135"/>
-      <c r="D143" s="136"/>
+      <c r="A143" s="134"/>
+      <c r="B143" s="135"/>
+      <c r="C143" s="136"/>
+      <c r="D143" s="137"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="140" t="s">
+      <c r="A144" s="149" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="119"/>
-      <c r="C144" s="119"/>
-      <c r="D144" s="127"/>
+      <c r="B144" s="112"/>
+      <c r="C144" s="112"/>
+      <c r="D144" s="120"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23565,19 +23565,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="133"/>
-      <c r="B182" s="134"/>
-      <c r="C182" s="135"/>
-      <c r="D182" s="136"/>
+      <c r="A182" s="134"/>
+      <c r="B182" s="135"/>
+      <c r="C182" s="136"/>
+      <c r="D182" s="137"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="139" t="s">
+      <c r="A183" s="133" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="119"/>
-      <c r="C183" s="119"/>
-      <c r="D183" s="119"/>
+      <c r="B183" s="112"/>
+      <c r="C183" s="112"/>
+      <c r="D183" s="112"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24439,19 +24439,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="133"/>
-      <c r="B241" s="134"/>
-      <c r="C241" s="135"/>
-      <c r="D241" s="136"/>
+      <c r="A241" s="134"/>
+      <c r="B241" s="135"/>
+      <c r="C241" s="136"/>
+      <c r="D241" s="137"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="139" t="s">
+      <c r="A242" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="119"/>
-      <c r="C242" s="119"/>
-      <c r="D242" s="119"/>
+      <c r="B242" s="112"/>
+      <c r="C242" s="112"/>
+      <c r="D242" s="112"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25672,21 +25672,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="133"/>
-      <c r="B324" s="134"/>
-      <c r="C324" s="135"/>
-      <c r="D324" s="136"/>
+      <c r="A324" s="134"/>
+      <c r="B324" s="135"/>
+      <c r="C324" s="136"/>
+      <c r="D324" s="137"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="139" t="s">
+      <c r="A325" s="133" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="119"/>
-      <c r="C325" s="119"/>
-      <c r="D325" s="119"/>
+      <c r="B325" s="112"/>
+      <c r="C325" s="112"/>
+      <c r="D325" s="112"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26183,19 +26183,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="133"/>
-      <c r="B355" s="134"/>
-      <c r="C355" s="135"/>
-      <c r="D355" s="136"/>
+      <c r="A355" s="134"/>
+      <c r="B355" s="135"/>
+      <c r="C355" s="136"/>
+      <c r="D355" s="137"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="139" t="s">
+      <c r="A356" s="133" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="119"/>
-      <c r="C356" s="119"/>
-      <c r="D356" s="119"/>
+      <c r="B356" s="112"/>
+      <c r="C356" s="112"/>
+      <c r="D356" s="112"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -27950,19 +27950,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="133"/>
-      <c r="B460" s="134"/>
-      <c r="C460" s="135"/>
-      <c r="D460" s="136"/>
+      <c r="A460" s="134"/>
+      <c r="B460" s="135"/>
+      <c r="C460" s="136"/>
+      <c r="D460" s="137"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="139" t="s">
+      <c r="A461" s="133" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="119"/>
-      <c r="C461" s="119"/>
-      <c r="D461" s="119"/>
+      <c r="B461" s="112"/>
+      <c r="C461" s="112"/>
+      <c r="D461" s="112"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28255,19 +28255,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="133"/>
-      <c r="B479" s="134"/>
-      <c r="C479" s="135"/>
-      <c r="D479" s="136"/>
+      <c r="A479" s="134"/>
+      <c r="B479" s="135"/>
+      <c r="C479" s="136"/>
+      <c r="D479" s="137"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="139" t="s">
+      <c r="A480" s="133" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="119"/>
-      <c r="C480" s="119"/>
-      <c r="D480" s="119"/>
+      <c r="B480" s="112"/>
+      <c r="C480" s="112"/>
+      <c r="D480" s="112"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28696,19 +28696,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="133"/>
-      <c r="B506" s="134"/>
-      <c r="C506" s="135"/>
-      <c r="D506" s="136"/>
+      <c r="A506" s="134"/>
+      <c r="B506" s="135"/>
+      <c r="C506" s="136"/>
+      <c r="D506" s="137"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="139" t="s">
+      <c r="A507" s="133" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="119"/>
-      <c r="C507" s="119"/>
-      <c r="D507" s="119"/>
+      <c r="B507" s="112"/>
+      <c r="C507" s="112"/>
+      <c r="D507" s="112"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30223,19 +30223,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="133"/>
-      <c r="B597" s="134"/>
-      <c r="C597" s="135"/>
-      <c r="D597" s="136"/>
+      <c r="A597" s="134"/>
+      <c r="B597" s="135"/>
+      <c r="C597" s="136"/>
+      <c r="D597" s="137"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="139" t="s">
+      <c r="A598" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="119"/>
-      <c r="C598" s="119"/>
-      <c r="D598" s="119"/>
+      <c r="B598" s="112"/>
+      <c r="C598" s="112"/>
+      <c r="D598" s="112"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30375,20 +30375,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="133"/>
-      <c r="B607" s="134"/>
-      <c r="C607" s="135"/>
-      <c r="D607" s="136"/>
+      <c r="A607" s="134"/>
+      <c r="B607" s="135"/>
+      <c r="C607" s="136"/>
+      <c r="D607" s="137"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="139" t="s">
+      <c r="A608" s="133" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="119"/>
-      <c r="C608" s="119"/>
-      <c r="D608" s="119"/>
+      <c r="B608" s="112"/>
+      <c r="C608" s="112"/>
+      <c r="D608" s="112"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30477,19 +30477,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="133"/>
-      <c r="B614" s="134"/>
-      <c r="C614" s="135"/>
-      <c r="D614" s="136"/>
+      <c r="A614" s="134"/>
+      <c r="B614" s="135"/>
+      <c r="C614" s="136"/>
+      <c r="D614" s="137"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="139" t="s">
+      <c r="A615" s="133" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="119"/>
-      <c r="C615" s="119"/>
-      <c r="D615" s="119"/>
+      <c r="B615" s="112"/>
+      <c r="C615" s="112"/>
+      <c r="D615" s="112"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31854,6 +31854,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31870,25 +31889,6 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2766265C-0C38-415A-A722-38C588AA0C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D8C31A-35AA-4EFD-A8FC-B554C14EB381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="LISTA DE PRODUTOS T" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PRODUTOS B'!$A$1:$E$905</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PRODUTOS B'!$A$1:$E$907</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4015" uniqueCount="1335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4021" uniqueCount="1337">
   <si>
     <t xml:space="preserve">    Tabela de Produtos e Preços</t>
   </si>
@@ -4030,6 +4030,12 @@
   </si>
   <si>
     <t>SAL MARINHO INTEGRAL OUROMAR CHURRASCO</t>
+  </si>
+  <si>
+    <t>MACA PERUANA NEGRA DJ</t>
+  </si>
+  <si>
+    <t>MACA PERUANA VERMELHA DJ</t>
   </si>
 </sst>
 </file>
@@ -5110,51 +5116,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5172,6 +5133,12 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5181,7 +5148,43 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5196,11 +5199,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5221,10 +5227,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5533,7 +5539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R916"/>
+  <dimension ref="A1:R918"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62.1640625" style="64" bestFit="1" customWidth="1"/>
@@ -5546,83 +5552,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="126"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="128"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127" t="s">
+      <c r="A3" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="128"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127" t="s">
+      <c r="A4" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="128"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="111"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="128"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="128"/>
+      <c r="A6" s="108"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="132"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="117"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="125"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="120"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -7308,20 +7314,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="102"/>
-      <c r="B109" s="103"/>
-      <c r="C109" s="103"/>
-      <c r="D109" s="104"/>
-      <c r="E109" s="105"/>
+      <c r="A109" s="121"/>
+      <c r="B109" s="109"/>
+      <c r="C109" s="109"/>
+      <c r="D109" s="110"/>
+      <c r="E109" s="117"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="118" t="s">
+      <c r="A110" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="112"/>
-      <c r="C110" s="112"/>
-      <c r="D110" s="112"/>
-      <c r="E110" s="113"/>
+      <c r="B110" s="119"/>
+      <c r="C110" s="119"/>
+      <c r="D110" s="119"/>
+      <c r="E110" s="120"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7613,20 +7619,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="102"/>
-      <c r="B128" s="103"/>
-      <c r="C128" s="103"/>
-      <c r="D128" s="104"/>
-      <c r="E128" s="105"/>
+      <c r="A128" s="121"/>
+      <c r="B128" s="109"/>
+      <c r="C128" s="109"/>
+      <c r="D128" s="110"/>
+      <c r="E128" s="117"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="118" t="s">
+      <c r="A129" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="112"/>
-      <c r="C129" s="112"/>
-      <c r="D129" s="112"/>
-      <c r="E129" s="113"/>
+      <c r="B129" s="119"/>
+      <c r="C129" s="119"/>
+      <c r="D129" s="119"/>
+      <c r="E129" s="120"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7782,20 +7788,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="102"/>
-      <c r="B139" s="103"/>
-      <c r="C139" s="103"/>
-      <c r="D139" s="104"/>
-      <c r="E139" s="105"/>
+      <c r="A139" s="121"/>
+      <c r="B139" s="109"/>
+      <c r="C139" s="109"/>
+      <c r="D139" s="110"/>
+      <c r="E139" s="117"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="119" t="s">
+      <c r="A140" s="126" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="112"/>
-      <c r="C140" s="112"/>
-      <c r="D140" s="112"/>
-      <c r="E140" s="120"/>
+      <c r="B140" s="119"/>
+      <c r="C140" s="119"/>
+      <c r="D140" s="119"/>
+      <c r="E140" s="127"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -9039,20 +9045,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="102"/>
-      <c r="B214" s="103"/>
-      <c r="C214" s="103"/>
-      <c r="D214" s="104"/>
-      <c r="E214" s="105"/>
+      <c r="A214" s="121"/>
+      <c r="B214" s="109"/>
+      <c r="C214" s="109"/>
+      <c r="D214" s="110"/>
+      <c r="E214" s="117"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="118" t="s">
+      <c r="A215" s="122" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="112"/>
-      <c r="C215" s="112"/>
-      <c r="D215" s="112"/>
-      <c r="E215" s="113"/>
+      <c r="B215" s="119"/>
+      <c r="C215" s="119"/>
+      <c r="D215" s="119"/>
+      <c r="E215" s="120"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -10260,20 +10266,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="114"/>
-      <c r="B287" s="103"/>
-      <c r="C287" s="103"/>
-      <c r="D287" s="104"/>
-      <c r="E287" s="105"/>
+      <c r="A287" s="116"/>
+      <c r="B287" s="109"/>
+      <c r="C287" s="109"/>
+      <c r="D287" s="110"/>
+      <c r="E287" s="117"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="118" t="s">
+      <c r="A288" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="112"/>
-      <c r="C288" s="112"/>
-      <c r="D288" s="112"/>
-      <c r="E288" s="113"/>
+      <c r="B288" s="119"/>
+      <c r="C288" s="119"/>
+      <c r="D288" s="119"/>
+      <c r="E288" s="120"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -11838,20 +11844,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="114"/>
-      <c r="B381" s="103"/>
-      <c r="C381" s="103"/>
-      <c r="D381" s="104"/>
-      <c r="E381" s="105"/>
+      <c r="A381" s="116"/>
+      <c r="B381" s="109"/>
+      <c r="C381" s="109"/>
+      <c r="D381" s="110"/>
+      <c r="E381" s="117"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="111" t="s">
+      <c r="A382" s="118" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="112"/>
-      <c r="C382" s="112"/>
-      <c r="D382" s="112"/>
-      <c r="E382" s="113"/>
+      <c r="B382" s="119"/>
+      <c r="C382" s="119"/>
+      <c r="D382" s="119"/>
+      <c r="E382" s="120"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12505,13 +12511,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="111" t="s">
+      <c r="A422" s="118" t="s">
         <v>1304</v>
       </c>
-      <c r="B422" s="112"/>
-      <c r="C422" s="112"/>
-      <c r="D422" s="112"/>
-      <c r="E422" s="113"/>
+      <c r="B422" s="119"/>
+      <c r="C422" s="119"/>
+      <c r="D422" s="119"/>
+      <c r="E422" s="120"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -14448,20 +14454,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="114"/>
-      <c r="B537" s="103"/>
-      <c r="C537" s="103"/>
-      <c r="D537" s="104"/>
-      <c r="E537" s="105"/>
+      <c r="A537" s="116"/>
+      <c r="B537" s="109"/>
+      <c r="C537" s="109"/>
+      <c r="D537" s="110"/>
+      <c r="E537" s="117"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="111" t="s">
+      <c r="A538" s="118" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="112"/>
-      <c r="C538" s="112"/>
-      <c r="D538" s="112"/>
-      <c r="E538" s="113"/>
+      <c r="B538" s="119"/>
+      <c r="C538" s="119"/>
+      <c r="D538" s="119"/>
+      <c r="E538" s="120"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14819,20 +14825,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="114"/>
-      <c r="B560" s="103"/>
-      <c r="C560" s="103"/>
-      <c r="D560" s="104"/>
-      <c r="E560" s="105"/>
+      <c r="A560" s="116"/>
+      <c r="B560" s="109"/>
+      <c r="C560" s="109"/>
+      <c r="D560" s="110"/>
+      <c r="E560" s="117"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="111" t="s">
+      <c r="A561" s="118" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="112"/>
-      <c r="C561" s="112"/>
-      <c r="D561" s="112"/>
-      <c r="E561" s="113"/>
+      <c r="B561" s="119"/>
+      <c r="C561" s="119"/>
+      <c r="D561" s="119"/>
+      <c r="E561" s="120"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15428,20 +15434,20 @@
       </c>
     </row>
     <row r="597" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="106"/>
-      <c r="B597" s="107"/>
-      <c r="C597" s="107"/>
-      <c r="D597" s="107"/>
-      <c r="E597" s="107"/>
+      <c r="A597" s="128"/>
+      <c r="B597" s="129"/>
+      <c r="C597" s="129"/>
+      <c r="D597" s="129"/>
+      <c r="E597" s="129"/>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="111" t="s">
+      <c r="A598" s="118" t="s">
         <v>370</v>
       </c>
-      <c r="B598" s="112"/>
-      <c r="C598" s="112"/>
-      <c r="D598" s="112"/>
-      <c r="E598" s="113"/>
+      <c r="B598" s="119"/>
+      <c r="C598" s="119"/>
+      <c r="D598" s="119"/>
+      <c r="E598" s="120"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="66" t="s">
@@ -16838,38 +16844,38 @@
         <v>270</v>
       </c>
     </row>
-    <row r="681" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="69" t="s">
-        <v>408</v>
+        <v>1335</v>
       </c>
       <c r="B681" s="69" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="C681" s="70">
-        <v>4204</v>
+        <v>4566</v>
       </c>
       <c r="D681" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E681" s="40">
-        <v>145.5</v>
-      </c>
-    </row>
-    <row r="682" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="69" t="s">
-        <v>408</v>
+        <v>1336</v>
       </c>
       <c r="B682" s="69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C682" s="70">
-        <v>4205</v>
+        <v>4567</v>
       </c>
       <c r="D682" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E682" s="40">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="683" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16877,186 +16883,186 @@
         <v>408</v>
       </c>
       <c r="B683" s="69" t="s">
-        <v>33</v>
+        <v>319</v>
       </c>
       <c r="C683" s="70">
-        <v>4225</v>
+        <v>4204</v>
       </c>
       <c r="D683" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E683" s="40">
-        <v>900</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="684" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="69" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B684" s="69" t="s">
         <v>18</v>
       </c>
       <c r="C684" s="70">
-        <v>4378</v>
+        <v>4205</v>
       </c>
       <c r="D684" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E684" s="40">
-        <v>430</v>
+        <v>360</v>
       </c>
     </row>
     <row r="685" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="69" t="s">
+        <v>408</v>
+      </c>
+      <c r="B685" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="C685" s="70">
+        <v>4225</v>
+      </c>
+      <c r="D685" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E685" s="40">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A686" s="69" t="s">
         <v>409</v>
       </c>
-      <c r="B685" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="C685" s="70">
-        <v>4379</v>
-      </c>
-      <c r="D685" s="69" t="s">
+      <c r="B686" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C686" s="70">
+        <v>4378</v>
+      </c>
+      <c r="D686" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="E685" s="40">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="686" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A686" s="69" t="s">
-        <v>410</v>
-      </c>
-      <c r="B686" s="69" t="s">
-        <v>411</v>
-      </c>
-      <c r="C686" s="70">
-        <v>3524</v>
-      </c>
-      <c r="D686" s="69" t="s">
-        <v>412</v>
-      </c>
       <c r="E686" s="40">
-        <v>350</v>
+        <v>430</v>
       </c>
     </row>
     <row r="687" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="69" t="s">
+        <v>409</v>
+      </c>
+      <c r="B687" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="C687" s="70">
+        <v>4379</v>
+      </c>
+      <c r="D687" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E687" s="40">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="688" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A688" s="69" t="s">
         <v>410</v>
       </c>
-      <c r="B687" s="69" t="s">
-        <v>110</v>
-      </c>
-      <c r="C687" s="70">
-        <v>3523</v>
-      </c>
-      <c r="D687" s="69" t="s">
+      <c r="B688" s="69" t="s">
+        <v>411</v>
+      </c>
+      <c r="C688" s="70">
+        <v>3524</v>
+      </c>
+      <c r="D688" s="69" t="s">
         <v>412</v>
       </c>
-      <c r="E687" s="40">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="688" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A688" s="69" t="s">
-        <v>1164</v>
-      </c>
-      <c r="B688" s="69" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C688" s="70">
-        <v>3521</v>
-      </c>
-      <c r="D688" s="69" t="s">
-        <v>15</v>
-      </c>
       <c r="E688" s="40">
-        <v>158</v>
+        <v>350</v>
       </c>
     </row>
     <row r="689" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="69" t="s">
+        <v>410</v>
+      </c>
+      <c r="B689" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="C689" s="70">
+        <v>3523</v>
+      </c>
+      <c r="D689" s="69" t="s">
+        <v>412</v>
+      </c>
+      <c r="E689" s="40">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="690" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A690" s="69" t="s">
         <v>1164</v>
       </c>
-      <c r="B689" s="69" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C689" s="70">
-        <v>3522</v>
-      </c>
-      <c r="D689" s="69" t="s">
+      <c r="B690" s="69" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C690" s="70">
+        <v>3521</v>
+      </c>
+      <c r="D690" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E689" s="40">
-        <v>216.5</v>
-      </c>
-    </row>
-    <row r="690" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A690" s="72" t="s">
-        <v>1167</v>
-      </c>
-      <c r="B690" s="72" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C690" s="73">
-        <v>64</v>
-      </c>
-      <c r="D690" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="E690" s="50">
-        <v>132</v>
+      <c r="E690" s="40">
+        <v>158</v>
       </c>
     </row>
     <row r="691" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="69" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="B691" s="69" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C691" s="70">
-        <v>90</v>
+        <v>3522</v>
       </c>
       <c r="D691" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E691" s="40">
+        <v>216.5</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A692" s="72" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B692" s="72" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C692" s="73">
+        <v>64</v>
+      </c>
+      <c r="D692" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E692" s="50">
         <v>132</v>
-      </c>
-    </row>
-    <row r="692" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A692" s="69" t="s">
-        <v>413</v>
-      </c>
-      <c r="B692" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C692" s="70">
-        <v>2805</v>
-      </c>
-      <c r="D692" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E692" s="40">
-        <v>160</v>
       </c>
     </row>
     <row r="693" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="69" t="s">
-        <v>413</v>
+        <v>1169</v>
       </c>
       <c r="B693" s="69" t="s">
-        <v>33</v>
+        <v>1168</v>
       </c>
       <c r="C693" s="70">
-        <v>3637</v>
+        <v>90</v>
       </c>
       <c r="D693" s="69" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E693" s="40">
-        <v>400</v>
+        <v>132</v>
       </c>
     </row>
     <row r="694" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17064,231 +17070,231 @@
         <v>413</v>
       </c>
       <c r="B694" s="69" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="C694" s="70">
-        <v>2427</v>
+        <v>2805</v>
       </c>
       <c r="D694" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E694" s="40">
-        <v>49</v>
+        <v>160</v>
       </c>
     </row>
     <row r="695" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="69" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B695" s="69" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C695" s="70">
-        <v>3437</v>
+        <v>3637</v>
       </c>
       <c r="D695" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E695" s="40">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="696" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="69" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B696" s="69" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C696" s="70">
-        <v>3396</v>
+        <v>2427</v>
       </c>
       <c r="D696" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E696" s="40">
-        <v>197</v>
+        <v>49</v>
       </c>
     </row>
     <row r="697" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="69" t="s">
-        <v>1170</v>
+        <v>414</v>
       </c>
       <c r="B697" s="69" t="s">
-        <v>1171</v>
+        <v>18</v>
       </c>
       <c r="C697" s="70">
-        <v>3395</v>
+        <v>3437</v>
       </c>
       <c r="D697" s="69" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E697" s="40">
-        <v>54</v>
+        <v>390</v>
       </c>
     </row>
     <row r="698" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="69" t="s">
-        <v>1172</v>
+        <v>414</v>
       </c>
       <c r="B698" s="69" t="s">
-        <v>1171</v>
+        <v>19</v>
       </c>
       <c r="C698" s="70">
-        <v>3490</v>
+        <v>3396</v>
       </c>
       <c r="D698" s="69" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E698" s="40">
-        <v>169</v>
+        <v>197</v>
       </c>
     </row>
     <row r="699" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="69" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="B699" s="69" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="C699" s="70">
-        <v>458</v>
+        <v>3395</v>
       </c>
       <c r="D699" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E699" s="40">
-        <v>269.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="700" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="69" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="B700" s="69" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="C700" s="70">
-        <v>2641</v>
+        <v>3490</v>
       </c>
       <c r="D700" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E700" s="40">
-        <v>222</v>
+        <v>169</v>
       </c>
     </row>
     <row r="701" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A701" s="75" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B701" s="75" t="s">
+      <c r="A701" s="69" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B701" s="69" t="s">
         <v>1174</v>
       </c>
-      <c r="C701" s="76">
-        <v>4293</v>
+      <c r="C701" s="70">
+        <v>458</v>
       </c>
       <c r="D701" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E701" s="44">
+      <c r="E701" s="40">
+        <v>269.5</v>
+      </c>
+    </row>
+    <row r="702" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A702" s="69" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B702" s="69" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C702" s="70">
+        <v>2641</v>
+      </c>
+      <c r="D702" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E702" s="40">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="703" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A703" s="75" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B703" s="75" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C703" s="76">
+        <v>4293</v>
+      </c>
+      <c r="D703" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E703" s="44">
         <v>210</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A702" s="75" t="s">
+    <row r="704" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A704" s="75" t="s">
         <v>415</v>
       </c>
-      <c r="B702" s="75" t="s">
+      <c r="B704" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C702" s="76">
+      <c r="C704" s="76">
         <v>2396</v>
       </c>
-      <c r="D702" s="75" t="s">
+      <c r="D704" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E702" s="44">
+      <c r="E704" s="44">
         <v>675</v>
-      </c>
-    </row>
-    <row r="703" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A703" s="80" t="s">
-        <v>415</v>
-      </c>
-      <c r="B703" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C703" s="81">
-        <v>2426</v>
-      </c>
-      <c r="D703" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="E703" s="42">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="704" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A704" s="80" t="s">
-        <v>416</v>
-      </c>
-      <c r="B704" s="80" t="s">
-        <v>110</v>
-      </c>
-      <c r="C704" s="81">
-        <v>4335</v>
-      </c>
-      <c r="D704" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="E704" s="42">
-        <v>424.5</v>
       </c>
     </row>
     <row r="705" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="80" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B705" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C705" s="81">
-        <v>4477</v>
+        <v>2426</v>
       </c>
       <c r="D705" s="80" t="s">
         <v>20</v>
       </c>
       <c r="E705" s="42">
-        <v>244.5</v>
+        <v>137</v>
       </c>
     </row>
     <row r="706" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="80" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B706" s="80" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C706" s="81">
-        <v>4479</v>
+        <v>4335</v>
       </c>
       <c r="D706" s="80" t="s">
         <v>20</v>
       </c>
       <c r="E706" s="42">
-        <v>244.5</v>
+        <v>424.5</v>
       </c>
     </row>
     <row r="707" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="80" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B707" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C707" s="81">
-        <v>4478</v>
+        <v>4477</v>
       </c>
       <c r="D707" s="80" t="s">
         <v>20</v>
@@ -17298,37 +17304,37 @@
       </c>
     </row>
     <row r="708" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A708" s="72" t="s">
-        <v>1265</v>
-      </c>
-      <c r="B708" s="72" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C708" s="73">
-        <v>2646</v>
-      </c>
-      <c r="D708" s="72" t="s">
-        <v>177</v>
-      </c>
-      <c r="E708" s="50">
-        <v>50.5</v>
+      <c r="A708" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="B708" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C708" s="81">
+        <v>4479</v>
+      </c>
+      <c r="D708" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E708" s="42">
+        <v>244.5</v>
       </c>
     </row>
     <row r="709" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A709" s="72" t="s">
-        <v>1265</v>
-      </c>
-      <c r="B709" s="72" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C709" s="73">
-        <v>2645</v>
-      </c>
-      <c r="D709" s="72" t="s">
-        <v>177</v>
-      </c>
-      <c r="E709" s="50">
-        <v>78</v>
+      <c r="A709" s="80" t="s">
+        <v>419</v>
+      </c>
+      <c r="B709" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C709" s="81">
+        <v>4478</v>
+      </c>
+      <c r="D709" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E709" s="42">
+        <v>244.5</v>
       </c>
     </row>
     <row r="710" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17336,318 +17342,318 @@
         <v>1265</v>
       </c>
       <c r="B710" s="72" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C710" s="73">
-        <v>2638</v>
+        <v>2646</v>
       </c>
       <c r="D710" s="72" t="s">
         <v>177</v>
       </c>
       <c r="E710" s="50">
-        <v>65</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="711" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="72" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="B711" s="72" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="C711" s="73">
-        <v>4294</v>
+        <v>2645</v>
       </c>
       <c r="D711" s="72" t="s">
         <v>177</v>
       </c>
       <c r="E711" s="50">
-        <v>150</v>
+        <v>78</v>
       </c>
     </row>
     <row r="712" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="72" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="B712" s="72" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="C712" s="73">
-        <v>4314</v>
+        <v>2638</v>
       </c>
       <c r="D712" s="72" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="E712" s="50">
-        <v>252</v>
+        <v>65</v>
       </c>
     </row>
     <row r="713" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="72" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B713" s="72" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C713" s="73">
+        <v>4294</v>
+      </c>
+      <c r="D713" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="E713" s="50">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="714" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A714" s="72" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B714" s="72" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C714" s="73">
+        <v>4314</v>
+      </c>
+      <c r="D714" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E714" s="50">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="715" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A715" s="72" t="s">
         <v>1273</v>
       </c>
-      <c r="B713" s="72" t="s">
+      <c r="B715" s="72" t="s">
         <v>1274</v>
       </c>
-      <c r="C713" s="73">
+      <c r="C715" s="73">
         <v>4315</v>
       </c>
-      <c r="D713" s="72" t="s">
+      <c r="D715" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="E713" s="50">
+      <c r="E715" s="50">
         <v>450</v>
       </c>
     </row>
-    <row r="714" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A714" s="114"/>
-      <c r="B714" s="103"/>
-      <c r="C714" s="103"/>
-      <c r="D714" s="104"/>
-      <c r="E714" s="105"/>
-    </row>
-    <row r="715" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A715" s="111" t="s">
+    <row r="716" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A716" s="116"/>
+      <c r="B716" s="109"/>
+      <c r="C716" s="109"/>
+      <c r="D716" s="110"/>
+      <c r="E716" s="117"/>
+    </row>
+    <row r="717" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A717" s="118" t="s">
         <v>420</v>
       </c>
-      <c r="B715" s="112"/>
-      <c r="C715" s="112"/>
-      <c r="D715" s="112"/>
-      <c r="E715" s="113"/>
-    </row>
-    <row r="716" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A716" s="66" t="s">
+      <c r="B717" s="119"/>
+      <c r="C717" s="119"/>
+      <c r="D717" s="119"/>
+      <c r="E717" s="120"/>
+    </row>
+    <row r="718" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A718" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B716" s="66"/>
-      <c r="C716" s="66" t="s">
+      <c r="B718" s="66"/>
+      <c r="C718" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D716" s="66" t="s">
+      <c r="D718" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E716" s="46" t="s">
+      <c r="E718" s="46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A717" s="69" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B717" s="69" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C717" s="70">
-        <v>3402</v>
-      </c>
-      <c r="D717" s="69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E717" s="40">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="718" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A718" s="69" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B718" s="69" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C718" s="70">
-        <v>3401</v>
-      </c>
-      <c r="D718" s="69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E718" s="40">
-        <v>66.5</v>
-      </c>
-    </row>
-    <row r="719" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="69" t="s">
         <v>1178</v>
       </c>
       <c r="B719" s="69" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C719" s="70">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="D719" s="69" t="s">
         <v>177</v>
       </c>
       <c r="E719" s="40">
-        <v>38.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="720" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="69" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="B720" s="69" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="C720" s="70">
-        <v>4032</v>
+        <v>3401</v>
       </c>
       <c r="D720" s="69" t="s">
         <v>177</v>
       </c>
       <c r="E720" s="40">
-        <v>57.5</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="721" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="69" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B721" s="75" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C721" s="76">
-        <v>4460</v>
+        <v>1178</v>
+      </c>
+      <c r="B721" s="69" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C721" s="70">
+        <v>3403</v>
       </c>
       <c r="D721" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="E721" s="44">
+      <c r="E721" s="40">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="722" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A722" s="69" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B722" s="69" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C722" s="70">
+        <v>4032</v>
+      </c>
+      <c r="D722" s="69" t="s">
+        <v>177</v>
+      </c>
+      <c r="E722" s="40">
         <v>57.5</v>
       </c>
     </row>
-    <row r="722" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A722" s="75" t="s">
+    <row r="723" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A723" s="69" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B723" s="75" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C723" s="76">
+        <v>4460</v>
+      </c>
+      <c r="D723" s="69" t="s">
+        <v>177</v>
+      </c>
+      <c r="E723" s="44">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="724" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A724" s="75" t="s">
         <v>1185</v>
       </c>
-      <c r="B722" s="75" t="s">
+      <c r="B724" s="75" t="s">
         <v>1186</v>
       </c>
-      <c r="C722" s="76">
+      <c r="C724" s="76">
         <v>4260</v>
       </c>
-      <c r="D722" s="75" t="s">
+      <c r="D724" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="E722" s="44">
+      <c r="E724" s="44">
         <v>58</v>
       </c>
     </row>
-    <row r="723" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A723" s="75" t="s">
+    <row r="725" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A725" s="75" t="s">
         <v>1187</v>
       </c>
-      <c r="B723" s="75" t="s">
+      <c r="B725" s="75" t="s">
         <v>1188</v>
       </c>
-      <c r="C723" s="76">
+      <c r="C725" s="76">
         <v>2551</v>
       </c>
-      <c r="D723" s="75" t="s">
+      <c r="D725" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="E723" s="44">
+      <c r="E725" s="44">
         <v>82</v>
       </c>
     </row>
-    <row r="724" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A724" s="80" t="s">
+    <row r="726" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A726" s="80" t="s">
         <v>1189</v>
       </c>
-      <c r="B724" s="80" t="s">
+      <c r="B726" s="80" t="s">
         <v>1190</v>
       </c>
-      <c r="C724" s="81">
+      <c r="C726" s="81">
         <v>2550</v>
       </c>
-      <c r="D724" s="80" t="s">
+      <c r="D726" s="80" t="s">
         <v>177</v>
       </c>
-      <c r="E724" s="42">
+      <c r="E726" s="42">
         <v>25.5</v>
       </c>
     </row>
-    <row r="725" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A725" s="80" t="s">
+    <row r="727" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A727" s="80" t="s">
         <v>1191</v>
       </c>
-      <c r="B725" s="80" t="s">
+      <c r="B727" s="80" t="s">
         <v>1192</v>
       </c>
-      <c r="C725" s="81">
+      <c r="C727" s="81">
         <v>4383</v>
       </c>
-      <c r="D725" s="80" t="s">
+      <c r="D727" s="80" t="s">
         <v>177</v>
       </c>
-      <c r="E725" s="42">
+      <c r="E727" s="42">
         <v>53</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A726" s="85"/>
-      <c r="B726" s="85"/>
-      <c r="C726" s="86"/>
-      <c r="D726" s="85"/>
-      <c r="E726" s="61"/>
-    </row>
-    <row r="727" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A727" s="111" t="s">
+    <row r="728" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A728" s="85"/>
+      <c r="B728" s="85"/>
+      <c r="C728" s="86"/>
+      <c r="D728" s="85"/>
+      <c r="E728" s="61"/>
+    </row>
+    <row r="729" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A729" s="118" t="s">
         <v>1305</v>
       </c>
-      <c r="B727" s="112"/>
-      <c r="C727" s="112"/>
-      <c r="D727" s="112"/>
-      <c r="E727" s="113"/>
-    </row>
-    <row r="728" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A728" s="72" t="s">
-        <v>1285</v>
-      </c>
-      <c r="B728" s="72" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C728" s="73">
-        <v>3642</v>
-      </c>
-      <c r="D728" s="74" t="s">
-        <v>160</v>
-      </c>
-      <c r="E728" s="48">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="729" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A729" s="72" t="s">
-        <v>1285</v>
-      </c>
-      <c r="B729" s="72" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C729" s="73">
-        <v>3644</v>
-      </c>
-      <c r="D729" s="74" t="s">
-        <v>160</v>
-      </c>
-      <c r="E729" s="49">
-        <v>84</v>
-      </c>
+      <c r="B729" s="119"/>
+      <c r="C729" s="119"/>
+      <c r="D729" s="119"/>
+      <c r="E729" s="120"/>
     </row>
     <row r="730" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="72" t="s">
         <v>1285</v>
       </c>
       <c r="B730" s="72" t="s">
-        <v>1252</v>
+        <v>1286</v>
       </c>
       <c r="C730" s="73">
-        <v>3641</v>
+        <v>3642</v>
       </c>
       <c r="D730" s="74" t="s">
         <v>160</v>
       </c>
       <c r="E730" s="48">
-        <v>84</v>
+        <v>162</v>
       </c>
     </row>
     <row r="731" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17655,149 +17661,149 @@
         <v>1285</v>
       </c>
       <c r="B731" s="72" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C731" s="73">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="D731" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="E731" s="48">
-        <v>162</v>
+      <c r="E731" s="49">
+        <v>84</v>
       </c>
     </row>
     <row r="732" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" s="72" t="s">
-        <v>1251</v>
+        <v>1285</v>
       </c>
       <c r="B732" s="72" t="s">
-        <v>1174</v>
+        <v>1252</v>
       </c>
       <c r="C732" s="73">
-        <v>3852</v>
+        <v>3641</v>
       </c>
       <c r="D732" s="74" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E732" s="48">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="733" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A733" s="72" t="s">
-        <v>1251</v>
+        <v>1285</v>
       </c>
       <c r="B733" s="72" t="s">
-        <v>1252</v>
+        <v>1288</v>
       </c>
       <c r="C733" s="73">
-        <v>3647</v>
+        <v>3645</v>
       </c>
       <c r="D733" s="74" t="s">
         <v>160</v>
       </c>
       <c r="E733" s="48">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="734" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="734" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A734" s="72" t="s">
         <v>1251</v>
       </c>
       <c r="B734" s="72" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C734" s="73">
+        <v>3852</v>
+      </c>
+      <c r="D734" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E734" s="48">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="735" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A735" s="72" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B735" s="72" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C735" s="73">
+        <v>3647</v>
+      </c>
+      <c r="D735" s="74" t="s">
+        <v>160</v>
+      </c>
+      <c r="E735" s="48">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="736" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A736" s="72" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B736" s="72" t="s">
         <v>1253</v>
       </c>
-      <c r="C734" s="73">
+      <c r="C736" s="73">
         <v>3648</v>
       </c>
-      <c r="D734" s="74" t="s">
+      <c r="D736" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="E734" s="48">
+      <c r="E736" s="48">
         <v>33</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A735" s="102"/>
-      <c r="B735" s="103"/>
-      <c r="C735" s="103"/>
-      <c r="D735" s="104"/>
-      <c r="E735" s="105"/>
-    </row>
-    <row r="736" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A736" s="111" t="s">
+    <row r="737" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A737" s="121"/>
+      <c r="B737" s="109"/>
+      <c r="C737" s="109"/>
+      <c r="D737" s="110"/>
+      <c r="E737" s="117"/>
+    </row>
+    <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A738" s="118" t="s">
         <v>421</v>
       </c>
-      <c r="B736" s="112"/>
-      <c r="C736" s="112"/>
-      <c r="D736" s="112"/>
-      <c r="E736" s="113"/>
-    </row>
-    <row r="737" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A737" s="66" t="s">
+      <c r="B738" s="119"/>
+      <c r="C738" s="119"/>
+      <c r="D738" s="119"/>
+      <c r="E738" s="120"/>
+    </row>
+    <row r="739" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A739" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B737" s="66"/>
-      <c r="C737" s="66" t="s">
+      <c r="B739" s="66"/>
+      <c r="C739" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D737" s="66" t="s">
+      <c r="D739" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E737" s="46" t="s">
+      <c r="E739" s="46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A738" s="69" t="s">
+    <row r="740" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A740" s="69" t="s">
         <v>1193</v>
-      </c>
-      <c r="B738" s="69" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C738" s="70">
-        <v>3056</v>
-      </c>
-      <c r="D738" s="69" t="s">
-        <v>160</v>
-      </c>
-      <c r="E738" s="40">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="739" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A739" s="69" t="s">
-        <v>1193</v>
-      </c>
-      <c r="B739" s="69" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C739" s="70">
-        <v>3083</v>
-      </c>
-      <c r="D739" s="69" t="s">
-        <v>160</v>
-      </c>
-      <c r="E739" s="40">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="740" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A740" s="69" t="s">
-        <v>1194</v>
       </c>
       <c r="B740" s="69" t="s">
         <v>1132</v>
       </c>
       <c r="C740" s="70">
-        <v>2264</v>
+        <v>3056</v>
       </c>
       <c r="D740" s="69" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E740" s="40">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="741" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -17808,174 +17814,174 @@
         <v>1139</v>
       </c>
       <c r="C741" s="70">
+        <v>3083</v>
+      </c>
+      <c r="D741" s="69" t="s">
+        <v>160</v>
+      </c>
+      <c r="E741" s="40">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="742" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A742" s="69" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B742" s="69" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C742" s="70">
+        <v>2264</v>
+      </c>
+      <c r="D742" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E742" s="40">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="743" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A743" s="69" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B743" s="69" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C743" s="70">
         <v>2355</v>
       </c>
-      <c r="D741" s="69" t="s">
+      <c r="D743" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E741" s="40">
+      <c r="E743" s="40">
         <v>59</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A742" s="75" t="s">
+    <row r="744" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A744" s="75" t="s">
         <v>1195</v>
       </c>
-      <c r="B742" s="75" t="s">
+      <c r="B744" s="75" t="s">
         <v>1132</v>
       </c>
-      <c r="C742" s="76">
+      <c r="C744" s="76">
         <v>573</v>
       </c>
-      <c r="D742" s="75" t="s">
+      <c r="D744" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="E742" s="44">
+      <c r="E744" s="44">
         <v>59</v>
       </c>
     </row>
-    <row r="743" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A743" s="80" t="s">
+    <row r="745" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A745" s="80" t="s">
         <v>1196</v>
       </c>
-      <c r="B743" s="80" t="s">
+      <c r="B745" s="80" t="s">
         <v>1197</v>
       </c>
-      <c r="C743" s="81">
+      <c r="C745" s="81">
         <v>572</v>
       </c>
-      <c r="D743" s="80" t="s">
+      <c r="D745" s="80" t="s">
         <v>177</v>
       </c>
-      <c r="E743" s="42">
+      <c r="E745" s="42">
         <v>60</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A744" s="65" t="s">
+    <row r="746" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A746" s="65" t="s">
         <v>1198</v>
       </c>
-      <c r="B744" s="65" t="s">
+      <c r="B746" s="65" t="s">
         <v>1156</v>
       </c>
-      <c r="C744" s="81">
+      <c r="C746" s="81">
         <v>4411</v>
       </c>
-      <c r="D744" s="80" t="s">
+      <c r="D746" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="E744" s="42">
+      <c r="E746" s="42">
         <v>93</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A745" s="65" t="s">
+    <row r="747" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A747" s="65" t="s">
         <v>1199</v>
       </c>
-      <c r="B745" s="65" t="s">
+      <c r="B747" s="65" t="s">
         <v>1200</v>
       </c>
-      <c r="C745" s="81">
+      <c r="C747" s="81">
         <v>4410</v>
       </c>
-      <c r="D745" s="80" t="s">
+      <c r="D747" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="E745" s="42">
+      <c r="E747" s="42">
         <v>95</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A746" s="102"/>
-      <c r="B746" s="103"/>
-      <c r="C746" s="103"/>
-      <c r="D746" s="104"/>
-      <c r="E746" s="105"/>
-    </row>
-    <row r="747" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A747" s="111" t="s">
+    <row r="748" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A748" s="121"/>
+      <c r="B748" s="109"/>
+      <c r="C748" s="109"/>
+      <c r="D748" s="110"/>
+      <c r="E748" s="117"/>
+    </row>
+    <row r="749" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A749" s="118" t="s">
         <v>1303</v>
       </c>
-      <c r="B747" s="112"/>
-      <c r="C747" s="112"/>
-      <c r="D747" s="112"/>
-      <c r="E747" s="113"/>
-    </row>
-    <row r="748" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A748" s="66" t="s">
+      <c r="B749" s="119"/>
+      <c r="C749" s="119"/>
+      <c r="D749" s="119"/>
+      <c r="E749" s="120"/>
+    </row>
+    <row r="750" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A750" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B748" s="66"/>
-      <c r="C748" s="66" t="s">
+      <c r="B750" s="66"/>
+      <c r="C750" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D748" s="66" t="s">
+      <c r="D750" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E748" s="47" t="s">
+      <c r="E750" s="47" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A749" s="82" t="s">
+    <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A751" s="82" t="s">
         <v>1330</v>
       </c>
-      <c r="B749" s="82" t="s">
+      <c r="B751" s="82" t="s">
         <v>1331</v>
       </c>
-      <c r="C749" s="82">
+      <c r="C751" s="82">
         <v>4044</v>
       </c>
-      <c r="D749" s="101" t="s">
+      <c r="D751" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E749" s="61">
+      <c r="E751" s="61">
         <v>22</v>
-      </c>
-    </row>
-    <row r="750" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A750" s="72" t="s">
-        <v>439</v>
-      </c>
-      <c r="B750" s="72" t="s">
-        <v>145</v>
-      </c>
-      <c r="C750" s="73">
-        <v>4043</v>
-      </c>
-      <c r="D750" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E750" s="48">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A751" s="72" t="s">
-        <v>440</v>
-      </c>
-      <c r="B751" s="72" t="s">
-        <v>145</v>
-      </c>
-      <c r="C751" s="73">
-        <v>3531</v>
-      </c>
-      <c r="D751" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E751" s="48">
-        <v>63</v>
       </c>
     </row>
     <row r="752" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A752" s="72" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B752" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C752" s="73">
-        <v>3974</v>
+        <v>4043</v>
       </c>
       <c r="D752" s="74" t="s">
         <v>20</v>
@@ -17984,15 +17990,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="753" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A753" s="72" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B753" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C753" s="73">
-        <v>3530</v>
+        <v>3531</v>
       </c>
       <c r="D753" s="74" t="s">
         <v>20</v>
@@ -18001,66 +18007,66 @@
         <v>63</v>
       </c>
     </row>
-    <row r="754" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="72" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B754" s="72" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="C754" s="73">
-        <v>4282</v>
+        <v>3974</v>
       </c>
       <c r="D754" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E754" s="48">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="755" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="72" t="s">
-        <v>1209</v>
+        <v>442</v>
       </c>
       <c r="B755" s="72" t="s">
-        <v>1208</v>
+        <v>145</v>
       </c>
       <c r="C755" s="73">
-        <v>3870</v>
+        <v>3530</v>
       </c>
       <c r="D755" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E755" s="48">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="756" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="72" t="s">
-        <v>1210</v>
+        <v>443</v>
       </c>
       <c r="B756" s="72" t="s">
-        <v>1208</v>
+        <v>78</v>
       </c>
       <c r="C756" s="73">
-        <v>3701</v>
+        <v>4282</v>
       </c>
       <c r="D756" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E756" s="48">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="757" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="72" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B757" s="72" t="s">
         <v>1208</v>
       </c>
       <c r="C757" s="73">
-        <v>3800</v>
+        <v>3870</v>
       </c>
       <c r="D757" s="74" t="s">
         <v>20</v>
@@ -18069,97 +18075,83 @@
         <v>22</v>
       </c>
     </row>
-    <row r="758" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="72" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B758" s="72" t="s">
         <v>1208</v>
       </c>
       <c r="C758" s="73">
-        <v>3725</v>
+        <v>3701</v>
       </c>
       <c r="D758" s="74" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E758" s="48">
         <v>22</v>
       </c>
     </row>
-    <row r="759" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="72" t="s">
-        <v>1237</v>
+        <v>1211</v>
       </c>
       <c r="B759" s="72" t="s">
         <v>1208</v>
       </c>
       <c r="C759" s="73">
-        <v>3871</v>
+        <v>3800</v>
       </c>
       <c r="D759" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E759" s="48">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="760" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="760" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="72" t="s">
-        <v>463</v>
+        <v>1212</v>
       </c>
       <c r="B760" s="72" t="s">
-        <v>145</v>
+        <v>1208</v>
       </c>
       <c r="C760" s="73">
-        <v>2825</v>
+        <v>3725</v>
       </c>
       <c r="D760" s="74" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E760" s="48">
-        <v>23.5</v>
-      </c>
-      <c r="F760" s="54"/>
-      <c r="G760" s="54"/>
-      <c r="I760" s="57"/>
-      <c r="J760" s="58"/>
-      <c r="K760" s="60"/>
-      <c r="L760" s="59"/>
-      <c r="M760" s="59"/>
-      <c r="N760" s="59"/>
-      <c r="O760" s="59"/>
-      <c r="P760" s="59"/>
-      <c r="Q760" s="59"/>
-      <c r="R760" s="58"/>
-    </row>
-    <row r="761" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="761" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A761" s="72" t="s">
-        <v>464</v>
+        <v>1237</v>
       </c>
       <c r="B761" s="72" t="s">
-        <v>145</v>
+        <v>1208</v>
       </c>
       <c r="C761" s="73">
-        <v>2828</v>
+        <v>3871</v>
       </c>
       <c r="D761" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E761" s="48">
-        <v>23.5</v>
-      </c>
-      <c r="G761" s="55"/>
-      <c r="H761" s="56"/>
+        <v>27</v>
+      </c>
     </row>
     <row r="762" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A762" s="72" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B762" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C762" s="73">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="D762" s="74" t="s">
         <v>20</v>
@@ -18167,16 +18159,28 @@
       <c r="E762" s="48">
         <v>23.5</v>
       </c>
+      <c r="F762" s="54"/>
+      <c r="G762" s="54"/>
+      <c r="I762" s="57"/>
+      <c r="J762" s="58"/>
+      <c r="K762" s="60"/>
+      <c r="L762" s="59"/>
+      <c r="M762" s="59"/>
+      <c r="N762" s="59"/>
+      <c r="O762" s="59"/>
+      <c r="P762" s="59"/>
+      <c r="Q762" s="59"/>
+      <c r="R762" s="58"/>
     </row>
     <row r="763" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="72" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B763" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C763" s="73">
-        <v>3058</v>
+        <v>2828</v>
       </c>
       <c r="D763" s="74" t="s">
         <v>20</v>
@@ -18184,16 +18188,18 @@
       <c r="E763" s="48">
         <v>23.5</v>
       </c>
+      <c r="G763" s="55"/>
+      <c r="H763" s="56"/>
     </row>
     <row r="764" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="72" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B764" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C764" s="73">
-        <v>3059</v>
+        <v>2826</v>
       </c>
       <c r="D764" s="74" t="s">
         <v>20</v>
@@ -18204,13 +18210,13 @@
     </row>
     <row r="765" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="72" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B765" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C765" s="73">
-        <v>2829</v>
+        <v>3058</v>
       </c>
       <c r="D765" s="74" t="s">
         <v>20</v>
@@ -18221,13 +18227,13 @@
     </row>
     <row r="766" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="72" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B766" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C766" s="73">
-        <v>4126</v>
+        <v>3059</v>
       </c>
       <c r="D766" s="74" t="s">
         <v>20</v>
@@ -18238,13 +18244,13 @@
     </row>
     <row r="767" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="72" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B767" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C767" s="73">
-        <v>2827</v>
+        <v>2829</v>
       </c>
       <c r="D767" s="74" t="s">
         <v>20</v>
@@ -18255,148 +18261,148 @@
     </row>
     <row r="768" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="72" t="s">
-        <v>1254</v>
+        <v>469</v>
       </c>
       <c r="B768" s="72" t="s">
-        <v>1208</v>
+        <v>145</v>
       </c>
       <c r="C768" s="73">
-        <v>3801</v>
+        <v>4126</v>
       </c>
       <c r="D768" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E768" s="48">
-        <v>25</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="769" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="72" t="s">
-        <v>1255</v>
+        <v>470</v>
       </c>
       <c r="B769" s="72" t="s">
-        <v>1208</v>
+        <v>145</v>
       </c>
       <c r="C769" s="73">
-        <v>3833</v>
+        <v>2827</v>
       </c>
       <c r="D769" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E769" s="48">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="770" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A770" s="72" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B770" s="72" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C770" s="73">
+        <v>3801</v>
+      </c>
+      <c r="D770" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E770" s="48">
         <v>25</v>
-      </c>
-    </row>
-    <row r="770" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A770" s="72" t="s">
-        <v>476</v>
-      </c>
-      <c r="B770" s="72" t="s">
-        <v>145</v>
-      </c>
-      <c r="C770" s="73">
-        <v>3897</v>
-      </c>
-      <c r="D770" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="E770" s="48">
-        <v>60</v>
       </c>
     </row>
     <row r="771" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="72" t="s">
-        <v>477</v>
+        <v>1255</v>
       </c>
       <c r="B771" s="72" t="s">
-        <v>145</v>
+        <v>1208</v>
       </c>
       <c r="C771" s="73">
-        <v>3764</v>
+        <v>3833</v>
       </c>
       <c r="D771" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E771" s="48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="772" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A772" s="72" t="s">
+        <v>476</v>
+      </c>
+      <c r="B772" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C772" s="73">
+        <v>3897</v>
+      </c>
+      <c r="D772" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="E772" s="48">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="773" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A773" s="72" t="s">
+        <v>477</v>
+      </c>
+      <c r="B773" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C773" s="73">
+        <v>3764</v>
+      </c>
+      <c r="D773" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E773" s="48">
         <v>78</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A772" s="96"/>
-      <c r="B772" s="96"/>
-      <c r="C772" s="97"/>
-      <c r="D772" s="96"/>
-      <c r="E772" s="98"/>
-    </row>
-    <row r="773" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A773" s="108" t="s">
+    <row r="774" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A774" s="96"/>
+      <c r="B774" s="96"/>
+      <c r="C774" s="97"/>
+      <c r="D774" s="96"/>
+      <c r="E774" s="98"/>
+    </row>
+    <row r="775" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A775" s="130" t="s">
         <v>1289</v>
       </c>
-      <c r="B773" s="109"/>
-      <c r="C773" s="109"/>
-      <c r="D773" s="109"/>
-      <c r="E773" s="110"/>
-    </row>
-    <row r="774" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A774" s="66" t="s">
+      <c r="B775" s="131"/>
+      <c r="C775" s="131"/>
+      <c r="D775" s="131"/>
+      <c r="E775" s="132"/>
+    </row>
+    <row r="776" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A776" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B774" s="66" t="s">
+      <c r="B776" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="C774" s="66" t="s">
+      <c r="C776" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D774" s="66" t="s">
+      <c r="D776" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E774" s="47" t="s">
+      <c r="E776" s="47" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="775" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A775" s="72" t="s">
-        <v>425</v>
-      </c>
-      <c r="B775" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C775" s="73">
-        <v>3438</v>
-      </c>
-      <c r="D775" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E775" s="48">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="776" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A776" s="72" t="s">
-        <v>425</v>
-      </c>
-      <c r="B776" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C776" s="73">
-        <v>3434</v>
-      </c>
-      <c r="D776" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E776" s="48">
-        <v>76</v>
       </c>
     </row>
     <row r="777" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="72" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B777" s="72" t="s">
         <v>120</v>
       </c>
       <c r="C777" s="73">
-        <v>3443</v>
+        <v>3438</v>
       </c>
       <c r="D777" s="74" t="s">
         <v>15</v>
@@ -18407,13 +18413,13 @@
     </row>
     <row r="778" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A778" s="72" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B778" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C778" s="73">
-        <v>3019</v>
+        <v>3434</v>
       </c>
       <c r="D778" s="74" t="s">
         <v>20</v>
@@ -18424,13 +18430,13 @@
     </row>
     <row r="779" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A779" s="72" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B779" s="72" t="s">
         <v>120</v>
       </c>
       <c r="C779" s="73">
-        <v>4489</v>
+        <v>3443</v>
       </c>
       <c r="D779" s="74" t="s">
         <v>15</v>
@@ -18439,15 +18445,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A780" s="72" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B780" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C780" s="73">
-        <v>4490</v>
+        <v>3019</v>
       </c>
       <c r="D780" s="74" t="s">
         <v>20</v>
@@ -18458,13 +18464,13 @@
     </row>
     <row r="781" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="72" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B781" s="72" t="s">
         <v>120</v>
       </c>
       <c r="C781" s="73">
-        <v>3476</v>
+        <v>4489</v>
       </c>
       <c r="D781" s="74" t="s">
         <v>15</v>
@@ -18473,15 +18479,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="782" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="72" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B782" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C782" s="73">
-        <v>3477</v>
+        <v>4490</v>
       </c>
       <c r="D782" s="74" t="s">
         <v>20</v>
@@ -18490,100 +18496,100 @@
         <v>76</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A783" s="72" t="s">
-        <v>1314</v>
+        <v>428</v>
       </c>
       <c r="B783" s="72" t="s">
-        <v>1156</v>
+        <v>120</v>
       </c>
       <c r="C783" s="73">
-        <v>4344</v>
+        <v>3476</v>
       </c>
       <c r="D783" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E783" s="48">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="784" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A784" s="72" t="s">
+        <v>428</v>
+      </c>
+      <c r="B784" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C784" s="73">
+        <v>3477</v>
+      </c>
+      <c r="D784" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E784" s="48">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="785" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A785" s="72" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B785" s="72" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C785" s="73">
+        <v>4344</v>
+      </c>
+      <c r="D785" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E785" s="48">
         <v>328</v>
       </c>
     </row>
-    <row r="784" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A784" s="72" t="s">
+    <row r="786" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A786" s="72" t="s">
         <v>429</v>
-      </c>
-      <c r="B784" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="C784" s="73">
-        <v>3123</v>
-      </c>
-      <c r="D784" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E784" s="48">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="785" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A785" s="72" t="s">
-        <v>429</v>
-      </c>
-      <c r="B785" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C785" s="73">
-        <v>2674</v>
-      </c>
-      <c r="D785" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E785" s="48">
-        <v>60.5</v>
-      </c>
-    </row>
-    <row r="786" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A786" s="72" t="s">
-        <v>430</v>
       </c>
       <c r="B786" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C786" s="73">
-        <v>3719</v>
+        <v>3123</v>
       </c>
       <c r="D786" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E786" s="48">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="787" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A787" s="72" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B787" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C787" s="73">
-        <v>3720</v>
+        <v>2674</v>
       </c>
       <c r="D787" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E787" s="48">
-        <v>69</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="788" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A788" s="72" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B788" s="72" t="s">
-        <v>1126</v>
+        <v>18</v>
       </c>
       <c r="C788" s="73">
-        <v>3765</v>
+        <v>3719</v>
       </c>
       <c r="D788" s="74" t="s">
         <v>15</v>
@@ -18594,13 +18600,13 @@
     </row>
     <row r="789" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A789" s="72" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B789" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C789" s="73">
-        <v>3766</v>
+        <v>3720</v>
       </c>
       <c r="D789" s="74" t="s">
         <v>15</v>
@@ -18611,47 +18617,47 @@
     </row>
     <row r="790" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B790" s="72" t="s">
-        <v>18</v>
+        <v>1126</v>
       </c>
       <c r="C790" s="73">
-        <v>3126</v>
+        <v>3765</v>
       </c>
       <c r="D790" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E790" s="48">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="791" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="791" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A791" s="72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B791" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C791" s="73">
-        <v>3127</v>
+        <v>3766</v>
       </c>
       <c r="D791" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E791" s="48">
-        <v>60.5</v>
-      </c>
-    </row>
-    <row r="792" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="792" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="72" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B792" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C792" s="73">
-        <v>3435</v>
+        <v>3126</v>
       </c>
       <c r="D792" s="74" t="s">
         <v>15</v>
@@ -18662,16 +18668,16 @@
     </row>
     <row r="793" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="72" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B793" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C793" s="73">
-        <v>3436</v>
+        <v>3127</v>
       </c>
       <c r="D793" s="74" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E793" s="48">
         <v>60.5</v>
@@ -18679,13 +18685,13 @@
     </row>
     <row r="794" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="72" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B794" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C794" s="73">
-        <v>3128</v>
+        <v>3435</v>
       </c>
       <c r="D794" s="74" t="s">
         <v>15</v>
@@ -18696,30 +18702,30 @@
     </row>
     <row r="795" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A795" s="72" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B795" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C795" s="73">
-        <v>3129</v>
+        <v>3436</v>
       </c>
       <c r="D795" s="74" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E795" s="48">
         <v>60.5</v>
       </c>
     </row>
-    <row r="796" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B796" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C796" s="73">
-        <v>4158</v>
+        <v>3128</v>
       </c>
       <c r="D796" s="74" t="s">
         <v>15</v>
@@ -18728,15 +18734,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="797" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A797" s="72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B797" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C797" s="73">
-        <v>4159</v>
+        <v>3129</v>
       </c>
       <c r="D797" s="74" t="s">
         <v>20</v>
@@ -18747,271 +18753,271 @@
     </row>
     <row r="798" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A798" s="72" t="s">
-        <v>1327</v>
+        <v>435</v>
       </c>
       <c r="B798" s="72" t="s">
-        <v>1126</v>
+        <v>18</v>
       </c>
       <c r="C798" s="73">
-        <v>4561</v>
+        <v>4158</v>
       </c>
       <c r="D798" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E798" s="48">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="799" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A799" s="72" t="s">
-        <v>1327</v>
+        <v>435</v>
       </c>
       <c r="B799" s="72" t="s">
-        <v>1328</v>
+        <v>19</v>
       </c>
       <c r="C799" s="73">
-        <v>4562</v>
+        <v>4159</v>
       </c>
       <c r="D799" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E799" s="48">
-        <v>69</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="800" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="72" t="s">
-        <v>436</v>
+        <v>1327</v>
       </c>
       <c r="B800" s="72" t="s">
-        <v>18</v>
+        <v>1126</v>
       </c>
       <c r="C800" s="73">
-        <v>3124</v>
+        <v>4561</v>
       </c>
       <c r="D800" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E800" s="48">
-        <v>161</v>
+        <v>138</v>
       </c>
     </row>
     <row r="801" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="72" t="s">
-        <v>436</v>
+        <v>1327</v>
       </c>
       <c r="B801" s="72" t="s">
-        <v>19</v>
+        <v>1328</v>
       </c>
       <c r="C801" s="73">
-        <v>2824</v>
+        <v>4562</v>
       </c>
       <c r="D801" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E801" s="48">
-        <v>80.5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="802" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="72" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B802" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C802" s="73">
-        <v>3130</v>
+        <v>3124</v>
       </c>
       <c r="D802" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E802" s="48">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="803" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A803" s="72" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B803" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C803" s="73">
-        <v>3131</v>
+        <v>2824</v>
       </c>
       <c r="D803" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E803" s="48">
-        <v>69</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="804" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="72" t="s">
-        <v>1201</v>
+        <v>437</v>
       </c>
       <c r="B804" s="72" t="s">
-        <v>1156</v>
+        <v>18</v>
       </c>
       <c r="C804" s="73">
-        <v>4346</v>
+        <v>3130</v>
       </c>
       <c r="D804" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E804" s="48">
-        <v>328</v>
+        <v>138</v>
       </c>
     </row>
     <row r="805" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A805" s="72" t="s">
-        <v>1202</v>
+        <v>437</v>
       </c>
       <c r="B805" s="72" t="s">
-        <v>1156</v>
+        <v>19</v>
       </c>
       <c r="C805" s="73">
-        <v>4345</v>
+        <v>3131</v>
       </c>
       <c r="D805" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E805" s="48">
-        <v>328</v>
+        <v>69</v>
       </c>
     </row>
     <row r="806" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="72" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B806" s="72" t="s">
-        <v>1132</v>
+        <v>1156</v>
       </c>
       <c r="C806" s="73">
-        <v>4347</v>
+        <v>4346</v>
       </c>
       <c r="D806" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E806" s="48">
-        <v>274</v>
+        <v>328</v>
       </c>
     </row>
     <row r="807" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="72" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B807" s="72" t="s">
         <v>1156</v>
       </c>
       <c r="C807" s="73">
-        <v>4446</v>
+        <v>4345</v>
       </c>
       <c r="D807" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E807" s="48">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="808" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="72" t="s">
-        <v>438</v>
+        <v>1203</v>
       </c>
       <c r="B808" s="72" t="s">
-        <v>78</v>
+        <v>1132</v>
       </c>
       <c r="C808" s="73">
-        <v>4476</v>
+        <v>4347</v>
       </c>
       <c r="D808" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E808" s="48">
-        <v>30</v>
+        <v>274</v>
       </c>
     </row>
     <row r="809" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="72" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B809" s="72" t="s">
         <v>1156</v>
       </c>
       <c r="C809" s="73">
-        <v>4348</v>
+        <v>4446</v>
       </c>
       <c r="D809" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E809" s="48">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="810" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="72" t="s">
-        <v>1206</v>
+        <v>438</v>
       </c>
       <c r="B810" s="72" t="s">
-        <v>1207</v>
+        <v>78</v>
       </c>
       <c r="C810" s="73">
-        <v>4456</v>
+        <v>4476</v>
       </c>
       <c r="D810" s="74" t="s">
-        <v>160</v>
+        <v>412</v>
       </c>
       <c r="E810" s="48">
-        <v>69</v>
+        <v>30</v>
       </c>
     </row>
     <row r="811" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="72" t="s">
-        <v>444</v>
+        <v>1205</v>
       </c>
       <c r="B811" s="72" t="s">
-        <v>110</v>
+        <v>1156</v>
       </c>
       <c r="C811" s="73">
-        <v>4051</v>
+        <v>4348</v>
       </c>
       <c r="D811" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E811" s="48">
-        <v>72</v>
+        <v>328</v>
       </c>
     </row>
     <row r="812" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="72" t="s">
-        <v>1315</v>
+        <v>1206</v>
       </c>
       <c r="B812" s="72" t="s">
-        <v>1151</v>
+        <v>1207</v>
       </c>
       <c r="C812" s="73">
-        <v>4408</v>
+        <v>4456</v>
       </c>
       <c r="D812" s="74" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E812" s="48">
-        <v>92</v>
+        <v>69</v>
       </c>
     </row>
     <row r="813" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="72" t="s">
-        <v>1213</v>
+        <v>444</v>
       </c>
       <c r="B813" s="72" t="s">
-        <v>1151</v>
+        <v>110</v>
       </c>
       <c r="C813" s="73">
-        <v>4341</v>
+        <v>4051</v>
       </c>
       <c r="D813" s="74" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="E813" s="48">
         <v>72</v>
@@ -19019,319 +19025,319 @@
     </row>
     <row r="814" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="72" t="s">
-        <v>448</v>
+        <v>1315</v>
       </c>
       <c r="B814" s="72" t="s">
-        <v>145</v>
+        <v>1151</v>
       </c>
       <c r="C814" s="73">
-        <v>4265</v>
+        <v>4408</v>
       </c>
       <c r="D814" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E814" s="48">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="815" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="72" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B815" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C815" s="73">
-        <v>4266</v>
+        <v>4341</v>
       </c>
       <c r="D815" s="74" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E815" s="48">
-        <v>81.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="816" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="72" t="s">
-        <v>1215</v>
+        <v>448</v>
       </c>
       <c r="B816" s="72" t="s">
-        <v>1151</v>
+        <v>145</v>
       </c>
       <c r="C816" s="73">
-        <v>4269</v>
+        <v>4265</v>
       </c>
       <c r="D816" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E816" s="48">
-        <v>87.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="817" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="72" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B817" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C817" s="73">
-        <v>4273</v>
+        <v>4266</v>
       </c>
       <c r="D817" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E817" s="48">
-        <v>94</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="818" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="72" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B818" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C818" s="73">
-        <v>4405</v>
+        <v>4269</v>
       </c>
       <c r="D818" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E818" s="48">
-        <v>78</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="819" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="72" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B819" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C819" s="73">
-        <v>4406</v>
+        <v>4273</v>
       </c>
       <c r="D819" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E819" s="48">
-        <v>130</v>
+        <v>94</v>
       </c>
     </row>
     <row r="820" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="72" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B820" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C820" s="73">
-        <v>4267</v>
+        <v>4405</v>
       </c>
       <c r="D820" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E820" s="48">
-        <v>81.5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="821" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="72" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B821" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C821" s="73">
-        <v>4271</v>
+        <v>4406</v>
       </c>
       <c r="D821" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E821" s="48">
-        <v>87.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="822" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="72" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B822" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C822" s="73">
-        <v>4276</v>
+        <v>4267</v>
       </c>
       <c r="D822" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E822" s="48">
-        <v>119</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="823" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="72" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B823" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C823" s="73">
-        <v>4342</v>
+        <v>4271</v>
       </c>
       <c r="D823" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E823" s="48">
-        <v>114</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="824" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="72" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B824" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C824" s="73">
-        <v>4398</v>
+        <v>4276</v>
       </c>
       <c r="D824" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E824" s="48">
-        <v>84</v>
+        <v>119</v>
       </c>
     </row>
     <row r="825" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="72" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B825" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C825" s="73">
-        <v>4270</v>
+        <v>4342</v>
       </c>
       <c r="D825" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E825" s="48">
-        <v>87.5</v>
+        <v>114</v>
       </c>
     </row>
     <row r="826" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="72" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B826" s="72" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="C826" s="73">
-        <v>4275</v>
+        <v>4398</v>
       </c>
       <c r="D826" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E826" s="48">
-        <v>54</v>
+        <v>84</v>
       </c>
     </row>
     <row r="827" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="72" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B827" s="72" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="C827" s="73">
-        <v>4274</v>
+        <v>4270</v>
       </c>
       <c r="D827" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E827" s="48">
-        <v>54</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="828" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="72" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B828" s="72" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C828" s="73">
-        <v>4399</v>
+        <v>4275</v>
       </c>
       <c r="D828" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E828" s="48">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="829" spans="1:5" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="829" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="72" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B829" s="72" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="C829" s="73">
-        <v>4404</v>
+        <v>4274</v>
       </c>
       <c r="D829" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E829" s="48">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="830" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="830" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="72" t="s">
-        <v>449</v>
+        <v>1227</v>
       </c>
       <c r="B830" s="72" t="s">
-        <v>145</v>
+        <v>1151</v>
       </c>
       <c r="C830" s="73">
-        <v>4262</v>
+        <v>4399</v>
       </c>
       <c r="D830" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E830" s="48">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="831" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="831" spans="1:5" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="72" t="s">
-        <v>450</v>
+        <v>1228</v>
       </c>
       <c r="B831" s="72" t="s">
-        <v>145</v>
+        <v>1151</v>
       </c>
       <c r="C831" s="73">
-        <v>4263</v>
+        <v>4404</v>
       </c>
       <c r="D831" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E831" s="48">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="832" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="832" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A832" s="72" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B832" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C832" s="73">
-        <v>4264</v>
+        <v>4262</v>
       </c>
       <c r="D832" s="74" t="s">
         <v>20</v>
@@ -19342,458 +19348,458 @@
     </row>
     <row r="833" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A833" s="72" t="s">
-        <v>1229</v>
+        <v>450</v>
       </c>
       <c r="B833" s="72" t="s">
-        <v>1151</v>
+        <v>145</v>
       </c>
       <c r="C833" s="73">
-        <v>4407</v>
+        <v>4263</v>
       </c>
       <c r="D833" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E833" s="48">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="834" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="72" t="s">
-        <v>1230</v>
+        <v>451</v>
       </c>
       <c r="B834" s="72" t="s">
-        <v>1151</v>
+        <v>145</v>
       </c>
       <c r="C834" s="73">
-        <v>4397</v>
+        <v>4264</v>
       </c>
       <c r="D834" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E834" s="48">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="835" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="72" t="s">
-        <v>452</v>
+        <v>1229</v>
       </c>
       <c r="B835" s="72" t="s">
-        <v>145</v>
+        <v>1151</v>
       </c>
       <c r="C835" s="73">
-        <v>4343</v>
+        <v>4407</v>
       </c>
       <c r="D835" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E835" s="48">
-        <v>67</v>
+        <v>92</v>
       </c>
     </row>
     <row r="836" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="72" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B836" s="72" t="s">
         <v>1151</v>
       </c>
       <c r="C836" s="73">
-        <v>4268</v>
+        <v>4397</v>
       </c>
       <c r="D836" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E836" s="48">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="837" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A837" s="72" t="s">
+        <v>452</v>
+      </c>
+      <c r="B837" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C837" s="73">
+        <v>4343</v>
+      </c>
+      <c r="D837" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E837" s="48">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="838" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A838" s="72" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B838" s="72" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C838" s="73">
+        <v>4268</v>
+      </c>
+      <c r="D838" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E838" s="48">
         <v>81.5</v>
-      </c>
-    </row>
-    <row r="837" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A837" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B837" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C837" s="70">
-        <v>2833</v>
-      </c>
-      <c r="D837" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E837" s="40">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="838" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A838" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B838" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C838" s="70">
-        <v>3125</v>
-      </c>
-      <c r="D838" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E838" s="40">
-        <v>162</v>
       </c>
     </row>
     <row r="839" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A839" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B839" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C839" s="70">
+        <v>2833</v>
+      </c>
+      <c r="D839" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E839" s="40">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="840" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A840" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="B840" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C839" s="70">
-        <v>3752</v>
-      </c>
-      <c r="D839" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E839" s="40">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="840" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A840" s="72" t="s">
-        <v>62</v>
-      </c>
-      <c r="B840" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C840" s="73">
-        <v>3753</v>
-      </c>
-      <c r="D840" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E840" s="50">
-        <v>83</v>
+      <c r="C840" s="70">
+        <v>3125</v>
+      </c>
+      <c r="D840" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E840" s="40">
+        <v>162</v>
       </c>
     </row>
     <row r="841" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A841" s="69" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B841" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C841" s="70">
+        <v>3752</v>
+      </c>
+      <c r="D841" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E841" s="40">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="842" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A842" s="72" t="s">
+        <v>62</v>
+      </c>
+      <c r="B842" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C841" s="70">
-        <v>2511</v>
-      </c>
-      <c r="D841" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E841" s="40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="842" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A842" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="B842" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C842" s="70">
-        <v>4311</v>
-      </c>
-      <c r="D842" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="E842" s="40">
-        <v>65</v>
+      <c r="C842" s="73">
+        <v>3753</v>
+      </c>
+      <c r="D842" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E842" s="50">
+        <v>83</v>
       </c>
     </row>
     <row r="843" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A843" s="69" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B843" s="69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C843" s="70">
-        <v>4046</v>
+        <v>2511</v>
       </c>
       <c r="D843" s="69" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="E843" s="40">
-        <v>166</v>
+        <v>61</v>
       </c>
     </row>
     <row r="844" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A844" s="69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B844" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C844" s="70">
-        <v>4047</v>
+        <v>4311</v>
       </c>
       <c r="D844" s="69" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E844" s="40">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="845" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A845" s="69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B845" s="69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C845" s="70">
-        <v>4312</v>
+        <v>4046</v>
       </c>
       <c r="D845" s="69" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E845" s="40">
-        <v>65</v>
+        <v>166</v>
       </c>
     </row>
     <row r="846" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A846" s="69" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B846" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C846" s="70">
+        <v>4047</v>
+      </c>
+      <c r="D846" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E846" s="40">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="847" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A847" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B847" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C847" s="70">
+        <v>4312</v>
+      </c>
+      <c r="D847" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E847" s="40">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="848" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A848" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B848" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C848" s="70">
         <v>4310</v>
       </c>
-      <c r="D846" s="69" t="s">
+      <c r="D848" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E846" s="40">
+      <c r="E848" s="40">
         <v>65</v>
-      </c>
-    </row>
-    <row r="847" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A847" s="72" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B847" s="72" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C847" s="73">
-        <v>4074</v>
-      </c>
-      <c r="D847" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E847" s="48">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="848" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A848" s="72" t="s">
-        <v>1234</v>
-      </c>
-      <c r="B848" s="72" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C848" s="73">
-        <v>4076</v>
-      </c>
-      <c r="D848" s="74" t="s">
-        <v>453</v>
-      </c>
-      <c r="E848" s="48">
-        <v>24</v>
       </c>
     </row>
     <row r="849" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A849" s="72" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="B849" s="72" t="s">
-        <v>1207</v>
+        <v>1233</v>
       </c>
       <c r="C849" s="73">
-        <v>4133</v>
+        <v>4074</v>
       </c>
       <c r="D849" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E849" s="48">
-        <v>72</v>
+        <v>27</v>
       </c>
     </row>
     <row r="850" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A850" s="72" t="s">
-        <v>455</v>
+        <v>1234</v>
       </c>
       <c r="B850" s="72" t="s">
-        <v>120</v>
+        <v>1235</v>
       </c>
       <c r="C850" s="73">
-        <v>3068</v>
+        <v>4076</v>
       </c>
       <c r="D850" s="74" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="E850" s="48">
-        <v>372</v>
+        <v>24</v>
       </c>
     </row>
     <row r="851" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A851" s="72" t="s">
-        <v>455</v>
+        <v>1236</v>
       </c>
       <c r="B851" s="72" t="s">
-        <v>19</v>
+        <v>1207</v>
       </c>
       <c r="C851" s="73">
-        <v>3087</v>
+        <v>4133</v>
       </c>
       <c r="D851" s="74" t="s">
-        <v>15</v>
+        <v>453</v>
       </c>
       <c r="E851" s="48">
-        <v>124</v>
+        <v>72</v>
       </c>
     </row>
     <row r="852" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A852" s="72" t="s">
-        <v>1326</v>
+        <v>455</v>
       </c>
       <c r="B852" s="72" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="C852" s="73">
-        <v>4560</v>
+        <v>3068</v>
       </c>
       <c r="D852" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E852" s="48">
-        <v>195</v>
+        <v>372</v>
       </c>
     </row>
     <row r="853" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A853" s="72" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B853" s="72" t="s">
-        <v>1132</v>
+        <v>19</v>
       </c>
       <c r="C853" s="73">
-        <v>4531</v>
+        <v>3087</v>
       </c>
       <c r="D853" s="74" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E853" s="48">
-        <v>880</v>
+        <v>124</v>
       </c>
     </row>
     <row r="854" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A854" s="72" t="s">
-        <v>456</v>
+        <v>1326</v>
       </c>
       <c r="B854" s="72" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="C854" s="73">
-        <v>4532</v>
+        <v>4560</v>
       </c>
       <c r="D854" s="74" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E854" s="48">
-        <v>88</v>
+        <v>195</v>
       </c>
     </row>
     <row r="855" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A855" s="72" t="s">
-        <v>1325</v>
+        <v>456</v>
       </c>
       <c r="B855" s="72" t="s">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="C855" s="73">
-        <v>4559</v>
+        <v>4531</v>
       </c>
       <c r="D855" s="74" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E855" s="48">
-        <v>210</v>
+        <v>880</v>
       </c>
     </row>
     <row r="856" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A856" s="72" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B856" s="72" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="C856" s="73">
-        <v>4493</v>
+        <v>4532</v>
       </c>
       <c r="D856" s="74" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E856" s="48">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="857" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="72" t="s">
-        <v>1238</v>
+        <v>1325</v>
       </c>
       <c r="B857" s="72" t="s">
-        <v>1239</v>
+        <v>1166</v>
       </c>
       <c r="C857" s="73">
-        <v>4102</v>
+        <v>4559</v>
       </c>
       <c r="D857" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E857" s="48">
-        <v>77</v>
+        <v>210</v>
       </c>
     </row>
     <row r="858" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A858" s="72" t="s">
-        <v>1240</v>
+        <v>457</v>
       </c>
       <c r="B858" s="72" t="s">
-        <v>1239</v>
+        <v>145</v>
       </c>
       <c r="C858" s="73">
-        <v>4103</v>
+        <v>4493</v>
       </c>
       <c r="D858" s="74" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E858" s="48">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="859" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="72" t="s">
-        <v>1316</v>
+        <v>1238</v>
       </c>
       <c r="B859" s="72" t="s">
         <v>1239</v>
       </c>
       <c r="C859" s="73">
-        <v>4547</v>
+        <v>4102</v>
       </c>
       <c r="D859" s="74" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E859" s="48">
         <v>77</v>
@@ -19801,13 +19807,13 @@
     </row>
     <row r="860" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="72" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B860" s="72" t="s">
         <v>1239</v>
       </c>
       <c r="C860" s="73">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="D860" s="74" t="s">
         <v>160</v>
@@ -19818,13 +19824,13 @@
     </row>
     <row r="861" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="72" t="s">
-        <v>1242</v>
+        <v>1316</v>
       </c>
       <c r="B861" s="72" t="s">
         <v>1239</v>
       </c>
       <c r="C861" s="73">
-        <v>4101</v>
+        <v>4547</v>
       </c>
       <c r="D861" s="74" t="s">
         <v>160</v>
@@ -19835,13 +19841,13 @@
     </row>
     <row r="862" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="72" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B862" s="72" t="s">
         <v>1239</v>
       </c>
       <c r="C862" s="73">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="D862" s="74" t="s">
         <v>160</v>
@@ -19850,222 +19856,222 @@
         <v>77</v>
       </c>
     </row>
-    <row r="863" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="72" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B863" s="72" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="C863" s="73">
-        <v>3705</v>
+        <v>4101</v>
       </c>
       <c r="D863" s="74" t="s">
         <v>160</v>
       </c>
       <c r="E863" s="48">
-        <v>123.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="864" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="72" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="B864" s="72" t="s">
         <v>1239</v>
       </c>
       <c r="C864" s="73">
-        <v>3823</v>
+        <v>4105</v>
       </c>
       <c r="D864" s="74" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E864" s="48">
         <v>77</v>
       </c>
     </row>
-    <row r="865" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="72" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="B865" s="72" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="C865" s="73">
-        <v>4308</v>
+        <v>3705</v>
       </c>
       <c r="D865" s="74" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E865" s="48">
-        <v>68.5</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="866" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A866" s="72" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="B866" s="72" t="s">
-        <v>1248</v>
+        <v>1239</v>
       </c>
       <c r="C866" s="73">
-        <v>4309</v>
+        <v>3823</v>
       </c>
       <c r="D866" s="74" t="s">
-        <v>453</v>
+        <v>15</v>
       </c>
       <c r="E866" s="48">
-        <v>68.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="867" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="72" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="B867" s="72" t="s">
-        <v>1151</v>
+        <v>1248</v>
       </c>
       <c r="C867" s="73">
-        <v>4412</v>
+        <v>4308</v>
       </c>
       <c r="D867" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E867" s="48">
-        <v>71.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="868" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="72" t="s">
-        <v>459</v>
+        <v>1249</v>
       </c>
       <c r="B868" s="72" t="s">
-        <v>33</v>
+        <v>1248</v>
       </c>
       <c r="C868" s="73">
-        <v>4413</v>
+        <v>4309</v>
       </c>
       <c r="D868" s="74" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="E868" s="48">
-        <v>496</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="869" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="72" t="s">
-        <v>459</v>
+        <v>1250</v>
       </c>
       <c r="B869" s="72" t="s">
-        <v>19</v>
+        <v>1151</v>
       </c>
       <c r="C869" s="73">
-        <v>4414</v>
+        <v>4412</v>
       </c>
       <c r="D869" s="74" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="E869" s="48">
-        <v>101</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="870" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="72" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B870" s="72" t="s">
         <v>33</v>
       </c>
       <c r="C870" s="73">
-        <v>4415</v>
+        <v>4413</v>
       </c>
       <c r="D870" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E870" s="48">
-        <v>414</v>
+        <v>496</v>
       </c>
     </row>
     <row r="871" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A871" s="72" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B871" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C871" s="73">
-        <v>4416</v>
+        <v>4414</v>
       </c>
       <c r="D871" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E871" s="48">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="872" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="872" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A872" s="72" t="s">
-        <v>1256</v>
+        <v>460</v>
       </c>
       <c r="B872" s="72" t="s">
-        <v>1257</v>
+        <v>33</v>
       </c>
       <c r="C872" s="73">
-        <v>4475</v>
+        <v>4415</v>
       </c>
       <c r="D872" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E872" s="48">
-        <v>8</v>
+        <v>414</v>
       </c>
     </row>
     <row r="873" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A873" s="72" t="s">
-        <v>1258</v>
+        <v>460</v>
       </c>
       <c r="B873" s="72" t="s">
-        <v>1259</v>
+        <v>19</v>
       </c>
       <c r="C873" s="73">
-        <v>4354</v>
+        <v>4416</v>
       </c>
       <c r="D873" s="74" t="s">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="E873" s="48">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="874" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="874" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="72" t="s">
-        <v>472</v>
+        <v>1256</v>
       </c>
       <c r="B874" s="72" t="s">
-        <v>473</v>
+        <v>1257</v>
       </c>
       <c r="C874" s="73">
-        <v>4445</v>
+        <v>4475</v>
       </c>
       <c r="D874" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E874" s="48">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="875" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="72" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B875" s="72" t="s">
         <v>1259</v>
       </c>
       <c r="C875" s="73">
-        <v>4353</v>
+        <v>4354</v>
       </c>
       <c r="D875" s="74" t="s">
-        <v>50</v>
+        <v>412</v>
       </c>
       <c r="E875" s="48">
         <v>74</v>
@@ -20073,16 +20079,16 @@
     </row>
     <row r="876" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="72" t="s">
-        <v>1261</v>
+        <v>472</v>
       </c>
       <c r="B876" s="72" t="s">
-        <v>1259</v>
+        <v>473</v>
       </c>
       <c r="C876" s="73">
-        <v>4350</v>
+        <v>4445</v>
       </c>
       <c r="D876" s="74" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E876" s="48">
         <v>74</v>
@@ -20090,13 +20096,13 @@
     </row>
     <row r="877" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="72" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B877" s="72" t="s">
         <v>1259</v>
       </c>
       <c r="C877" s="73">
-        <v>4352</v>
+        <v>4353</v>
       </c>
       <c r="D877" s="74" t="s">
         <v>50</v>
@@ -20107,13 +20113,13 @@
     </row>
     <row r="878" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="72" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="B878" s="72" t="s">
         <v>1259</v>
       </c>
       <c r="C878" s="73">
-        <v>4349</v>
+        <v>4350</v>
       </c>
       <c r="D878" s="74" t="s">
         <v>50</v>
@@ -20124,13 +20130,13 @@
     </row>
     <row r="879" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="72" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B879" s="72" t="s">
         <v>1259</v>
       </c>
       <c r="C879" s="73">
-        <v>4351</v>
+        <v>4352</v>
       </c>
       <c r="D879" s="74" t="s">
         <v>50</v>
@@ -20140,137 +20146,157 @@
       </c>
     </row>
     <row r="880" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A880" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="B880" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C880" s="81">
-        <v>4096</v>
-      </c>
-      <c r="D880" s="80" t="s">
-        <v>49</v>
-      </c>
-      <c r="E880" s="42">
-        <v>79</v>
+      <c r="A880" s="72" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B880" s="72" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C880" s="73">
+        <v>4349</v>
+      </c>
+      <c r="D880" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="E880" s="48">
+        <v>74</v>
       </c>
     </row>
     <row r="881" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="72" t="s">
-        <v>1275</v>
+        <v>1264</v>
       </c>
       <c r="B881" s="72" t="s">
-        <v>1276</v>
+        <v>1259</v>
       </c>
       <c r="C881" s="73">
-        <v>4123</v>
+        <v>4351</v>
       </c>
       <c r="D881" s="74" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E881" s="48">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="882" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A882" s="72" t="s">
-        <v>1277</v>
-      </c>
-      <c r="B882" s="72" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C882" s="73">
-        <v>4306</v>
-      </c>
-      <c r="D882" s="74" t="s">
-        <v>453</v>
-      </c>
-      <c r="E882" s="48">
-        <v>81</v>
+      <c r="A882" s="80" t="s">
+        <v>85</v>
+      </c>
+      <c r="B882" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C882" s="81">
+        <v>4096</v>
+      </c>
+      <c r="D882" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="E882" s="42">
+        <v>79</v>
       </c>
     </row>
     <row r="883" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A883" s="72" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B883" s="72" t="s">
-        <v>1239</v>
+        <v>1276</v>
       </c>
       <c r="C883" s="73">
-        <v>4307</v>
+        <v>4123</v>
       </c>
       <c r="D883" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E883" s="48">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="884" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A884" s="72" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B884" s="72" t="s">
-        <v>1280</v>
+        <v>1239</v>
       </c>
       <c r="C884" s="73">
-        <v>2659</v>
-      </c>
-      <c r="D884" s="72" t="s">
-        <v>160</v>
-      </c>
-      <c r="E884" s="50">
-        <v>27.5</v>
+        <v>4306</v>
+      </c>
+      <c r="D884" s="74" t="s">
+        <v>453</v>
+      </c>
+      <c r="E884" s="48">
+        <v>81</v>
       </c>
     </row>
     <row r="885" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A885" s="72" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B885" s="72" t="s">
-        <v>1281</v>
+        <v>1239</v>
       </c>
       <c r="C885" s="73">
-        <v>2621</v>
-      </c>
-      <c r="D885" s="72" t="s">
-        <v>160</v>
-      </c>
-      <c r="E885" s="50">
-        <v>24.5</v>
+        <v>4307</v>
+      </c>
+      <c r="D885" s="74" t="s">
+        <v>453</v>
+      </c>
+      <c r="E885" s="48">
+        <v>81</v>
       </c>
     </row>
     <row r="886" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="72" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="B886" s="72" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="C886" s="73">
-        <v>3656</v>
+        <v>2659</v>
       </c>
       <c r="D886" s="72" t="s">
         <v>160</v>
       </c>
       <c r="E886" s="50">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="887" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A887" s="72" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B887" s="72" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C887" s="73">
+        <v>2621</v>
+      </c>
+      <c r="D887" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="E887" s="50">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="888" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A888" s="72" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B888" s="72" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C888" s="73">
+        <v>3656</v>
+      </c>
+      <c r="D888" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="E888" s="50">
         <v>27</v>
       </c>
-    </row>
-    <row r="887" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A887" s="99"/>
-      <c r="B887" s="99"/>
-      <c r="C887" s="99"/>
-      <c r="D887" s="99"/>
-      <c r="E887" s="100"/>
-    </row>
-    <row r="888" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A888" s="99"/>
-      <c r="B888" s="99"/>
-      <c r="C888" s="99"/>
-      <c r="D888" s="99"/>
-      <c r="E888" s="100"/>
     </row>
     <row r="889" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="99"/>
@@ -20279,272 +20305,284 @@
       <c r="D889" s="99"/>
       <c r="E889" s="100"/>
     </row>
-    <row r="890" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A890" s="121" t="s">
+    <row r="890" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A890" s="99"/>
+      <c r="B890" s="99"/>
+      <c r="C890" s="99"/>
+      <c r="D890" s="99"/>
+      <c r="E890" s="100"/>
+    </row>
+    <row r="891" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A891" s="99"/>
+      <c r="B891" s="99"/>
+      <c r="C891" s="99"/>
+      <c r="D891" s="99"/>
+      <c r="E891" s="100"/>
+    </row>
+    <row r="892" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A892" s="102" t="s">
         <v>1290</v>
       </c>
-      <c r="B890" s="122"/>
-      <c r="C890" s="122"/>
-      <c r="D890" s="122"/>
-      <c r="E890" s="123"/>
-    </row>
-    <row r="891" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A891" s="87" t="s">
+      <c r="B892" s="103"/>
+      <c r="C892" s="103"/>
+      <c r="D892" s="103"/>
+      <c r="E892" s="104"/>
+    </row>
+    <row r="893" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A893" s="87" t="s">
         <v>1293</v>
       </c>
-      <c r="B891" s="87" t="s">
+      <c r="B893" s="87" t="s">
         <v>1291</v>
       </c>
-      <c r="C891" s="88">
+      <c r="C893" s="88">
         <v>3460</v>
       </c>
-      <c r="D891" s="89" t="s">
+      <c r="D893" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E891" s="63">
+      <c r="E893" s="63">
         <v>90</v>
-      </c>
-    </row>
-    <row r="892" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A892" s="72" t="s">
-        <v>1292</v>
-      </c>
-      <c r="B892" s="72" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C892" s="73">
-        <v>3459</v>
-      </c>
-      <c r="D892" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E892" s="48">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="893" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A893" s="72" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B893" s="72" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C893" s="73">
-        <v>3803</v>
-      </c>
-      <c r="D893" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E893" s="48">
-        <v>23</v>
       </c>
     </row>
     <row r="894" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="72" t="s">
-        <v>480</v>
+        <v>1292</v>
       </c>
       <c r="B894" s="72" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="C894" s="73">
-        <v>3425</v>
+        <v>3459</v>
       </c>
       <c r="D894" s="74" t="s">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="E894" s="48">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="895" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="72" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="B895" s="72" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="C895" s="73">
-        <v>3426</v>
+        <v>3803</v>
       </c>
       <c r="D895" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E895" s="48">
-        <v>252</v>
+        <v>23</v>
       </c>
     </row>
     <row r="896" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="72" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B896" s="72" t="s">
         <v>1296</v>
       </c>
       <c r="C896" s="73">
-        <v>3427</v>
+        <v>3425</v>
       </c>
       <c r="D896" s="74" t="s">
         <v>412</v>
       </c>
       <c r="E896" s="48">
-        <v>57</v>
+        <v>27</v>
       </c>
     </row>
     <row r="897" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="72" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B897" s="72" t="s">
         <v>1295</v>
       </c>
       <c r="C897" s="73">
-        <v>3428</v>
+        <v>3426</v>
       </c>
       <c r="D897" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E897" s="48">
-        <v>540</v>
+        <v>252</v>
       </c>
     </row>
     <row r="898" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="72" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B898" s="72" t="s">
         <v>1296</v>
       </c>
       <c r="C898" s="73">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="D898" s="74" t="s">
         <v>412</v>
       </c>
       <c r="E898" s="48">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="899" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="72" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B899" s="72" t="s">
         <v>1295</v>
       </c>
       <c r="C899" s="73">
-        <v>3430</v>
+        <v>3428</v>
       </c>
       <c r="D899" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E899" s="48">
-        <v>660</v>
+        <v>540</v>
       </c>
     </row>
     <row r="900" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="72" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B900" s="72" t="s">
         <v>1296</v>
       </c>
       <c r="C900" s="73">
-        <v>3913</v>
+        <v>3429</v>
       </c>
       <c r="D900" s="74" t="s">
         <v>412</v>
       </c>
       <c r="E900" s="48">
-        <v>62.5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="901" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="72" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B901" s="72" t="s">
         <v>1295</v>
       </c>
       <c r="C901" s="73">
-        <v>3872</v>
+        <v>3430</v>
       </c>
       <c r="D901" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E901" s="48">
-        <v>582</v>
+        <v>660</v>
       </c>
     </row>
     <row r="902" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="72" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B902" s="72" t="s">
         <v>1296</v>
       </c>
       <c r="C902" s="73">
-        <v>3422</v>
+        <v>3913</v>
       </c>
       <c r="D902" s="74" t="s">
         <v>412</v>
       </c>
       <c r="E902" s="48">
-        <v>18</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="903" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="72" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B903" s="72" t="s">
         <v>1295</v>
       </c>
       <c r="C903" s="73">
-        <v>3423</v>
+        <v>3872</v>
       </c>
       <c r="D903" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E903" s="48">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="904" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A904" s="83" t="s">
-        <v>485</v>
-      </c>
-      <c r="B904" s="83" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C904" s="84">
-        <v>3431</v>
+        <v>582</v>
+      </c>
+    </row>
+    <row r="904" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A904" s="72" t="s">
+        <v>484</v>
+      </c>
+      <c r="B904" s="72" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C904" s="73">
+        <v>3422</v>
       </c>
       <c r="D904" s="74" t="s">
         <v>412</v>
       </c>
       <c r="E904" s="48">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="905" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A905" s="72" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B905" s="72" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C905" s="73">
+        <v>3423</v>
+      </c>
+      <c r="D905" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E905" s="48">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="906" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A906" s="83" t="s">
+        <v>485</v>
+      </c>
+      <c r="B906" s="83" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C906" s="84">
+        <v>3431</v>
+      </c>
+      <c r="D906" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="E906" s="48">
         <v>105</v>
       </c>
     </row>
-    <row r="905" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A905" s="90" t="s">
+    <row r="907" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A907" s="90" t="s">
         <v>485</v>
       </c>
-      <c r="B905" s="90" t="s">
+      <c r="B907" s="90" t="s">
         <v>1295</v>
       </c>
-      <c r="C905" s="91">
+      <c r="C907" s="91">
         <v>3432</v>
       </c>
-      <c r="D905" s="92" t="s">
+      <c r="D907" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="E905" s="48">
+      <c r="E907" s="48">
         <v>996</v>
       </c>
     </row>
-    <row r="906" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
-    <row r="907" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="908" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="909" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="910" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
@@ -20552,29 +20590,25 @@
     <row r="912" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="913" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="914" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
-    <row r="916" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A916" s="64" t="s">
+    <row r="915" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
+    <row r="916" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
+    <row r="918" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A918" s="64" t="s">
         <v>386</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A890:E890"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A287:E287"/>
-    <mergeCell ref="A598:E598"/>
-    <mergeCell ref="A715:E715"/>
-    <mergeCell ref="A736:E736"/>
-    <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A560:E560"/>
-    <mergeCell ref="A714:E714"/>
-    <mergeCell ref="A288:E288"/>
+    <mergeCell ref="A737:E737"/>
+    <mergeCell ref="A597:E597"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A775:E775"/>
+    <mergeCell ref="A729:E729"/>
+    <mergeCell ref="A748:E748"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A538:E538"/>
     <mergeCell ref="A8:E8"/>
@@ -20586,16 +20620,22 @@
     <mergeCell ref="A381:E381"/>
     <mergeCell ref="A140:E140"/>
     <mergeCell ref="A215:E215"/>
-    <mergeCell ref="A735:E735"/>
-    <mergeCell ref="A597:E597"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A773:E773"/>
-    <mergeCell ref="A727:E727"/>
-    <mergeCell ref="A746:E746"/>
-    <mergeCell ref="A747:E747"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
+    <mergeCell ref="A892:E892"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A287:E287"/>
+    <mergeCell ref="A598:E598"/>
+    <mergeCell ref="A717:E717"/>
+    <mergeCell ref="A738:E738"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A560:E560"/>
+    <mergeCell ref="A716:E716"/>
+    <mergeCell ref="A288:E288"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20635,78 +20675,78 @@
       <c r="A2" s="148" t="s">
         <v>486</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="139"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="138"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="150" t="s">
+      <c r="A3" s="137" t="s">
         <v>487</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="139"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="138"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="149" t="s">
         <v>488</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="139"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="138"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="137" t="s">
         <v>489</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="139"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="138"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="135"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="139"/>
+      <c r="B6" s="134"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="138"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>490</v>
       </c>
-      <c r="B7" s="135"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="139"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="138"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="139"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="138"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="139"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="138"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="140" t="s">
+      <c r="A10" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="120"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22429,19 +22469,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="134"/>
-      <c r="B112" s="135"/>
-      <c r="C112" s="136"/>
-      <c r="D112" s="137"/>
+      <c r="A112" s="133"/>
+      <c r="B112" s="134"/>
+      <c r="C112" s="135"/>
+      <c r="D112" s="136"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="149" t="s">
+      <c r="A113" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="112"/>
-      <c r="C113" s="112"/>
-      <c r="D113" s="120"/>
+      <c r="B113" s="119"/>
+      <c r="C113" s="119"/>
+      <c r="D113" s="127"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22734,19 +22774,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="134"/>
-      <c r="B131" s="135"/>
-      <c r="C131" s="136"/>
-      <c r="D131" s="137"/>
+      <c r="A131" s="133"/>
+      <c r="B131" s="134"/>
+      <c r="C131" s="135"/>
+      <c r="D131" s="136"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="149" t="s">
+      <c r="A132" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="112"/>
-      <c r="C132" s="112"/>
-      <c r="D132" s="120"/>
+      <c r="B132" s="119"/>
+      <c r="C132" s="119"/>
+      <c r="D132" s="127"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22920,19 +22960,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="134"/>
-      <c r="B143" s="135"/>
-      <c r="C143" s="136"/>
-      <c r="D143" s="137"/>
+      <c r="A143" s="133"/>
+      <c r="B143" s="134"/>
+      <c r="C143" s="135"/>
+      <c r="D143" s="136"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="149" t="s">
+      <c r="A144" s="140" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="112"/>
-      <c r="C144" s="112"/>
-      <c r="D144" s="120"/>
+      <c r="B144" s="119"/>
+      <c r="C144" s="119"/>
+      <c r="D144" s="127"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23565,19 +23605,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="134"/>
-      <c r="B182" s="135"/>
-      <c r="C182" s="136"/>
-      <c r="D182" s="137"/>
+      <c r="A182" s="133"/>
+      <c r="B182" s="134"/>
+      <c r="C182" s="135"/>
+      <c r="D182" s="136"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="133" t="s">
+      <c r="A183" s="139" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="112"/>
-      <c r="C183" s="112"/>
-      <c r="D183" s="112"/>
+      <c r="B183" s="119"/>
+      <c r="C183" s="119"/>
+      <c r="D183" s="119"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24439,19 +24479,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="134"/>
-      <c r="B241" s="135"/>
-      <c r="C241" s="136"/>
-      <c r="D241" s="137"/>
+      <c r="A241" s="133"/>
+      <c r="B241" s="134"/>
+      <c r="C241" s="135"/>
+      <c r="D241" s="136"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="133" t="s">
+      <c r="A242" s="139" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="112"/>
-      <c r="C242" s="112"/>
-      <c r="D242" s="112"/>
+      <c r="B242" s="119"/>
+      <c r="C242" s="119"/>
+      <c r="D242" s="119"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25672,21 +25712,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="134"/>
-      <c r="B324" s="135"/>
-      <c r="C324" s="136"/>
-      <c r="D324" s="137"/>
+      <c r="A324" s="133"/>
+      <c r="B324" s="134"/>
+      <c r="C324" s="135"/>
+      <c r="D324" s="136"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="133" t="s">
+      <c r="A325" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="112"/>
-      <c r="C325" s="112"/>
-      <c r="D325" s="112"/>
+      <c r="B325" s="119"/>
+      <c r="C325" s="119"/>
+      <c r="D325" s="119"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26183,19 +26223,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="134"/>
-      <c r="B355" s="135"/>
-      <c r="C355" s="136"/>
-      <c r="D355" s="137"/>
+      <c r="A355" s="133"/>
+      <c r="B355" s="134"/>
+      <c r="C355" s="135"/>
+      <c r="D355" s="136"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="133" t="s">
+      <c r="A356" s="139" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="112"/>
-      <c r="C356" s="112"/>
-      <c r="D356" s="112"/>
+      <c r="B356" s="119"/>
+      <c r="C356" s="119"/>
+      <c r="D356" s="119"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -27950,19 +27990,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="134"/>
-      <c r="B460" s="135"/>
-      <c r="C460" s="136"/>
-      <c r="D460" s="137"/>
+      <c r="A460" s="133"/>
+      <c r="B460" s="134"/>
+      <c r="C460" s="135"/>
+      <c r="D460" s="136"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="133" t="s">
+      <c r="A461" s="139" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="112"/>
-      <c r="C461" s="112"/>
-      <c r="D461" s="112"/>
+      <c r="B461" s="119"/>
+      <c r="C461" s="119"/>
+      <c r="D461" s="119"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28255,19 +28295,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="134"/>
-      <c r="B479" s="135"/>
-      <c r="C479" s="136"/>
-      <c r="D479" s="137"/>
+      <c r="A479" s="133"/>
+      <c r="B479" s="134"/>
+      <c r="C479" s="135"/>
+      <c r="D479" s="136"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="133" t="s">
+      <c r="A480" s="139" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="112"/>
-      <c r="C480" s="112"/>
-      <c r="D480" s="112"/>
+      <c r="B480" s="119"/>
+      <c r="C480" s="119"/>
+      <c r="D480" s="119"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28696,19 +28736,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="134"/>
-      <c r="B506" s="135"/>
-      <c r="C506" s="136"/>
-      <c r="D506" s="137"/>
+      <c r="A506" s="133"/>
+      <c r="B506" s="134"/>
+      <c r="C506" s="135"/>
+      <c r="D506" s="136"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="133" t="s">
+      <c r="A507" s="139" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="112"/>
-      <c r="C507" s="112"/>
-      <c r="D507" s="112"/>
+      <c r="B507" s="119"/>
+      <c r="C507" s="119"/>
+      <c r="D507" s="119"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30223,19 +30263,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="134"/>
-      <c r="B597" s="135"/>
-      <c r="C597" s="136"/>
-      <c r="D597" s="137"/>
+      <c r="A597" s="133"/>
+      <c r="B597" s="134"/>
+      <c r="C597" s="135"/>
+      <c r="D597" s="136"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="133" t="s">
+      <c r="A598" s="139" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="112"/>
-      <c r="C598" s="112"/>
-      <c r="D598" s="112"/>
+      <c r="B598" s="119"/>
+      <c r="C598" s="119"/>
+      <c r="D598" s="119"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30375,20 +30415,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="134"/>
-      <c r="B607" s="135"/>
-      <c r="C607" s="136"/>
-      <c r="D607" s="137"/>
+      <c r="A607" s="133"/>
+      <c r="B607" s="134"/>
+      <c r="C607" s="135"/>
+      <c r="D607" s="136"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="133" t="s">
+      <c r="A608" s="139" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="112"/>
-      <c r="C608" s="112"/>
-      <c r="D608" s="112"/>
+      <c r="B608" s="119"/>
+      <c r="C608" s="119"/>
+      <c r="D608" s="119"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30477,19 +30517,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="134"/>
-      <c r="B614" s="135"/>
-      <c r="C614" s="136"/>
-      <c r="D614" s="137"/>
+      <c r="A614" s="133"/>
+      <c r="B614" s="134"/>
+      <c r="C614" s="135"/>
+      <c r="D614" s="136"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="133" t="s">
+      <c r="A615" s="139" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="112"/>
-      <c r="C615" s="112"/>
-      <c r="D615" s="112"/>
+      <c r="B615" s="119"/>
+      <c r="C615" s="119"/>
+      <c r="D615" s="119"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31854,25 +31894,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31889,6 +31910,25 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D8C31A-35AA-4EFD-A8FC-B554C14EB381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E71658-BF65-43BB-9194-B025E55FA67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9690" yWindow="3030" windowWidth="13710" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PRODUTOS B" sheetId="1" r:id="rId1"/>
@@ -7191,7 +7191,7 @@
         <v>50</v>
       </c>
       <c r="E101" s="40">
-        <v>690</v>
+        <v>630</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7208,7 +7208,7 @@
         <v>49</v>
       </c>
       <c r="E102" s="40">
-        <v>347</v>
+        <v>317</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7970,7 +7970,7 @@
         <v>50</v>
       </c>
       <c r="E150" s="40">
-        <v>320</v>
+        <v>300</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7987,7 +7987,7 @@
         <v>49</v>
       </c>
       <c r="E151" s="40">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8259,7 +8259,7 @@
         <v>84</v>
       </c>
       <c r="E167" s="40">
-        <v>1125</v>
+        <v>850</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -8276,7 +8276,7 @@
         <v>49</v>
       </c>
       <c r="E168" s="40">
-        <v>227</v>
+        <v>172.5</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -8565,7 +8565,7 @@
         <v>34</v>
       </c>
       <c r="E185" s="40">
-        <v>650</v>
+        <v>725</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -8582,7 +8582,7 @@
         <v>34</v>
       </c>
       <c r="E186" s="40">
-        <v>520</v>
+        <v>580</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -8599,7 +8599,7 @@
         <v>49</v>
       </c>
       <c r="E187" s="40">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10058,7 +10058,7 @@
         <v>34</v>
       </c>
       <c r="E274" s="40">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="275" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10378,7 +10378,7 @@
         <v>84</v>
       </c>
       <c r="E294" s="40">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="295" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10395,7 +10395,7 @@
         <v>49</v>
       </c>
       <c r="E295" s="40">
-        <v>15</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="296" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10412,7 +10412,7 @@
         <v>84</v>
       </c>
       <c r="E296" s="40">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="297" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10429,10 +10429,10 @@
         <v>49</v>
       </c>
       <c r="E297" s="40">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A298" s="69" t="s">
         <v>192</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>49</v>
       </c>
       <c r="E298" s="40">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="299" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10463,7 +10463,7 @@
         <v>84</v>
       </c>
       <c r="E299" s="40">
-        <v>15</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="300" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12483,7 +12483,7 @@
         <v>84</v>
       </c>
       <c r="E419" s="51">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="420" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -12500,7 +12500,7 @@
         <v>49</v>
       </c>
       <c r="E420" s="42">
-        <v>26</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="421" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -14399,7 +14399,7 @@
         <v>49</v>
       </c>
       <c r="E533" s="40">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="534" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -14416,7 +14416,7 @@
         <v>49</v>
       </c>
       <c r="E534" s="40">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="535" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16722,7 +16722,7 @@
         <v>34</v>
       </c>
       <c r="E673" s="40">
-        <v>285</v>
+        <v>250</v>
       </c>
     </row>
     <row r="674" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16739,7 +16739,7 @@
         <v>20</v>
       </c>
       <c r="E674" s="40">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="675" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -17070,16 +17070,16 @@
         <v>413</v>
       </c>
       <c r="B694" s="69" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C694" s="70">
-        <v>2805</v>
+        <v>3637</v>
       </c>
       <c r="D694" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E694" s="40">
-        <v>160</v>
+        <v>375</v>
       </c>
     </row>
     <row r="695" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17087,16 +17087,16 @@
         <v>413</v>
       </c>
       <c r="B695" s="69" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C695" s="70">
-        <v>3637</v>
+        <v>2805</v>
       </c>
       <c r="D695" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E695" s="40">
-        <v>400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="696" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17113,7 +17113,7 @@
         <v>20</v>
       </c>
       <c r="E696" s="40">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="697" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E71658-BF65-43BB-9194-B025E55FA67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC9039B-D5DC-4194-8407-A32866F91CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9690" yWindow="3030" windowWidth="13710" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTA DE PRODUTOS B" sheetId="1" r:id="rId1"/>
     <sheet name="LISTA DE PRODUTOS T" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PRODUTOS B'!$A$1:$E$907</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PRODUTOS B'!$A$1:$E$908</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4021" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4024" uniqueCount="1337">
   <si>
     <t xml:space="preserve">    Tabela de Produtos e Preços</t>
   </si>
@@ -1440,12 +1440,6 @@
   </si>
   <si>
     <t>MANDIOCA FRITA CHIPS 500G</t>
-  </si>
-  <si>
-    <t>MARSHMALLOW RECHEADO PINTA LÍNGUA 12X</t>
-  </si>
-  <si>
-    <t>220KG</t>
   </si>
   <si>
     <t>MELADO 12X300ML</t>
@@ -4036,6 +4030,12 @@
   </si>
   <si>
     <t>MACA PERUANA VERMELHA DJ</t>
+  </si>
+  <si>
+    <t>MARSHMALLOW RECHEADO PINTA LÍNGUA-80075</t>
+  </si>
+  <si>
+    <t>MARSHMALLOW MIX FOFURAS-81274</t>
   </si>
 </sst>
 </file>
@@ -4809,7 +4809,7 @@
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -5116,6 +5116,51 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5133,12 +5178,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5148,43 +5187,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5199,14 +5202,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5227,11 +5227,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5539,7 +5545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R918"/>
+  <dimension ref="A1:R919"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62.1640625" style="64" bestFit="1" customWidth="1"/>
@@ -5552,83 +5558,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="126"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="128"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="111"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="128"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="111"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="128"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="128"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="108"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="111"/>
+      <c r="A6" s="127"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="128"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="114"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="125"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="117"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="122" t="s">
+      <c r="A9" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="120"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -6094,7 +6100,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="69" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C37" s="70">
         <v>2263</v>
@@ -6332,7 +6338,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="72" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C51" s="73">
         <v>2452</v>
@@ -6349,7 +6355,7 @@
         <v>45</v>
       </c>
       <c r="B52" s="72" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C52" s="73">
         <v>150</v>
@@ -6485,7 +6491,7 @@
         <v>51</v>
       </c>
       <c r="B60" s="72" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C60" s="73">
         <v>2442</v>
@@ -6519,7 +6525,7 @@
         <v>52</v>
       </c>
       <c r="B62" s="72" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C62" s="73">
         <v>3441</v>
@@ -6570,7 +6576,7 @@
         <v>53</v>
       </c>
       <c r="B65" s="72" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="C65" s="73">
         <v>2273</v>
@@ -6771,7 +6777,7 @@
     </row>
     <row r="77" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="69" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B77" s="69" t="s">
         <v>28</v>
@@ -6856,7 +6862,7 @@
     </row>
     <row r="82" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="69" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B82" s="69" t="s">
         <v>19</v>
@@ -6907,7 +6913,7 @@
     </row>
     <row r="85" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="69" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B85" s="69" t="s">
         <v>19</v>
@@ -7216,7 +7222,7 @@
         <v>81</v>
       </c>
       <c r="B103" s="75" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="C103" s="76">
         <v>4179</v>
@@ -7314,27 +7320,27 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="121"/>
-      <c r="B109" s="109"/>
-      <c r="C109" s="109"/>
-      <c r="D109" s="110"/>
-      <c r="E109" s="117"/>
+      <c r="A109" s="102"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="103"/>
+      <c r="D109" s="104"/>
+      <c r="E109" s="105"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="122" t="s">
+      <c r="A110" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="119"/>
-      <c r="C110" s="119"/>
-      <c r="D110" s="119"/>
-      <c r="E110" s="120"/>
+      <c r="B110" s="112"/>
+      <c r="C110" s="112"/>
+      <c r="D110" s="112"/>
+      <c r="E110" s="113"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
         <v>8</v>
       </c>
       <c r="B111" s="66" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C111" s="66" t="s">
         <v>10</v>
@@ -7619,20 +7625,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="121"/>
-      <c r="B128" s="109"/>
-      <c r="C128" s="109"/>
-      <c r="D128" s="110"/>
-      <c r="E128" s="117"/>
+      <c r="A128" s="102"/>
+      <c r="B128" s="103"/>
+      <c r="C128" s="103"/>
+      <c r="D128" s="104"/>
+      <c r="E128" s="105"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="122" t="s">
+      <c r="A129" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="119"/>
-      <c r="C129" s="119"/>
-      <c r="D129" s="119"/>
-      <c r="E129" s="120"/>
+      <c r="B129" s="112"/>
+      <c r="C129" s="112"/>
+      <c r="D129" s="112"/>
+      <c r="E129" s="113"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7788,20 +7794,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="121"/>
-      <c r="B139" s="109"/>
-      <c r="C139" s="109"/>
-      <c r="D139" s="110"/>
-      <c r="E139" s="117"/>
+      <c r="A139" s="102"/>
+      <c r="B139" s="103"/>
+      <c r="C139" s="103"/>
+      <c r="D139" s="104"/>
+      <c r="E139" s="105"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="126" t="s">
+      <c r="A140" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="119"/>
-      <c r="C140" s="119"/>
-      <c r="D140" s="119"/>
-      <c r="E140" s="127"/>
+      <c r="B140" s="112"/>
+      <c r="C140" s="112"/>
+      <c r="D140" s="112"/>
+      <c r="E140" s="120"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -7842,7 +7848,7 @@
         <v>107</v>
       </c>
       <c r="B143" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C143" s="73">
         <v>2832</v>
@@ -8029,7 +8035,7 @@
         <v>114</v>
       </c>
       <c r="B154" s="69" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="C154" s="70">
         <v>2540</v>
@@ -9045,20 +9051,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="121"/>
-      <c r="B214" s="109"/>
-      <c r="C214" s="109"/>
-      <c r="D214" s="110"/>
-      <c r="E214" s="117"/>
+      <c r="A214" s="102"/>
+      <c r="B214" s="103"/>
+      <c r="C214" s="103"/>
+      <c r="D214" s="104"/>
+      <c r="E214" s="105"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="122" t="s">
+      <c r="A215" s="118" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="119"/>
-      <c r="C215" s="119"/>
-      <c r="D215" s="119"/>
-      <c r="E215" s="120"/>
+      <c r="B215" s="112"/>
+      <c r="C215" s="112"/>
+      <c r="D215" s="112"/>
+      <c r="E215" s="113"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -9128,7 +9134,7 @@
     </row>
     <row r="220" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="69" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="B220" s="69" t="s">
         <v>33</v>
@@ -9145,7 +9151,7 @@
     </row>
     <row r="221" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="69" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B221" s="69" t="s">
         <v>33</v>
@@ -9335,7 +9341,7 @@
         <v>157</v>
       </c>
       <c r="B232" s="69" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C232" s="70">
         <v>3415</v>
@@ -9386,7 +9392,7 @@
         <v>159</v>
       </c>
       <c r="B235" s="69" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C235" s="70">
         <v>3416</v>
@@ -9400,7 +9406,7 @@
     </row>
     <row r="236" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="69" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="B236" s="69" t="s">
         <v>33</v>
@@ -9417,7 +9423,7 @@
     </row>
     <row r="237" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="69" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="B237" s="69" t="s">
         <v>110</v>
@@ -9947,7 +9953,7 @@
         <v>176</v>
       </c>
       <c r="B268" s="69" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C268" s="70">
         <v>2246</v>
@@ -9998,7 +10004,7 @@
         <v>178</v>
       </c>
       <c r="B271" s="69" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C271" s="70">
         <v>258</v>
@@ -10063,7 +10069,7 @@
     </row>
     <row r="275" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="69" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B275" s="69" t="s">
         <v>33</v>
@@ -10148,10 +10154,10 @@
     </row>
     <row r="280" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="69" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B280" s="69" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C280" s="70">
         <v>4086</v>
@@ -10266,20 +10272,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="116"/>
-      <c r="B287" s="109"/>
-      <c r="C287" s="109"/>
-      <c r="D287" s="110"/>
-      <c r="E287" s="117"/>
+      <c r="A287" s="114"/>
+      <c r="B287" s="103"/>
+      <c r="C287" s="103"/>
+      <c r="D287" s="104"/>
+      <c r="E287" s="105"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="122" t="s">
+      <c r="A288" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="119"/>
-      <c r="C288" s="119"/>
-      <c r="D288" s="119"/>
-      <c r="E288" s="120"/>
+      <c r="B288" s="112"/>
+      <c r="C288" s="112"/>
+      <c r="D288" s="112"/>
+      <c r="E288" s="113"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -10420,7 +10426,7 @@
         <v>190</v>
       </c>
       <c r="B297" s="69" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C297" s="70">
         <v>2501</v>
@@ -10556,7 +10562,7 @@
         <v>197</v>
       </c>
       <c r="B305" s="69" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C305" s="70">
         <v>4017</v>
@@ -10587,10 +10593,10 @@
     </row>
     <row r="307" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="69" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B307" s="69" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C307" s="70">
         <v>4545</v>
@@ -10604,10 +10610,10 @@
     </row>
     <row r="308" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="69" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B308" s="69" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C308" s="70">
         <v>3363</v>
@@ -10922,7 +10928,7 @@
         <v>84</v>
       </c>
       <c r="E326" s="40">
-        <v>210</v>
+        <v>260</v>
       </c>
     </row>
     <row r="327" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10939,7 +10945,7 @@
         <v>49</v>
       </c>
       <c r="E327" s="40">
-        <v>37</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="328" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -11151,7 +11157,7 @@
         <v>215</v>
       </c>
       <c r="B340" s="69" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C340" s="70">
         <v>2666</v>
@@ -11576,7 +11582,7 @@
         <v>227</v>
       </c>
       <c r="B365" s="69" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C365" s="70">
         <v>67</v>
@@ -11593,7 +11599,7 @@
         <v>227</v>
       </c>
       <c r="B366" s="69" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="C366" s="70">
         <v>2244</v>
@@ -11624,7 +11630,7 @@
     </row>
     <row r="368" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="69" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B368" s="69" t="s">
         <v>33</v>
@@ -11644,7 +11650,7 @@
         <v>229</v>
       </c>
       <c r="B369" s="69" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C369" s="70">
         <v>4546</v>
@@ -11844,20 +11850,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="116"/>
-      <c r="B381" s="109"/>
-      <c r="C381" s="109"/>
-      <c r="D381" s="110"/>
-      <c r="E381" s="117"/>
+      <c r="A381" s="114"/>
+      <c r="B381" s="103"/>
+      <c r="C381" s="103"/>
+      <c r="D381" s="104"/>
+      <c r="E381" s="105"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="118" t="s">
+      <c r="A382" s="111" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="119"/>
-      <c r="C382" s="119"/>
-      <c r="D382" s="119"/>
-      <c r="E382" s="120"/>
+      <c r="B382" s="112"/>
+      <c r="C382" s="112"/>
+      <c r="D382" s="112"/>
+      <c r="E382" s="113"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12148,10 +12154,10 @@
     </row>
     <row r="400" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="85" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B400" s="85" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C400" s="86">
         <v>4558</v>
@@ -12165,10 +12171,10 @@
     </row>
     <row r="401" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="80" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="B401" s="80" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C401" s="81">
         <v>4048</v>
@@ -12511,13 +12517,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="118" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B422" s="119"/>
-      <c r="C422" s="119"/>
-      <c r="D422" s="119"/>
-      <c r="E422" s="120"/>
+      <c r="A422" s="111" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B422" s="112"/>
+      <c r="C422" s="112"/>
+      <c r="D422" s="112"/>
+      <c r="E422" s="113"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -12638,7 +12644,7 @@
     </row>
     <row r="430" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="69" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B430" s="69" t="s">
         <v>18</v>
@@ -12655,7 +12661,7 @@
     </row>
     <row r="431" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="69" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B431" s="69" t="s">
         <v>19</v>
@@ -13044,10 +13050,10 @@
     </row>
     <row r="454" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="69" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B454" s="69" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C454" s="70">
         <v>4029</v>
@@ -13061,10 +13067,10 @@
     </row>
     <row r="455" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="69" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="B455" s="69" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C455" s="70">
         <v>4203</v>
@@ -13078,10 +13084,10 @@
     </row>
     <row r="456" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="69" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B456" s="69" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C456" s="70">
         <v>3936</v>
@@ -13095,10 +13101,10 @@
     </row>
     <row r="457" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="72" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B457" s="72" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C457" s="73">
         <v>4302</v>
@@ -13132,7 +13138,7 @@
         <v>280</v>
       </c>
       <c r="B459" s="69" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C459" s="70">
         <v>3026</v>
@@ -13166,7 +13172,7 @@
         <v>281</v>
       </c>
       <c r="B461" s="69" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C461" s="70">
         <v>3515</v>
@@ -13625,7 +13631,7 @@
         <v>304</v>
       </c>
       <c r="B488" s="69" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C488" s="70">
         <v>2734</v>
@@ -14454,20 +14460,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="116"/>
-      <c r="B537" s="109"/>
-      <c r="C537" s="109"/>
-      <c r="D537" s="110"/>
-      <c r="E537" s="117"/>
+      <c r="A537" s="114"/>
+      <c r="B537" s="103"/>
+      <c r="C537" s="103"/>
+      <c r="D537" s="104"/>
+      <c r="E537" s="105"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="118" t="s">
+      <c r="A538" s="111" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="119"/>
-      <c r="C538" s="119"/>
-      <c r="D538" s="119"/>
-      <c r="E538" s="120"/>
+      <c r="B538" s="112"/>
+      <c r="C538" s="112"/>
+      <c r="D538" s="112"/>
+      <c r="E538" s="113"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14608,7 +14614,7 @@
         <v>344</v>
       </c>
       <c r="B547" s="69" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C547" s="70">
         <v>3651</v>
@@ -14676,7 +14682,7 @@
         <v>347</v>
       </c>
       <c r="B551" s="69" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C551" s="70">
         <v>2756</v>
@@ -14707,10 +14713,10 @@
     </row>
     <row r="553" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="69" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B553" s="69" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C553" s="70">
         <v>4491</v>
@@ -14724,10 +14730,10 @@
     </row>
     <row r="554" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="69" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B554" s="69" t="s">
         <v>1149</v>
-      </c>
-      <c r="B554" s="69" t="s">
-        <v>1151</v>
       </c>
       <c r="C554" s="70">
         <v>4492</v>
@@ -14825,20 +14831,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="116"/>
-      <c r="B560" s="109"/>
-      <c r="C560" s="109"/>
-      <c r="D560" s="110"/>
-      <c r="E560" s="117"/>
+      <c r="A560" s="114"/>
+      <c r="B560" s="103"/>
+      <c r="C560" s="103"/>
+      <c r="D560" s="104"/>
+      <c r="E560" s="105"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="118" t="s">
+      <c r="A561" s="111" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="119"/>
-      <c r="C561" s="119"/>
-      <c r="D561" s="119"/>
-      <c r="E561" s="120"/>
+      <c r="B561" s="112"/>
+      <c r="C561" s="112"/>
+      <c r="D561" s="112"/>
+      <c r="E561" s="113"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15146,10 +15152,10 @@
     </row>
     <row r="580" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="72" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B580" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C580" s="73">
         <v>4202</v>
@@ -15163,10 +15169,10 @@
     </row>
     <row r="581" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="72" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B581" s="72" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C581" s="73">
         <v>4201</v>
@@ -15434,20 +15440,20 @@
       </c>
     </row>
     <row r="597" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="128"/>
-      <c r="B597" s="129"/>
-      <c r="C597" s="129"/>
-      <c r="D597" s="129"/>
-      <c r="E597" s="129"/>
+      <c r="A597" s="106"/>
+      <c r="B597" s="107"/>
+      <c r="C597" s="107"/>
+      <c r="D597" s="107"/>
+      <c r="E597" s="107"/>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="118" t="s">
+      <c r="A598" s="111" t="s">
         <v>370</v>
       </c>
-      <c r="B598" s="119"/>
-      <c r="C598" s="119"/>
-      <c r="D598" s="119"/>
-      <c r="E598" s="120"/>
+      <c r="B598" s="112"/>
+      <c r="C598" s="112"/>
+      <c r="D598" s="112"/>
+      <c r="E598" s="113"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="66" t="s">
@@ -15520,7 +15526,7 @@
         <v>373</v>
       </c>
       <c r="B603" s="69" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C603" s="70">
         <v>2297</v>
@@ -15554,7 +15560,7 @@
         <v>373</v>
       </c>
       <c r="B605" s="69" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C605" s="70">
         <v>2339</v>
@@ -15568,10 +15574,10 @@
     </row>
     <row r="606" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="69" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B606" s="69" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C606" s="70">
         <v>2223</v>
@@ -15585,10 +15591,10 @@
     </row>
     <row r="607" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="69" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B607" s="69" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C607" s="70">
         <v>3707</v>
@@ -15602,7 +15608,7 @@
     </row>
     <row r="608" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="69" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B608" s="69" t="s">
         <v>33</v>
@@ -15636,7 +15642,7 @@
     </row>
     <row r="610" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="69" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B610" s="69" t="s">
         <v>110</v>
@@ -15653,7 +15659,7 @@
     </row>
     <row r="611" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="69" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B611" s="69" t="s">
         <v>110</v>
@@ -15687,7 +15693,7 @@
     </row>
     <row r="613" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="69" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B613" s="69" t="s">
         <v>110</v>
@@ -15806,7 +15812,7 @@
     </row>
     <row r="620" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="69" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="B620" s="69" t="s">
         <v>19</v>
@@ -15823,7 +15829,7 @@
     </row>
     <row r="621" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="69" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B621" s="69" t="s">
         <v>19</v>
@@ -15877,7 +15883,7 @@
         <v>380</v>
       </c>
       <c r="B624" s="69" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C624" s="70">
         <v>2783</v>
@@ -15894,7 +15900,7 @@
         <v>380</v>
       </c>
       <c r="B625" s="69" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C625" s="70">
         <v>3755</v>
@@ -16183,10 +16189,10 @@
     </row>
     <row r="642" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="69" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B642" s="69" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C642" s="70">
         <v>3537</v>
@@ -16302,10 +16308,10 @@
     </row>
     <row r="649" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="69" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B649" s="69" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C649" s="70">
         <v>4498</v>
@@ -16356,7 +16362,7 @@
         <v>397</v>
       </c>
       <c r="B652" s="69" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C652" s="70">
         <v>4249</v>
@@ -16373,7 +16379,7 @@
         <v>397</v>
       </c>
       <c r="B653" s="69" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C653" s="70">
         <v>3724</v>
@@ -16387,10 +16393,10 @@
     </row>
     <row r="654" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="69" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B654" s="69" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C654" s="70">
         <v>3736</v>
@@ -16404,10 +16410,10 @@
     </row>
     <row r="655" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="69" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B655" s="69" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C655" s="70">
         <v>4499</v>
@@ -16421,10 +16427,10 @@
     </row>
     <row r="656" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="69" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="B656" s="69" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C656" s="70">
         <v>3536</v>
@@ -16472,10 +16478,10 @@
     </row>
     <row r="659" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="72" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B659" s="72" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C659" s="73">
         <v>4497</v>
@@ -16506,10 +16512,10 @@
     </row>
     <row r="661" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="69" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="B661" s="69" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C661" s="70">
         <v>3535</v>
@@ -16574,7 +16580,7 @@
     </row>
     <row r="665" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="72" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B665" s="72" t="s">
         <v>33</v>
@@ -16591,7 +16597,7 @@
     </row>
     <row r="666" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="72" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B666" s="72" t="s">
         <v>19</v>
@@ -16846,7 +16852,7 @@
     </row>
     <row r="681" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="69" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B681" s="69" t="s">
         <v>19</v>
@@ -16863,7 +16869,7 @@
     </row>
     <row r="682" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="69" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B682" s="69" t="s">
         <v>19</v>
@@ -16999,10 +17005,10 @@
     </row>
     <row r="690" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="69" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B690" s="69" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C690" s="70">
         <v>3521</v>
@@ -17016,10 +17022,10 @@
     </row>
     <row r="691" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="69" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B691" s="69" t="s">
         <v>1164</v>
-      </c>
-      <c r="B691" s="69" t="s">
-        <v>1166</v>
       </c>
       <c r="C691" s="70">
         <v>3522</v>
@@ -17033,10 +17039,10 @@
     </row>
     <row r="692" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="72" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="B692" s="72" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C692" s="73">
         <v>64</v>
@@ -17050,10 +17056,10 @@
     </row>
     <row r="693" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="69" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B693" s="69" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C693" s="70">
         <v>90</v>
@@ -17152,10 +17158,10 @@
     </row>
     <row r="699" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="69" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B699" s="69" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C699" s="70">
         <v>3395</v>
@@ -17169,10 +17175,10 @@
     </row>
     <row r="700" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="69" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B700" s="69" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C700" s="70">
         <v>3490</v>
@@ -17186,10 +17192,10 @@
     </row>
     <row r="701" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="69" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B701" s="69" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C701" s="70">
         <v>458</v>
@@ -17203,10 +17209,10 @@
     </row>
     <row r="702" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="69" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="B702" s="69" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C702" s="70">
         <v>2641</v>
@@ -17220,10 +17226,10 @@
     </row>
     <row r="703" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="75" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B703" s="75" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C703" s="76">
         <v>4293</v>
@@ -17339,10 +17345,10 @@
     </row>
     <row r="710" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="72" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="B710" s="72" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C710" s="73">
         <v>2646</v>
@@ -17356,10 +17362,10 @@
     </row>
     <row r="711" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="72" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B711" s="72" t="s">
         <v>1265</v>
-      </c>
-      <c r="B711" s="72" t="s">
-        <v>1267</v>
       </c>
       <c r="C711" s="73">
         <v>2645</v>
@@ -17373,10 +17379,10 @@
     </row>
     <row r="712" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="72" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="B712" s="72" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C712" s="73">
         <v>2638</v>
@@ -17390,10 +17396,10 @@
     </row>
     <row r="713" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="72" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B713" s="72" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C713" s="73">
         <v>4294</v>
@@ -17407,10 +17413,10 @@
     </row>
     <row r="714" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="72" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B714" s="72" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C714" s="73">
         <v>4314</v>
@@ -17424,10 +17430,10 @@
     </row>
     <row r="715" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="72" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B715" s="72" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C715" s="73">
         <v>4315</v>
@@ -17440,20 +17446,20 @@
       </c>
     </row>
     <row r="716" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A716" s="116"/>
-      <c r="B716" s="109"/>
-      <c r="C716" s="109"/>
-      <c r="D716" s="110"/>
-      <c r="E716" s="117"/>
+      <c r="A716" s="114"/>
+      <c r="B716" s="103"/>
+      <c r="C716" s="103"/>
+      <c r="D716" s="104"/>
+      <c r="E716" s="105"/>
     </row>
     <row r="717" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="118" t="s">
+      <c r="A717" s="111" t="s">
         <v>420</v>
       </c>
-      <c r="B717" s="119"/>
-      <c r="C717" s="119"/>
-      <c r="D717" s="119"/>
-      <c r="E717" s="120"/>
+      <c r="B717" s="112"/>
+      <c r="C717" s="112"/>
+      <c r="D717" s="112"/>
+      <c r="E717" s="113"/>
     </row>
     <row r="718" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="66" t="s">
@@ -17472,10 +17478,10 @@
     </row>
     <row r="719" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="69" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="B719" s="69" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C719" s="70">
         <v>3402</v>
@@ -17489,10 +17495,10 @@
     </row>
     <row r="720" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="69" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B720" s="69" t="s">
         <v>1178</v>
-      </c>
-      <c r="B720" s="69" t="s">
-        <v>1180</v>
       </c>
       <c r="C720" s="70">
         <v>3401</v>
@@ -17506,10 +17512,10 @@
     </row>
     <row r="721" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="69" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="B721" s="69" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C721" s="70">
         <v>3403</v>
@@ -17523,10 +17529,10 @@
     </row>
     <row r="722" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="69" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="B722" s="69" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C722" s="70">
         <v>4032</v>
@@ -17540,10 +17546,10 @@
     </row>
     <row r="723" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="69" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="B723" s="75" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C723" s="76">
         <v>4460</v>
@@ -17557,10 +17563,10 @@
     </row>
     <row r="724" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A724" s="75" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B724" s="75" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C724" s="76">
         <v>4260</v>
@@ -17574,10 +17580,10 @@
     </row>
     <row r="725" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="75" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B725" s="75" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C725" s="76">
         <v>2551</v>
@@ -17591,10 +17597,10 @@
     </row>
     <row r="726" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A726" s="80" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B726" s="80" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C726" s="81">
         <v>2550</v>
@@ -17608,10 +17614,10 @@
     </row>
     <row r="727" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A727" s="80" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B727" s="80" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C727" s="81">
         <v>4383</v>
@@ -17631,20 +17637,20 @@
       <c r="E728" s="61"/>
     </row>
     <row r="729" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A729" s="118" t="s">
-        <v>1305</v>
-      </c>
-      <c r="B729" s="119"/>
-      <c r="C729" s="119"/>
-      <c r="D729" s="119"/>
-      <c r="E729" s="120"/>
+      <c r="A729" s="111" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B729" s="112"/>
+      <c r="C729" s="112"/>
+      <c r="D729" s="112"/>
+      <c r="E729" s="113"/>
     </row>
     <row r="730" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="72" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B730" s="72" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C730" s="73">
         <v>3642</v>
@@ -17658,10 +17664,10 @@
     </row>
     <row r="731" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="72" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B731" s="72" t="s">
         <v>1285</v>
-      </c>
-      <c r="B731" s="72" t="s">
-        <v>1287</v>
       </c>
       <c r="C731" s="73">
         <v>3644</v>
@@ -17675,10 +17681,10 @@
     </row>
     <row r="732" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" s="72" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B732" s="72" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C732" s="73">
         <v>3641</v>
@@ -17692,10 +17698,10 @@
     </row>
     <row r="733" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A733" s="72" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B733" s="72" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C733" s="73">
         <v>3645</v>
@@ -17709,10 +17715,10 @@
     </row>
     <row r="734" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A734" s="72" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B734" s="72" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C734" s="73">
         <v>3852</v>
@@ -17726,10 +17732,10 @@
     </row>
     <row r="735" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A735" s="72" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B735" s="72" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C735" s="73">
         <v>3647</v>
@@ -17743,10 +17749,10 @@
     </row>
     <row r="736" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="72" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B736" s="72" t="s">
         <v>1251</v>
-      </c>
-      <c r="B736" s="72" t="s">
-        <v>1253</v>
       </c>
       <c r="C736" s="73">
         <v>3648</v>
@@ -17759,20 +17765,20 @@
       </c>
     </row>
     <row r="737" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A737" s="121"/>
-      <c r="B737" s="109"/>
-      <c r="C737" s="109"/>
-      <c r="D737" s="110"/>
-      <c r="E737" s="117"/>
+      <c r="A737" s="102"/>
+      <c r="B737" s="103"/>
+      <c r="C737" s="103"/>
+      <c r="D737" s="104"/>
+      <c r="E737" s="105"/>
     </row>
     <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="118" t="s">
+      <c r="A738" s="111" t="s">
         <v>421</v>
       </c>
-      <c r="B738" s="119"/>
-      <c r="C738" s="119"/>
-      <c r="D738" s="119"/>
-      <c r="E738" s="120"/>
+      <c r="B738" s="112"/>
+      <c r="C738" s="112"/>
+      <c r="D738" s="112"/>
+      <c r="E738" s="113"/>
     </row>
     <row r="739" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A739" s="66" t="s">
@@ -17791,10 +17797,10 @@
     </row>
     <row r="740" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="69" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B740" s="69" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C740" s="70">
         <v>3056</v>
@@ -17808,10 +17814,10 @@
     </row>
     <row r="741" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A741" s="69" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B741" s="69" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C741" s="70">
         <v>3083</v>
@@ -17825,10 +17831,10 @@
     </row>
     <row r="742" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A742" s="69" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="B742" s="69" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C742" s="70">
         <v>2264</v>
@@ -17842,10 +17848,10 @@
     </row>
     <row r="743" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A743" s="69" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B743" s="69" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C743" s="70">
         <v>2355</v>
@@ -17859,10 +17865,10 @@
     </row>
     <row r="744" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A744" s="75" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B744" s="75" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C744" s="76">
         <v>573</v>
@@ -17876,10 +17882,10 @@
     </row>
     <row r="745" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A745" s="80" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B745" s="80" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C745" s="81">
         <v>572</v>
@@ -17893,10 +17899,10 @@
     </row>
     <row r="746" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A746" s="65" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="B746" s="65" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C746" s="81">
         <v>4411</v>
@@ -17910,10 +17916,10 @@
     </row>
     <row r="747" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A747" s="65" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="B747" s="65" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C747" s="81">
         <v>4410</v>
@@ -17926,20 +17932,20 @@
       </c>
     </row>
     <row r="748" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A748" s="121"/>
-      <c r="B748" s="109"/>
-      <c r="C748" s="109"/>
-      <c r="D748" s="110"/>
-      <c r="E748" s="117"/>
+      <c r="A748" s="102"/>
+      <c r="B748" s="103"/>
+      <c r="C748" s="103"/>
+      <c r="D748" s="104"/>
+      <c r="E748" s="105"/>
     </row>
     <row r="749" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="118" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B749" s="119"/>
-      <c r="C749" s="119"/>
-      <c r="D749" s="119"/>
-      <c r="E749" s="120"/>
+      <c r="A749" s="111" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B749" s="112"/>
+      <c r="C749" s="112"/>
+      <c r="D749" s="112"/>
+      <c r="E749" s="113"/>
     </row>
     <row r="750" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A750" s="66" t="s">
@@ -17958,10 +17964,10 @@
     </row>
     <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="82" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B751" s="82" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C751" s="82">
         <v>4044</v>
@@ -18060,10 +18066,10 @@
     </row>
     <row r="757" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="72" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B757" s="72" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C757" s="73">
         <v>3870</v>
@@ -18077,10 +18083,10 @@
     </row>
     <row r="758" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="72" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B758" s="72" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C758" s="73">
         <v>3701</v>
@@ -18094,10 +18100,10 @@
     </row>
     <row r="759" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="72" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="B759" s="72" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C759" s="73">
         <v>3800</v>
@@ -18111,10 +18117,10 @@
     </row>
     <row r="760" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="72" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B760" s="72" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C760" s="73">
         <v>3725</v>
@@ -18128,10 +18134,10 @@
     </row>
     <row r="761" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A761" s="72" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B761" s="72" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C761" s="73">
         <v>3871</v>
@@ -18295,10 +18301,10 @@
     </row>
     <row r="770" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="72" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B770" s="72" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C770" s="73">
         <v>3801</v>
@@ -18312,10 +18318,10 @@
     </row>
     <row r="771" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="72" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B771" s="72" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C771" s="73">
         <v>3833</v>
@@ -18329,7 +18335,7 @@
     </row>
     <row r="772" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="72" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B772" s="72" t="s">
         <v>145</v>
@@ -18346,7 +18352,7 @@
     </row>
     <row r="773" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A773" s="72" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B773" s="72" t="s">
         <v>145</v>
@@ -18369,13 +18375,13 @@
       <c r="E774" s="98"/>
     </row>
     <row r="775" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A775" s="130" t="s">
-        <v>1289</v>
-      </c>
-      <c r="B775" s="131"/>
-      <c r="C775" s="131"/>
-      <c r="D775" s="131"/>
-      <c r="E775" s="132"/>
+      <c r="A775" s="108" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B775" s="109"/>
+      <c r="C775" s="109"/>
+      <c r="D775" s="109"/>
+      <c r="E775" s="110"/>
     </row>
     <row r="776" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="66" t="s">
@@ -18532,10 +18538,10 @@
     </row>
     <row r="785" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A785" s="72" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="B785" s="72" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C785" s="73">
         <v>4344</v>
@@ -18620,7 +18626,7 @@
         <v>431</v>
       </c>
       <c r="B790" s="72" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C790" s="73">
         <v>3765</v>
@@ -18787,10 +18793,10 @@
     </row>
     <row r="800" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="72" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B800" s="72" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C800" s="73">
         <v>4561</v>
@@ -18804,10 +18810,10 @@
     </row>
     <row r="801" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="72" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B801" s="72" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C801" s="73">
         <v>4562</v>
@@ -18889,10 +18895,10 @@
     </row>
     <row r="806" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="72" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="B806" s="72" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C806" s="73">
         <v>4346</v>
@@ -18906,10 +18912,10 @@
     </row>
     <row r="807" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="72" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B807" s="72" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C807" s="73">
         <v>4345</v>
@@ -18923,10 +18929,10 @@
     </row>
     <row r="808" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="72" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B808" s="72" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C808" s="73">
         <v>4347</v>
@@ -18940,10 +18946,10 @@
     </row>
     <row r="809" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="72" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B809" s="72" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C809" s="73">
         <v>4446</v>
@@ -18974,10 +18980,10 @@
     </row>
     <row r="811" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="72" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="B811" s="72" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C811" s="73">
         <v>4348</v>
@@ -18991,10 +18997,10 @@
     </row>
     <row r="812" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="72" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B812" s="72" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C812" s="73">
         <v>4456</v>
@@ -19025,10 +19031,10 @@
     </row>
     <row r="814" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="72" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B814" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C814" s="73">
         <v>4408</v>
@@ -19042,10 +19048,10 @@
     </row>
     <row r="815" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="72" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="B815" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C815" s="73">
         <v>4341</v>
@@ -19076,10 +19082,10 @@
     </row>
     <row r="817" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="72" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="B817" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C817" s="73">
         <v>4266</v>
@@ -19093,10 +19099,10 @@
     </row>
     <row r="818" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="72" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B818" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C818" s="73">
         <v>4269</v>
@@ -19110,10 +19116,10 @@
     </row>
     <row r="819" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="72" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B819" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C819" s="73">
         <v>4273</v>
@@ -19127,10 +19133,10 @@
     </row>
     <row r="820" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="72" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B820" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C820" s="73">
         <v>4405</v>
@@ -19144,10 +19150,10 @@
     </row>
     <row r="821" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="72" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B821" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C821" s="73">
         <v>4406</v>
@@ -19161,10 +19167,10 @@
     </row>
     <row r="822" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="72" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B822" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C822" s="73">
         <v>4267</v>
@@ -19178,10 +19184,10 @@
     </row>
     <row r="823" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="72" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B823" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C823" s="73">
         <v>4271</v>
@@ -19195,10 +19201,10 @@
     </row>
     <row r="824" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="72" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B824" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C824" s="73">
         <v>4276</v>
@@ -19212,10 +19218,10 @@
     </row>
     <row r="825" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="72" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B825" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C825" s="73">
         <v>4342</v>
@@ -19229,10 +19235,10 @@
     </row>
     <row r="826" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="72" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B826" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C826" s="73">
         <v>4398</v>
@@ -19246,10 +19252,10 @@
     </row>
     <row r="827" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="72" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B827" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C827" s="73">
         <v>4270</v>
@@ -19263,10 +19269,10 @@
     </row>
     <row r="828" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="72" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B828" s="72" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C828" s="73">
         <v>4275</v>
@@ -19280,10 +19286,10 @@
     </row>
     <row r="829" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="72" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B829" s="72" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C829" s="73">
         <v>4274</v>
@@ -19297,10 +19303,10 @@
     </row>
     <row r="830" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="72" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B830" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C830" s="73">
         <v>4399</v>
@@ -19314,10 +19320,10 @@
     </row>
     <row r="831" spans="1:5" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="72" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B831" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C831" s="73">
         <v>4404</v>
@@ -19382,10 +19388,10 @@
     </row>
     <row r="835" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="72" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B835" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C835" s="73">
         <v>4407</v>
@@ -19399,10 +19405,10 @@
     </row>
     <row r="836" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="72" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B836" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C836" s="73">
         <v>4397</v>
@@ -19433,10 +19439,10 @@
     </row>
     <row r="838" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A838" s="72" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B838" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C838" s="73">
         <v>4268</v>
@@ -19620,10 +19626,10 @@
     </row>
     <row r="849" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A849" s="72" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B849" s="72" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C849" s="73">
         <v>4074</v>
@@ -19637,10 +19643,10 @@
     </row>
     <row r="850" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A850" s="72" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B850" s="72" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C850" s="73">
         <v>4076</v>
@@ -19654,10 +19660,10 @@
     </row>
     <row r="851" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A851" s="72" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B851" s="72" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C851" s="73">
         <v>4133</v>
@@ -19705,7 +19711,7 @@
     </row>
     <row r="854" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A854" s="72" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B854" s="72" t="s">
         <v>19</v>
@@ -19725,7 +19731,7 @@
         <v>456</v>
       </c>
       <c r="B855" s="72" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C855" s="73">
         <v>4531</v>
@@ -19756,10 +19762,10 @@
     </row>
     <row r="857" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="72" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="B857" s="72" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C857" s="73">
         <v>4559</v>
@@ -19790,10 +19796,10 @@
     </row>
     <row r="859" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="72" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B859" s="72" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C859" s="73">
         <v>4102</v>
@@ -19807,10 +19813,10 @@
     </row>
     <row r="860" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="72" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B860" s="72" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C860" s="73">
         <v>4103</v>
@@ -19824,10 +19830,10 @@
     </row>
     <row r="861" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="72" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B861" s="72" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C861" s="73">
         <v>4547</v>
@@ -19841,10 +19847,10 @@
     </row>
     <row r="862" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="72" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B862" s="72" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C862" s="73">
         <v>4104</v>
@@ -19858,10 +19864,10 @@
     </row>
     <row r="863" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="72" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B863" s="72" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C863" s="73">
         <v>4101</v>
@@ -19875,10 +19881,10 @@
     </row>
     <row r="864" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="72" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B864" s="72" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C864" s="73">
         <v>4105</v>
@@ -19892,10 +19898,10 @@
     </row>
     <row r="865" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="72" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B865" s="72" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C865" s="73">
         <v>3705</v>
@@ -19909,10 +19915,10 @@
     </row>
     <row r="866" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A866" s="72" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B866" s="72" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C866" s="73">
         <v>3823</v>
@@ -19926,10 +19932,10 @@
     </row>
     <row r="867" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="72" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B867" s="72" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C867" s="73">
         <v>4308</v>
@@ -19943,10 +19949,10 @@
     </row>
     <row r="868" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="72" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="B868" s="72" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C868" s="73">
         <v>4309</v>
@@ -19960,10 +19966,10 @@
     </row>
     <row r="869" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="72" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="B869" s="72" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C869" s="73">
         <v>4412</v>
@@ -20045,10 +20051,10 @@
     </row>
     <row r="874" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="72" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B874" s="72" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C874" s="73">
         <v>4475</v>
@@ -20062,10 +20068,10 @@
     </row>
     <row r="875" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="72" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B875" s="72" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C875" s="73">
         <v>4354</v>
@@ -20079,16 +20085,16 @@
     </row>
     <row r="876" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="72" t="s">
-        <v>472</v>
+        <v>1335</v>
       </c>
       <c r="B876" s="72" t="s">
-        <v>473</v>
+        <v>1257</v>
       </c>
       <c r="C876" s="73">
         <v>4445</v>
       </c>
       <c r="D876" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E876" s="48">
         <v>74</v>
@@ -20096,10 +20102,10 @@
     </row>
     <row r="877" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="72" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B877" s="72" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C877" s="73">
         <v>4353</v>
@@ -20113,10 +20119,10 @@
     </row>
     <row r="878" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="72" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="B878" s="72" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C878" s="73">
         <v>4350</v>
@@ -20130,10 +20136,10 @@
     </row>
     <row r="879" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="72" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B879" s="72" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C879" s="73">
         <v>4352</v>
@@ -20147,10 +20153,10 @@
     </row>
     <row r="880" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="72" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="B880" s="72" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C880" s="73">
         <v>4349</v>
@@ -20164,10 +20170,10 @@
     </row>
     <row r="881" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="72" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B881" s="72" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C881" s="73">
         <v>4351</v>
@@ -20180,65 +20186,65 @@
       </c>
     </row>
     <row r="882" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A882" s="80" t="s">
+      <c r="A882" s="151" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B882" s="151" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C882" s="152">
+        <v>4581</v>
+      </c>
+      <c r="D882" s="151" t="s">
+        <v>15</v>
+      </c>
+      <c r="E882" s="48">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="883" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A883" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="B882" s="80" t="s">
+      <c r="B883" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="C882" s="81">
+      <c r="C883" s="81">
         <v>4096</v>
       </c>
-      <c r="D882" s="80" t="s">
-        <v>49</v>
-      </c>
-      <c r="E882" s="42">
+      <c r="D883" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="E883" s="42">
         <v>79</v>
-      </c>
-    </row>
-    <row r="883" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A883" s="72" t="s">
-        <v>1275</v>
-      </c>
-      <c r="B883" s="72" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C883" s="73">
-        <v>4123</v>
-      </c>
-      <c r="D883" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E883" s="48">
-        <v>60</v>
       </c>
     </row>
     <row r="884" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A884" s="72" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="B884" s="72" t="s">
-        <v>1239</v>
+        <v>1274</v>
       </c>
       <c r="C884" s="73">
-        <v>4306</v>
+        <v>4123</v>
       </c>
       <c r="D884" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E884" s="48">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="885" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A885" s="72" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B885" s="72" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C885" s="73">
-        <v>4307</v>
+        <v>4306</v>
       </c>
       <c r="D885" s="74" t="s">
         <v>453</v>
@@ -20249,61 +20255,71 @@
     </row>
     <row r="886" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="72" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="B886" s="72" t="s">
-        <v>1280</v>
+        <v>1237</v>
       </c>
       <c r="C886" s="73">
-        <v>2659</v>
-      </c>
-      <c r="D886" s="72" t="s">
-        <v>160</v>
-      </c>
-      <c r="E886" s="50">
-        <v>27.5</v>
+        <v>4307</v>
+      </c>
+      <c r="D886" s="74" t="s">
+        <v>453</v>
+      </c>
+      <c r="E886" s="48">
+        <v>81</v>
       </c>
     </row>
     <row r="887" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A887" s="72" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B887" s="72" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="C887" s="73">
-        <v>2621</v>
+        <v>2659</v>
       </c>
       <c r="D887" s="72" t="s">
         <v>160</v>
       </c>
       <c r="E887" s="50">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="888" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A888" s="72" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="B888" s="72" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="C888" s="73">
-        <v>3656</v>
+        <v>2621</v>
       </c>
       <c r="D888" s="72" t="s">
         <v>160</v>
       </c>
       <c r="E888" s="50">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="889" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A889" s="72" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B889" s="72" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C889" s="73">
+        <v>3656</v>
+      </c>
+      <c r="D889" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="E889" s="50">
         <v>27</v>
       </c>
-    </row>
-    <row r="889" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A889" s="99"/>
-      <c r="B889" s="99"/>
-      <c r="C889" s="99"/>
-      <c r="D889" s="99"/>
-      <c r="E889" s="100"/>
     </row>
     <row r="890" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A890" s="99"/>
@@ -20319,271 +20335,277 @@
       <c r="D891" s="99"/>
       <c r="E891" s="100"/>
     </row>
-    <row r="892" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A892" s="102" t="s">
-        <v>1290</v>
-      </c>
-      <c r="B892" s="103"/>
-      <c r="C892" s="103"/>
-      <c r="D892" s="103"/>
-      <c r="E892" s="104"/>
-    </row>
-    <row r="893" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A893" s="87" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B893" s="87" t="s">
+    <row r="892" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A892" s="99"/>
+      <c r="B892" s="99"/>
+      <c r="C892" s="99"/>
+      <c r="D892" s="99"/>
+      <c r="E892" s="100"/>
+    </row>
+    <row r="893" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A893" s="121" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B893" s="122"/>
+      <c r="C893" s="122"/>
+      <c r="D893" s="122"/>
+      <c r="E893" s="123"/>
+    </row>
+    <row r="894" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A894" s="87" t="s">
         <v>1291</v>
       </c>
-      <c r="C893" s="88">
+      <c r="B894" s="87" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C894" s="88">
         <v>3460</v>
       </c>
-      <c r="D893" s="89" t="s">
+      <c r="D894" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E893" s="63">
+      <c r="E894" s="63">
         <v>90</v>
-      </c>
-    </row>
-    <row r="894" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A894" s="72" t="s">
-        <v>1292</v>
-      </c>
-      <c r="B894" s="72" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C894" s="73">
-        <v>3459</v>
-      </c>
-      <c r="D894" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E894" s="48">
-        <v>45</v>
       </c>
     </row>
     <row r="895" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="72" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="B895" s="72" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C895" s="73">
-        <v>3803</v>
+        <v>3459</v>
       </c>
       <c r="D895" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E895" s="48">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="896" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="72" t="s">
-        <v>480</v>
+        <v>1292</v>
       </c>
       <c r="B896" s="72" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
       <c r="C896" s="73">
-        <v>3425</v>
+        <v>3803</v>
       </c>
       <c r="D896" s="74" t="s">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="E896" s="48">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="897" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="72" t="s">
-        <v>1297</v>
+        <v>478</v>
       </c>
       <c r="B897" s="72" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C897" s="73">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="D897" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E897" s="48">
-        <v>252</v>
+        <v>27</v>
       </c>
     </row>
     <row r="898" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="72" t="s">
-        <v>481</v>
+        <v>1295</v>
       </c>
       <c r="B898" s="72" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="C898" s="73">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="D898" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E898" s="48">
-        <v>57</v>
+        <v>252</v>
       </c>
     </row>
     <row r="899" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="72" t="s">
-        <v>1298</v>
+        <v>479</v>
       </c>
       <c r="B899" s="72" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C899" s="73">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="D899" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E899" s="48">
-        <v>540</v>
+        <v>57</v>
       </c>
     </row>
     <row r="900" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="72" t="s">
-        <v>482</v>
+        <v>1296</v>
       </c>
       <c r="B900" s="72" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="C900" s="73">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="D900" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E900" s="48">
-        <v>70</v>
+        <v>540</v>
       </c>
     </row>
     <row r="901" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="72" t="s">
-        <v>1299</v>
+        <v>480</v>
       </c>
       <c r="B901" s="72" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C901" s="73">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="D901" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E901" s="48">
-        <v>660</v>
+        <v>70</v>
       </c>
     </row>
     <row r="902" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="72" t="s">
-        <v>483</v>
+        <v>1297</v>
       </c>
       <c r="B902" s="72" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="C902" s="73">
-        <v>3913</v>
+        <v>3430</v>
       </c>
       <c r="D902" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E902" s="48">
-        <v>62.5</v>
+        <v>660</v>
       </c>
     </row>
     <row r="903" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="72" t="s">
-        <v>1300</v>
+        <v>481</v>
       </c>
       <c r="B903" s="72" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C903" s="73">
-        <v>3872</v>
+        <v>3913</v>
       </c>
       <c r="D903" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E903" s="48">
-        <v>582</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="904" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="72" t="s">
-        <v>484</v>
+        <v>1298</v>
       </c>
       <c r="B904" s="72" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
       <c r="C904" s="73">
-        <v>3422</v>
+        <v>3872</v>
       </c>
       <c r="D904" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E904" s="48">
-        <v>18</v>
+        <v>582</v>
       </c>
     </row>
     <row r="905" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="72" t="s">
-        <v>1301</v>
+        <v>482</v>
       </c>
       <c r="B905" s="72" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C905" s="73">
+        <v>3422</v>
+      </c>
+      <c r="D905" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="E905" s="48">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="906" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A906" s="72" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B906" s="72" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C906" s="73">
         <v>3423</v>
       </c>
-      <c r="D905" s="74" t="s">
+      <c r="D906" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="E905" s="48">
+      <c r="E906" s="48">
         <v>168</v>
       </c>
     </row>
-    <row r="906" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A906" s="83" t="s">
-        <v>485</v>
-      </c>
-      <c r="B906" s="83" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C906" s="84">
+    <row r="907" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A907" s="83" t="s">
+        <v>483</v>
+      </c>
+      <c r="B907" s="83" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C907" s="84">
         <v>3431</v>
       </c>
-      <c r="D906" s="74" t="s">
+      <c r="D907" s="74" t="s">
         <v>412</v>
       </c>
-      <c r="E906" s="48">
+      <c r="E907" s="48">
         <v>105</v>
       </c>
     </row>
-    <row r="907" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A907" s="90" t="s">
-        <v>485</v>
-      </c>
-      <c r="B907" s="90" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C907" s="91">
+    <row r="908" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A908" s="90" t="s">
+        <v>483</v>
+      </c>
+      <c r="B908" s="90" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C908" s="91">
         <v>3432</v>
       </c>
-      <c r="D907" s="92" t="s">
+      <c r="D908" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="E907" s="48">
+      <c r="E908" s="48">
         <v>996</v>
       </c>
     </row>
-    <row r="908" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="909" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="910" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="911" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
@@ -20592,35 +20614,15 @@
     <row r="914" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="915" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="916" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
-    <row r="918" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A918" s="64" t="s">
+    <row r="917" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
+    <row r="919" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A919" s="64" t="s">
         <v>386</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A737:E737"/>
-    <mergeCell ref="A597:E597"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A775:E775"/>
-    <mergeCell ref="A729:E729"/>
-    <mergeCell ref="A748:E748"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A538:E538"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A422:E422"/>
-    <mergeCell ref="A382:E382"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A381:E381"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A215:E215"/>
-    <mergeCell ref="A892:E892"/>
+    <mergeCell ref="A893:E893"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A3:E3"/>
@@ -20636,6 +20638,27 @@
     <mergeCell ref="A560:E560"/>
     <mergeCell ref="A716:E716"/>
     <mergeCell ref="A288:E288"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A538:E538"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A422:E422"/>
+    <mergeCell ref="A382:E382"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A215:E215"/>
+    <mergeCell ref="A737:E737"/>
+    <mergeCell ref="A597:E597"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A775:E775"/>
+    <mergeCell ref="A729:E729"/>
+    <mergeCell ref="A748:E748"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20673,80 +20696,80 @@
     </row>
     <row r="2" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="148" t="s">
+        <v>484</v>
+      </c>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="139"/>
+    </row>
+    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="150" t="s">
+        <v>485</v>
+      </c>
+      <c r="B3" s="135"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="139"/>
+    </row>
+    <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="138" t="s">
         <v>486</v>
       </c>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="138"/>
-    </row>
-    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="137" t="s">
+      <c r="B4" s="135"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="139"/>
+    </row>
+    <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="150" t="s">
         <v>487</v>
       </c>
-      <c r="B3" s="134"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="138"/>
-    </row>
-    <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="149" t="s">
-        <v>488</v>
-      </c>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="138"/>
-    </row>
-    <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="137" t="s">
-        <v>489</v>
-      </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="138"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="139"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="134"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="138"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="139"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
-        <v>490</v>
-      </c>
-      <c r="B7" s="134"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="138"/>
+        <v>488</v>
+      </c>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="139"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="138"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="139"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="138"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="139"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="150" t="s">
+      <c r="A10" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -20759,10 +20782,10 @@
         <v>11</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>386</v>
@@ -20770,7 +20793,7 @@
     </row>
     <row r="12" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B12" s="13">
         <v>467</v>
@@ -20787,7 +20810,7 @@
     </row>
     <row r="13" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B13" s="13">
         <v>2661</v>
@@ -20804,7 +20827,7 @@
     </row>
     <row r="14" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B14" s="13">
         <v>585</v>
@@ -20821,7 +20844,7 @@
     </row>
     <row r="15" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B15" s="13">
         <v>2547</v>
@@ -20838,7 +20861,7 @@
     </row>
     <row r="16" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B16" s="13">
         <v>2405</v>
@@ -20855,7 +20878,7 @@
     </row>
     <row r="17" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B17" s="13">
         <v>2444</v>
@@ -20872,7 +20895,7 @@
     </row>
     <row r="18" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B18" s="13">
         <v>3105</v>
@@ -20889,7 +20912,7 @@
     </row>
     <row r="19" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B19" s="13">
         <v>2445</v>
@@ -20906,7 +20929,7 @@
     </row>
     <row r="20" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B20" s="13">
         <v>3865</v>
@@ -20923,7 +20946,7 @@
     </row>
     <row r="21" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B21" s="13">
         <v>3866</v>
@@ -20940,7 +20963,7 @@
     </row>
     <row r="22" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B22" s="13">
         <v>2446</v>
@@ -20957,7 +20980,7 @@
     </row>
     <row r="23" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B23" s="13">
         <v>2781</v>
@@ -20974,7 +20997,7 @@
     </row>
     <row r="24" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B24" s="13">
         <v>3368</v>
@@ -20991,7 +21014,7 @@
     </row>
     <row r="25" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B25" s="13">
         <v>3372</v>
@@ -21008,7 +21031,7 @@
     </row>
     <row r="26" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B26" s="13">
         <v>3380</v>
@@ -21025,7 +21048,7 @@
     </row>
     <row r="27" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B27" s="13">
         <v>3379</v>
@@ -21034,7 +21057,7 @@
         <v>49</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E27" s="17">
         <v>87</v>
@@ -21042,7 +21065,7 @@
     </row>
     <row r="28" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B28" s="13">
         <v>3367</v>
@@ -21059,7 +21082,7 @@
     </row>
     <row r="29" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B29" s="13">
         <v>2263</v>
@@ -21076,7 +21099,7 @@
     </row>
     <row r="30" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B30" s="13">
         <v>465</v>
@@ -21093,7 +21116,7 @@
     </row>
     <row r="31" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B31" s="13">
         <v>2643</v>
@@ -21110,7 +21133,7 @@
     </row>
     <row r="32" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B32" s="13">
         <v>2644</v>
@@ -21127,7 +21150,7 @@
     </row>
     <row r="33" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B33" s="13">
         <v>1675</v>
@@ -21144,7 +21167,7 @@
     </row>
     <row r="34" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B34" s="13">
         <v>2570</v>
@@ -21161,7 +21184,7 @@
     </row>
     <row r="35" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B35" s="13">
         <v>3021</v>
@@ -21178,7 +21201,7 @@
     </row>
     <row r="36" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B36" s="16">
         <v>109</v>
@@ -21195,7 +21218,7 @@
     </row>
     <row r="37" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B37" s="13">
         <v>2419</v>
@@ -21212,7 +21235,7 @@
     </row>
     <row r="38" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B38" s="13">
         <v>3505</v>
@@ -21229,7 +21252,7 @@
     </row>
     <row r="39" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B39" s="13">
         <v>2443</v>
@@ -21246,7 +21269,7 @@
     </row>
     <row r="40" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B40" s="13">
         <v>2283</v>
@@ -21263,7 +21286,7 @@
     </row>
     <row r="41" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B41" s="13">
         <v>103</v>
@@ -21280,7 +21303,7 @@
     </row>
     <row r="42" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B42" s="13">
         <v>2629</v>
@@ -21297,7 +21320,7 @@
     </row>
     <row r="43" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B43" s="13">
         <v>2452</v>
@@ -21314,7 +21337,7 @@
     </row>
     <row r="44" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B44" s="13">
         <v>150</v>
@@ -21331,7 +21354,7 @@
     </row>
     <row r="45" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B45" s="13">
         <v>2453</v>
@@ -21348,7 +21371,7 @@
     </row>
     <row r="46" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B46" s="13">
         <v>2450</v>
@@ -21365,7 +21388,7 @@
     </row>
     <row r="47" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B47" s="13">
         <v>7</v>
@@ -21382,7 +21405,7 @@
     </row>
     <row r="48" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B48" s="13">
         <v>2451</v>
@@ -21399,7 +21422,7 @@
     </row>
     <row r="49" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B49" s="13">
         <v>1323</v>
@@ -21416,7 +21439,7 @@
     </row>
     <row r="50" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B50" s="13">
         <v>1322</v>
@@ -21433,7 +21456,7 @@
     </row>
     <row r="51" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B51" s="13">
         <v>1325</v>
@@ -21450,7 +21473,7 @@
     </row>
     <row r="52" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B52" s="13">
         <v>1324</v>
@@ -21467,7 +21490,7 @@
     </row>
     <row r="53" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B53" s="13">
         <v>1674</v>
@@ -21484,7 +21507,7 @@
     </row>
     <row r="54" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B54" s="13">
         <v>2508</v>
@@ -21501,7 +21524,7 @@
     </row>
     <row r="55" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B55" s="13">
         <v>2442</v>
@@ -21518,7 +21541,7 @@
     </row>
     <row r="56" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B56" s="13">
         <v>2524</v>
@@ -21535,7 +21558,7 @@
     </row>
     <row r="57" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B57" s="13">
         <v>3410</v>
@@ -21552,7 +21575,7 @@
     </row>
     <row r="58" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B58" s="13">
         <v>3412</v>
@@ -21569,7 +21592,7 @@
     </row>
     <row r="59" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B59" s="13">
         <v>3411</v>
@@ -21586,7 +21609,7 @@
     </row>
     <row r="60" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B60" s="13">
         <v>3413</v>
@@ -21603,7 +21626,7 @@
     </row>
     <row r="61" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B61" s="13">
         <v>875</v>
@@ -21620,7 +21643,7 @@
     </row>
     <row r="62" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B62" s="13">
         <v>2523</v>
@@ -21637,7 +21660,7 @@
     </row>
     <row r="63" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B63" s="13">
         <v>3408</v>
@@ -21654,7 +21677,7 @@
     </row>
     <row r="64" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B64" s="13">
         <v>2273</v>
@@ -21671,7 +21694,7 @@
     </row>
     <row r="65" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B65" s="13">
         <v>2271</v>
@@ -21688,7 +21711,7 @@
     </row>
     <row r="66" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B66" s="13">
         <v>3409</v>
@@ -21705,7 +21728,7 @@
     </row>
     <row r="67" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B67" s="13">
         <v>459</v>
@@ -21722,7 +21745,7 @@
     </row>
     <row r="68" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B68" s="13">
         <v>285</v>
@@ -21739,7 +21762,7 @@
     </row>
     <row r="69" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B69" s="13">
         <v>3607</v>
@@ -21756,7 +21779,7 @@
     </row>
     <row r="70" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B70" s="9">
         <v>3064</v>
@@ -21773,7 +21796,7 @@
     </row>
     <row r="71" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B71" s="9">
         <v>3065</v>
@@ -21790,7 +21813,7 @@
     </row>
     <row r="72" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B72" s="13">
         <v>2252</v>
@@ -21807,7 +21830,7 @@
     </row>
     <row r="73" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B73" s="13">
         <v>2291</v>
@@ -21824,7 +21847,7 @@
     </row>
     <row r="74" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B74" s="13">
         <v>3121</v>
@@ -21833,7 +21856,7 @@
         <v>50</v>
       </c>
       <c r="D74" s="36" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E74" s="17">
         <v>1200</v>
@@ -21841,7 +21864,7 @@
     </row>
     <row r="75" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B75" s="13">
         <v>3534</v>
@@ -21858,7 +21881,7 @@
     </row>
     <row r="76" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B76" s="13">
         <v>2293</v>
@@ -21875,7 +21898,7 @@
     </row>
     <row r="77" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B77" s="13">
         <v>2250</v>
@@ -21892,7 +21915,7 @@
     </row>
     <row r="78" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B78" s="13">
         <v>2340</v>
@@ -21909,7 +21932,7 @@
     </row>
     <row r="79" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B79" s="13">
         <v>3533</v>
@@ -21926,7 +21949,7 @@
     </row>
     <row r="80" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B80" s="13">
         <v>2251</v>
@@ -21943,7 +21966,7 @@
     </row>
     <row r="81" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B81" s="13">
         <v>3532</v>
@@ -21960,7 +21983,7 @@
     </row>
     <row r="82" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B82" s="13">
         <v>3081</v>
@@ -21977,7 +22000,7 @@
     </row>
     <row r="83" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B83" s="13">
         <v>3082</v>
@@ -21994,7 +22017,7 @@
     </row>
     <row r="84" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B84" s="13">
         <v>2534</v>
@@ -22011,7 +22034,7 @@
     </row>
     <row r="85" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B85" s="13">
         <v>2234</v>
@@ -22028,7 +22051,7 @@
     </row>
     <row r="86" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B86" s="13">
         <v>2855</v>
@@ -22045,7 +22068,7 @@
     </row>
     <row r="87" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B87" s="13">
         <v>3125</v>
@@ -22062,7 +22085,7 @@
     </row>
     <row r="88" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B88" s="13">
         <v>3753</v>
@@ -22079,7 +22102,7 @@
     </row>
     <row r="89" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B89" s="13">
         <v>3752</v>
@@ -22096,7 +22119,7 @@
     </row>
     <row r="90" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B90" s="13">
         <v>2238</v>
@@ -22113,7 +22136,7 @@
     </row>
     <row r="91" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B91" s="13">
         <v>2535</v>
@@ -22130,7 +22153,7 @@
     </row>
     <row r="92" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B92" s="13">
         <v>2512</v>
@@ -22147,7 +22170,7 @@
     </row>
     <row r="93" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B93" s="13">
         <v>2537</v>
@@ -22164,7 +22187,7 @@
     </row>
     <row r="94" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B94" s="13">
         <v>2511</v>
@@ -22181,7 +22204,7 @@
     </row>
     <row r="95" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B95" s="13">
         <v>2236</v>
@@ -22198,7 +22221,7 @@
     </row>
     <row r="96" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B96" s="13">
         <v>2546</v>
@@ -22215,7 +22238,7 @@
     </row>
     <row r="97" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B97" s="13">
         <v>3711</v>
@@ -22232,7 +22255,7 @@
     </row>
     <row r="98" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B98" s="13">
         <v>3713</v>
@@ -22249,7 +22272,7 @@
     </row>
     <row r="99" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B99" s="13">
         <v>3712</v>
@@ -22266,7 +22289,7 @@
     </row>
     <row r="100" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B100" s="13">
         <v>1558</v>
@@ -22283,7 +22306,7 @@
     </row>
     <row r="101" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B101" s="13">
         <v>1657</v>
@@ -22300,7 +22323,7 @@
     </row>
     <row r="102" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B102" s="13">
         <v>1660</v>
@@ -22309,7 +22332,7 @@
         <v>49</v>
       </c>
       <c r="D102" s="36" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E102" s="17">
         <v>69.5</v>
@@ -22317,7 +22340,7 @@
     </row>
     <row r="103" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B103" s="13">
         <v>2232</v>
@@ -22334,7 +22357,7 @@
     </row>
     <row r="104" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B104" s="13">
         <v>2536</v>
@@ -22351,7 +22374,7 @@
     </row>
     <row r="105" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B105" s="13">
         <v>2974</v>
@@ -22368,7 +22391,7 @@
     </row>
     <row r="106" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B106" s="13">
         <v>2852</v>
@@ -22385,7 +22408,7 @@
     </row>
     <row r="107" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B107" s="13">
         <v>3093</v>
@@ -22402,7 +22425,7 @@
     </row>
     <row r="108" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B108" s="13">
         <v>2632</v>
@@ -22419,7 +22442,7 @@
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B109" s="13">
         <v>3874</v>
@@ -22436,7 +22459,7 @@
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B110" s="13">
         <v>2330</v>
@@ -22453,7 +22476,7 @@
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B111" s="13">
         <v>2385</v>
@@ -22469,19 +22492,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="133"/>
-      <c r="B112" s="134"/>
-      <c r="C112" s="135"/>
-      <c r="D112" s="136"/>
+      <c r="A112" s="134"/>
+      <c r="B112" s="135"/>
+      <c r="C112" s="136"/>
+      <c r="D112" s="137"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="140" t="s">
+      <c r="A113" s="149" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="119"/>
-      <c r="C113" s="119"/>
-      <c r="D113" s="127"/>
+      <c r="B113" s="112"/>
+      <c r="C113" s="112"/>
+      <c r="D113" s="120"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22495,7 +22518,7 @@
         <v>11</v>
       </c>
       <c r="D114" s="33" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E114" s="18" t="s">
         <v>12</v>
@@ -22503,7 +22526,7 @@
     </row>
     <row r="115" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B115" s="13">
         <v>85</v>
@@ -22520,7 +22543,7 @@
     </row>
     <row r="116" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B116" s="13">
         <v>2447</v>
@@ -22537,7 +22560,7 @@
     </row>
     <row r="117" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B117" s="13">
         <v>551</v>
@@ -22554,7 +22577,7 @@
     </row>
     <row r="118" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B118" s="13">
         <v>2448</v>
@@ -22571,7 +22594,7 @@
     </row>
     <row r="119" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B119" s="13">
         <v>3559</v>
@@ -22588,7 +22611,7 @@
     </row>
     <row r="120" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B120" s="13">
         <v>3560</v>
@@ -22605,7 +22628,7 @@
     </row>
     <row r="121" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B121" s="13">
         <v>255</v>
@@ -22622,7 +22645,7 @@
     </row>
     <row r="122" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B122" s="13">
         <v>2456</v>
@@ -22639,7 +22662,7 @@
     </row>
     <row r="123" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B123" s="13">
         <v>80</v>
@@ -22656,7 +22679,7 @@
     </row>
     <row r="124" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B124" s="13">
         <v>2457</v>
@@ -22673,7 +22696,7 @@
     </row>
     <row r="125" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B125" s="13">
         <v>94</v>
@@ -22690,7 +22713,7 @@
     </row>
     <row r="126" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B126" s="13">
         <v>2458</v>
@@ -22707,7 +22730,7 @@
     </row>
     <row r="127" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B127" s="13">
         <v>2454</v>
@@ -22724,7 +22747,7 @@
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B128" s="13">
         <v>2455</v>
@@ -22741,7 +22764,7 @@
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B129" s="13">
         <v>450</v>
@@ -22758,7 +22781,7 @@
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B130" s="13">
         <v>2459</v>
@@ -22774,19 +22797,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="133"/>
-      <c r="B131" s="134"/>
-      <c r="C131" s="135"/>
-      <c r="D131" s="136"/>
+      <c r="A131" s="134"/>
+      <c r="B131" s="135"/>
+      <c r="C131" s="136"/>
+      <c r="D131" s="137"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="140" t="s">
+      <c r="A132" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="119"/>
-      <c r="C132" s="119"/>
-      <c r="D132" s="127"/>
+      <c r="B132" s="112"/>
+      <c r="C132" s="112"/>
+      <c r="D132" s="120"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22800,7 +22823,7 @@
         <v>11</v>
       </c>
       <c r="D133" s="33" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E133" s="38" t="s">
         <v>12</v>
@@ -22808,7 +22831,7 @@
     </row>
     <row r="134" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B134" s="13">
         <v>2314</v>
@@ -22825,7 +22848,7 @@
     </row>
     <row r="135" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B135" s="13">
         <v>2664</v>
@@ -22842,7 +22865,7 @@
     </row>
     <row r="136" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B136" s="13">
         <v>2313</v>
@@ -22859,7 +22882,7 @@
     </row>
     <row r="137" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B137" s="13">
         <v>2316</v>
@@ -22876,7 +22899,7 @@
     </row>
     <row r="138" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B138" s="13">
         <v>2312</v>
@@ -22893,7 +22916,7 @@
     </row>
     <row r="139" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B139" s="13">
         <v>2663</v>
@@ -22910,7 +22933,7 @@
     </row>
     <row r="140" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B140" s="13">
         <v>2315</v>
@@ -22927,7 +22950,7 @@
     </row>
     <row r="141" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B141" s="13">
         <v>2617</v>
@@ -22944,7 +22967,7 @@
     </row>
     <row r="142" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B142" s="13">
         <v>2311</v>
@@ -22960,19 +22983,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="133"/>
-      <c r="B143" s="134"/>
-      <c r="C143" s="135"/>
-      <c r="D143" s="136"/>
+      <c r="A143" s="134"/>
+      <c r="B143" s="135"/>
+      <c r="C143" s="136"/>
+      <c r="D143" s="137"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="140" t="s">
+      <c r="A144" s="149" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="119"/>
-      <c r="C144" s="119"/>
-      <c r="D144" s="127"/>
+      <c r="B144" s="112"/>
+      <c r="C144" s="112"/>
+      <c r="D144" s="120"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22986,7 +23009,7 @@
         <v>11</v>
       </c>
       <c r="D145" s="33" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E145" s="18" t="s">
         <v>12</v>
@@ -22994,7 +23017,7 @@
     </row>
     <row r="146" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B146" s="13">
         <v>2625</v>
@@ -23011,7 +23034,7 @@
     </row>
     <row r="147" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B147" s="13">
         <v>2573</v>
@@ -23028,7 +23051,7 @@
     </row>
     <row r="148" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B148" s="13">
         <v>2504</v>
@@ -23045,7 +23068,7 @@
     </row>
     <row r="149" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B149" s="13">
         <v>2505</v>
@@ -23062,7 +23085,7 @@
     </row>
     <row r="150" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B150" s="13">
         <v>2557</v>
@@ -23079,7 +23102,7 @@
     </row>
     <row r="151" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B151" s="13">
         <v>2540</v>
@@ -23096,7 +23119,7 @@
     </row>
     <row r="152" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B152" s="13">
         <v>3504</v>
@@ -23113,7 +23136,7 @@
     </row>
     <row r="153" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B153" s="13">
         <v>2692</v>
@@ -23130,7 +23153,7 @@
     </row>
     <row r="154" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B154" s="13">
         <v>3484</v>
@@ -23147,7 +23170,7 @@
     </row>
     <row r="155" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B155" s="13">
         <v>3485</v>
@@ -23164,7 +23187,7 @@
     </row>
     <row r="156" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B156" s="13">
         <v>2780</v>
@@ -23181,7 +23204,7 @@
     </row>
     <row r="157" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B157" s="13">
         <v>3041</v>
@@ -23198,7 +23221,7 @@
     </row>
     <row r="158" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B158" s="13">
         <v>2559</v>
@@ -23215,7 +23238,7 @@
     </row>
     <row r="159" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B159" s="13">
         <v>3107</v>
@@ -23232,7 +23255,7 @@
     </row>
     <row r="160" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B160" s="13">
         <v>3108</v>
@@ -23249,7 +23272,7 @@
     </row>
     <row r="161" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B161" s="13">
         <v>2526</v>
@@ -23266,7 +23289,7 @@
     </row>
     <row r="162" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B162" s="13">
         <v>2527</v>
@@ -23283,7 +23306,7 @@
     </row>
     <row r="163" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B163" s="13">
         <v>3063</v>
@@ -23300,7 +23323,7 @@
     </row>
     <row r="164" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B164" s="13">
         <v>2560</v>
@@ -23317,7 +23340,7 @@
     </row>
     <row r="165" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B165" s="13">
         <v>2744</v>
@@ -23334,7 +23357,7 @@
     </row>
     <row r="166" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B166" s="13">
         <v>3035</v>
@@ -23351,7 +23374,7 @@
     </row>
     <row r="167" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B167" s="13">
         <v>2697</v>
@@ -23368,7 +23391,7 @@
     </row>
     <row r="168" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B168" s="13">
         <v>2746</v>
@@ -23385,7 +23408,7 @@
     </row>
     <row r="169" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B169" s="13">
         <v>2713</v>
@@ -23402,7 +23425,7 @@
     </row>
     <row r="170" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B170" s="13">
         <v>3038</v>
@@ -23419,7 +23442,7 @@
     </row>
     <row r="171" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B171" s="13">
         <v>2436</v>
@@ -23436,7 +23459,7 @@
     </row>
     <row r="172" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B172" s="13">
         <v>2248</v>
@@ -23453,7 +23476,7 @@
     </row>
     <row r="173" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B173" s="13">
         <v>2563</v>
@@ -23470,7 +23493,7 @@
     </row>
     <row r="174" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B174" s="13">
         <v>2562</v>
@@ -23487,7 +23510,7 @@
     </row>
     <row r="175" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B175" s="13">
         <v>2745</v>
@@ -23504,7 +23527,7 @@
     </row>
     <row r="176" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B176" s="13">
         <v>3034</v>
@@ -23521,7 +23544,7 @@
     </row>
     <row r="177" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B177" s="13">
         <v>2576</v>
@@ -23538,7 +23561,7 @@
     </row>
     <row r="178" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B178" s="13">
         <v>3032</v>
@@ -23555,7 +23578,7 @@
     </row>
     <row r="179" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B179" s="13">
         <v>2743</v>
@@ -23572,7 +23595,7 @@
     </row>
     <row r="180" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B180" s="13">
         <v>2558</v>
@@ -23589,7 +23612,7 @@
     </row>
     <row r="181" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B181" s="13">
         <v>2561</v>
@@ -23605,19 +23628,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="133"/>
-      <c r="B182" s="134"/>
-      <c r="C182" s="135"/>
-      <c r="D182" s="136"/>
+      <c r="A182" s="134"/>
+      <c r="B182" s="135"/>
+      <c r="C182" s="136"/>
+      <c r="D182" s="137"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="139" t="s">
+      <c r="A183" s="133" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="119"/>
-      <c r="C183" s="119"/>
-      <c r="D183" s="119"/>
+      <c r="B183" s="112"/>
+      <c r="C183" s="112"/>
+      <c r="D183" s="112"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23631,7 +23654,7 @@
         <v>11</v>
       </c>
       <c r="D184" s="33" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E184" s="18" t="s">
         <v>12</v>
@@ -23639,7 +23662,7 @@
     </row>
     <row r="185" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B185" s="13">
         <v>203</v>
@@ -23654,7 +23677,7 @@
     </row>
     <row r="186" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B186" s="13">
         <v>2490</v>
@@ -23669,7 +23692,7 @@
     </row>
     <row r="187" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B187" s="13">
         <v>2242</v>
@@ -23684,7 +23707,7 @@
     </row>
     <row r="188" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B188" s="13">
         <v>2518</v>
@@ -23699,7 +23722,7 @@
     </row>
     <row r="189" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B189" s="13">
         <v>845</v>
@@ -23714,7 +23737,7 @@
     </row>
     <row r="190" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B190" s="13">
         <v>2517</v>
@@ -23729,7 +23752,7 @@
     </row>
     <row r="191" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B191" s="13">
         <v>2631</v>
@@ -23744,7 +23767,7 @@
     </row>
     <row r="192" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B192" s="13">
         <v>3088</v>
@@ -23759,7 +23782,7 @@
     </row>
     <row r="193" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B193" s="13">
         <v>1710</v>
@@ -23774,7 +23797,7 @@
     </row>
     <row r="194" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B194" s="13">
         <v>1711</v>
@@ -23789,7 +23812,7 @@
     </row>
     <row r="195" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B195" s="13">
         <v>3061</v>
@@ -23804,7 +23827,7 @@
     </row>
     <row r="196" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B196" s="13">
         <v>2489</v>
@@ -23819,7 +23842,7 @@
     </row>
     <row r="197" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B197" s="13">
         <v>2437</v>
@@ -23834,7 +23857,7 @@
     </row>
     <row r="198" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B198" s="13">
         <v>582</v>
@@ -23847,12 +23870,12 @@
         <v>120</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="199" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="9" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B199" s="9">
         <v>3415</v>
@@ -23867,7 +23890,7 @@
     </row>
     <row r="200" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B200" s="13">
         <v>2485</v>
@@ -23882,7 +23905,7 @@
     </row>
     <row r="201" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B201" s="13">
         <v>583</v>
@@ -23897,7 +23920,7 @@
     </row>
     <row r="202" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B202" s="13">
         <v>3416</v>
@@ -23912,7 +23935,7 @@
     </row>
     <row r="203" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B203" s="13">
         <v>564</v>
@@ -23927,7 +23950,7 @@
     </row>
     <row r="204" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B204" s="13">
         <v>2256</v>
@@ -23942,7 +23965,7 @@
     </row>
     <row r="205" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B205" s="13">
         <v>3398</v>
@@ -23957,7 +23980,7 @@
     </row>
     <row r="206" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B206" s="13">
         <v>2924</v>
@@ -23972,7 +23995,7 @@
     </row>
     <row r="207" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B207" s="13">
         <v>3078</v>
@@ -23987,7 +24010,7 @@
     </row>
     <row r="208" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B208" s="13">
         <v>2348</v>
@@ -24002,7 +24025,7 @@
     </row>
     <row r="209" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B209" s="13">
         <v>2538</v>
@@ -24017,7 +24040,7 @@
     </row>
     <row r="210" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B210" s="13">
         <v>415</v>
@@ -24032,7 +24055,7 @@
     </row>
     <row r="211" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B211" s="13">
         <v>93</v>
@@ -24047,7 +24070,7 @@
     </row>
     <row r="212" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B212" s="13">
         <v>261</v>
@@ -24062,7 +24085,7 @@
     </row>
     <row r="213" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B213" s="13">
         <v>2475</v>
@@ -24077,7 +24100,7 @@
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B214" s="13">
         <v>92</v>
@@ -24092,7 +24115,7 @@
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B215" s="13">
         <v>2476</v>
@@ -24107,7 +24130,7 @@
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B216" s="13">
         <v>18</v>
@@ -24122,7 +24145,7 @@
     </row>
     <row r="217" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B217" s="13">
         <v>2477</v>
@@ -24137,7 +24160,7 @@
     </row>
     <row r="218" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B218" s="13">
         <v>19</v>
@@ -24152,7 +24175,7 @@
     </row>
     <row r="219" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B219" s="13">
         <v>2246</v>
@@ -24167,7 +24190,7 @@
     </row>
     <row r="220" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B220" s="13">
         <v>575</v>
@@ -24182,7 +24205,7 @@
     </row>
     <row r="221" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B221" s="13">
         <v>221</v>
@@ -24197,7 +24220,7 @@
     </row>
     <row r="222" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B222" s="13">
         <v>258</v>
@@ -24212,7 +24235,7 @@
     </row>
     <row r="223" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B223" s="13">
         <v>20</v>
@@ -24227,7 +24250,7 @@
     </row>
     <row r="224" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B224" s="13">
         <v>21</v>
@@ -24242,7 +24265,7 @@
     </row>
     <row r="225" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B225" s="13">
         <v>2520</v>
@@ -24257,7 +24280,7 @@
     </row>
     <row r="226" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B226" s="13">
         <v>262</v>
@@ -24272,7 +24295,7 @@
     </row>
     <row r="227" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B227" s="13">
         <v>2513</v>
@@ -24287,7 +24310,7 @@
     </row>
     <row r="228" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B228" s="13">
         <v>16</v>
@@ -24302,7 +24325,7 @@
     </row>
     <row r="229" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B229" s="13">
         <v>3114</v>
@@ -24317,7 +24340,7 @@
     </row>
     <row r="230" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B230" s="13">
         <v>3452</v>
@@ -24330,7 +24353,7 @@
     </row>
     <row r="231" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B231" s="13">
         <v>3439</v>
@@ -24345,7 +24368,7 @@
     </row>
     <row r="232" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B232" s="13">
         <v>3384</v>
@@ -24360,7 +24383,7 @@
     </row>
     <row r="233" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B233" s="13">
         <v>15</v>
@@ -24375,7 +24398,7 @@
     </row>
     <row r="234" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B234" s="13">
         <v>3115</v>
@@ -24390,7 +24413,7 @@
     </row>
     <row r="235" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B235" s="13">
         <v>3649</v>
@@ -24405,7 +24428,7 @@
     </row>
     <row r="236" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B236" s="13">
         <v>3650</v>
@@ -24420,7 +24443,7 @@
     </row>
     <row r="237" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B237" s="13">
         <v>3386</v>
@@ -24435,7 +24458,7 @@
     </row>
     <row r="238" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B238" s="13">
         <v>3285</v>
@@ -24450,7 +24473,7 @@
     </row>
     <row r="239" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B239" s="13">
         <v>3085</v>
@@ -24465,7 +24488,7 @@
     </row>
     <row r="240" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B240" s="13">
         <v>3086</v>
@@ -24479,19 +24502,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="133"/>
-      <c r="B241" s="134"/>
-      <c r="C241" s="135"/>
-      <c r="D241" s="136"/>
+      <c r="A241" s="134"/>
+      <c r="B241" s="135"/>
+      <c r="C241" s="136"/>
+      <c r="D241" s="137"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="139" t="s">
+      <c r="A242" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="119"/>
-      <c r="C242" s="119"/>
-      <c r="D242" s="119"/>
+      <c r="B242" s="112"/>
+      <c r="C242" s="112"/>
+      <c r="D242" s="112"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24513,7 +24536,7 @@
     </row>
     <row r="244" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B244" s="13">
         <v>11</v>
@@ -24528,7 +24551,7 @@
     </row>
     <row r="245" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B245" s="13">
         <v>2471</v>
@@ -24543,7 +24566,7 @@
     </row>
     <row r="246" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B246" s="13">
         <v>10</v>
@@ -24558,7 +24581,7 @@
     </row>
     <row r="247" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B247" s="13">
         <v>2472</v>
@@ -24573,7 +24596,7 @@
     </row>
     <row r="248" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B248" s="13">
         <v>133</v>
@@ -24588,7 +24611,7 @@
     </row>
     <row r="249" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B249" s="13">
         <v>2590</v>
@@ -24603,7 +24626,7 @@
     </row>
     <row r="250" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B250" s="13">
         <v>127</v>
@@ -24618,7 +24641,7 @@
     </row>
     <row r="251" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B251" s="13">
         <v>12</v>
@@ -24648,7 +24671,7 @@
     </row>
     <row r="253" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B253" s="13">
         <v>24</v>
@@ -24663,7 +24686,7 @@
     </row>
     <row r="254" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B254" s="13">
         <v>2580</v>
@@ -24678,7 +24701,7 @@
     </row>
     <row r="255" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B255" s="13">
         <v>123</v>
@@ -24693,7 +24716,7 @@
     </row>
     <row r="256" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B256" s="13">
         <v>144</v>
@@ -24708,7 +24731,7 @@
     </row>
     <row r="257" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B257" s="13">
         <v>2566</v>
@@ -24723,7 +24746,7 @@
     </row>
     <row r="258" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B258" s="13">
         <v>210</v>
@@ -24738,7 +24761,7 @@
     </row>
     <row r="259" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B259" s="13">
         <v>2482</v>
@@ -24753,7 +24776,7 @@
     </row>
     <row r="260" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B260" s="13">
         <v>34</v>
@@ -24768,7 +24791,7 @@
     </row>
     <row r="261" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B261" s="13">
         <v>114</v>
@@ -24783,7 +24806,7 @@
     </row>
     <row r="262" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B262" s="13">
         <v>89</v>
@@ -24798,7 +24821,7 @@
     </row>
     <row r="263" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B263" s="13">
         <v>3362</v>
@@ -24813,7 +24836,7 @@
     </row>
     <row r="264" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B264" s="13">
         <v>3363</v>
@@ -24828,7 +24851,7 @@
     </row>
     <row r="265" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B265" s="13">
         <v>2486</v>
@@ -24843,7 +24866,7 @@
     </row>
     <row r="266" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B266" s="13">
         <v>2241</v>
@@ -24858,7 +24881,7 @@
     </row>
     <row r="267" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B267" s="13">
         <v>2487</v>
@@ -24873,7 +24896,7 @@
     </row>
     <row r="268" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B268" s="13">
         <v>23</v>
@@ -24888,7 +24911,7 @@
     </row>
     <row r="269" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B269" s="13">
         <v>2260</v>
@@ -24903,7 +24926,7 @@
     </row>
     <row r="270" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B270" s="13">
         <v>214</v>
@@ -24918,7 +24941,7 @@
     </row>
     <row r="271" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B271" s="13">
         <v>28</v>
@@ -24933,7 +24956,7 @@
     </row>
     <row r="272" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B272" s="13">
         <v>68</v>
@@ -24948,7 +24971,7 @@
     </row>
     <row r="273" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B273" s="13">
         <v>2302</v>
@@ -24963,7 +24986,7 @@
     </row>
     <row r="274" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B274" s="13">
         <v>320</v>
@@ -24978,7 +25001,7 @@
     </row>
     <row r="275" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B275" s="13">
         <v>130</v>
@@ -24993,7 +25016,7 @@
     </row>
     <row r="276" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B276" s="13">
         <v>2464</v>
@@ -25008,7 +25031,7 @@
     </row>
     <row r="277" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B277" s="13">
         <v>101</v>
@@ -25023,7 +25046,7 @@
     </row>
     <row r="278" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B278" s="13">
         <v>2465</v>
@@ -25038,7 +25061,7 @@
     </row>
     <row r="279" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B279" s="13">
         <v>2624</v>
@@ -25053,7 +25076,7 @@
     </row>
     <row r="280" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B280" s="13">
         <v>65</v>
@@ -25068,7 +25091,7 @@
     </row>
     <row r="281" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B281" s="13">
         <v>119</v>
@@ -25083,7 +25106,7 @@
     </row>
     <row r="282" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B282" s="13">
         <v>2834</v>
@@ -25098,7 +25121,7 @@
     </row>
     <row r="283" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B283" s="13">
         <v>141</v>
@@ -25113,7 +25136,7 @@
     </row>
     <row r="284" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B284" s="13">
         <v>3025</v>
@@ -25128,7 +25151,7 @@
     </row>
     <row r="285" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B285" s="13">
         <v>2543</v>
@@ -25143,7 +25166,7 @@
     </row>
     <row r="286" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B286" s="13">
         <v>98</v>
@@ -25158,7 +25181,7 @@
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B287" s="13">
         <v>35</v>
@@ -25173,7 +25196,7 @@
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B288" s="13">
         <v>2353</v>
@@ -25188,7 +25211,7 @@
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B289" s="13">
         <v>2466</v>
@@ -25203,7 +25226,7 @@
     </row>
     <row r="290" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B290" s="13">
         <v>2666</v>
@@ -25218,7 +25241,7 @@
     </row>
     <row r="291" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B291" s="13">
         <v>2667</v>
@@ -25233,7 +25256,7 @@
     </row>
     <row r="292" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B292" s="13">
         <v>190</v>
@@ -25248,7 +25271,7 @@
     </row>
     <row r="293" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B293" s="13">
         <v>2335</v>
@@ -25263,7 +25286,7 @@
     </row>
     <row r="294" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B294" s="13">
         <v>3446</v>
@@ -25278,7 +25301,7 @@
     </row>
     <row r="295" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B295" s="13">
         <v>3447</v>
@@ -25293,7 +25316,7 @@
     </row>
     <row r="296" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B296" s="13">
         <v>100</v>
@@ -25308,7 +25331,7 @@
     </row>
     <row r="297" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B297" s="13">
         <v>136</v>
@@ -25323,7 +25346,7 @@
     </row>
     <row r="298" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B298" s="13">
         <v>259</v>
@@ -25338,7 +25361,7 @@
     </row>
     <row r="299" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B299" s="13">
         <v>2319</v>
@@ -25353,7 +25376,7 @@
     </row>
     <row r="300" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B300" s="13">
         <v>125</v>
@@ -25368,7 +25391,7 @@
     </row>
     <row r="301" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B301" s="13">
         <v>2468</v>
@@ -25383,7 +25406,7 @@
     </row>
     <row r="302" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B302" s="13">
         <v>62</v>
@@ -25398,7 +25421,7 @@
     </row>
     <row r="303" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B303" s="13">
         <v>2469</v>
@@ -25413,7 +25436,7 @@
     </row>
     <row r="304" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B304" s="13">
         <v>3006</v>
@@ -25428,7 +25451,7 @@
     </row>
     <row r="305" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B305" s="13">
         <v>3007</v>
@@ -25443,7 +25466,7 @@
     </row>
     <row r="306" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B306" s="13">
         <v>117</v>
@@ -25458,7 +25481,7 @@
     </row>
     <row r="307" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B307" s="13">
         <v>2320</v>
@@ -25473,7 +25496,7 @@
     </row>
     <row r="308" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B308" s="13">
         <v>60</v>
@@ -25488,7 +25511,7 @@
     </row>
     <row r="309" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B309" s="13">
         <v>2321</v>
@@ -25503,7 +25526,7 @@
     </row>
     <row r="310" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B310" s="13">
         <v>211</v>
@@ -25518,7 +25541,7 @@
     </row>
     <row r="311" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B311" s="13">
         <v>41</v>
@@ -25533,7 +25556,7 @@
     </row>
     <row r="312" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B312" s="13">
         <v>2322</v>
@@ -25548,7 +25571,7 @@
     </row>
     <row r="313" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B313" s="13">
         <v>2244</v>
@@ -25563,7 +25586,7 @@
     </row>
     <row r="314" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B314" s="13">
         <v>2488</v>
@@ -25593,7 +25616,7 @@
     </row>
     <row r="316" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B316" s="13">
         <v>2344</v>
@@ -25608,7 +25631,7 @@
     </row>
     <row r="317" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B317" s="13">
         <v>3695</v>
@@ -25623,7 +25646,7 @@
     </row>
     <row r="318" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B318" s="13">
         <v>2460</v>
@@ -25638,7 +25661,7 @@
     </row>
     <row r="319" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B319" s="13">
         <v>3110</v>
@@ -25653,7 +25676,7 @@
     </row>
     <row r="320" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B320" s="13">
         <v>135</v>
@@ -25668,7 +25691,7 @@
     </row>
     <row r="321" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B321" s="13">
         <v>2463</v>
@@ -25683,7 +25706,7 @@
     </row>
     <row r="322" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B322" s="13">
         <v>55</v>
@@ -25698,7 +25721,7 @@
     </row>
     <row r="323" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B323" s="13">
         <v>51</v>
@@ -25712,21 +25735,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="133"/>
-      <c r="B324" s="134"/>
-      <c r="C324" s="135"/>
-      <c r="D324" s="136"/>
+      <c r="A324" s="134"/>
+      <c r="B324" s="135"/>
+      <c r="C324" s="136"/>
+      <c r="D324" s="137"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="139" t="s">
+      <c r="A325" s="133" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="119"/>
-      <c r="C325" s="119"/>
-      <c r="D325" s="119"/>
+      <c r="B325" s="112"/>
+      <c r="C325" s="112"/>
+      <c r="D325" s="112"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25748,7 +25771,7 @@
     </row>
     <row r="327" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B327" s="13">
         <v>8</v>
@@ -25765,7 +25788,7 @@
     </row>
     <row r="328" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B328" s="13">
         <v>1707</v>
@@ -25782,7 +25805,7 @@
     </row>
     <row r="329" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B329" s="13">
         <v>2391</v>
@@ -25799,7 +25822,7 @@
     </row>
     <row r="330" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B330" s="13">
         <v>2529</v>
@@ -25816,7 +25839,7 @@
     </row>
     <row r="331" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B331" s="13">
         <v>27</v>
@@ -25833,7 +25856,7 @@
     </row>
     <row r="332" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B332" s="13">
         <v>2255</v>
@@ -25850,7 +25873,7 @@
     </row>
     <row r="333" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B333" s="13">
         <v>2519</v>
@@ -25867,7 +25890,7 @@
     </row>
     <row r="334" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B334" s="13">
         <v>2525</v>
@@ -25884,7 +25907,7 @@
     </row>
     <row r="335" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B335" s="13">
         <v>3433</v>
@@ -25901,7 +25924,7 @@
     </row>
     <row r="336" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B336" s="13">
         <v>3394</v>
@@ -25918,7 +25941,7 @@
     </row>
     <row r="337" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B337" s="13">
         <v>47</v>
@@ -25935,7 +25958,7 @@
     </row>
     <row r="338" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B338" s="13">
         <v>46</v>
@@ -25952,7 +25975,7 @@
     </row>
     <row r="339" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="9" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B339" s="9">
         <v>3100</v>
@@ -25969,7 +25992,7 @@
     </row>
     <row r="340" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B340" s="13">
         <v>462</v>
@@ -25986,7 +26009,7 @@
     </row>
     <row r="341" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B341" s="13">
         <v>3639</v>
@@ -26003,7 +26026,7 @@
     </row>
     <row r="342" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B342" s="13">
         <v>461</v>
@@ -26020,7 +26043,7 @@
     </row>
     <row r="343" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B343" s="13">
         <v>2415</v>
@@ -26037,7 +26060,7 @@
     </row>
     <row r="344" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B344" s="13">
         <v>464</v>
@@ -26054,7 +26077,7 @@
     </row>
     <row r="345" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B345" s="13">
         <v>3640</v>
@@ -26071,7 +26094,7 @@
     </row>
     <row r="346" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B346" s="13">
         <v>463</v>
@@ -26088,7 +26111,7 @@
     </row>
     <row r="347" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B347" s="13">
         <v>2416</v>
@@ -26105,7 +26128,7 @@
     </row>
     <row r="348" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B348" s="13">
         <v>50</v>
@@ -26122,7 +26145,7 @@
     </row>
     <row r="349" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B349" s="13">
         <v>2533</v>
@@ -26139,7 +26162,7 @@
     </row>
     <row r="350" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B350" s="13">
         <v>52</v>
@@ -26156,7 +26179,7 @@
     </row>
     <row r="351" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B351" s="13">
         <v>2470</v>
@@ -26173,7 +26196,7 @@
     </row>
     <row r="352" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B352" s="13">
         <v>3414</v>
@@ -26190,7 +26213,7 @@
     </row>
     <row r="353" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B353" s="13">
         <v>53</v>
@@ -26207,7 +26230,7 @@
     </row>
     <row r="354" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B354" s="13">
         <v>2435</v>
@@ -26223,19 +26246,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="133"/>
-      <c r="B355" s="134"/>
-      <c r="C355" s="135"/>
-      <c r="D355" s="136"/>
+      <c r="A355" s="134"/>
+      <c r="B355" s="135"/>
+      <c r="C355" s="136"/>
+      <c r="D355" s="137"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="139" t="s">
+      <c r="A356" s="133" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="119"/>
-      <c r="C356" s="119"/>
-      <c r="D356" s="119"/>
+      <c r="B356" s="112"/>
+      <c r="C356" s="112"/>
+      <c r="D356" s="112"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26257,7 +26280,7 @@
     </row>
     <row r="358" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B358" s="13">
         <v>3383</v>
@@ -26274,7 +26297,7 @@
     </row>
     <row r="359" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B359" s="13">
         <v>3381</v>
@@ -26291,7 +26314,7 @@
     </row>
     <row r="360" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B360" s="2">
         <v>3440</v>
@@ -26308,7 +26331,7 @@
     </row>
     <row r="361" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B361" s="2">
         <v>2832</v>
@@ -26325,7 +26348,7 @@
     </row>
     <row r="362" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B362" s="13">
         <v>2222</v>
@@ -26342,7 +26365,7 @@
     </row>
     <row r="363" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B363" s="13">
         <v>3572</v>
@@ -26359,7 +26382,7 @@
     </row>
     <row r="364" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B364" s="13">
         <v>2522</v>
@@ -26376,7 +26399,7 @@
     </row>
     <row r="365" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B365" s="13">
         <v>2521</v>
@@ -26393,7 +26416,7 @@
     </row>
     <row r="366" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B366" s="13">
         <v>2571</v>
@@ -26410,7 +26433,7 @@
     </row>
     <row r="367" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B367" s="13">
         <v>2575</v>
@@ -26427,7 +26450,7 @@
     </row>
     <row r="368" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B368" s="13">
         <v>3392</v>
@@ -26444,7 +26467,7 @@
     </row>
     <row r="369" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B369" s="13">
         <v>2615</v>
@@ -26461,7 +26484,7 @@
     </row>
     <row r="370" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B370" s="13">
         <v>2657</v>
@@ -26478,7 +26501,7 @@
     </row>
     <row r="371" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B371" s="13">
         <v>2658</v>
@@ -26495,7 +26518,7 @@
     </row>
     <row r="372" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B372" s="13">
         <v>3461</v>
@@ -26512,7 +26535,7 @@
     </row>
     <row r="373" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B373" s="13">
         <v>3462</v>
@@ -26529,7 +26552,7 @@
     </row>
     <row r="374" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B374" s="13">
         <v>460</v>
@@ -26546,7 +26569,7 @@
     </row>
     <row r="375" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B375" s="13">
         <v>2473</v>
@@ -26563,7 +26586,7 @@
     </row>
     <row r="376" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B376" s="13">
         <v>128</v>
@@ -26580,7 +26603,7 @@
     </row>
     <row r="377" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B377" s="13">
         <v>2474</v>
@@ -26597,7 +26620,7 @@
     </row>
     <row r="378" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B378" s="13">
         <v>2417</v>
@@ -26614,7 +26637,7 @@
     </row>
     <row r="379" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="9" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B379" s="9">
         <v>3109</v>
@@ -26631,7 +26654,7 @@
     </row>
     <row r="380" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B380" s="13">
         <v>2651</v>
@@ -26648,7 +26671,7 @@
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B381" s="13">
         <v>2652</v>
@@ -26665,7 +26688,7 @@
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B382" s="13">
         <v>2646</v>
@@ -26682,7 +26705,7 @@
     </row>
     <row r="383" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B383" s="13">
         <v>2645</v>
@@ -26699,7 +26722,7 @@
     </row>
     <row r="384" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B384" s="13">
         <v>2638</v>
@@ -26716,7 +26739,7 @@
     </row>
     <row r="385" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B385" s="13">
         <v>2857</v>
@@ -26733,7 +26756,7 @@
     </row>
     <row r="386" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B386" s="13">
         <v>2858</v>
@@ -26750,7 +26773,7 @@
     </row>
     <row r="387" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B387" s="13">
         <v>2492</v>
@@ -26767,7 +26790,7 @@
     </row>
     <row r="388" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B388" s="13">
         <v>2499</v>
@@ -26784,7 +26807,7 @@
     </row>
     <row r="389" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B389" s="13">
         <v>1515</v>
@@ -26801,7 +26824,7 @@
     </row>
     <row r="390" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B390" s="13">
         <v>2552</v>
@@ -26818,7 +26841,7 @@
     </row>
     <row r="391" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B391" s="13">
         <v>3092</v>
@@ -26835,7 +26858,7 @@
     </row>
     <row r="392" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B392" s="13">
         <v>2606</v>
@@ -26852,7 +26875,7 @@
     </row>
     <row r="393" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B393" s="13">
         <v>2425</v>
@@ -26869,7 +26892,7 @@
     </row>
     <row r="394" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B394" s="13">
         <v>2579</v>
@@ -26886,7 +26909,7 @@
     </row>
     <row r="395" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="2" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B395" s="13">
         <v>2243</v>
@@ -26903,7 +26926,7 @@
     </row>
     <row r="396" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B396" s="13">
         <v>2659</v>
@@ -26920,7 +26943,7 @@
     </row>
     <row r="397" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B397" s="13">
         <v>2621</v>
@@ -26937,7 +26960,7 @@
     </row>
     <row r="398" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B398" s="13">
         <v>3475</v>
@@ -26954,7 +26977,7 @@
     </row>
     <row r="399" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="2" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B399" s="13">
         <v>3474</v>
@@ -26971,7 +26994,7 @@
     </row>
     <row r="400" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="2" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B400" s="13">
         <v>3137</v>
@@ -26988,7 +27011,7 @@
     </row>
     <row r="401" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B401" s="13">
         <v>3136</v>
@@ -27005,7 +27028,7 @@
     </row>
     <row r="402" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B402" s="13">
         <v>580</v>
@@ -27022,7 +27045,7 @@
     </row>
     <row r="403" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="2" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B403" s="13">
         <v>581</v>
@@ -27039,7 +27062,7 @@
     </row>
     <row r="404" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="10" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B404" s="11">
         <v>3027</v>
@@ -27056,7 +27079,7 @@
     </row>
     <row r="405" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="10" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B405" s="12">
         <v>3026</v>
@@ -27073,7 +27096,7 @@
     </row>
     <row r="406" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="10" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B406" s="12">
         <v>3514</v>
@@ -27090,7 +27113,7 @@
     </row>
     <row r="407" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="10" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B407" s="12">
         <v>3515</v>
@@ -27107,7 +27130,7 @@
     </row>
     <row r="408" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="10" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B408" s="12">
         <v>3791</v>
@@ -27124,7 +27147,7 @@
     </row>
     <row r="409" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="10" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B409" s="12">
         <v>3794</v>
@@ -27141,7 +27164,7 @@
     </row>
     <row r="410" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="10" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B410" s="11">
         <v>3792</v>
@@ -27158,7 +27181,7 @@
     </row>
     <row r="411" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="10" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B411" s="11">
         <v>3793</v>
@@ -27175,7 +27198,7 @@
     </row>
     <row r="412" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="2" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B412" s="13">
         <v>3448</v>
@@ -27192,7 +27215,7 @@
     </row>
     <row r="413" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B413" s="13">
         <v>3450</v>
@@ -27209,7 +27232,7 @@
     </row>
     <row r="414" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B414" s="13">
         <v>3449</v>
@@ -27226,7 +27249,7 @@
     </row>
     <row r="415" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B415" s="13">
         <v>3451</v>
@@ -27243,7 +27266,7 @@
     </row>
     <row r="416" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B416" s="13">
         <v>3342</v>
@@ -27260,7 +27283,7 @@
     </row>
     <row r="417" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="2" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B417" s="13">
         <v>2592</v>
@@ -27277,7 +27300,7 @@
     </row>
     <row r="418" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B418" s="13">
         <v>2597</v>
@@ -27294,7 +27317,7 @@
     </row>
     <row r="419" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B419" s="13">
         <v>2686</v>
@@ -27311,7 +27334,7 @@
     </row>
     <row r="420" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B420" s="13">
         <v>2687</v>
@@ -27328,7 +27351,7 @@
     </row>
     <row r="421" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B421" s="13">
         <v>2681</v>
@@ -27345,7 +27368,7 @@
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B422" s="13">
         <v>2682</v>
@@ -27362,7 +27385,7 @@
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B423" s="13">
         <v>2683</v>
@@ -27379,7 +27402,7 @@
     </row>
     <row r="424" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B424" s="13">
         <v>2600</v>
@@ -27396,7 +27419,7 @@
     </row>
     <row r="425" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="2" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B425" s="13">
         <v>2595</v>
@@ -27413,7 +27436,7 @@
     </row>
     <row r="426" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="2" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B426" s="13">
         <v>2707</v>
@@ -27430,7 +27453,7 @@
     </row>
     <row r="427" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="2" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B427" s="13">
         <v>3605</v>
@@ -27447,7 +27470,7 @@
     </row>
     <row r="428" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="2" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B428" s="13">
         <v>3606</v>
@@ -27464,7 +27487,7 @@
     </row>
     <row r="429" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="2" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B429" s="13">
         <v>2684</v>
@@ -27481,7 +27504,7 @@
     </row>
     <row r="430" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="2" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B430" s="13">
         <v>2723</v>
@@ -27498,7 +27521,7 @@
     </row>
     <row r="431" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="2" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B431" s="13">
         <v>2723</v>
@@ -27515,7 +27538,7 @@
     </row>
     <row r="432" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="2" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B432" s="13">
         <v>2719</v>
@@ -27532,7 +27555,7 @@
     </row>
     <row r="433" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B433" s="13">
         <v>3094</v>
@@ -27549,7 +27572,7 @@
     </row>
     <row r="434" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="2" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B434" s="13">
         <v>2685</v>
@@ -27566,7 +27589,7 @@
     </row>
     <row r="435" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B435" s="13">
         <v>3570</v>
@@ -27583,7 +27606,7 @@
     </row>
     <row r="436" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B436" s="13">
         <v>2596</v>
@@ -27600,7 +27623,7 @@
     </row>
     <row r="437" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B437" s="13">
         <v>2612</v>
@@ -27617,7 +27640,7 @@
     </row>
     <row r="438" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B438" s="13">
         <v>2605</v>
@@ -27634,7 +27657,7 @@
     </row>
     <row r="439" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B439" s="13">
         <v>2653</v>
@@ -27651,7 +27674,7 @@
     </row>
     <row r="440" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="2" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B440" s="13">
         <v>3675</v>
@@ -27668,7 +27691,7 @@
     </row>
     <row r="441" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="2" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B441" s="13">
         <v>2777</v>
@@ -27685,7 +27708,7 @@
     </row>
     <row r="442" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="2" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B442" s="13">
         <v>2776</v>
@@ -27702,7 +27725,7 @@
     </row>
     <row r="443" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B443" s="13">
         <v>2689</v>
@@ -27719,7 +27742,7 @@
     </row>
     <row r="444" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="2" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B444" s="13">
         <v>2785</v>
@@ -27736,7 +27759,7 @@
     </row>
     <row r="445" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="2" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B445" s="13">
         <v>2784</v>
@@ -27753,7 +27776,7 @@
     </row>
     <row r="446" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="2" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B446" s="13">
         <v>2788</v>
@@ -27770,7 +27793,7 @@
     </row>
     <row r="447" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="2" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B447" s="13">
         <v>2789</v>
@@ -27787,7 +27810,7 @@
     </row>
     <row r="448" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="9" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="B448" s="9">
         <v>3495</v>
@@ -27804,7 +27827,7 @@
     </row>
     <row r="449" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="2" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B449" s="13">
         <v>2786</v>
@@ -27821,7 +27844,7 @@
     </row>
     <row r="450" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B450" s="13">
         <v>2787</v>
@@ -27838,7 +27861,7 @@
     </row>
     <row r="451" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="2" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B451" s="13">
         <v>2598</v>
@@ -27855,7 +27878,7 @@
     </row>
     <row r="452" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="2" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B452" s="13">
         <v>2690</v>
@@ -27872,7 +27895,7 @@
     </row>
     <row r="453" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="2" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B453" s="13">
         <v>3024</v>
@@ -27889,7 +27912,7 @@
     </row>
     <row r="454" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B454" s="13">
         <v>2589</v>
@@ -27906,7 +27929,7 @@
     </row>
     <row r="455" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="2" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B455" s="13">
         <v>2588</v>
@@ -27923,7 +27946,7 @@
     </row>
     <row r="456" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="2" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B456" s="13">
         <v>2688</v>
@@ -27940,7 +27963,7 @@
     </row>
     <row r="457" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="2" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B457" s="13">
         <v>2599</v>
@@ -27957,7 +27980,7 @@
     </row>
     <row r="458" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="2" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B458" s="13">
         <v>2240</v>
@@ -27974,7 +27997,7 @@
     </row>
     <row r="459" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="2" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B459" s="13">
         <v>2424</v>
@@ -27990,19 +28013,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="133"/>
-      <c r="B460" s="134"/>
-      <c r="C460" s="135"/>
-      <c r="D460" s="136"/>
+      <c r="A460" s="134"/>
+      <c r="B460" s="135"/>
+      <c r="C460" s="136"/>
+      <c r="D460" s="137"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="139" t="s">
+      <c r="A461" s="133" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="119"/>
-      <c r="C461" s="119"/>
-      <c r="D461" s="119"/>
+      <c r="B461" s="112"/>
+      <c r="C461" s="112"/>
+      <c r="D461" s="112"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28024,7 +28047,7 @@
     </row>
     <row r="463" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="B463" s="13">
         <v>3051</v>
@@ -28041,7 +28064,7 @@
     </row>
     <row r="464" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="2" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B464" s="13">
         <v>2675</v>
@@ -28058,7 +28081,7 @@
     </row>
     <row r="465" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B465" s="13">
         <v>2791</v>
@@ -28075,7 +28098,7 @@
     </row>
     <row r="466" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="2" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B466" s="13">
         <v>3090</v>
@@ -28092,7 +28115,7 @@
     </row>
     <row r="467" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B467" s="13">
         <v>2227</v>
@@ -28109,7 +28132,7 @@
     </row>
     <row r="468" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B468" s="13">
         <v>2414</v>
@@ -28126,7 +28149,7 @@
     </row>
     <row r="469" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B469" s="13">
         <v>2418</v>
@@ -28143,7 +28166,7 @@
     </row>
     <row r="470" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="2" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B470" s="13">
         <v>2272</v>
@@ -28160,7 +28183,7 @@
     </row>
     <row r="471" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="2" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B471" s="13">
         <v>3651</v>
@@ -28177,7 +28200,7 @@
     </row>
     <row r="472" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="2" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B472" s="13">
         <v>3652</v>
@@ -28194,7 +28217,7 @@
     </row>
     <row r="473" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="2" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B473" s="13">
         <v>2756</v>
@@ -28211,7 +28234,7 @@
     </row>
     <row r="474" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="2" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B474" s="13">
         <v>2757</v>
@@ -28228,7 +28251,7 @@
     </row>
     <row r="475" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B475" s="13">
         <v>2350</v>
@@ -28245,7 +28268,7 @@
     </row>
     <row r="476" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="2" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B476" s="13">
         <v>2362</v>
@@ -28262,7 +28285,7 @@
     </row>
     <row r="477" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="2" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B477" s="13">
         <v>2406</v>
@@ -28279,7 +28302,7 @@
     </row>
     <row r="478" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="2" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B478" s="13">
         <v>2229</v>
@@ -28295,19 +28318,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="133"/>
-      <c r="B479" s="134"/>
-      <c r="C479" s="135"/>
-      <c r="D479" s="136"/>
+      <c r="A479" s="134"/>
+      <c r="B479" s="135"/>
+      <c r="C479" s="136"/>
+      <c r="D479" s="137"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="139" t="s">
+      <c r="A480" s="133" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="119"/>
-      <c r="C480" s="119"/>
-      <c r="D480" s="119"/>
+      <c r="B480" s="112"/>
+      <c r="C480" s="112"/>
+      <c r="D480" s="112"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28329,7 +28352,7 @@
     </row>
     <row r="482" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B482" s="13">
         <v>189</v>
@@ -28346,7 +28369,7 @@
     </row>
     <row r="483" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="2" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B483" s="13">
         <v>2553</v>
@@ -28363,7 +28386,7 @@
     </row>
     <row r="484" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="2" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B484" s="13">
         <v>2614</v>
@@ -28380,7 +28403,7 @@
     </row>
     <row r="485" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="2" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B485" s="13">
         <v>2613</v>
@@ -28397,7 +28420,7 @@
     </row>
     <row r="486" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="2" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B486" s="13">
         <v>2555</v>
@@ -28414,7 +28437,7 @@
     </row>
     <row r="487" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="2" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B487" s="13">
         <v>2556</v>
@@ -28431,7 +28454,7 @@
     </row>
     <row r="488" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="2" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B488" s="13">
         <v>99</v>
@@ -28448,7 +28471,7 @@
     </row>
     <row r="489" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="2" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B489" s="13">
         <v>521</v>
@@ -28465,7 +28488,7 @@
     </row>
     <row r="490" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B490" s="13">
         <v>3669</v>
@@ -28482,7 +28505,7 @@
     </row>
     <row r="491" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="2" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B491" s="13">
         <v>38</v>
@@ -28499,7 +28522,7 @@
     </row>
     <row r="492" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B492" s="13">
         <v>2479</v>
@@ -28516,7 +28539,7 @@
     </row>
     <row r="493" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="2" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B493" s="13">
         <v>105</v>
@@ -28533,7 +28556,7 @@
     </row>
     <row r="494" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="2" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B494" s="13">
         <v>212</v>
@@ -28550,7 +28573,7 @@
     </row>
     <row r="495" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B495" s="13">
         <v>3397</v>
@@ -28567,7 +28590,7 @@
     </row>
     <row r="496" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="2" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B496" s="13">
         <v>653</v>
@@ -28584,7 +28607,7 @@
     </row>
     <row r="497" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="2" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B497" s="13">
         <v>2484</v>
@@ -28601,7 +28624,7 @@
     </row>
     <row r="498" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="2" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B498" s="13">
         <v>560</v>
@@ -28618,7 +28641,7 @@
     </row>
     <row r="499" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="2" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B499" s="13">
         <v>2478</v>
@@ -28635,7 +28658,7 @@
     </row>
     <row r="500" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B500" s="13">
         <v>3375</v>
@@ -28652,7 +28675,7 @@
     </row>
     <row r="501" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="2" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B501" s="13">
         <v>3376</v>
@@ -28669,7 +28692,7 @@
     </row>
     <row r="502" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="2" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B502" s="13">
         <v>2680</v>
@@ -28686,7 +28709,7 @@
     </row>
     <row r="503" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="2" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B503" s="13">
         <v>2676</v>
@@ -28703,7 +28726,7 @@
     </row>
     <row r="504" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="5" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B504" s="14">
         <v>571</v>
@@ -28720,7 +28743,7 @@
     </row>
     <row r="505" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="2" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B505" s="13">
         <v>2245</v>
@@ -28736,19 +28759,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="133"/>
-      <c r="B506" s="134"/>
-      <c r="C506" s="135"/>
-      <c r="D506" s="136"/>
+      <c r="A506" s="134"/>
+      <c r="B506" s="135"/>
+      <c r="C506" s="136"/>
+      <c r="D506" s="137"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="139" t="s">
+      <c r="A507" s="133" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="119"/>
-      <c r="C507" s="119"/>
-      <c r="D507" s="119"/>
+      <c r="B507" s="112"/>
+      <c r="C507" s="112"/>
+      <c r="D507" s="112"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28770,7 +28793,7 @@
     </row>
     <row r="509" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="9" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B509" s="11">
         <v>2618</v>
@@ -28787,7 +28810,7 @@
     </row>
     <row r="510" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="9" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B510" s="11">
         <v>2398</v>
@@ -28804,7 +28827,7 @@
     </row>
     <row r="511" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B511" s="9">
         <v>3</v>
@@ -28821,7 +28844,7 @@
     </row>
     <row r="512" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B512" s="9">
         <v>2224</v>
@@ -28838,7 +28861,7 @@
     </row>
     <row r="513" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B513" s="9">
         <v>208</v>
@@ -28855,7 +28878,7 @@
     </row>
     <row r="514" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="9" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B514" s="11">
         <v>2297</v>
@@ -28872,7 +28895,7 @@
     </row>
     <row r="515" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="9" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B515" s="11">
         <v>3653</v>
@@ -28889,7 +28912,7 @@
     </row>
     <row r="516" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="9" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B516" s="11">
         <v>2339</v>
@@ -28906,7 +28929,7 @@
     </row>
     <row r="517" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="9" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B517" s="9">
         <v>2225</v>
@@ -28923,7 +28946,7 @@
     </row>
     <row r="518" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="9" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B518" s="11">
         <v>2223</v>
@@ -28940,7 +28963,7 @@
     </row>
     <row r="519" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B519" s="11">
         <v>3707</v>
@@ -28957,7 +28980,7 @@
     </row>
     <row r="520" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B520" s="13">
         <v>282</v>
@@ -28974,7 +28997,7 @@
     </row>
     <row r="521" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="2" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B521" s="13">
         <v>2259</v>
@@ -28991,7 +29014,7 @@
     </row>
     <row r="522" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="2" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B522" s="13">
         <v>3541</v>
@@ -29008,7 +29031,7 @@
     </row>
     <row r="523" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B523" s="13">
         <v>3540</v>
@@ -29025,7 +29048,7 @@
     </row>
     <row r="524" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B524" s="13">
         <v>569</v>
@@ -29042,7 +29065,7 @@
     </row>
     <row r="525" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B525" s="13">
         <v>2422</v>
@@ -29059,7 +29082,7 @@
     </row>
     <row r="526" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="2" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B526" s="13">
         <v>2336</v>
@@ -29076,7 +29099,7 @@
     </row>
     <row r="527" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="2" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B527" s="13">
         <v>2421</v>
@@ -29093,7 +29116,7 @@
     </row>
     <row r="528" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="2" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B528" s="13">
         <v>2568</v>
@@ -29110,7 +29133,7 @@
     </row>
     <row r="529" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="2" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B529" s="13">
         <v>3009</v>
@@ -29127,7 +29150,7 @@
     </row>
     <row r="530" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="2" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B530" s="13">
         <v>2305</v>
@@ -29144,7 +29167,7 @@
     </row>
     <row r="531" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="2" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B531" s="13">
         <v>2778</v>
@@ -29161,7 +29184,7 @@
     </row>
     <row r="532" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="2" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B532" s="13">
         <v>3696</v>
@@ -29178,7 +29201,7 @@
     </row>
     <row r="533" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="2" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B533" s="13">
         <v>2569</v>
@@ -29212,7 +29235,7 @@
     </row>
     <row r="535" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="2" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B535" s="13">
         <v>2783</v>
@@ -29229,7 +29252,7 @@
     </row>
     <row r="536" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="2" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B536" s="13">
         <v>3486</v>
@@ -29246,7 +29269,7 @@
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="2" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B537" s="13">
         <v>3487</v>
@@ -29263,7 +29286,7 @@
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B538" s="13">
         <v>2462</v>
@@ -29280,7 +29303,7 @@
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B539" s="13">
         <v>2601</v>
@@ -29297,7 +29320,7 @@
     </row>
     <row r="540" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="2" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B540" s="13">
         <v>3400</v>
@@ -29314,7 +29337,7 @@
     </row>
     <row r="541" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B541" s="13">
         <v>3488</v>
@@ -29331,7 +29354,7 @@
     </row>
     <row r="542" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="2" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B542" s="13">
         <v>565</v>
@@ -29348,7 +29371,7 @@
     </row>
     <row r="543" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="2" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B543" s="13">
         <v>2257</v>
@@ -29365,7 +29388,7 @@
     </row>
     <row r="544" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="2" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B544" s="13">
         <v>3537</v>
@@ -29382,7 +29405,7 @@
     </row>
     <row r="545" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="2" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B545" s="13">
         <v>3539</v>
@@ -29399,7 +29422,7 @@
     </row>
     <row r="546" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="2" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B546" s="13">
         <v>1601</v>
@@ -29416,7 +29439,7 @@
     </row>
     <row r="547" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="2" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B547" s="13">
         <v>2732</v>
@@ -29433,7 +29456,7 @@
     </row>
     <row r="548" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="2" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B548" s="13">
         <v>2733</v>
@@ -29450,7 +29473,7 @@
     </row>
     <row r="549" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="2" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B549" s="13">
         <v>2584</v>
@@ -29467,7 +29490,7 @@
     </row>
     <row r="550" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B550" s="13">
         <v>2585</v>
@@ -29484,7 +29507,7 @@
     </row>
     <row r="551" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B551" s="13">
         <v>2495</v>
@@ -29501,7 +29524,7 @@
     </row>
     <row r="552" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="2" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B552" s="13">
         <v>2496</v>
@@ -29518,7 +29541,7 @@
     </row>
     <row r="553" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B553" s="13">
         <v>3538</v>
@@ -29535,7 +29558,7 @@
     </row>
     <row r="554" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B554" s="13">
         <v>1603</v>
@@ -29552,7 +29575,7 @@
     </row>
     <row r="555" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B555" s="13">
         <v>3536</v>
@@ -29569,7 +29592,7 @@
     </row>
     <row r="556" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B556" s="13">
         <v>2494</v>
@@ -29586,7 +29609,7 @@
     </row>
     <row r="557" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B557" s="13">
         <v>2497</v>
@@ -29603,7 +29626,7 @@
     </row>
     <row r="558" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="2" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B558" s="13">
         <v>2493</v>
@@ -29620,7 +29643,7 @@
     </row>
     <row r="559" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="2" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B559" s="13">
         <v>3535</v>
@@ -29637,7 +29660,7 @@
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B560" s="13">
         <v>3673</v>
@@ -29654,7 +29677,7 @@
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B561" s="13">
         <v>1602</v>
@@ -29671,7 +29694,7 @@
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="2" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B562" s="13">
         <v>2498</v>
@@ -29688,7 +29711,7 @@
     </row>
     <row r="563" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B563" s="13">
         <v>2806</v>
@@ -29705,7 +29728,7 @@
     </row>
     <row r="564" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="2" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B564" s="13">
         <v>2807</v>
@@ -29722,7 +29745,7 @@
     </row>
     <row r="565" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B565" s="13">
         <v>195</v>
@@ -29739,7 +29762,7 @@
     </row>
     <row r="566" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B566" s="13">
         <v>54</v>
@@ -29756,7 +29779,7 @@
     </row>
     <row r="567" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="2" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B567" s="13">
         <v>63</v>
@@ -29773,7 +29796,7 @@
     </row>
     <row r="568" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="2" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B568" s="13">
         <v>2483</v>
@@ -29790,7 +29813,7 @@
     </row>
     <row r="569" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="2" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B569" s="13">
         <v>2856</v>
@@ -29807,7 +29830,7 @@
     </row>
     <row r="570" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="2" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B570" s="13">
         <v>2284</v>
@@ -29824,7 +29847,7 @@
     </row>
     <row r="571" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="2" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B571" s="13">
         <v>3117</v>
@@ -29841,7 +29864,7 @@
     </row>
     <row r="572" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B572" s="13">
         <v>3507</v>
@@ -29858,7 +29881,7 @@
     </row>
     <row r="573" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="2" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="B573" s="13">
         <v>3116</v>
@@ -29875,7 +29898,7 @@
     </row>
     <row r="574" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="2" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B574" s="13">
         <v>1230</v>
@@ -29892,7 +29915,7 @@
     </row>
     <row r="575" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="2" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B575" s="13">
         <v>1231</v>
@@ -29909,7 +29932,7 @@
     </row>
     <row r="576" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B576" s="13">
         <v>2799</v>
@@ -29926,7 +29949,7 @@
     </row>
     <row r="577" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="2" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B577" s="13">
         <v>3511</v>
@@ -29943,7 +29966,7 @@
     </row>
     <row r="578" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="2" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B578" s="13">
         <v>3510</v>
@@ -29960,7 +29983,7 @@
     </row>
     <row r="579" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="2" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B579" s="13">
         <v>2816</v>
@@ -29977,7 +30000,7 @@
     </row>
     <row r="580" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="2" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B580" s="13">
         <v>2370</v>
@@ -29994,7 +30017,7 @@
     </row>
     <row r="581" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="2" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B581" s="13">
         <v>3508</v>
@@ -30011,7 +30034,7 @@
     </row>
     <row r="582" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="2" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B582" s="13">
         <v>64</v>
@@ -30028,7 +30051,7 @@
     </row>
     <row r="583" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="2" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B583" s="13">
         <v>3420</v>
@@ -30045,7 +30068,7 @@
     </row>
     <row r="584" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="B584" s="13">
         <v>2230</v>
@@ -30062,7 +30085,7 @@
     </row>
     <row r="585" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B585" s="13">
         <v>90</v>
@@ -30079,7 +30102,7 @@
     </row>
     <row r="586" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="2" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B586" s="13">
         <v>3419</v>
@@ -30096,7 +30119,7 @@
     </row>
     <row r="587" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="2" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B587" s="13">
         <v>3509</v>
@@ -30113,7 +30136,7 @@
     </row>
     <row r="588" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B588" s="13">
         <v>2395</v>
@@ -30130,7 +30153,7 @@
     </row>
     <row r="589" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="2" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B589" s="13">
         <v>2427</v>
@@ -30147,7 +30170,7 @@
     </row>
     <row r="590" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="2" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B590" s="13">
         <v>3396</v>
@@ -30164,7 +30187,7 @@
     </row>
     <row r="591" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="2" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B591" s="13"/>
       <c r="C591" s="2" t="s">
@@ -30179,7 +30202,7 @@
     </row>
     <row r="592" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="2" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B592" s="13">
         <v>3395</v>
@@ -30196,7 +30219,7 @@
     </row>
     <row r="593" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="2" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B593" s="13">
         <v>458</v>
@@ -30213,7 +30236,7 @@
     </row>
     <row r="594" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B594" s="13">
         <v>2641</v>
@@ -30230,7 +30253,7 @@
     </row>
     <row r="595" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="2" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B595" s="13">
         <v>2396</v>
@@ -30247,7 +30270,7 @@
     </row>
     <row r="596" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="2" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B596" s="13">
         <v>2426</v>
@@ -30263,19 +30286,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="133"/>
-      <c r="B597" s="134"/>
-      <c r="C597" s="135"/>
-      <c r="D597" s="136"/>
+      <c r="A597" s="134"/>
+      <c r="B597" s="135"/>
+      <c r="C597" s="136"/>
+      <c r="D597" s="137"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="139" t="s">
+      <c r="A598" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="119"/>
-      <c r="C598" s="119"/>
-      <c r="D598" s="119"/>
+      <c r="B598" s="112"/>
+      <c r="C598" s="112"/>
+      <c r="D598" s="112"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30297,7 +30320,7 @@
     </row>
     <row r="600" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B600" s="13">
         <v>3402</v>
@@ -30314,7 +30337,7 @@
     </row>
     <row r="601" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B601" s="13">
         <v>3403</v>
@@ -30331,7 +30354,7 @@
     </row>
     <row r="602" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="2" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B602" s="13">
         <v>3401</v>
@@ -30348,7 +30371,7 @@
     </row>
     <row r="603" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="2" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B603" s="13">
         <v>2551</v>
@@ -30365,7 +30388,7 @@
     </row>
     <row r="604" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="2" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B604" s="13">
         <v>2550</v>
@@ -30382,7 +30405,7 @@
     </row>
     <row r="605" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B605" s="13">
         <v>3638</v>
@@ -30399,7 +30422,7 @@
     </row>
     <row r="606" spans="1:7" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B606" s="13">
         <v>3622</v>
@@ -30415,20 +30438,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="133"/>
-      <c r="B607" s="134"/>
-      <c r="C607" s="135"/>
-      <c r="D607" s="136"/>
+      <c r="A607" s="134"/>
+      <c r="B607" s="135"/>
+      <c r="C607" s="136"/>
+      <c r="D607" s="137"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="139" t="s">
+      <c r="A608" s="133" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="119"/>
-      <c r="C608" s="119"/>
-      <c r="D608" s="119"/>
+      <c r="B608" s="112"/>
+      <c r="C608" s="112"/>
+      <c r="D608" s="112"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30450,7 +30473,7 @@
     </row>
     <row r="610" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B610" s="13">
         <v>3056</v>
@@ -30467,7 +30490,7 @@
     </row>
     <row r="611" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B611" s="13">
         <v>3083</v>
@@ -30484,7 +30507,7 @@
     </row>
     <row r="612" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="2" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B612" s="13">
         <v>573</v>
@@ -30501,7 +30524,7 @@
     </row>
     <row r="613" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="2" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B613" s="13">
         <v>572</v>
@@ -30517,19 +30540,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="133"/>
-      <c r="B614" s="134"/>
-      <c r="C614" s="135"/>
-      <c r="D614" s="136"/>
+      <c r="A614" s="134"/>
+      <c r="B614" s="135"/>
+      <c r="C614" s="136"/>
+      <c r="D614" s="137"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="139" t="s">
+      <c r="A615" s="133" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="119"/>
-      <c r="C615" s="119"/>
-      <c r="D615" s="119"/>
+      <c r="B615" s="112"/>
+      <c r="C615" s="112"/>
+      <c r="D615" s="112"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30551,7 +30574,7 @@
     </row>
     <row r="617" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="2" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B617" s="2">
         <v>3642</v>
@@ -30602,7 +30625,7 @@
     </row>
     <row r="620" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="2" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B620" s="2">
         <v>3646</v>
@@ -30619,7 +30642,7 @@
     </row>
     <row r="621" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="2" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B621" s="2">
         <v>3645</v>
@@ -30636,7 +30659,7 @@
     </row>
     <row r="622" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B622" s="13">
         <v>3438</v>
@@ -30653,7 +30676,7 @@
     </row>
     <row r="623" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B623" s="13">
         <v>3434</v>
@@ -30670,7 +30693,7 @@
     </row>
     <row r="624" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B624" s="13">
         <v>3443</v>
@@ -30687,7 +30710,7 @@
     </row>
     <row r="625" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B625" s="13">
         <v>3019</v>
@@ -30704,7 +30727,7 @@
     </row>
     <row r="626" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B626" s="13">
         <v>3476</v>
@@ -30721,7 +30744,7 @@
     </row>
     <row r="627" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B627" s="13">
         <v>3477</v>
@@ -30738,7 +30761,7 @@
     </row>
     <row r="628" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B628" s="13">
         <v>3132</v>
@@ -30755,7 +30778,7 @@
     </row>
     <row r="629" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B629" s="13">
         <v>3133</v>
@@ -30772,7 +30795,7 @@
     </row>
     <row r="630" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B630" s="13">
         <v>2722</v>
@@ -30789,7 +30812,7 @@
     </row>
     <row r="631" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="2" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B631" s="13">
         <v>2674</v>
@@ -30806,7 +30829,7 @@
     </row>
     <row r="632" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="2" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B632" s="13">
         <v>1681</v>
@@ -30823,7 +30846,7 @@
     </row>
     <row r="633" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="2" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B633" s="13">
         <v>1680</v>
@@ -30840,7 +30863,7 @@
     </row>
     <row r="634" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="2" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B634" s="13">
         <v>3719</v>
@@ -30857,7 +30880,7 @@
     </row>
     <row r="635" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="2" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B635" s="13">
         <v>3720</v>
@@ -30874,7 +30897,7 @@
     </row>
     <row r="636" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="2" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B636" s="13">
         <v>3765</v>
@@ -30891,7 +30914,7 @@
     </row>
     <row r="637" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="2" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B637" s="13">
         <v>1609</v>
@@ -30908,7 +30931,7 @@
     </row>
     <row r="638" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B638" s="13">
         <v>3126</v>
@@ -30925,7 +30948,7 @@
     </row>
     <row r="639" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B639" s="13">
         <v>3127</v>
@@ -30942,7 +30965,7 @@
     </row>
     <row r="640" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B640" s="13">
         <v>3435</v>
@@ -30959,7 +30982,7 @@
     </row>
     <row r="641" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B641" s="13">
         <v>3436</v>
@@ -30976,7 +30999,7 @@
     </row>
     <row r="642" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="2" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B642" s="13">
         <v>3128</v>
@@ -30993,7 +31016,7 @@
     </row>
     <row r="643" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="2" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B643" s="13">
         <v>3129</v>
@@ -31010,7 +31033,7 @@
     </row>
     <row r="644" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="2" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B644" s="13">
         <v>3124</v>
@@ -31027,7 +31050,7 @@
     </row>
     <row r="645" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="2" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B645" s="13">
         <v>2854</v>
@@ -31044,7 +31067,7 @@
     </row>
     <row r="646" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="2" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B646" s="13">
         <v>3130</v>
@@ -31061,7 +31084,7 @@
     </row>
     <row r="647" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B647" s="13">
         <v>3131</v>
@@ -31078,7 +31101,7 @@
     </row>
     <row r="648" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="2" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B648" s="13">
         <v>3531</v>
@@ -31095,7 +31118,7 @@
     </row>
     <row r="649" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="2" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B649" s="13">
         <v>3529</v>
@@ -31112,7 +31135,7 @@
     </row>
     <row r="650" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="2" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B650" s="13">
         <v>3530</v>
@@ -31129,7 +31152,7 @@
     </row>
     <row r="651" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="2" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B651" s="13">
         <v>3502</v>
@@ -31146,7 +31169,7 @@
     </row>
     <row r="652" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="2" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B652" s="13">
         <v>3501</v>
@@ -31163,7 +31186,7 @@
     </row>
     <row r="653" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="2" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B653" s="13">
         <v>3500</v>
@@ -31248,7 +31271,7 @@
     </row>
     <row r="658" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="2" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B658" s="13">
         <v>3068</v>
@@ -31265,7 +31288,7 @@
     </row>
     <row r="659" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="2" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B659" s="13">
         <v>3087</v>
@@ -31282,7 +31305,7 @@
     </row>
     <row r="660" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="2" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B660" s="13">
         <v>1665</v>
@@ -31299,7 +31322,7 @@
     </row>
     <row r="661" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="2" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B661" s="13">
         <v>1666</v>
@@ -31316,7 +31339,7 @@
     </row>
     <row r="662" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="2" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B662" s="13">
         <v>1650</v>
@@ -31333,7 +31356,7 @@
     </row>
     <row r="663" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="2" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B663" s="13">
         <v>1651</v>
@@ -31350,7 +31373,7 @@
     </row>
     <row r="664" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="2" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B664" s="13">
         <v>1653</v>
@@ -31367,7 +31390,7 @@
     </row>
     <row r="665" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="2" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B665" s="13">
         <v>1649</v>
@@ -31384,7 +31407,7 @@
     </row>
     <row r="666" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="2" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B666" s="13">
         <v>1652</v>
@@ -31401,7 +31424,7 @@
     </row>
     <row r="667" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="2" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B667" s="13">
         <v>1683</v>
@@ -31418,7 +31441,7 @@
     </row>
     <row r="668" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="2" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B668" s="13">
         <v>1684</v>
@@ -31435,7 +31458,7 @@
     </row>
     <row r="669" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="2" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B669" s="13">
         <v>1685</v>
@@ -31452,7 +31475,7 @@
     </row>
     <row r="670" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="2" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="B670" s="13">
         <v>1686</v>
@@ -31486,7 +31509,7 @@
     </row>
     <row r="672" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="B672" s="13">
         <v>3648</v>
@@ -31503,7 +31526,7 @@
     </row>
     <row r="673" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="2" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B673" s="13">
         <v>3405</v>
@@ -31520,7 +31543,7 @@
     </row>
     <row r="674" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="2" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="B674" s="13">
         <v>1387</v>
@@ -31537,7 +31560,7 @@
     </row>
     <row r="675" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="2" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B675" s="13">
         <v>1654</v>
@@ -31554,7 +31577,7 @@
     </row>
     <row r="676" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="2" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="B676" s="13">
         <v>1655</v>
@@ -31571,7 +31594,7 @@
     </row>
     <row r="677" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="2" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="B677" s="13">
         <v>1656</v>
@@ -31588,7 +31611,7 @@
     </row>
     <row r="678" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="2" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B678" s="13">
         <v>2849</v>
@@ -31605,7 +31628,7 @@
     </row>
     <row r="679" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="2" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B679" s="13">
         <v>2851</v>
@@ -31622,7 +31645,7 @@
     </row>
     <row r="680" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="2" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B680" s="13">
         <v>2852</v>
@@ -31639,7 +31662,7 @@
     </row>
     <row r="681" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="2" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B681" s="13">
         <v>3058</v>
@@ -31656,7 +31679,7 @@
     </row>
     <row r="682" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="2" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="B682" s="13">
         <v>3059</v>
@@ -31673,7 +31696,7 @@
     </row>
     <row r="683" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="2" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B683" s="13">
         <v>3527</v>
@@ -31690,7 +31713,7 @@
     </row>
     <row r="684" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="2" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="B684" s="13">
         <v>3544</v>
@@ -31707,7 +31730,7 @@
     </row>
     <row r="685" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="2" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B685" s="13">
         <v>3545</v>
@@ -31724,7 +31747,7 @@
     </row>
     <row r="686" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="2" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="B686" s="13">
         <v>3676</v>
@@ -31741,7 +31764,7 @@
     </row>
     <row r="687" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="2" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="B687" s="13">
         <v>5853</v>
@@ -31758,7 +31781,7 @@
     </row>
     <row r="688" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="2" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B688" s="13">
         <v>2850</v>
@@ -31775,7 +31798,7 @@
     </row>
     <row r="689" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="2" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="B689" s="13">
         <v>3542</v>
@@ -31792,7 +31815,7 @@
     </row>
     <row r="690" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="2" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B690" s="13">
         <v>3543</v>
@@ -31826,7 +31849,7 @@
     </row>
     <row r="692" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="2" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B692" s="13">
         <v>1676</v>
@@ -31843,7 +31866,7 @@
     </row>
     <row r="693" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="2" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B693" s="13">
         <v>3518</v>
@@ -31860,7 +31883,7 @@
     </row>
     <row r="694" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="2" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B694" s="13">
         <v>3861</v>
@@ -31877,7 +31900,7 @@
     </row>
     <row r="695" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="8" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B695" s="8">
         <v>3849</v>
@@ -31894,6 +31917,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31910,25 +31952,6 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC9039B-D5DC-4194-8407-A32866F91CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B3B3E4-D16C-4099-86D8-F61A9B9D6B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4809,7 +4809,7 @@
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -5116,51 +5116,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5178,6 +5133,12 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5187,7 +5148,43 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5202,11 +5199,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5227,17 +5227,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5558,83 +5552,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="126"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="128"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127" t="s">
+      <c r="A3" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="128"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127" t="s">
+      <c r="A4" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="128"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="111"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="128"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="128"/>
+      <c r="A6" s="108"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="132"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="117"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="125"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="120"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -7320,20 +7314,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="102"/>
-      <c r="B109" s="103"/>
-      <c r="C109" s="103"/>
-      <c r="D109" s="104"/>
-      <c r="E109" s="105"/>
+      <c r="A109" s="121"/>
+      <c r="B109" s="109"/>
+      <c r="C109" s="109"/>
+      <c r="D109" s="110"/>
+      <c r="E109" s="117"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="118" t="s">
+      <c r="A110" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="112"/>
-      <c r="C110" s="112"/>
-      <c r="D110" s="112"/>
-      <c r="E110" s="113"/>
+      <c r="B110" s="119"/>
+      <c r="C110" s="119"/>
+      <c r="D110" s="119"/>
+      <c r="E110" s="120"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7625,20 +7619,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="102"/>
-      <c r="B128" s="103"/>
-      <c r="C128" s="103"/>
-      <c r="D128" s="104"/>
-      <c r="E128" s="105"/>
+      <c r="A128" s="121"/>
+      <c r="B128" s="109"/>
+      <c r="C128" s="109"/>
+      <c r="D128" s="110"/>
+      <c r="E128" s="117"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="118" t="s">
+      <c r="A129" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="112"/>
-      <c r="C129" s="112"/>
-      <c r="D129" s="112"/>
-      <c r="E129" s="113"/>
+      <c r="B129" s="119"/>
+      <c r="C129" s="119"/>
+      <c r="D129" s="119"/>
+      <c r="E129" s="120"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7794,20 +7788,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="102"/>
-      <c r="B139" s="103"/>
-      <c r="C139" s="103"/>
-      <c r="D139" s="104"/>
-      <c r="E139" s="105"/>
+      <c r="A139" s="121"/>
+      <c r="B139" s="109"/>
+      <c r="C139" s="109"/>
+      <c r="D139" s="110"/>
+      <c r="E139" s="117"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="119" t="s">
+      <c r="A140" s="126" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="112"/>
-      <c r="C140" s="112"/>
-      <c r="D140" s="112"/>
-      <c r="E140" s="120"/>
+      <c r="B140" s="119"/>
+      <c r="C140" s="119"/>
+      <c r="D140" s="119"/>
+      <c r="E140" s="127"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -9051,20 +9045,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="102"/>
-      <c r="B214" s="103"/>
-      <c r="C214" s="103"/>
-      <c r="D214" s="104"/>
-      <c r="E214" s="105"/>
+      <c r="A214" s="121"/>
+      <c r="B214" s="109"/>
+      <c r="C214" s="109"/>
+      <c r="D214" s="110"/>
+      <c r="E214" s="117"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="118" t="s">
+      <c r="A215" s="122" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="112"/>
-      <c r="C215" s="112"/>
-      <c r="D215" s="112"/>
-      <c r="E215" s="113"/>
+      <c r="B215" s="119"/>
+      <c r="C215" s="119"/>
+      <c r="D215" s="119"/>
+      <c r="E215" s="120"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -9911,7 +9905,7 @@
         <v>84</v>
       </c>
       <c r="E265" s="50">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="266" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -9928,7 +9922,7 @@
         <v>49</v>
       </c>
       <c r="E266" s="40">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="267" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10272,20 +10266,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="114"/>
-      <c r="B287" s="103"/>
-      <c r="C287" s="103"/>
-      <c r="D287" s="104"/>
-      <c r="E287" s="105"/>
+      <c r="A287" s="116"/>
+      <c r="B287" s="109"/>
+      <c r="C287" s="109"/>
+      <c r="D287" s="110"/>
+      <c r="E287" s="117"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="118" t="s">
+      <c r="A288" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="112"/>
-      <c r="C288" s="112"/>
-      <c r="D288" s="112"/>
-      <c r="E288" s="113"/>
+      <c r="B288" s="119"/>
+      <c r="C288" s="119"/>
+      <c r="D288" s="119"/>
+      <c r="E288" s="120"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -11850,20 +11844,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="114"/>
-      <c r="B381" s="103"/>
-      <c r="C381" s="103"/>
-      <c r="D381" s="104"/>
-      <c r="E381" s="105"/>
+      <c r="A381" s="116"/>
+      <c r="B381" s="109"/>
+      <c r="C381" s="109"/>
+      <c r="D381" s="110"/>
+      <c r="E381" s="117"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="111" t="s">
+      <c r="A382" s="118" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="112"/>
-      <c r="C382" s="112"/>
-      <c r="D382" s="112"/>
-      <c r="E382" s="113"/>
+      <c r="B382" s="119"/>
+      <c r="C382" s="119"/>
+      <c r="D382" s="119"/>
+      <c r="E382" s="120"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12517,13 +12511,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="111" t="s">
+      <c r="A422" s="118" t="s">
         <v>1302</v>
       </c>
-      <c r="B422" s="112"/>
-      <c r="C422" s="112"/>
-      <c r="D422" s="112"/>
-      <c r="E422" s="113"/>
+      <c r="B422" s="119"/>
+      <c r="C422" s="119"/>
+      <c r="D422" s="119"/>
+      <c r="E422" s="120"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -14460,20 +14454,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="114"/>
-      <c r="B537" s="103"/>
-      <c r="C537" s="103"/>
-      <c r="D537" s="104"/>
-      <c r="E537" s="105"/>
+      <c r="A537" s="116"/>
+      <c r="B537" s="109"/>
+      <c r="C537" s="109"/>
+      <c r="D537" s="110"/>
+      <c r="E537" s="117"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="111" t="s">
+      <c r="A538" s="118" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="112"/>
-      <c r="C538" s="112"/>
-      <c r="D538" s="112"/>
-      <c r="E538" s="113"/>
+      <c r="B538" s="119"/>
+      <c r="C538" s="119"/>
+      <c r="D538" s="119"/>
+      <c r="E538" s="120"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14776,7 +14770,7 @@
         <v>50</v>
       </c>
       <c r="E556" s="40">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="557" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -14831,20 +14825,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="114"/>
-      <c r="B560" s="103"/>
-      <c r="C560" s="103"/>
-      <c r="D560" s="104"/>
-      <c r="E560" s="105"/>
+      <c r="A560" s="116"/>
+      <c r="B560" s="109"/>
+      <c r="C560" s="109"/>
+      <c r="D560" s="110"/>
+      <c r="E560" s="117"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="111" t="s">
+      <c r="A561" s="118" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="112"/>
-      <c r="C561" s="112"/>
-      <c r="D561" s="112"/>
-      <c r="E561" s="113"/>
+      <c r="B561" s="119"/>
+      <c r="C561" s="119"/>
+      <c r="D561" s="119"/>
+      <c r="E561" s="120"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15440,20 +15434,20 @@
       </c>
     </row>
     <row r="597" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="106"/>
-      <c r="B597" s="107"/>
-      <c r="C597" s="107"/>
-      <c r="D597" s="107"/>
-      <c r="E597" s="107"/>
+      <c r="A597" s="128"/>
+      <c r="B597" s="129"/>
+      <c r="C597" s="129"/>
+      <c r="D597" s="129"/>
+      <c r="E597" s="129"/>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="111" t="s">
+      <c r="A598" s="118" t="s">
         <v>370</v>
       </c>
-      <c r="B598" s="112"/>
-      <c r="C598" s="112"/>
-      <c r="D598" s="112"/>
-      <c r="E598" s="113"/>
+      <c r="B598" s="119"/>
+      <c r="C598" s="119"/>
+      <c r="D598" s="119"/>
+      <c r="E598" s="120"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="66" t="s">
@@ -17446,20 +17440,20 @@
       </c>
     </row>
     <row r="716" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A716" s="114"/>
-      <c r="B716" s="103"/>
-      <c r="C716" s="103"/>
-      <c r="D716" s="104"/>
-      <c r="E716" s="105"/>
+      <c r="A716" s="116"/>
+      <c r="B716" s="109"/>
+      <c r="C716" s="109"/>
+      <c r="D716" s="110"/>
+      <c r="E716" s="117"/>
     </row>
     <row r="717" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="111" t="s">
+      <c r="A717" s="118" t="s">
         <v>420</v>
       </c>
-      <c r="B717" s="112"/>
-      <c r="C717" s="112"/>
-      <c r="D717" s="112"/>
-      <c r="E717" s="113"/>
+      <c r="B717" s="119"/>
+      <c r="C717" s="119"/>
+      <c r="D717" s="119"/>
+      <c r="E717" s="120"/>
     </row>
     <row r="718" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="66" t="s">
@@ -17637,13 +17631,13 @@
       <c r="E728" s="61"/>
     </row>
     <row r="729" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A729" s="111" t="s">
+      <c r="A729" s="118" t="s">
         <v>1303</v>
       </c>
-      <c r="B729" s="112"/>
-      <c r="C729" s="112"/>
-      <c r="D729" s="112"/>
-      <c r="E729" s="113"/>
+      <c r="B729" s="119"/>
+      <c r="C729" s="119"/>
+      <c r="D729" s="119"/>
+      <c r="E729" s="120"/>
     </row>
     <row r="730" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="72" t="s">
@@ -17765,20 +17759,20 @@
       </c>
     </row>
     <row r="737" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A737" s="102"/>
-      <c r="B737" s="103"/>
-      <c r="C737" s="103"/>
-      <c r="D737" s="104"/>
-      <c r="E737" s="105"/>
+      <c r="A737" s="121"/>
+      <c r="B737" s="109"/>
+      <c r="C737" s="109"/>
+      <c r="D737" s="110"/>
+      <c r="E737" s="117"/>
     </row>
     <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="111" t="s">
+      <c r="A738" s="118" t="s">
         <v>421</v>
       </c>
-      <c r="B738" s="112"/>
-      <c r="C738" s="112"/>
-      <c r="D738" s="112"/>
-      <c r="E738" s="113"/>
+      <c r="B738" s="119"/>
+      <c r="C738" s="119"/>
+      <c r="D738" s="119"/>
+      <c r="E738" s="120"/>
     </row>
     <row r="739" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A739" s="66" t="s">
@@ -17932,20 +17926,20 @@
       </c>
     </row>
     <row r="748" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A748" s="102"/>
-      <c r="B748" s="103"/>
-      <c r="C748" s="103"/>
-      <c r="D748" s="104"/>
-      <c r="E748" s="105"/>
+      <c r="A748" s="121"/>
+      <c r="B748" s="109"/>
+      <c r="C748" s="109"/>
+      <c r="D748" s="110"/>
+      <c r="E748" s="117"/>
     </row>
     <row r="749" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="111" t="s">
+      <c r="A749" s="118" t="s">
         <v>1301</v>
       </c>
-      <c r="B749" s="112"/>
-      <c r="C749" s="112"/>
-      <c r="D749" s="112"/>
-      <c r="E749" s="113"/>
+      <c r="B749" s="119"/>
+      <c r="C749" s="119"/>
+      <c r="D749" s="119"/>
+      <c r="E749" s="120"/>
     </row>
     <row r="750" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A750" s="66" t="s">
@@ -18375,13 +18369,13 @@
       <c r="E774" s="98"/>
     </row>
     <row r="775" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A775" s="108" t="s">
+      <c r="A775" s="130" t="s">
         <v>1287</v>
       </c>
-      <c r="B775" s="109"/>
-      <c r="C775" s="109"/>
-      <c r="D775" s="109"/>
-      <c r="E775" s="110"/>
+      <c r="B775" s="131"/>
+      <c r="C775" s="131"/>
+      <c r="D775" s="131"/>
+      <c r="E775" s="132"/>
     </row>
     <row r="776" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="66" t="s">
@@ -20186,16 +20180,16 @@
       </c>
     </row>
     <row r="882" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A882" s="151" t="s">
+      <c r="A882" s="96" t="s">
         <v>1336</v>
       </c>
-      <c r="B882" s="151" t="s">
+      <c r="B882" s="96" t="s">
         <v>1257</v>
       </c>
-      <c r="C882" s="152">
+      <c r="C882" s="97">
         <v>4581</v>
       </c>
-      <c r="D882" s="151" t="s">
+      <c r="D882" s="96" t="s">
         <v>15</v>
       </c>
       <c r="E882" s="48">
@@ -20343,13 +20337,13 @@
       <c r="E892" s="100"/>
     </row>
     <row r="893" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A893" s="121" t="s">
+      <c r="A893" s="102" t="s">
         <v>1288</v>
       </c>
-      <c r="B893" s="122"/>
-      <c r="C893" s="122"/>
-      <c r="D893" s="122"/>
-      <c r="E893" s="123"/>
+      <c r="B893" s="103"/>
+      <c r="C893" s="103"/>
+      <c r="D893" s="103"/>
+      <c r="E893" s="104"/>
     </row>
     <row r="894" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="87" t="s">
@@ -20622,6 +20616,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A737:E737"/>
+    <mergeCell ref="A597:E597"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A775:E775"/>
+    <mergeCell ref="A729:E729"/>
+    <mergeCell ref="A748:E748"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A538:E538"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A422:E422"/>
+    <mergeCell ref="A382:E382"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A215:E215"/>
     <mergeCell ref="A893:E893"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
@@ -20638,27 +20653,6 @@
     <mergeCell ref="A560:E560"/>
     <mergeCell ref="A716:E716"/>
     <mergeCell ref="A288:E288"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A538:E538"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A422:E422"/>
-    <mergeCell ref="A382:E382"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A381:E381"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A215:E215"/>
-    <mergeCell ref="A737:E737"/>
-    <mergeCell ref="A597:E597"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A775:E775"/>
-    <mergeCell ref="A729:E729"/>
-    <mergeCell ref="A748:E748"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20698,78 +20692,78 @@
       <c r="A2" s="148" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="139"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="138"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="150" t="s">
+      <c r="A3" s="137" t="s">
         <v>485</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="139"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="138"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="149" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="139"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="138"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="137" t="s">
         <v>487</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="139"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="138"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="135"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="139"/>
+      <c r="B6" s="134"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="138"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="135"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="139"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="138"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="139"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="138"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="139"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="138"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="140" t="s">
+      <c r="A10" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="120"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22492,19 +22486,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="134"/>
-      <c r="B112" s="135"/>
-      <c r="C112" s="136"/>
-      <c r="D112" s="137"/>
+      <c r="A112" s="133"/>
+      <c r="B112" s="134"/>
+      <c r="C112" s="135"/>
+      <c r="D112" s="136"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="149" t="s">
+      <c r="A113" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="112"/>
-      <c r="C113" s="112"/>
-      <c r="D113" s="120"/>
+      <c r="B113" s="119"/>
+      <c r="C113" s="119"/>
+      <c r="D113" s="127"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22797,19 +22791,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="134"/>
-      <c r="B131" s="135"/>
-      <c r="C131" s="136"/>
-      <c r="D131" s="137"/>
+      <c r="A131" s="133"/>
+      <c r="B131" s="134"/>
+      <c r="C131" s="135"/>
+      <c r="D131" s="136"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="149" t="s">
+      <c r="A132" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="112"/>
-      <c r="C132" s="112"/>
-      <c r="D132" s="120"/>
+      <c r="B132" s="119"/>
+      <c r="C132" s="119"/>
+      <c r="D132" s="127"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22983,19 +22977,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="134"/>
-      <c r="B143" s="135"/>
-      <c r="C143" s="136"/>
-      <c r="D143" s="137"/>
+      <c r="A143" s="133"/>
+      <c r="B143" s="134"/>
+      <c r="C143" s="135"/>
+      <c r="D143" s="136"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="149" t="s">
+      <c r="A144" s="140" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="112"/>
-      <c r="C144" s="112"/>
-      <c r="D144" s="120"/>
+      <c r="B144" s="119"/>
+      <c r="C144" s="119"/>
+      <c r="D144" s="127"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23628,19 +23622,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="134"/>
-      <c r="B182" s="135"/>
-      <c r="C182" s="136"/>
-      <c r="D182" s="137"/>
+      <c r="A182" s="133"/>
+      <c r="B182" s="134"/>
+      <c r="C182" s="135"/>
+      <c r="D182" s="136"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="133" t="s">
+      <c r="A183" s="139" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="112"/>
-      <c r="C183" s="112"/>
-      <c r="D183" s="112"/>
+      <c r="B183" s="119"/>
+      <c r="C183" s="119"/>
+      <c r="D183" s="119"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24502,19 +24496,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="134"/>
-      <c r="B241" s="135"/>
-      <c r="C241" s="136"/>
-      <c r="D241" s="137"/>
+      <c r="A241" s="133"/>
+      <c r="B241" s="134"/>
+      <c r="C241" s="135"/>
+      <c r="D241" s="136"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="133" t="s">
+      <c r="A242" s="139" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="112"/>
-      <c r="C242" s="112"/>
-      <c r="D242" s="112"/>
+      <c r="B242" s="119"/>
+      <c r="C242" s="119"/>
+      <c r="D242" s="119"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25735,21 +25729,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="134"/>
-      <c r="B324" s="135"/>
-      <c r="C324" s="136"/>
-      <c r="D324" s="137"/>
+      <c r="A324" s="133"/>
+      <c r="B324" s="134"/>
+      <c r="C324" s="135"/>
+      <c r="D324" s="136"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="133" t="s">
+      <c r="A325" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="112"/>
-      <c r="C325" s="112"/>
-      <c r="D325" s="112"/>
+      <c r="B325" s="119"/>
+      <c r="C325" s="119"/>
+      <c r="D325" s="119"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26246,19 +26240,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="134"/>
-      <c r="B355" s="135"/>
-      <c r="C355" s="136"/>
-      <c r="D355" s="137"/>
+      <c r="A355" s="133"/>
+      <c r="B355" s="134"/>
+      <c r="C355" s="135"/>
+      <c r="D355" s="136"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="133" t="s">
+      <c r="A356" s="139" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="112"/>
-      <c r="C356" s="112"/>
-      <c r="D356" s="112"/>
+      <c r="B356" s="119"/>
+      <c r="C356" s="119"/>
+      <c r="D356" s="119"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28013,19 +28007,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="134"/>
-      <c r="B460" s="135"/>
-      <c r="C460" s="136"/>
-      <c r="D460" s="137"/>
+      <c r="A460" s="133"/>
+      <c r="B460" s="134"/>
+      <c r="C460" s="135"/>
+      <c r="D460" s="136"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="133" t="s">
+      <c r="A461" s="139" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="112"/>
-      <c r="C461" s="112"/>
-      <c r="D461" s="112"/>
+      <c r="B461" s="119"/>
+      <c r="C461" s="119"/>
+      <c r="D461" s="119"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28318,19 +28312,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="134"/>
-      <c r="B479" s="135"/>
-      <c r="C479" s="136"/>
-      <c r="D479" s="137"/>
+      <c r="A479" s="133"/>
+      <c r="B479" s="134"/>
+      <c r="C479" s="135"/>
+      <c r="D479" s="136"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="133" t="s">
+      <c r="A480" s="139" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="112"/>
-      <c r="C480" s="112"/>
-      <c r="D480" s="112"/>
+      <c r="B480" s="119"/>
+      <c r="C480" s="119"/>
+      <c r="D480" s="119"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28759,19 +28753,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="134"/>
-      <c r="B506" s="135"/>
-      <c r="C506" s="136"/>
-      <c r="D506" s="137"/>
+      <c r="A506" s="133"/>
+      <c r="B506" s="134"/>
+      <c r="C506" s="135"/>
+      <c r="D506" s="136"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="133" t="s">
+      <c r="A507" s="139" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="112"/>
-      <c r="C507" s="112"/>
-      <c r="D507" s="112"/>
+      <c r="B507" s="119"/>
+      <c r="C507" s="119"/>
+      <c r="D507" s="119"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30286,19 +30280,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="134"/>
-      <c r="B597" s="135"/>
-      <c r="C597" s="136"/>
-      <c r="D597" s="137"/>
+      <c r="A597" s="133"/>
+      <c r="B597" s="134"/>
+      <c r="C597" s="135"/>
+      <c r="D597" s="136"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="133" t="s">
+      <c r="A598" s="139" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="112"/>
-      <c r="C598" s="112"/>
-      <c r="D598" s="112"/>
+      <c r="B598" s="119"/>
+      <c r="C598" s="119"/>
+      <c r="D598" s="119"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30438,20 +30432,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="134"/>
-      <c r="B607" s="135"/>
-      <c r="C607" s="136"/>
-      <c r="D607" s="137"/>
+      <c r="A607" s="133"/>
+      <c r="B607" s="134"/>
+      <c r="C607" s="135"/>
+      <c r="D607" s="136"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="133" t="s">
+      <c r="A608" s="139" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="112"/>
-      <c r="C608" s="112"/>
-      <c r="D608" s="112"/>
+      <c r="B608" s="119"/>
+      <c r="C608" s="119"/>
+      <c r="D608" s="119"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30540,19 +30534,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="134"/>
-      <c r="B614" s="135"/>
-      <c r="C614" s="136"/>
-      <c r="D614" s="137"/>
+      <c r="A614" s="133"/>
+      <c r="B614" s="134"/>
+      <c r="C614" s="135"/>
+      <c r="D614" s="136"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="133" t="s">
+      <c r="A615" s="139" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="112"/>
-      <c r="C615" s="112"/>
-      <c r="D615" s="112"/>
+      <c r="B615" s="119"/>
+      <c r="C615" s="119"/>
+      <c r="D615" s="119"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31917,25 +31911,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31952,6 +31927,25 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B3B3E4-D16C-4099-86D8-F61A9B9D6B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998F3869-57AC-4AF0-BC92-C075C4C86F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5116,6 +5116,51 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5133,12 +5178,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5148,43 +5187,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5199,14 +5202,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5227,10 +5227,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5552,83 +5552,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="126"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="128"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="111"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="128"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="111"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="128"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="128"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="108"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="111"/>
+      <c r="A6" s="127"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="128"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="114"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="125"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="117"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="122" t="s">
+      <c r="A9" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="120"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -7314,20 +7314,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="121"/>
-      <c r="B109" s="109"/>
-      <c r="C109" s="109"/>
-      <c r="D109" s="110"/>
-      <c r="E109" s="117"/>
+      <c r="A109" s="102"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="103"/>
+      <c r="D109" s="104"/>
+      <c r="E109" s="105"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="122" t="s">
+      <c r="A110" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="119"/>
-      <c r="C110" s="119"/>
-      <c r="D110" s="119"/>
-      <c r="E110" s="120"/>
+      <c r="B110" s="112"/>
+      <c r="C110" s="112"/>
+      <c r="D110" s="112"/>
+      <c r="E110" s="113"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7360,7 +7360,7 @@
         <v>34</v>
       </c>
       <c r="E112" s="40">
-        <v>162</v>
+        <v>144</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7377,7 +7377,7 @@
         <v>20</v>
       </c>
       <c r="E113" s="40">
-        <v>34.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7394,7 +7394,7 @@
         <v>34</v>
       </c>
       <c r="E114" s="40">
-        <v>229</v>
+        <v>190</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7411,7 +7411,7 @@
         <v>20</v>
       </c>
       <c r="E115" s="40">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7619,20 +7619,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="121"/>
-      <c r="B128" s="109"/>
-      <c r="C128" s="109"/>
-      <c r="D128" s="110"/>
-      <c r="E128" s="117"/>
+      <c r="A128" s="102"/>
+      <c r="B128" s="103"/>
+      <c r="C128" s="103"/>
+      <c r="D128" s="104"/>
+      <c r="E128" s="105"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="122" t="s">
+      <c r="A129" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="119"/>
-      <c r="C129" s="119"/>
-      <c r="D129" s="119"/>
-      <c r="E129" s="120"/>
+      <c r="B129" s="112"/>
+      <c r="C129" s="112"/>
+      <c r="D129" s="112"/>
+      <c r="E129" s="113"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7788,20 +7788,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="121"/>
-      <c r="B139" s="109"/>
-      <c r="C139" s="109"/>
-      <c r="D139" s="110"/>
-      <c r="E139" s="117"/>
+      <c r="A139" s="102"/>
+      <c r="B139" s="103"/>
+      <c r="C139" s="103"/>
+      <c r="D139" s="104"/>
+      <c r="E139" s="105"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="126" t="s">
+      <c r="A140" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="119"/>
-      <c r="C140" s="119"/>
-      <c r="D140" s="119"/>
-      <c r="E140" s="127"/>
+      <c r="B140" s="112"/>
+      <c r="C140" s="112"/>
+      <c r="D140" s="112"/>
+      <c r="E140" s="120"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -9045,20 +9045,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="121"/>
-      <c r="B214" s="109"/>
-      <c r="C214" s="109"/>
-      <c r="D214" s="110"/>
-      <c r="E214" s="117"/>
+      <c r="A214" s="102"/>
+      <c r="B214" s="103"/>
+      <c r="C214" s="103"/>
+      <c r="D214" s="104"/>
+      <c r="E214" s="105"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="122" t="s">
+      <c r="A215" s="118" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="119"/>
-      <c r="C215" s="119"/>
-      <c r="D215" s="119"/>
-      <c r="E215" s="120"/>
+      <c r="B215" s="112"/>
+      <c r="C215" s="112"/>
+      <c r="D215" s="112"/>
+      <c r="E215" s="113"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -10266,20 +10266,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="116"/>
-      <c r="B287" s="109"/>
-      <c r="C287" s="109"/>
-      <c r="D287" s="110"/>
-      <c r="E287" s="117"/>
+      <c r="A287" s="114"/>
+      <c r="B287" s="103"/>
+      <c r="C287" s="103"/>
+      <c r="D287" s="104"/>
+      <c r="E287" s="105"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="122" t="s">
+      <c r="A288" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="119"/>
-      <c r="C288" s="119"/>
-      <c r="D288" s="119"/>
-      <c r="E288" s="120"/>
+      <c r="B288" s="112"/>
+      <c r="C288" s="112"/>
+      <c r="D288" s="112"/>
+      <c r="E288" s="113"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -11844,20 +11844,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="116"/>
-      <c r="B381" s="109"/>
-      <c r="C381" s="109"/>
-      <c r="D381" s="110"/>
-      <c r="E381" s="117"/>
+      <c r="A381" s="114"/>
+      <c r="B381" s="103"/>
+      <c r="C381" s="103"/>
+      <c r="D381" s="104"/>
+      <c r="E381" s="105"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="118" t="s">
+      <c r="A382" s="111" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="119"/>
-      <c r="C382" s="119"/>
-      <c r="D382" s="119"/>
-      <c r="E382" s="120"/>
+      <c r="B382" s="112"/>
+      <c r="C382" s="112"/>
+      <c r="D382" s="112"/>
+      <c r="E382" s="113"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12511,13 +12511,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="118" t="s">
+      <c r="A422" s="111" t="s">
         <v>1302</v>
       </c>
-      <c r="B422" s="119"/>
-      <c r="C422" s="119"/>
-      <c r="D422" s="119"/>
-      <c r="E422" s="120"/>
+      <c r="B422" s="112"/>
+      <c r="C422" s="112"/>
+      <c r="D422" s="112"/>
+      <c r="E422" s="113"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -14454,20 +14454,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="116"/>
-      <c r="B537" s="109"/>
-      <c r="C537" s="109"/>
-      <c r="D537" s="110"/>
-      <c r="E537" s="117"/>
+      <c r="A537" s="114"/>
+      <c r="B537" s="103"/>
+      <c r="C537" s="103"/>
+      <c r="D537" s="104"/>
+      <c r="E537" s="105"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="118" t="s">
+      <c r="A538" s="111" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="119"/>
-      <c r="C538" s="119"/>
-      <c r="D538" s="119"/>
-      <c r="E538" s="120"/>
+      <c r="B538" s="112"/>
+      <c r="C538" s="112"/>
+      <c r="D538" s="112"/>
+      <c r="E538" s="113"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14825,20 +14825,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="116"/>
-      <c r="B560" s="109"/>
-      <c r="C560" s="109"/>
-      <c r="D560" s="110"/>
-      <c r="E560" s="117"/>
+      <c r="A560" s="114"/>
+      <c r="B560" s="103"/>
+      <c r="C560" s="103"/>
+      <c r="D560" s="104"/>
+      <c r="E560" s="105"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="118" t="s">
+      <c r="A561" s="111" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="119"/>
-      <c r="C561" s="119"/>
-      <c r="D561" s="119"/>
-      <c r="E561" s="120"/>
+      <c r="B561" s="112"/>
+      <c r="C561" s="112"/>
+      <c r="D561" s="112"/>
+      <c r="E561" s="113"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15434,20 +15434,20 @@
       </c>
     </row>
     <row r="597" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="128"/>
-      <c r="B597" s="129"/>
-      <c r="C597" s="129"/>
-      <c r="D597" s="129"/>
-      <c r="E597" s="129"/>
+      <c r="A597" s="106"/>
+      <c r="B597" s="107"/>
+      <c r="C597" s="107"/>
+      <c r="D597" s="107"/>
+      <c r="E597" s="107"/>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="118" t="s">
+      <c r="A598" s="111" t="s">
         <v>370</v>
       </c>
-      <c r="B598" s="119"/>
-      <c r="C598" s="119"/>
-      <c r="D598" s="119"/>
-      <c r="E598" s="120"/>
+      <c r="B598" s="112"/>
+      <c r="C598" s="112"/>
+      <c r="D598" s="112"/>
+      <c r="E598" s="113"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="66" t="s">
@@ -17440,20 +17440,20 @@
       </c>
     </row>
     <row r="716" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A716" s="116"/>
-      <c r="B716" s="109"/>
-      <c r="C716" s="109"/>
-      <c r="D716" s="110"/>
-      <c r="E716" s="117"/>
+      <c r="A716" s="114"/>
+      <c r="B716" s="103"/>
+      <c r="C716" s="103"/>
+      <c r="D716" s="104"/>
+      <c r="E716" s="105"/>
     </row>
     <row r="717" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="118" t="s">
+      <c r="A717" s="111" t="s">
         <v>420</v>
       </c>
-      <c r="B717" s="119"/>
-      <c r="C717" s="119"/>
-      <c r="D717" s="119"/>
-      <c r="E717" s="120"/>
+      <c r="B717" s="112"/>
+      <c r="C717" s="112"/>
+      <c r="D717" s="112"/>
+      <c r="E717" s="113"/>
     </row>
     <row r="718" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="66" t="s">
@@ -17631,13 +17631,13 @@
       <c r="E728" s="61"/>
     </row>
     <row r="729" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A729" s="118" t="s">
+      <c r="A729" s="111" t="s">
         <v>1303</v>
       </c>
-      <c r="B729" s="119"/>
-      <c r="C729" s="119"/>
-      <c r="D729" s="119"/>
-      <c r="E729" s="120"/>
+      <c r="B729" s="112"/>
+      <c r="C729" s="112"/>
+      <c r="D729" s="112"/>
+      <c r="E729" s="113"/>
     </row>
     <row r="730" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="72" t="s">
@@ -17759,20 +17759,20 @@
       </c>
     </row>
     <row r="737" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A737" s="121"/>
-      <c r="B737" s="109"/>
-      <c r="C737" s="109"/>
-      <c r="D737" s="110"/>
-      <c r="E737" s="117"/>
+      <c r="A737" s="102"/>
+      <c r="B737" s="103"/>
+      <c r="C737" s="103"/>
+      <c r="D737" s="104"/>
+      <c r="E737" s="105"/>
     </row>
     <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="118" t="s">
+      <c r="A738" s="111" t="s">
         <v>421</v>
       </c>
-      <c r="B738" s="119"/>
-      <c r="C738" s="119"/>
-      <c r="D738" s="119"/>
-      <c r="E738" s="120"/>
+      <c r="B738" s="112"/>
+      <c r="C738" s="112"/>
+      <c r="D738" s="112"/>
+      <c r="E738" s="113"/>
     </row>
     <row r="739" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A739" s="66" t="s">
@@ -17926,20 +17926,20 @@
       </c>
     </row>
     <row r="748" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A748" s="121"/>
-      <c r="B748" s="109"/>
-      <c r="C748" s="109"/>
-      <c r="D748" s="110"/>
-      <c r="E748" s="117"/>
+      <c r="A748" s="102"/>
+      <c r="B748" s="103"/>
+      <c r="C748" s="103"/>
+      <c r="D748" s="104"/>
+      <c r="E748" s="105"/>
     </row>
     <row r="749" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="118" t="s">
+      <c r="A749" s="111" t="s">
         <v>1301</v>
       </c>
-      <c r="B749" s="119"/>
-      <c r="C749" s="119"/>
-      <c r="D749" s="119"/>
-      <c r="E749" s="120"/>
+      <c r="B749" s="112"/>
+      <c r="C749" s="112"/>
+      <c r="D749" s="112"/>
+      <c r="E749" s="113"/>
     </row>
     <row r="750" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A750" s="66" t="s">
@@ -18369,13 +18369,13 @@
       <c r="E774" s="98"/>
     </row>
     <row r="775" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A775" s="130" t="s">
+      <c r="A775" s="108" t="s">
         <v>1287</v>
       </c>
-      <c r="B775" s="131"/>
-      <c r="C775" s="131"/>
-      <c r="D775" s="131"/>
-      <c r="E775" s="132"/>
+      <c r="B775" s="109"/>
+      <c r="C775" s="109"/>
+      <c r="D775" s="109"/>
+      <c r="E775" s="110"/>
     </row>
     <row r="776" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="66" t="s">
@@ -20337,13 +20337,13 @@
       <c r="E892" s="100"/>
     </row>
     <row r="893" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A893" s="102" t="s">
+      <c r="A893" s="121" t="s">
         <v>1288</v>
       </c>
-      <c r="B893" s="103"/>
-      <c r="C893" s="103"/>
-      <c r="D893" s="103"/>
-      <c r="E893" s="104"/>
+      <c r="B893" s="122"/>
+      <c r="C893" s="122"/>
+      <c r="D893" s="122"/>
+      <c r="E893" s="123"/>
     </row>
     <row r="894" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="87" t="s">
@@ -20616,27 +20616,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A737:E737"/>
-    <mergeCell ref="A597:E597"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A775:E775"/>
-    <mergeCell ref="A729:E729"/>
-    <mergeCell ref="A748:E748"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A538:E538"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A422:E422"/>
-    <mergeCell ref="A382:E382"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A381:E381"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A215:E215"/>
     <mergeCell ref="A893:E893"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
@@ -20653,6 +20632,27 @@
     <mergeCell ref="A560:E560"/>
     <mergeCell ref="A716:E716"/>
     <mergeCell ref="A288:E288"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A538:E538"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A422:E422"/>
+    <mergeCell ref="A382:E382"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A215:E215"/>
+    <mergeCell ref="A737:E737"/>
+    <mergeCell ref="A597:E597"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A775:E775"/>
+    <mergeCell ref="A729:E729"/>
+    <mergeCell ref="A748:E748"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20692,78 +20692,78 @@
       <c r="A2" s="148" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="138"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="139"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="150" t="s">
         <v>485</v>
       </c>
-      <c r="B3" s="134"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="138"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="139"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="149" t="s">
+      <c r="A4" s="138" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="138"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="139"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="150" t="s">
         <v>487</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="138"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="139"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="134"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="138"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="139"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="134"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="138"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="139"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="138"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="139"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="138"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="139"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="150" t="s">
+      <c r="A10" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22486,19 +22486,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="133"/>
-      <c r="B112" s="134"/>
-      <c r="C112" s="135"/>
-      <c r="D112" s="136"/>
+      <c r="A112" s="134"/>
+      <c r="B112" s="135"/>
+      <c r="C112" s="136"/>
+      <c r="D112" s="137"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="140" t="s">
+      <c r="A113" s="149" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="119"/>
-      <c r="C113" s="119"/>
-      <c r="D113" s="127"/>
+      <c r="B113" s="112"/>
+      <c r="C113" s="112"/>
+      <c r="D113" s="120"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22791,19 +22791,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="133"/>
-      <c r="B131" s="134"/>
-      <c r="C131" s="135"/>
-      <c r="D131" s="136"/>
+      <c r="A131" s="134"/>
+      <c r="B131" s="135"/>
+      <c r="C131" s="136"/>
+      <c r="D131" s="137"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="140" t="s">
+      <c r="A132" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="119"/>
-      <c r="C132" s="119"/>
-      <c r="D132" s="127"/>
+      <c r="B132" s="112"/>
+      <c r="C132" s="112"/>
+      <c r="D132" s="120"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22977,19 +22977,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="133"/>
-      <c r="B143" s="134"/>
-      <c r="C143" s="135"/>
-      <c r="D143" s="136"/>
+      <c r="A143" s="134"/>
+      <c r="B143" s="135"/>
+      <c r="C143" s="136"/>
+      <c r="D143" s="137"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="140" t="s">
+      <c r="A144" s="149" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="119"/>
-      <c r="C144" s="119"/>
-      <c r="D144" s="127"/>
+      <c r="B144" s="112"/>
+      <c r="C144" s="112"/>
+      <c r="D144" s="120"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23622,19 +23622,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="133"/>
-      <c r="B182" s="134"/>
-      <c r="C182" s="135"/>
-      <c r="D182" s="136"/>
+      <c r="A182" s="134"/>
+      <c r="B182" s="135"/>
+      <c r="C182" s="136"/>
+      <c r="D182" s="137"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="139" t="s">
+      <c r="A183" s="133" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="119"/>
-      <c r="C183" s="119"/>
-      <c r="D183" s="119"/>
+      <c r="B183" s="112"/>
+      <c r="C183" s="112"/>
+      <c r="D183" s="112"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24496,19 +24496,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="133"/>
-      <c r="B241" s="134"/>
-      <c r="C241" s="135"/>
-      <c r="D241" s="136"/>
+      <c r="A241" s="134"/>
+      <c r="B241" s="135"/>
+      <c r="C241" s="136"/>
+      <c r="D241" s="137"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="139" t="s">
+      <c r="A242" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="119"/>
-      <c r="C242" s="119"/>
-      <c r="D242" s="119"/>
+      <c r="B242" s="112"/>
+      <c r="C242" s="112"/>
+      <c r="D242" s="112"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25729,21 +25729,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="133"/>
-      <c r="B324" s="134"/>
-      <c r="C324" s="135"/>
-      <c r="D324" s="136"/>
+      <c r="A324" s="134"/>
+      <c r="B324" s="135"/>
+      <c r="C324" s="136"/>
+      <c r="D324" s="137"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="139" t="s">
+      <c r="A325" s="133" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="119"/>
-      <c r="C325" s="119"/>
-      <c r="D325" s="119"/>
+      <c r="B325" s="112"/>
+      <c r="C325" s="112"/>
+      <c r="D325" s="112"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26240,19 +26240,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="133"/>
-      <c r="B355" s="134"/>
-      <c r="C355" s="135"/>
-      <c r="D355" s="136"/>
+      <c r="A355" s="134"/>
+      <c r="B355" s="135"/>
+      <c r="C355" s="136"/>
+      <c r="D355" s="137"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="139" t="s">
+      <c r="A356" s="133" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="119"/>
-      <c r="C356" s="119"/>
-      <c r="D356" s="119"/>
+      <c r="B356" s="112"/>
+      <c r="C356" s="112"/>
+      <c r="D356" s="112"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28007,19 +28007,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="133"/>
-      <c r="B460" s="134"/>
-      <c r="C460" s="135"/>
-      <c r="D460" s="136"/>
+      <c r="A460" s="134"/>
+      <c r="B460" s="135"/>
+      <c r="C460" s="136"/>
+      <c r="D460" s="137"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="139" t="s">
+      <c r="A461" s="133" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="119"/>
-      <c r="C461" s="119"/>
-      <c r="D461" s="119"/>
+      <c r="B461" s="112"/>
+      <c r="C461" s="112"/>
+      <c r="D461" s="112"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28312,19 +28312,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="133"/>
-      <c r="B479" s="134"/>
-      <c r="C479" s="135"/>
-      <c r="D479" s="136"/>
+      <c r="A479" s="134"/>
+      <c r="B479" s="135"/>
+      <c r="C479" s="136"/>
+      <c r="D479" s="137"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="139" t="s">
+      <c r="A480" s="133" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="119"/>
-      <c r="C480" s="119"/>
-      <c r="D480" s="119"/>
+      <c r="B480" s="112"/>
+      <c r="C480" s="112"/>
+      <c r="D480" s="112"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28753,19 +28753,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="133"/>
-      <c r="B506" s="134"/>
-      <c r="C506" s="135"/>
-      <c r="D506" s="136"/>
+      <c r="A506" s="134"/>
+      <c r="B506" s="135"/>
+      <c r="C506" s="136"/>
+      <c r="D506" s="137"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="139" t="s">
+      <c r="A507" s="133" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="119"/>
-      <c r="C507" s="119"/>
-      <c r="D507" s="119"/>
+      <c r="B507" s="112"/>
+      <c r="C507" s="112"/>
+      <c r="D507" s="112"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30280,19 +30280,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="133"/>
-      <c r="B597" s="134"/>
-      <c r="C597" s="135"/>
-      <c r="D597" s="136"/>
+      <c r="A597" s="134"/>
+      <c r="B597" s="135"/>
+      <c r="C597" s="136"/>
+      <c r="D597" s="137"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="139" t="s">
+      <c r="A598" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="119"/>
-      <c r="C598" s="119"/>
-      <c r="D598" s="119"/>
+      <c r="B598" s="112"/>
+      <c r="C598" s="112"/>
+      <c r="D598" s="112"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30432,20 +30432,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="133"/>
-      <c r="B607" s="134"/>
-      <c r="C607" s="135"/>
-      <c r="D607" s="136"/>
+      <c r="A607" s="134"/>
+      <c r="B607" s="135"/>
+      <c r="C607" s="136"/>
+      <c r="D607" s="137"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="139" t="s">
+      <c r="A608" s="133" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="119"/>
-      <c r="C608" s="119"/>
-      <c r="D608" s="119"/>
+      <c r="B608" s="112"/>
+      <c r="C608" s="112"/>
+      <c r="D608" s="112"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30534,19 +30534,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="133"/>
-      <c r="B614" s="134"/>
-      <c r="C614" s="135"/>
-      <c r="D614" s="136"/>
+      <c r="A614" s="134"/>
+      <c r="B614" s="135"/>
+      <c r="C614" s="136"/>
+      <c r="D614" s="137"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="139" t="s">
+      <c r="A615" s="133" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="119"/>
-      <c r="C615" s="119"/>
-      <c r="D615" s="119"/>
+      <c r="B615" s="112"/>
+      <c r="C615" s="112"/>
+      <c r="D615" s="112"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31911,6 +31911,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31927,25 +31946,6 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998F3869-57AC-4AF0-BC92-C075C4C86F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D192A961-F9B8-402F-87D4-FDE104B3ACB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="LISTA DE PRODUTOS T" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PRODUTOS B'!$A$1:$E$908</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PRODUTOS B'!$A$1:$E$909</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4024" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4027" uniqueCount="1337">
   <si>
     <t xml:space="preserve">    Tabela de Produtos e Preços</t>
   </si>
@@ -5116,51 +5116,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5178,6 +5133,12 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5187,7 +5148,43 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5202,11 +5199,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5227,10 +5227,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5539,7 +5539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R919"/>
+  <dimension ref="A1:R920"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62.1640625" style="64" bestFit="1" customWidth="1"/>
@@ -5552,83 +5552,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="126"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="128"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127" t="s">
+      <c r="A3" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="128"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127" t="s">
+      <c r="A4" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="128"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="111"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="128"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="128"/>
+      <c r="A6" s="108"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="132"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="117"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="125"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="120"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -7314,20 +7314,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="102"/>
-      <c r="B109" s="103"/>
-      <c r="C109" s="103"/>
-      <c r="D109" s="104"/>
-      <c r="E109" s="105"/>
+      <c r="A109" s="121"/>
+      <c r="B109" s="109"/>
+      <c r="C109" s="109"/>
+      <c r="D109" s="110"/>
+      <c r="E109" s="117"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="118" t="s">
+      <c r="A110" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="112"/>
-      <c r="C110" s="112"/>
-      <c r="D110" s="112"/>
-      <c r="E110" s="113"/>
+      <c r="B110" s="119"/>
+      <c r="C110" s="119"/>
+      <c r="D110" s="119"/>
+      <c r="E110" s="120"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7619,20 +7619,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="102"/>
-      <c r="B128" s="103"/>
-      <c r="C128" s="103"/>
-      <c r="D128" s="104"/>
-      <c r="E128" s="105"/>
+      <c r="A128" s="121"/>
+      <c r="B128" s="109"/>
+      <c r="C128" s="109"/>
+      <c r="D128" s="110"/>
+      <c r="E128" s="117"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="118" t="s">
+      <c r="A129" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="112"/>
-      <c r="C129" s="112"/>
-      <c r="D129" s="112"/>
-      <c r="E129" s="113"/>
+      <c r="B129" s="119"/>
+      <c r="C129" s="119"/>
+      <c r="D129" s="119"/>
+      <c r="E129" s="120"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7788,20 +7788,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="102"/>
-      <c r="B139" s="103"/>
-      <c r="C139" s="103"/>
-      <c r="D139" s="104"/>
-      <c r="E139" s="105"/>
+      <c r="A139" s="121"/>
+      <c r="B139" s="109"/>
+      <c r="C139" s="109"/>
+      <c r="D139" s="110"/>
+      <c r="E139" s="117"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="119" t="s">
+      <c r="A140" s="126" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="112"/>
-      <c r="C140" s="112"/>
-      <c r="D140" s="112"/>
-      <c r="E140" s="120"/>
+      <c r="B140" s="119"/>
+      <c r="C140" s="119"/>
+      <c r="D140" s="119"/>
+      <c r="E140" s="127"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -8063,7 +8063,7 @@
         <v>115</v>
       </c>
       <c r="B156" s="69" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C156" s="70">
         <v>2691</v>
@@ -8072,7 +8072,7 @@
         <v>84</v>
       </c>
       <c r="E156" s="40">
-        <v>156</v>
+        <v>225</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -8089,7 +8089,7 @@
         <v>49</v>
       </c>
       <c r="E157" s="40">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -8565,7 +8565,7 @@
         <v>34</v>
       </c>
       <c r="E185" s="40">
-        <v>725</v>
+        <v>900</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -8582,7 +8582,7 @@
         <v>34</v>
       </c>
       <c r="E186" s="40">
-        <v>580</v>
+        <v>720</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -8599,7 +8599,7 @@
         <v>49</v>
       </c>
       <c r="E187" s="40">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -9045,20 +9045,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="102"/>
-      <c r="B214" s="103"/>
-      <c r="C214" s="103"/>
-      <c r="D214" s="104"/>
-      <c r="E214" s="105"/>
+      <c r="A214" s="121"/>
+      <c r="B214" s="109"/>
+      <c r="C214" s="109"/>
+      <c r="D214" s="110"/>
+      <c r="E214" s="117"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="118" t="s">
+      <c r="A215" s="122" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="112"/>
-      <c r="C215" s="112"/>
-      <c r="D215" s="112"/>
-      <c r="E215" s="113"/>
+      <c r="B215" s="119"/>
+      <c r="C215" s="119"/>
+      <c r="D215" s="119"/>
+      <c r="E215" s="120"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -10266,20 +10266,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="114"/>
-      <c r="B287" s="103"/>
-      <c r="C287" s="103"/>
-      <c r="D287" s="104"/>
-      <c r="E287" s="105"/>
+      <c r="A287" s="116"/>
+      <c r="B287" s="109"/>
+      <c r="C287" s="109"/>
+      <c r="D287" s="110"/>
+      <c r="E287" s="117"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="118" t="s">
+      <c r="A288" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="112"/>
-      <c r="C288" s="112"/>
-      <c r="D288" s="112"/>
-      <c r="E288" s="113"/>
+      <c r="B288" s="119"/>
+      <c r="C288" s="119"/>
+      <c r="D288" s="119"/>
+      <c r="E288" s="120"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -11844,20 +11844,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="114"/>
-      <c r="B381" s="103"/>
-      <c r="C381" s="103"/>
-      <c r="D381" s="104"/>
-      <c r="E381" s="105"/>
+      <c r="A381" s="116"/>
+      <c r="B381" s="109"/>
+      <c r="C381" s="109"/>
+      <c r="D381" s="110"/>
+      <c r="E381" s="117"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="111" t="s">
+      <c r="A382" s="118" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="112"/>
-      <c r="C382" s="112"/>
-      <c r="D382" s="112"/>
-      <c r="E382" s="113"/>
+      <c r="B382" s="119"/>
+      <c r="C382" s="119"/>
+      <c r="D382" s="119"/>
+      <c r="E382" s="120"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12511,13 +12511,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="111" t="s">
+      <c r="A422" s="118" t="s">
         <v>1302</v>
       </c>
-      <c r="B422" s="112"/>
-      <c r="C422" s="112"/>
-      <c r="D422" s="112"/>
-      <c r="E422" s="113"/>
+      <c r="B422" s="119"/>
+      <c r="C422" s="119"/>
+      <c r="D422" s="119"/>
+      <c r="E422" s="120"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -13005,7 +13005,7 @@
         <v>34</v>
       </c>
       <c r="E451" s="40">
-        <v>87.5</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="452" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -13022,7 +13022,7 @@
         <v>84</v>
       </c>
       <c r="E452" s="40">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="453" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -14454,20 +14454,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="114"/>
-      <c r="B537" s="103"/>
-      <c r="C537" s="103"/>
-      <c r="D537" s="104"/>
-      <c r="E537" s="105"/>
+      <c r="A537" s="116"/>
+      <c r="B537" s="109"/>
+      <c r="C537" s="109"/>
+      <c r="D537" s="110"/>
+      <c r="E537" s="117"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="111" t="s">
+      <c r="A538" s="118" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="112"/>
-      <c r="C538" s="112"/>
-      <c r="D538" s="112"/>
-      <c r="E538" s="113"/>
+      <c r="B538" s="119"/>
+      <c r="C538" s="119"/>
+      <c r="D538" s="119"/>
+      <c r="E538" s="120"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14825,20 +14825,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="114"/>
-      <c r="B560" s="103"/>
-      <c r="C560" s="103"/>
-      <c r="D560" s="104"/>
-      <c r="E560" s="105"/>
+      <c r="A560" s="116"/>
+      <c r="B560" s="109"/>
+      <c r="C560" s="109"/>
+      <c r="D560" s="110"/>
+      <c r="E560" s="117"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="111" t="s">
+      <c r="A561" s="118" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="112"/>
-      <c r="C561" s="112"/>
-      <c r="D561" s="112"/>
-      <c r="E561" s="113"/>
+      <c r="B561" s="119"/>
+      <c r="C561" s="119"/>
+      <c r="D561" s="119"/>
+      <c r="E561" s="120"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15212,21 +15212,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="584" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="69" t="s">
         <v>363</v>
       </c>
       <c r="B584" s="69" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C584" s="70">
-        <v>2716</v>
+        <v>3417</v>
       </c>
       <c r="D584" s="69" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E584" s="40">
-        <v>295</v>
+        <v>350</v>
       </c>
     </row>
     <row r="585" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -15234,33 +15234,33 @@
         <v>363</v>
       </c>
       <c r="B585" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C585" s="70">
+        <v>2716</v>
+      </c>
+      <c r="D585" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="E585" s="40">
+        <v>317.5</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A586" s="69" t="s">
+        <v>363</v>
+      </c>
+      <c r="B586" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C585" s="70">
+      <c r="C586" s="70">
         <v>2478</v>
       </c>
-      <c r="D585" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E585" s="40">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="586" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A586" s="72" t="s">
-        <v>364</v>
-      </c>
-      <c r="B586" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C586" s="73">
-        <v>2606</v>
-      </c>
-      <c r="D586" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="E586" s="50">
-        <v>450</v>
+      <c r="D586" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E586" s="40">
+        <v>72</v>
       </c>
     </row>
     <row r="587" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -15268,16 +15268,16 @@
         <v>364</v>
       </c>
       <c r="B587" s="72" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="C587" s="73">
-        <v>2338</v>
+        <v>2606</v>
       </c>
       <c r="D587" s="72" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="E587" s="50">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row r="588" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -15285,217 +15285,217 @@
         <v>364</v>
       </c>
       <c r="B588" s="72" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="C588" s="73">
-        <v>2425</v>
+        <v>2338</v>
       </c>
       <c r="D588" s="72" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E588" s="50">
-        <v>91</v>
+        <v>600</v>
       </c>
     </row>
     <row r="589" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="72" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B589" s="72" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C589" s="73">
-        <v>2579</v>
+        <v>2425</v>
       </c>
       <c r="D589" s="72" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="E589" s="50">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="590" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="72" t="s">
+        <v>365</v>
+      </c>
+      <c r="B590" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C590" s="73">
+        <v>2579</v>
+      </c>
+      <c r="D590" s="72" t="s">
+        <v>84</v>
+      </c>
+      <c r="E590" s="50">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="591" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A591" s="72" t="s">
         <v>366</v>
       </c>
-      <c r="B590" s="72" t="s">
+      <c r="B591" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="C590" s="73">
+      <c r="C591" s="73">
         <v>2243</v>
       </c>
-      <c r="D590" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="E590" s="50">
+      <c r="D591" s="72" t="s">
+        <v>84</v>
+      </c>
+      <c r="E591" s="50">
         <v>500</v>
-      </c>
-    </row>
-    <row r="591" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A591" s="69" t="s">
-        <v>367</v>
-      </c>
-      <c r="B591" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="C591" s="70">
-        <v>4400</v>
-      </c>
-      <c r="D591" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E591" s="40">
-        <v>900</v>
       </c>
     </row>
     <row r="592" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="69" t="s">
         <v>367</v>
       </c>
-      <c r="B592" s="69">
-        <v>20</v>
+      <c r="B592" s="69" t="s">
+        <v>33</v>
       </c>
       <c r="C592" s="70">
-        <v>2680</v>
+        <v>4400</v>
       </c>
       <c r="D592" s="69" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E592" s="40">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="593" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="593" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="69" t="s">
         <v>367</v>
       </c>
-      <c r="B593" s="69" t="s">
-        <v>19</v>
+      <c r="B593" s="69">
+        <v>20</v>
       </c>
       <c r="C593" s="70">
-        <v>2676</v>
+        <v>2680</v>
       </c>
       <c r="D593" s="69" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="E593" s="40">
-        <v>182</v>
+        <v>720</v>
       </c>
     </row>
     <row r="594" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="69" t="s">
+        <v>367</v>
+      </c>
+      <c r="B594" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C594" s="70">
+        <v>2676</v>
+      </c>
+      <c r="D594" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="E594" s="40">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="595" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A595" s="69" t="s">
         <v>368</v>
       </c>
-      <c r="B594" s="69" t="s">
+      <c r="B595" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="C594" s="70">
+      <c r="C595" s="70">
         <v>571</v>
       </c>
-      <c r="D594" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E594" s="40">
+      <c r="D595" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E595" s="40">
         <v>525</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A595" s="75" t="s">
+    <row r="596" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A596" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="B595" s="75" t="s">
+      <c r="B596" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="C595" s="76">
+      <c r="C596" s="76">
         <v>2245</v>
       </c>
-      <c r="D595" s="75" t="s">
+      <c r="D596" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E595" s="44">
+      <c r="E596" s="44">
         <v>107</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A596" s="80" t="s">
+    <row r="597" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A597" s="80" t="s">
         <v>369</v>
       </c>
-      <c r="B596" s="80" t="s">
+      <c r="B597" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="C596" s="81">
+      <c r="C597" s="81">
         <v>3754</v>
       </c>
-      <c r="D596" s="80" t="s">
+      <c r="D597" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="E596" s="42">
+      <c r="E597" s="42">
         <v>450</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="106"/>
-      <c r="B597" s="107"/>
-      <c r="C597" s="107"/>
-      <c r="D597" s="107"/>
-      <c r="E597" s="107"/>
-    </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="111" t="s">
+      <c r="A598" s="128"/>
+      <c r="B598" s="129"/>
+      <c r="C598" s="129"/>
+      <c r="D598" s="129"/>
+      <c r="E598" s="129"/>
+    </row>
+    <row r="599" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A599" s="118" t="s">
         <v>370</v>
       </c>
-      <c r="B598" s="112"/>
-      <c r="C598" s="112"/>
-      <c r="D598" s="112"/>
-      <c r="E598" s="113"/>
-    </row>
-    <row r="599" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A599" s="66" t="s">
+      <c r="B599" s="119"/>
+      <c r="C599" s="119"/>
+      <c r="D599" s="119"/>
+      <c r="E599" s="120"/>
+    </row>
+    <row r="600" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A600" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B599" s="66"/>
-      <c r="C599" s="66" t="s">
+      <c r="B600" s="66"/>
+      <c r="C600" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D599" s="66" t="s">
+      <c r="D600" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E599" s="46" t="s">
+      <c r="E600" s="46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="600" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A600" s="82" t="s">
+    <row r="601" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A601" s="82" t="s">
         <v>371</v>
       </c>
-      <c r="B600" s="82" t="s">
+      <c r="B601" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="C600" s="82">
+      <c r="C601" s="82">
         <v>4336</v>
       </c>
-      <c r="D600" s="82" t="s">
+      <c r="D601" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="E600" s="43">
+      <c r="E601" s="43">
         <v>329.5</v>
-      </c>
-    </row>
-    <row r="601" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A601" s="69" t="s">
-        <v>372</v>
-      </c>
-      <c r="B601" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C601" s="70">
-        <v>2618</v>
-      </c>
-      <c r="D601" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E601" s="40">
-        <v>245</v>
       </c>
     </row>
     <row r="602" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -15503,33 +15503,33 @@
         <v>372</v>
       </c>
       <c r="B602" s="69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C602" s="70">
-        <v>2398</v>
+        <v>2618</v>
       </c>
       <c r="D602" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E602" s="40">
-        <v>124.5</v>
+        <v>245</v>
       </c>
     </row>
     <row r="603" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="69" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B603" s="69" t="s">
-        <v>1154</v>
+        <v>19</v>
       </c>
       <c r="C603" s="70">
-        <v>2297</v>
+        <v>2398</v>
       </c>
       <c r="D603" s="69" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E603" s="40">
-        <v>77.5</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="604" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -15537,16 +15537,16 @@
         <v>373</v>
       </c>
       <c r="B604" s="69" t="s">
-        <v>19</v>
+        <v>1154</v>
       </c>
       <c r="C604" s="70">
-        <v>3653</v>
+        <v>2297</v>
       </c>
       <c r="D604" s="69" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E604" s="40">
-        <v>29</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="605" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -15554,33 +15554,33 @@
         <v>373</v>
       </c>
       <c r="B605" s="69" t="s">
-        <v>1175</v>
+        <v>19</v>
       </c>
       <c r="C605" s="70">
-        <v>2339</v>
+        <v>3653</v>
       </c>
       <c r="D605" s="69" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E605" s="40">
-        <v>173</v>
+        <v>29</v>
       </c>
     </row>
     <row r="606" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="69" t="s">
-        <v>1151</v>
+        <v>373</v>
       </c>
       <c r="B606" s="69" t="s">
-        <v>1130</v>
+        <v>1175</v>
       </c>
       <c r="C606" s="70">
-        <v>2223</v>
+        <v>2339</v>
       </c>
       <c r="D606" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E606" s="40">
-        <v>57.5</v>
+        <v>173</v>
       </c>
     </row>
     <row r="607" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -15588,81 +15588,81 @@
         <v>1151</v>
       </c>
       <c r="B607" s="69" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="C607" s="70">
-        <v>3707</v>
+        <v>2223</v>
       </c>
       <c r="D607" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E607" s="40">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="608" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="608" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="69" t="s">
         <v>1151</v>
       </c>
       <c r="B608" s="69" t="s">
-        <v>33</v>
+        <v>1137</v>
       </c>
       <c r="C608" s="70">
-        <v>4090</v>
+        <v>3707</v>
       </c>
       <c r="D608" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E608" s="40">
-        <v>141.5</v>
-      </c>
-    </row>
-    <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="69" t="s">
-        <v>374</v>
+        <v>1151</v>
       </c>
       <c r="B609" s="69" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C609" s="70">
-        <v>4279</v>
+        <v>4090</v>
       </c>
       <c r="D609" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E609" s="40">
-        <v>295</v>
+        <v>141.5</v>
       </c>
     </row>
     <row r="610" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="69" t="s">
-        <v>1307</v>
+        <v>374</v>
       </c>
       <c r="B610" s="69" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="C610" s="70">
-        <v>2259</v>
+        <v>4279</v>
       </c>
       <c r="D610" s="69" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E610" s="40">
-        <v>15.5</v>
+        <v>295</v>
       </c>
     </row>
     <row r="611" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="69" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B611" s="69" t="s">
         <v>110</v>
       </c>
       <c r="C611" s="70">
-        <v>3540</v>
+        <v>2259</v>
       </c>
       <c r="D611" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E611" s="40">
         <v>15.5</v>
@@ -15670,64 +15670,64 @@
     </row>
     <row r="612" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="69" t="s">
-        <v>375</v>
+        <v>1306</v>
       </c>
       <c r="B612" s="69" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="C612" s="70">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="D612" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E612" s="40">
-        <v>120</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="613" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="69" t="s">
-        <v>1305</v>
+        <v>375</v>
       </c>
       <c r="B613" s="69" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="C613" s="70">
-        <v>2422</v>
+        <v>3541</v>
       </c>
       <c r="D613" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E613" s="40">
-        <v>15.5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="614" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="69" t="s">
-        <v>376</v>
+        <v>1305</v>
       </c>
       <c r="B614" s="69" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="C614" s="70">
-        <v>569</v>
+        <v>2422</v>
       </c>
       <c r="D614" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E614" s="40">
-        <v>118</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="615" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="69" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B615" s="69" t="s">
         <v>33</v>
       </c>
       <c r="C615" s="70">
-        <v>282</v>
+        <v>569</v>
       </c>
       <c r="D615" s="69" t="s">
         <v>34</v>
@@ -15738,19 +15738,19 @@
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="69" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B616" s="69" t="s">
         <v>33</v>
       </c>
       <c r="C616" s="70">
-        <v>2336</v>
+        <v>282</v>
       </c>
       <c r="D616" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E616" s="40">
-        <v>750</v>
+        <v>118</v>
       </c>
     </row>
     <row r="617" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -15758,118 +15758,118 @@
         <v>378</v>
       </c>
       <c r="B617" s="69" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="C617" s="70">
-        <v>2421</v>
+        <v>2336</v>
       </c>
       <c r="D617" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E617" s="40">
-        <v>91</v>
+        <v>750</v>
       </c>
     </row>
     <row r="618" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="69" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B618" s="69" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="C618" s="70">
-        <v>2568</v>
+        <v>2421</v>
       </c>
       <c r="D618" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E618" s="40">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="619" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="619" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="69" t="s">
         <v>379</v>
       </c>
       <c r="B619" s="69" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="C619" s="70">
-        <v>3009</v>
+        <v>2568</v>
       </c>
       <c r="D619" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E619" s="40">
-        <v>78</v>
+        <v>260</v>
       </c>
     </row>
     <row r="620" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="69" t="s">
+        <v>379</v>
+      </c>
+      <c r="B620" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="C620" s="70">
+        <v>3009</v>
+      </c>
+      <c r="D620" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E620" s="40">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="621" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A621" s="69" t="s">
         <v>1320</v>
-      </c>
-      <c r="B620" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C620" s="70">
-        <v>2778</v>
-      </c>
-      <c r="D620" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E620" s="40">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="621" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A621" s="69" t="s">
-        <v>1319</v>
       </c>
       <c r="B621" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C621" s="70">
+        <v>2778</v>
+      </c>
+      <c r="D621" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E621" s="40">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A622" s="69" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B622" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C622" s="70">
         <v>3106</v>
       </c>
-      <c r="D621" s="69" t="s">
+      <c r="D622" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E621" s="40">
+      <c r="E622" s="40">
         <v>260</v>
       </c>
     </row>
-    <row r="622" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A622" s="72" t="s">
+    <row r="623" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A623" s="72" t="s">
         <v>380</v>
       </c>
-      <c r="B622" s="72" t="s">
+      <c r="B623" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="C622" s="73">
+      <c r="C623" s="73">
         <v>3489</v>
       </c>
-      <c r="D622" s="72" t="s">
+      <c r="D623" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="E622" s="50">
+      <c r="E623" s="50">
         <v>700</v>
-      </c>
-    </row>
-    <row r="623" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A623" s="69" t="s">
-        <v>380</v>
-      </c>
-      <c r="B623" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C623" s="70">
-        <v>3696</v>
-      </c>
-      <c r="D623" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E623" s="40">
-        <v>280</v>
       </c>
     </row>
     <row r="624" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -15877,16 +15877,16 @@
         <v>380</v>
       </c>
       <c r="B624" s="69" t="s">
-        <v>1133</v>
+        <v>18</v>
       </c>
       <c r="C624" s="70">
-        <v>2783</v>
+        <v>3696</v>
       </c>
       <c r="D624" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E624" s="40">
-        <v>142</v>
+        <v>280</v>
       </c>
     </row>
     <row r="625" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -15894,50 +15894,50 @@
         <v>380</v>
       </c>
       <c r="B625" s="69" t="s">
-        <v>1152</v>
+        <v>1133</v>
       </c>
       <c r="C625" s="70">
-        <v>3755</v>
+        <v>2783</v>
       </c>
       <c r="D625" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E625" s="40">
-        <v>85</v>
+        <v>142</v>
       </c>
     </row>
     <row r="626" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="69" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B626" s="69" t="s">
-        <v>18</v>
+        <v>1152</v>
       </c>
       <c r="C626" s="70">
-        <v>3486</v>
+        <v>3755</v>
       </c>
       <c r="D626" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E626" s="40">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="627" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="69" t="s">
         <v>382</v>
       </c>
       <c r="B627" s="69" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="C627" s="70">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="D627" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E627" s="40">
-        <v>163</v>
+        <v>540</v>
       </c>
     </row>
     <row r="628" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -15945,84 +15945,84 @@
         <v>382</v>
       </c>
       <c r="B628" s="69" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C628" s="70">
-        <v>4488</v>
+        <v>3487</v>
       </c>
       <c r="D628" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E628" s="40">
-        <v>272</v>
+        <v>163</v>
       </c>
     </row>
     <row r="629" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="69" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B629" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C629" s="70">
-        <v>4333</v>
+        <v>4488</v>
       </c>
       <c r="D629" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E629" s="40">
-        <v>259.5</v>
+        <v>272</v>
       </c>
     </row>
     <row r="630" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="69" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B630" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C630" s="70">
-        <v>4388</v>
+        <v>4333</v>
       </c>
       <c r="D630" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E630" s="40">
-        <v>145</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="631" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="69" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B631" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C631" s="70">
-        <v>4389</v>
+        <v>4388</v>
       </c>
       <c r="D631" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E631" s="40">
-        <v>102</v>
+        <v>145</v>
       </c>
     </row>
     <row r="632" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="69" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B632" s="69" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C632" s="70">
-        <v>3488</v>
+        <v>4389</v>
       </c>
       <c r="D632" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E632" s="40">
-        <v>220</v>
+        <v>102</v>
       </c>
     </row>
     <row r="633" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16030,33 +16030,33 @@
         <v>387</v>
       </c>
       <c r="B633" s="69" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C633" s="70">
-        <v>3400</v>
+        <v>3488</v>
       </c>
       <c r="D633" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E633" s="40">
-        <v>57</v>
+        <v>220</v>
       </c>
     </row>
     <row r="634" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="69" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B634" s="69" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="C634" s="70">
-        <v>2257</v>
+        <v>3400</v>
       </c>
       <c r="D634" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E634" s="40">
-        <v>16</v>
+        <v>57</v>
       </c>
     </row>
     <row r="635" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16064,44 +16064,44 @@
         <v>388</v>
       </c>
       <c r="B635" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="C635" s="70">
+        <v>2257</v>
+      </c>
+      <c r="D635" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E635" s="40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A636" s="69" t="s">
+        <v>388</v>
+      </c>
+      <c r="B636" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="C635" s="70">
+      <c r="C636" s="70">
         <v>565</v>
       </c>
-      <c r="D635" s="69" t="s">
+      <c r="D636" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="E635" s="40">
+      <c r="E636" s="40">
         <v>123</v>
-      </c>
-    </row>
-    <row r="636" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A636" s="72" t="s">
-        <v>389</v>
-      </c>
-      <c r="B636" s="72" t="s">
-        <v>110</v>
-      </c>
-      <c r="C636" s="73">
-        <v>4474</v>
-      </c>
-      <c r="D636" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E636" s="50">
-        <v>39</v>
       </c>
     </row>
     <row r="637" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="72" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B637" s="72" t="s">
         <v>110</v>
       </c>
       <c r="C637" s="73">
-        <v>4473</v>
+        <v>4474</v>
       </c>
       <c r="D637" s="72" t="s">
         <v>20</v>
@@ -16112,13 +16112,13 @@
     </row>
     <row r="638" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="72" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B638" s="72" t="s">
         <v>110</v>
       </c>
       <c r="C638" s="73">
-        <v>2658</v>
+        <v>4473</v>
       </c>
       <c r="D638" s="72" t="s">
         <v>20</v>
@@ -16129,13 +16129,13 @@
     </row>
     <row r="639" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="72" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B639" s="72" t="s">
         <v>110</v>
       </c>
       <c r="C639" s="73">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="D639" s="72" t="s">
         <v>20</v>
@@ -16146,30 +16146,30 @@
     </row>
     <row r="640" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="72" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B640" s="72" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C640" s="73">
         <v>2657</v>
       </c>
       <c r="D640" s="72" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E640" s="50">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="641" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="72" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B641" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C641" s="73">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="D641" s="72" t="s">
         <v>49</v>
@@ -16177,42 +16177,42 @@
       <c r="E641" s="50">
         <v>65</v>
       </c>
-      <c r="F641" s="1" t="s">
+    </row>
+    <row r="642" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A642" s="72" t="s">
+        <v>391</v>
+      </c>
+      <c r="B642" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C642" s="73">
+        <v>2658</v>
+      </c>
+      <c r="D642" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E642" s="50">
+        <v>65</v>
+      </c>
+      <c r="F642" s="1" t="s">
         <v>386</v>
-      </c>
-    </row>
-    <row r="642" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A642" s="69" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B642" s="69" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C642" s="70">
-        <v>3537</v>
-      </c>
-      <c r="D642" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E642" s="40">
-        <v>162</v>
       </c>
     </row>
     <row r="643" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="69" t="s">
-        <v>394</v>
+        <v>1153</v>
       </c>
       <c r="B643" s="69" t="s">
-        <v>18</v>
+        <v>1154</v>
       </c>
       <c r="C643" s="70">
-        <v>2732</v>
+        <v>3537</v>
       </c>
       <c r="D643" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E643" s="40">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="644" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16220,33 +16220,33 @@
         <v>394</v>
       </c>
       <c r="B644" s="69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C644" s="70">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="D644" s="69" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E644" s="40">
-        <v>87.5</v>
+        <v>175</v>
       </c>
     </row>
     <row r="645" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="69" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B645" s="69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C645" s="70">
-        <v>2584</v>
+        <v>2733</v>
       </c>
       <c r="D645" s="69" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E645" s="40">
-        <v>205</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="646" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16254,33 +16254,33 @@
         <v>395</v>
       </c>
       <c r="B646" s="69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C646" s="70">
-        <v>2677</v>
+        <v>2584</v>
       </c>
       <c r="D646" s="69" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E646" s="40">
-        <v>104.5</v>
+        <v>205</v>
       </c>
     </row>
     <row r="647" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="69" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B647" s="69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C647" s="70">
-        <v>2495</v>
+        <v>2677</v>
       </c>
       <c r="D647" s="69" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E647" s="40">
-        <v>197</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="648" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16288,50 +16288,50 @@
         <v>396</v>
       </c>
       <c r="B648" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C648" s="70">
+        <v>2495</v>
+      </c>
+      <c r="D648" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E648" s="40">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A649" s="69" t="s">
+        <v>396</v>
+      </c>
+      <c r="B649" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C648" s="70">
+      <c r="C649" s="70">
         <v>2678</v>
       </c>
-      <c r="D648" s="69" t="s">
+      <c r="D649" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E648" s="40">
+      <c r="E649" s="40">
         <v>100.5</v>
       </c>
     </row>
-    <row r="649" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A649" s="69" t="s">
+    <row r="650" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A650" s="69" t="s">
         <v>1155</v>
       </c>
-      <c r="B649" s="69" t="s">
+      <c r="B650" s="69" t="s">
         <v>1130</v>
       </c>
-      <c r="C649" s="70">
+      <c r="C650" s="70">
         <v>4498</v>
       </c>
-      <c r="D649" s="69" t="s">
+      <c r="D650" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="E649" s="40">
+      <c r="E650" s="40">
         <v>240</v>
-      </c>
-    </row>
-    <row r="650" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A650" s="69" t="s">
-        <v>397</v>
-      </c>
-      <c r="B650" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C650" s="70">
-        <v>4253</v>
-      </c>
-      <c r="D650" s="69" t="s">
-        <v>160</v>
-      </c>
-      <c r="E650" s="40">
-        <v>112</v>
       </c>
     </row>
     <row r="651" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16339,16 +16339,16 @@
         <v>397</v>
       </c>
       <c r="B651" s="69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C651" s="70">
-        <v>4500</v>
+        <v>4253</v>
       </c>
       <c r="D651" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E651" s="40">
-        <v>224</v>
+        <v>112</v>
       </c>
     </row>
     <row r="652" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16356,16 +16356,16 @@
         <v>397</v>
       </c>
       <c r="B652" s="69" t="s">
-        <v>1156</v>
+        <v>18</v>
       </c>
       <c r="C652" s="70">
-        <v>4249</v>
+        <v>4500</v>
       </c>
       <c r="D652" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E652" s="40">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="653" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16373,186 +16373,186 @@
         <v>397</v>
       </c>
       <c r="B653" s="69" t="s">
-        <v>1130</v>
+        <v>1156</v>
       </c>
       <c r="C653" s="70">
-        <v>3724</v>
+        <v>4249</v>
       </c>
       <c r="D653" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E653" s="40">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="654" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="69" t="s">
-        <v>1157</v>
+        <v>397</v>
       </c>
       <c r="B654" s="69" t="s">
-        <v>1154</v>
+        <v>1130</v>
       </c>
       <c r="C654" s="70">
-        <v>3736</v>
+        <v>3724</v>
       </c>
       <c r="D654" s="69" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E654" s="40">
-        <v>162</v>
+        <v>224</v>
       </c>
     </row>
     <row r="655" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="69" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B655" s="69" t="s">
-        <v>1130</v>
+        <v>1154</v>
       </c>
       <c r="C655" s="70">
-        <v>4499</v>
+        <v>3736</v>
       </c>
       <c r="D655" s="69" t="s">
-        <v>177</v>
+        <v>15</v>
       </c>
       <c r="E655" s="40">
-        <v>240</v>
+        <v>162</v>
       </c>
     </row>
     <row r="656" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="69" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B656" s="69" t="s">
-        <v>1154</v>
+        <v>1130</v>
       </c>
       <c r="C656" s="70">
-        <v>3536</v>
+        <v>4499</v>
       </c>
       <c r="D656" s="69" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="E656" s="40">
-        <v>162</v>
+        <v>240</v>
       </c>
     </row>
     <row r="657" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="69" t="s">
-        <v>398</v>
+        <v>1159</v>
       </c>
       <c r="B657" s="69" t="s">
-        <v>18</v>
+        <v>1154</v>
       </c>
       <c r="C657" s="70">
-        <v>2494</v>
+        <v>3536</v>
       </c>
       <c r="D657" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E657" s="40">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="658" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A658" s="69" t="s">
+        <v>398</v>
+      </c>
+      <c r="B658" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C658" s="70">
+        <v>2494</v>
+      </c>
+      <c r="D658" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E658" s="40">
         <v>170</v>
-      </c>
-    </row>
-    <row r="658" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A658" s="72" t="s">
-        <v>398</v>
-      </c>
-      <c r="B658" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C658" s="73">
-        <v>2679</v>
-      </c>
-      <c r="D658" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E658" s="50">
-        <v>87</v>
       </c>
     </row>
     <row r="659" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="72" t="s">
+        <v>398</v>
+      </c>
+      <c r="B659" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C659" s="73">
+        <v>2679</v>
+      </c>
+      <c r="D659" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E659" s="50">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A660" s="72" t="s">
         <v>1160</v>
       </c>
-      <c r="B659" s="72" t="s">
+      <c r="B660" s="72" t="s">
         <v>1130</v>
       </c>
-      <c r="C659" s="73">
+      <c r="C660" s="73">
         <v>4497</v>
       </c>
-      <c r="D659" s="72" t="s">
+      <c r="D660" s="72" t="s">
         <v>177</v>
       </c>
-      <c r="E659" s="50">
+      <c r="E660" s="50">
         <v>240</v>
-      </c>
-    </row>
-    <row r="660" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A660" s="69" t="s">
-        <v>399</v>
-      </c>
-      <c r="B660" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C660" s="70">
-        <v>2493</v>
-      </c>
-      <c r="D660" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E660" s="40">
-        <v>170</v>
       </c>
     </row>
     <row r="661" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="69" t="s">
-        <v>1161</v>
+        <v>399</v>
       </c>
       <c r="B661" s="69" t="s">
-        <v>1154</v>
+        <v>18</v>
       </c>
       <c r="C661" s="70">
-        <v>3535</v>
+        <v>2493</v>
       </c>
       <c r="D661" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E661" s="40">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="662" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="69" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B662" s="69" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C662" s="70">
+        <v>3535</v>
+      </c>
+      <c r="D662" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E662" s="40">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="663" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A663" s="69" t="s">
         <v>399</v>
       </c>
-      <c r="B662" s="69" t="s">
+      <c r="B663" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C662" s="70">
+      <c r="C663" s="70">
         <v>2498</v>
       </c>
-      <c r="D662" s="69" t="s">
+      <c r="D663" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E662" s="40">
+      <c r="E663" s="40">
         <v>87</v>
-      </c>
-    </row>
-    <row r="663" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A663" s="72" t="s">
-        <v>462</v>
-      </c>
-      <c r="B663" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C663" s="73">
-        <v>2806</v>
-      </c>
-      <c r="D663" s="74" t="s">
-        <v>160</v>
-      </c>
-      <c r="E663" s="48">
-        <v>472.5</v>
       </c>
     </row>
     <row r="664" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16560,33 +16560,33 @@
         <v>462</v>
       </c>
       <c r="B664" s="72" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="C664" s="73">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="D664" s="74" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E664" s="48">
-        <v>159.5</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="665" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="72" t="s">
-        <v>1321</v>
+        <v>462</v>
       </c>
       <c r="B665" s="72" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C665" s="73">
-        <v>4556</v>
+        <v>2807</v>
       </c>
       <c r="D665" s="74" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E665" s="48">
-        <v>900</v>
+        <v>159.5</v>
       </c>
     </row>
     <row r="666" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16594,33 +16594,33 @@
         <v>1321</v>
       </c>
       <c r="B666" s="72" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C666" s="73">
-        <v>4557</v>
+        <v>4556</v>
       </c>
       <c r="D666" s="74" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E666" s="48">
-        <v>182</v>
+        <v>900</v>
       </c>
     </row>
     <row r="667" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="72" t="s">
-        <v>400</v>
+        <v>1321</v>
       </c>
       <c r="B667" s="72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C667" s="73">
-        <v>4018</v>
-      </c>
-      <c r="D667" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E667" s="50">
-        <v>230</v>
+        <v>4557</v>
+      </c>
+      <c r="D667" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E667" s="48">
+        <v>182</v>
       </c>
     </row>
     <row r="668" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16628,33 +16628,33 @@
         <v>400</v>
       </c>
       <c r="B668" s="72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C668" s="73">
-        <v>2652</v>
+        <v>4018</v>
       </c>
       <c r="D668" s="72" t="s">
         <v>49</v>
       </c>
       <c r="E668" s="50">
-        <v>117</v>
+        <v>230</v>
       </c>
     </row>
     <row r="669" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="72" t="s">
-        <v>458</v>
+        <v>400</v>
       </c>
       <c r="B669" s="72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C669" s="73">
-        <v>4049</v>
-      </c>
-      <c r="D669" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E669" s="48">
-        <v>210</v>
+        <v>2652</v>
+      </c>
+      <c r="D669" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E669" s="50">
+        <v>117</v>
       </c>
     </row>
     <row r="670" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16662,67 +16662,67 @@
         <v>458</v>
       </c>
       <c r="B670" s="72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C670" s="73">
-        <v>3737</v>
+        <v>4049</v>
       </c>
       <c r="D670" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E670" s="48">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="671" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A671" s="72" t="s">
+        <v>458</v>
+      </c>
+      <c r="B671" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C671" s="73">
+        <v>3737</v>
+      </c>
+      <c r="D671" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E671" s="48">
         <v>107</v>
-      </c>
-    </row>
-    <row r="671" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A671" s="69" t="s">
-        <v>401</v>
-      </c>
-      <c r="B671" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="C671" s="70">
-        <v>4301</v>
-      </c>
-      <c r="D671" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="E671" s="40">
-        <v>235</v>
       </c>
     </row>
     <row r="672" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="69" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B672" s="69" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="C672" s="70">
-        <v>4334</v>
+        <v>4301</v>
       </c>
       <c r="D672" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E672" s="40">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A673" s="69" t="s">
+        <v>402</v>
+      </c>
+      <c r="B673" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C673" s="70">
+        <v>4334</v>
+      </c>
+      <c r="D673" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E673" s="40">
         <v>376.5</v>
-      </c>
-    </row>
-    <row r="673" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A673" s="69" t="s">
-        <v>403</v>
-      </c>
-      <c r="B673" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="C673" s="70">
-        <v>195</v>
-      </c>
-      <c r="D673" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E673" s="40">
-        <v>250</v>
       </c>
     </row>
     <row r="674" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16730,33 +16730,33 @@
         <v>403</v>
       </c>
       <c r="B674" s="69" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C674" s="70">
-        <v>54</v>
+        <v>195</v>
       </c>
       <c r="D674" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E674" s="40">
-        <v>52</v>
+        <v>250</v>
       </c>
     </row>
     <row r="675" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="69" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B675" s="69" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C675" s="70">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D675" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E675" s="40">
-        <v>220</v>
+        <v>52</v>
       </c>
     </row>
     <row r="676" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16764,33 +16764,33 @@
         <v>404</v>
       </c>
       <c r="B676" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="C676" s="70">
+        <v>63</v>
+      </c>
+      <c r="D676" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E676" s="40">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A677" s="69" t="s">
+        <v>404</v>
+      </c>
+      <c r="B677" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C676" s="70">
+      <c r="C677" s="70">
         <v>2483</v>
       </c>
-      <c r="D676" s="69" t="s">
+      <c r="D677" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E676" s="40">
+      <c r="E677" s="40">
         <v>46</v>
-      </c>
-    </row>
-    <row r="677" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A677" s="69" t="s">
-        <v>405</v>
-      </c>
-      <c r="B677" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C677" s="70">
-        <v>2974</v>
-      </c>
-      <c r="D677" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E677" s="40">
-        <v>250</v>
       </c>
     </row>
     <row r="678" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16798,44 +16798,44 @@
         <v>405</v>
       </c>
       <c r="B678" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C678" s="70">
+        <v>2974</v>
+      </c>
+      <c r="D678" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E678" s="40">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A679" s="69" t="s">
+        <v>405</v>
+      </c>
+      <c r="B679" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C678" s="70">
+      <c r="C679" s="70">
         <v>2831</v>
-      </c>
-      <c r="D678" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="E678" s="40">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="679" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A679" s="69" t="s">
-        <v>406</v>
-      </c>
-      <c r="B679" s="69" t="s">
-        <v>110</v>
-      </c>
-      <c r="C679" s="70">
-        <v>4137</v>
       </c>
       <c r="D679" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E679" s="40">
-        <v>270</v>
+        <v>127</v>
       </c>
     </row>
     <row r="680" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="69" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B680" s="69" t="s">
         <v>110</v>
       </c>
       <c r="C680" s="70">
-        <v>4380</v>
+        <v>4137</v>
       </c>
       <c r="D680" s="69" t="s">
         <v>20</v>
@@ -16846,30 +16846,30 @@
     </row>
     <row r="681" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="69" t="s">
-        <v>1333</v>
+        <v>407</v>
       </c>
       <c r="B681" s="69" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C681" s="70">
-        <v>4566</v>
+        <v>4380</v>
       </c>
       <c r="D681" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E681" s="40">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="682" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="69" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B682" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C682" s="70">
-        <v>4567</v>
+        <v>4566</v>
       </c>
       <c r="D682" s="69" t="s">
         <v>20</v>
@@ -16878,21 +16878,21 @@
         <v>240</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="69" t="s">
-        <v>408</v>
+        <v>1334</v>
       </c>
       <c r="B683" s="69" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="C683" s="70">
-        <v>4204</v>
+        <v>4567</v>
       </c>
       <c r="D683" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E683" s="40">
-        <v>145.5</v>
+        <v>240</v>
       </c>
     </row>
     <row r="684" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16900,16 +16900,16 @@
         <v>408</v>
       </c>
       <c r="B684" s="69" t="s">
-        <v>18</v>
+        <v>319</v>
       </c>
       <c r="C684" s="70">
-        <v>4205</v>
+        <v>4204</v>
       </c>
       <c r="D684" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E684" s="40">
-        <v>360</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="685" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16917,33 +16917,33 @@
         <v>408</v>
       </c>
       <c r="B685" s="69" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C685" s="70">
-        <v>4225</v>
+        <v>4205</v>
       </c>
       <c r="D685" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E685" s="40">
-        <v>900</v>
+        <v>360</v>
       </c>
     </row>
     <row r="686" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="69" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B686" s="69" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C686" s="70">
-        <v>4378</v>
+        <v>4225</v>
       </c>
       <c r="D686" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E686" s="40">
-        <v>430</v>
+        <v>900</v>
       </c>
     </row>
     <row r="687" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16951,67 +16951,67 @@
         <v>409</v>
       </c>
       <c r="B687" s="69" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="C687" s="70">
-        <v>4379</v>
+        <v>4378</v>
       </c>
       <c r="D687" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E687" s="40">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="688" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A688" s="69" t="s">
+        <v>409</v>
+      </c>
+      <c r="B688" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="C688" s="70">
+        <v>4379</v>
+      </c>
+      <c r="D688" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E688" s="40">
         <v>43</v>
       </c>
     </row>
-    <row r="688" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A688" s="69" t="s">
-        <v>410</v>
-      </c>
-      <c r="B688" s="69" t="s">
-        <v>411</v>
-      </c>
-      <c r="C688" s="70">
-        <v>3524</v>
-      </c>
-      <c r="D688" s="69" t="s">
-        <v>412</v>
-      </c>
-      <c r="E688" s="40">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="689" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="69" t="s">
         <v>410</v>
       </c>
       <c r="B689" s="69" t="s">
-        <v>110</v>
+        <v>411</v>
       </c>
       <c r="C689" s="70">
-        <v>3523</v>
+        <v>3524</v>
       </c>
       <c r="D689" s="69" t="s">
         <v>412</v>
       </c>
       <c r="E689" s="40">
-        <v>72</v>
+        <v>350</v>
       </c>
     </row>
     <row r="690" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="69" t="s">
-        <v>1162</v>
+        <v>410</v>
       </c>
       <c r="B690" s="69" t="s">
-        <v>1163</v>
+        <v>110</v>
       </c>
       <c r="C690" s="70">
-        <v>3521</v>
+        <v>3523</v>
       </c>
       <c r="D690" s="69" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E690" s="40">
-        <v>158</v>
+        <v>72</v>
       </c>
     </row>
     <row r="691" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17019,67 +17019,67 @@
         <v>1162</v>
       </c>
       <c r="B691" s="69" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C691" s="70">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="D691" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E691" s="40">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A692" s="69" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B692" s="69" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C692" s="70">
+        <v>3522</v>
+      </c>
+      <c r="D692" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E692" s="40">
         <v>216.5</v>
       </c>
     </row>
-    <row r="692" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A692" s="72" t="s">
+    <row r="693" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A693" s="72" t="s">
         <v>1165</v>
       </c>
-      <c r="B692" s="72" t="s">
+      <c r="B693" s="72" t="s">
         <v>1166</v>
       </c>
-      <c r="C692" s="73">
+      <c r="C693" s="73">
         <v>64</v>
       </c>
-      <c r="D692" s="72" t="s">
+      <c r="D693" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="E692" s="50">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="693" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A693" s="69" t="s">
-        <v>1167</v>
-      </c>
-      <c r="B693" s="69" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C693" s="70">
-        <v>90</v>
-      </c>
-      <c r="D693" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E693" s="40">
+      <c r="E693" s="50">
         <v>132</v>
       </c>
     </row>
     <row r="694" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="69" t="s">
-        <v>413</v>
+        <v>1167</v>
       </c>
       <c r="B694" s="69" t="s">
-        <v>33</v>
+        <v>1166</v>
       </c>
       <c r="C694" s="70">
-        <v>3637</v>
+        <v>90</v>
       </c>
       <c r="D694" s="69" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E694" s="40">
-        <v>375</v>
+        <v>132</v>
       </c>
     </row>
     <row r="695" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17087,16 +17087,16 @@
         <v>413</v>
       </c>
       <c r="B695" s="69" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C695" s="70">
-        <v>2805</v>
+        <v>3637</v>
       </c>
       <c r="D695" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E695" s="40">
-        <v>150</v>
+        <v>375</v>
       </c>
     </row>
     <row r="696" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17104,33 +17104,33 @@
         <v>413</v>
       </c>
       <c r="B696" s="69" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="C696" s="70">
-        <v>2427</v>
+        <v>2805</v>
       </c>
       <c r="D696" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E696" s="40">
-        <v>46</v>
+        <v>150</v>
       </c>
     </row>
     <row r="697" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="69" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B697" s="69" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="C697" s="70">
-        <v>3437</v>
+        <v>2427</v>
       </c>
       <c r="D697" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E697" s="40">
-        <v>390</v>
+        <v>46</v>
       </c>
     </row>
     <row r="698" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17138,180 +17138,180 @@
         <v>414</v>
       </c>
       <c r="B698" s="69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C698" s="70">
-        <v>3396</v>
+        <v>3437</v>
       </c>
       <c r="D698" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E698" s="40">
-        <v>197</v>
+        <v>390</v>
       </c>
     </row>
     <row r="699" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="69" t="s">
-        <v>1168</v>
+        <v>414</v>
       </c>
       <c r="B699" s="69" t="s">
-        <v>1169</v>
+        <v>19</v>
       </c>
       <c r="C699" s="70">
-        <v>3395</v>
+        <v>3396</v>
       </c>
       <c r="D699" s="69" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E699" s="40">
-        <v>54</v>
+        <v>197</v>
       </c>
     </row>
     <row r="700" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="69" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B700" s="69" t="s">
         <v>1169</v>
       </c>
       <c r="C700" s="70">
-        <v>3490</v>
+        <v>3395</v>
       </c>
       <c r="D700" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E700" s="40">
-        <v>169</v>
+        <v>54</v>
       </c>
     </row>
     <row r="701" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="69" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B701" s="69" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="C701" s="70">
-        <v>458</v>
+        <v>3490</v>
       </c>
       <c r="D701" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E701" s="40">
-        <v>269.5</v>
+        <v>169</v>
       </c>
     </row>
     <row r="702" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="69" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B702" s="69" t="s">
         <v>1172</v>
       </c>
       <c r="C702" s="70">
-        <v>2641</v>
+        <v>458</v>
       </c>
       <c r="D702" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E702" s="40">
-        <v>222</v>
+        <v>269.5</v>
       </c>
     </row>
     <row r="703" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A703" s="75" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B703" s="75" t="s">
+      <c r="A703" s="69" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B703" s="69" t="s">
         <v>1172</v>
       </c>
-      <c r="C703" s="76">
-        <v>4293</v>
+      <c r="C703" s="70">
+        <v>2641</v>
       </c>
       <c r="D703" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E703" s="44">
-        <v>210</v>
+      <c r="E703" s="40">
+        <v>222</v>
       </c>
     </row>
     <row r="704" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="75" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B704" s="75" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C704" s="76">
+        <v>4293</v>
+      </c>
+      <c r="D704" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E704" s="44">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="705" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A705" s="75" t="s">
         <v>415</v>
       </c>
-      <c r="B704" s="75" t="s">
+      <c r="B705" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C704" s="76">
+      <c r="C705" s="76">
         <v>2396</v>
       </c>
-      <c r="D704" s="75" t="s">
+      <c r="D705" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E704" s="44">
+      <c r="E705" s="44">
         <v>675</v>
-      </c>
-    </row>
-    <row r="705" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A705" s="80" t="s">
-        <v>415</v>
-      </c>
-      <c r="B705" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C705" s="81">
-        <v>2426</v>
-      </c>
-      <c r="D705" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="E705" s="42">
-        <v>137</v>
       </c>
     </row>
     <row r="706" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="80" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B706" s="80" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="C706" s="81">
-        <v>4335</v>
+        <v>2426</v>
       </c>
       <c r="D706" s="80" t="s">
         <v>20</v>
       </c>
       <c r="E706" s="42">
-        <v>424.5</v>
+        <v>137</v>
       </c>
     </row>
     <row r="707" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="80" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B707" s="80" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C707" s="81">
-        <v>4477</v>
+        <v>4335</v>
       </c>
       <c r="D707" s="80" t="s">
         <v>20</v>
       </c>
       <c r="E707" s="42">
-        <v>244.5</v>
+        <v>424.5</v>
       </c>
     </row>
     <row r="708" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="80" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B708" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C708" s="81">
-        <v>4479</v>
+        <v>4477</v>
       </c>
       <c r="D708" s="80" t="s">
         <v>20</v>
@@ -17322,13 +17322,13 @@
     </row>
     <row r="709" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="80" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B709" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C709" s="81">
-        <v>4478</v>
+        <v>4479</v>
       </c>
       <c r="D709" s="80" t="s">
         <v>20</v>
@@ -17338,20 +17338,20 @@
       </c>
     </row>
     <row r="710" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A710" s="72" t="s">
-        <v>1263</v>
-      </c>
-      <c r="B710" s="72" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C710" s="73">
-        <v>2646</v>
-      </c>
-      <c r="D710" s="72" t="s">
-        <v>177</v>
-      </c>
-      <c r="E710" s="50">
-        <v>50.5</v>
+      <c r="A710" s="80" t="s">
+        <v>419</v>
+      </c>
+      <c r="B710" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C710" s="81">
+        <v>4478</v>
+      </c>
+      <c r="D710" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E710" s="42">
+        <v>244.5</v>
       </c>
     </row>
     <row r="711" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17359,16 +17359,16 @@
         <v>1263</v>
       </c>
       <c r="B711" s="72" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C711" s="73">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="D711" s="72" t="s">
         <v>177</v>
       </c>
       <c r="E711" s="50">
-        <v>78</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="712" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17376,132 +17376,132 @@
         <v>1263</v>
       </c>
       <c r="B712" s="72" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C712" s="73">
-        <v>2638</v>
+        <v>2645</v>
       </c>
       <c r="D712" s="72" t="s">
         <v>177</v>
       </c>
       <c r="E712" s="50">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="713" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="72" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="B713" s="72" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C713" s="73">
-        <v>4294</v>
+        <v>2638</v>
       </c>
       <c r="D713" s="72" t="s">
         <v>177</v>
       </c>
       <c r="E713" s="50">
-        <v>150</v>
+        <v>65</v>
       </c>
     </row>
     <row r="714" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="72" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B714" s="72" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C714" s="73">
-        <v>4314</v>
+        <v>4294</v>
       </c>
       <c r="D714" s="72" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="E714" s="50">
-        <v>252</v>
+        <v>150</v>
       </c>
     </row>
     <row r="715" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="72" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B715" s="72" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C715" s="73">
-        <v>4315</v>
+        <v>4314</v>
       </c>
       <c r="D715" s="72" t="s">
         <v>15</v>
       </c>
       <c r="E715" s="50">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="716" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A716" s="72" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B716" s="72" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C716" s="73">
+        <v>4315</v>
+      </c>
+      <c r="D716" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E716" s="50">
         <v>450</v>
       </c>
     </row>
-    <row r="716" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A716" s="114"/>
-      <c r="B716" s="103"/>
-      <c r="C716" s="103"/>
-      <c r="D716" s="104"/>
-      <c r="E716" s="105"/>
-    </row>
-    <row r="717" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="111" t="s">
+    <row r="717" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A717" s="116"/>
+      <c r="B717" s="109"/>
+      <c r="C717" s="109"/>
+      <c r="D717" s="110"/>
+      <c r="E717" s="117"/>
+    </row>
+    <row r="718" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A718" s="118" t="s">
         <v>420</v>
       </c>
-      <c r="B717" s="112"/>
-      <c r="C717" s="112"/>
-      <c r="D717" s="112"/>
-      <c r="E717" s="113"/>
-    </row>
-    <row r="718" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A718" s="66" t="s">
+      <c r="B718" s="119"/>
+      <c r="C718" s="119"/>
+      <c r="D718" s="119"/>
+      <c r="E718" s="120"/>
+    </row>
+    <row r="719" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A719" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B718" s="66"/>
-      <c r="C718" s="66" t="s">
+      <c r="B719" s="66"/>
+      <c r="C719" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D718" s="66" t="s">
+      <c r="D719" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E718" s="46" t="s">
+      <c r="E719" s="46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A719" s="69" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B719" s="69" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C719" s="70">
-        <v>3402</v>
-      </c>
-      <c r="D719" s="69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E719" s="40">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="720" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="69" t="s">
         <v>1176</v>
       </c>
       <c r="B720" s="69" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C720" s="70">
-        <v>3401</v>
+        <v>3402</v>
       </c>
       <c r="D720" s="69" t="s">
         <v>177</v>
       </c>
       <c r="E720" s="40">
-        <v>66.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="721" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17509,168 +17509,168 @@
         <v>1176</v>
       </c>
       <c r="B721" s="69" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C721" s="70">
-        <v>3403</v>
+        <v>3401</v>
       </c>
       <c r="D721" s="69" t="s">
         <v>177</v>
       </c>
       <c r="E721" s="40">
-        <v>38.5</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="722" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="69" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="B722" s="69" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C722" s="70">
-        <v>4032</v>
+        <v>3403</v>
       </c>
       <c r="D722" s="69" t="s">
         <v>177</v>
       </c>
       <c r="E722" s="40">
-        <v>57.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="723" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="69" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B723" s="75" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B723" s="69" t="s">
         <v>1181</v>
       </c>
-      <c r="C723" s="76">
-        <v>4460</v>
+      <c r="C723" s="70">
+        <v>4032</v>
       </c>
       <c r="D723" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="E723" s="44">
+      <c r="E723" s="40">
         <v>57.5</v>
       </c>
     </row>
     <row r="724" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A724" s="75" t="s">
-        <v>1183</v>
+      <c r="A724" s="69" t="s">
+        <v>1182</v>
       </c>
       <c r="B724" s="75" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="C724" s="76">
-        <v>4260</v>
-      </c>
-      <c r="D724" s="75" t="s">
+        <v>4460</v>
+      </c>
+      <c r="D724" s="69" t="s">
         <v>177</v>
       </c>
       <c r="E724" s="44">
-        <v>58</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="725" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="75" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B725" s="75" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C725" s="76">
-        <v>2551</v>
+        <v>4260</v>
       </c>
       <c r="D725" s="75" t="s">
         <v>177</v>
       </c>
       <c r="E725" s="44">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="726" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A726" s="75" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B726" s="75" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C726" s="76">
+        <v>2551</v>
+      </c>
+      <c r="D726" s="75" t="s">
+        <v>177</v>
+      </c>
+      <c r="E726" s="44">
         <v>82</v>
       </c>
     </row>
-    <row r="726" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A726" s="80" t="s">
+    <row r="727" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A727" s="80" t="s">
         <v>1187</v>
       </c>
-      <c r="B726" s="80" t="s">
+      <c r="B727" s="80" t="s">
         <v>1188</v>
       </c>
-      <c r="C726" s="81">
+      <c r="C727" s="81">
         <v>2550</v>
-      </c>
-      <c r="D726" s="80" t="s">
-        <v>177</v>
-      </c>
-      <c r="E726" s="42">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="727" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A727" s="80" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B727" s="80" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C727" s="81">
-        <v>4383</v>
       </c>
       <c r="D727" s="80" t="s">
         <v>177</v>
       </c>
       <c r="E727" s="42">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="728" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A728" s="80" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B728" s="80" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C728" s="81">
+        <v>4383</v>
+      </c>
+      <c r="D728" s="80" t="s">
+        <v>177</v>
+      </c>
+      <c r="E728" s="42">
         <v>53</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A728" s="85"/>
-      <c r="B728" s="85"/>
-      <c r="C728" s="86"/>
-      <c r="D728" s="85"/>
-      <c r="E728" s="61"/>
-    </row>
     <row r="729" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A729" s="111" t="s">
+      <c r="A729" s="85"/>
+      <c r="B729" s="85"/>
+      <c r="C729" s="86"/>
+      <c r="D729" s="85"/>
+      <c r="E729" s="61"/>
+    </row>
+    <row r="730" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A730" s="118" t="s">
         <v>1303</v>
       </c>
-      <c r="B729" s="112"/>
-      <c r="C729" s="112"/>
-      <c r="D729" s="112"/>
-      <c r="E729" s="113"/>
-    </row>
-    <row r="730" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A730" s="72" t="s">
-        <v>1283</v>
-      </c>
-      <c r="B730" s="72" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C730" s="73">
-        <v>3642</v>
-      </c>
-      <c r="D730" s="74" t="s">
-        <v>160</v>
-      </c>
-      <c r="E730" s="48">
-        <v>162</v>
-      </c>
+      <c r="B730" s="119"/>
+      <c r="C730" s="119"/>
+      <c r="D730" s="119"/>
+      <c r="E730" s="120"/>
     </row>
     <row r="731" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="72" t="s">
         <v>1283</v>
       </c>
       <c r="B731" s="72" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C731" s="73">
-        <v>3644</v>
+        <v>3642</v>
       </c>
       <c r="D731" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="E731" s="49">
-        <v>84</v>
+      <c r="E731" s="48">
+        <v>162</v>
       </c>
     </row>
     <row r="732" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17678,15 +17678,15 @@
         <v>1283</v>
       </c>
       <c r="B732" s="72" t="s">
-        <v>1250</v>
+        <v>1285</v>
       </c>
       <c r="C732" s="73">
-        <v>3641</v>
+        <v>3644</v>
       </c>
       <c r="D732" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="E732" s="48">
+      <c r="E732" s="49">
         <v>84</v>
       </c>
     </row>
@@ -17695,33 +17695,33 @@
         <v>1283</v>
       </c>
       <c r="B733" s="72" t="s">
-        <v>1286</v>
+        <v>1250</v>
       </c>
       <c r="C733" s="73">
-        <v>3645</v>
+        <v>3641</v>
       </c>
       <c r="D733" s="74" t="s">
         <v>160</v>
       </c>
       <c r="E733" s="48">
-        <v>162</v>
+        <v>84</v>
       </c>
     </row>
     <row r="734" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A734" s="72" t="s">
-        <v>1249</v>
+        <v>1283</v>
       </c>
       <c r="B734" s="72" t="s">
-        <v>1172</v>
+        <v>1286</v>
       </c>
       <c r="C734" s="73">
-        <v>3852</v>
+        <v>3645</v>
       </c>
       <c r="D734" s="74" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E734" s="48">
-        <v>26</v>
+        <v>162</v>
       </c>
     </row>
     <row r="735" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17729,276 +17729,276 @@
         <v>1249</v>
       </c>
       <c r="B735" s="72" t="s">
-        <v>1250</v>
+        <v>1172</v>
       </c>
       <c r="C735" s="73">
-        <v>3647</v>
+        <v>3852</v>
       </c>
       <c r="D735" s="74" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E735" s="48">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="736" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="736" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="72" t="s">
         <v>1249</v>
       </c>
       <c r="B736" s="72" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C736" s="73">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="D736" s="74" t="s">
         <v>160</v>
       </c>
       <c r="E736" s="48">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="737" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A737" s="72" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B737" s="72" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C737" s="73">
+        <v>3648</v>
+      </c>
+      <c r="D737" s="74" t="s">
+        <v>160</v>
+      </c>
+      <c r="E737" s="48">
         <v>33</v>
       </c>
     </row>
-    <row r="737" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A737" s="102"/>
-      <c r="B737" s="103"/>
-      <c r="C737" s="103"/>
-      <c r="D737" s="104"/>
-      <c r="E737" s="105"/>
-    </row>
     <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="111" t="s">
+      <c r="A738" s="121"/>
+      <c r="B738" s="109"/>
+      <c r="C738" s="109"/>
+      <c r="D738" s="110"/>
+      <c r="E738" s="117"/>
+    </row>
+    <row r="739" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A739" s="118" t="s">
         <v>421</v>
       </c>
-      <c r="B738" s="112"/>
-      <c r="C738" s="112"/>
-      <c r="D738" s="112"/>
-      <c r="E738" s="113"/>
-    </row>
-    <row r="739" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A739" s="66" t="s">
+      <c r="B739" s="119"/>
+      <c r="C739" s="119"/>
+      <c r="D739" s="119"/>
+      <c r="E739" s="120"/>
+    </row>
+    <row r="740" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A740" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B739" s="66"/>
-      <c r="C739" s="66" t="s">
+      <c r="B740" s="66"/>
+      <c r="C740" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D739" s="66" t="s">
+      <c r="D740" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E739" s="46" t="s">
+      <c r="E740" s="46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="740" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A740" s="69" t="s">
-        <v>1191</v>
-      </c>
-      <c r="B740" s="69" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C740" s="70">
-        <v>3056</v>
-      </c>
-      <c r="D740" s="69" t="s">
-        <v>160</v>
-      </c>
-      <c r="E740" s="40">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="741" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A741" s="69" t="s">
         <v>1191</v>
       </c>
       <c r="B741" s="69" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="C741" s="70">
-        <v>3083</v>
+        <v>3056</v>
       </c>
       <c r="D741" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E741" s="40">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="742" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A742" s="69" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B742" s="69" t="s">
-        <v>1130</v>
+        <v>1137</v>
       </c>
       <c r="C742" s="70">
-        <v>2264</v>
+        <v>3083</v>
       </c>
       <c r="D742" s="69" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E742" s="40">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="743" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A743" s="69" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B743" s="69" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="C743" s="70">
-        <v>2355</v>
+        <v>2264</v>
       </c>
       <c r="D743" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E743" s="40">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="744" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A744" s="69" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B744" s="69" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C744" s="70">
+        <v>2355</v>
+      </c>
+      <c r="D744" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E744" s="40">
         <v>59</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A744" s="75" t="s">
+    <row r="745" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A745" s="75" t="s">
         <v>1193</v>
       </c>
-      <c r="B744" s="75" t="s">
+      <c r="B745" s="75" t="s">
         <v>1130</v>
       </c>
-      <c r="C744" s="76">
+      <c r="C745" s="76">
         <v>573</v>
       </c>
-      <c r="D744" s="75" t="s">
+      <c r="D745" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="E744" s="44">
+      <c r="E745" s="44">
         <v>59</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A745" s="80" t="s">
+    <row r="746" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A746" s="80" t="s">
         <v>1194</v>
       </c>
-      <c r="B745" s="80" t="s">
+      <c r="B746" s="80" t="s">
         <v>1195</v>
       </c>
-      <c r="C745" s="81">
+      <c r="C746" s="81">
         <v>572</v>
       </c>
-      <c r="D745" s="80" t="s">
+      <c r="D746" s="80" t="s">
         <v>177</v>
       </c>
-      <c r="E745" s="42">
+      <c r="E746" s="42">
         <v>60</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A746" s="65" t="s">
+    <row r="747" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A747" s="65" t="s">
         <v>1196</v>
       </c>
-      <c r="B746" s="65" t="s">
+      <c r="B747" s="65" t="s">
         <v>1154</v>
       </c>
-      <c r="C746" s="81">
+      <c r="C747" s="81">
         <v>4411</v>
-      </c>
-      <c r="D746" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="E746" s="42">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="747" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A747" s="65" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B747" s="65" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C747" s="81">
-        <v>4410</v>
       </c>
       <c r="D747" s="80" t="s">
         <v>15</v>
       </c>
       <c r="E747" s="42">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="748" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A748" s="65" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B748" s="65" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C748" s="81">
+        <v>4410</v>
+      </c>
+      <c r="D748" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="E748" s="42">
         <v>95</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A748" s="102"/>
-      <c r="B748" s="103"/>
-      <c r="C748" s="103"/>
-      <c r="D748" s="104"/>
-      <c r="E748" s="105"/>
-    </row>
-    <row r="749" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="111" t="s">
+    <row r="749" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A749" s="121"/>
+      <c r="B749" s="109"/>
+      <c r="C749" s="109"/>
+      <c r="D749" s="110"/>
+      <c r="E749" s="117"/>
+    </row>
+    <row r="750" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A750" s="118" t="s">
         <v>1301</v>
       </c>
-      <c r="B749" s="112"/>
-      <c r="C749" s="112"/>
-      <c r="D749" s="112"/>
-      <c r="E749" s="113"/>
-    </row>
-    <row r="750" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A750" s="66" t="s">
+      <c r="B750" s="119"/>
+      <c r="C750" s="119"/>
+      <c r="D750" s="119"/>
+      <c r="E750" s="120"/>
+    </row>
+    <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A751" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B750" s="66"/>
-      <c r="C750" s="66" t="s">
+      <c r="B751" s="66"/>
+      <c r="C751" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D750" s="66" t="s">
+      <c r="D751" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E750" s="47" t="s">
+      <c r="E751" s="47" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A751" s="82" t="s">
+    <row r="752" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A752" s="82" t="s">
         <v>1328</v>
       </c>
-      <c r="B751" s="82" t="s">
+      <c r="B752" s="82" t="s">
         <v>1329</v>
       </c>
-      <c r="C751" s="82">
+      <c r="C752" s="82">
         <v>4044</v>
       </c>
-      <c r="D751" s="101" t="s">
+      <c r="D752" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E751" s="61">
+      <c r="E752" s="61">
         <v>22</v>
-      </c>
-    </row>
-    <row r="752" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A752" s="72" t="s">
-        <v>439</v>
-      </c>
-      <c r="B752" s="72" t="s">
-        <v>145</v>
-      </c>
-      <c r="C752" s="73">
-        <v>4043</v>
-      </c>
-      <c r="D752" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E752" s="48">
-        <v>63</v>
       </c>
     </row>
     <row r="753" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A753" s="72" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B753" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C753" s="73">
-        <v>3531</v>
+        <v>4043</v>
       </c>
       <c r="D753" s="74" t="s">
         <v>20</v>
@@ -18009,13 +18009,13 @@
     </row>
     <row r="754" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="72" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B754" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C754" s="73">
-        <v>3974</v>
+        <v>3531</v>
       </c>
       <c r="D754" s="74" t="s">
         <v>20</v>
@@ -18024,15 +18024,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="755" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="72" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B755" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C755" s="73">
-        <v>3530</v>
+        <v>3974</v>
       </c>
       <c r="D755" s="74" t="s">
         <v>20</v>
@@ -18043,47 +18043,47 @@
     </row>
     <row r="756" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="72" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B756" s="72" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="C756" s="73">
-        <v>4282</v>
+        <v>3530</v>
       </c>
       <c r="D756" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E756" s="48">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="757" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="72" t="s">
-        <v>1207</v>
+        <v>443</v>
       </c>
       <c r="B757" s="72" t="s">
-        <v>1206</v>
+        <v>78</v>
       </c>
       <c r="C757" s="73">
-        <v>3870</v>
+        <v>4282</v>
       </c>
       <c r="D757" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E757" s="48">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="758" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="72" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B758" s="72" t="s">
         <v>1206</v>
       </c>
       <c r="C758" s="73">
-        <v>3701</v>
+        <v>3870</v>
       </c>
       <c r="D758" s="74" t="s">
         <v>20</v>
@@ -18094,13 +18094,13 @@
     </row>
     <row r="759" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="72" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B759" s="72" t="s">
         <v>1206</v>
       </c>
       <c r="C759" s="73">
-        <v>3800</v>
+        <v>3701</v>
       </c>
       <c r="D759" s="74" t="s">
         <v>20</v>
@@ -18109,78 +18109,66 @@
         <v>22</v>
       </c>
     </row>
-    <row r="760" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="72" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B760" s="72" t="s">
         <v>1206</v>
       </c>
       <c r="C760" s="73">
-        <v>3725</v>
+        <v>3800</v>
       </c>
       <c r="D760" s="74" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E760" s="48">
         <v>22</v>
       </c>
     </row>
-    <row r="761" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A761" s="72" t="s">
-        <v>1235</v>
+        <v>1210</v>
       </c>
       <c r="B761" s="72" t="s">
         <v>1206</v>
       </c>
       <c r="C761" s="73">
+        <v>3725</v>
+      </c>
+      <c r="D761" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="E761" s="48">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="762" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A762" s="72" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B762" s="72" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C762" s="73">
         <v>3871</v>
-      </c>
-      <c r="D761" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E761" s="48">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="762" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A762" s="72" t="s">
-        <v>463</v>
-      </c>
-      <c r="B762" s="72" t="s">
-        <v>145</v>
-      </c>
-      <c r="C762" s="73">
-        <v>2825</v>
       </c>
       <c r="D762" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E762" s="48">
-        <v>23.5</v>
-      </c>
-      <c r="F762" s="54"/>
-      <c r="G762" s="54"/>
-      <c r="I762" s="57"/>
-      <c r="J762" s="58"/>
-      <c r="K762" s="60"/>
-      <c r="L762" s="59"/>
-      <c r="M762" s="59"/>
-      <c r="N762" s="59"/>
-      <c r="O762" s="59"/>
-      <c r="P762" s="59"/>
-      <c r="Q762" s="59"/>
-      <c r="R762" s="58"/>
+        <v>27</v>
+      </c>
     </row>
     <row r="763" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="72" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B763" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C763" s="73">
-        <v>2828</v>
+        <v>2825</v>
       </c>
       <c r="D763" s="74" t="s">
         <v>20</v>
@@ -18188,18 +18176,28 @@
       <c r="E763" s="48">
         <v>23.5</v>
       </c>
-      <c r="G763" s="55"/>
-      <c r="H763" s="56"/>
+      <c r="F763" s="54"/>
+      <c r="G763" s="54"/>
+      <c r="I763" s="57"/>
+      <c r="J763" s="58"/>
+      <c r="K763" s="60"/>
+      <c r="L763" s="59"/>
+      <c r="M763" s="59"/>
+      <c r="N763" s="59"/>
+      <c r="O763" s="59"/>
+      <c r="P763" s="59"/>
+      <c r="Q763" s="59"/>
+      <c r="R763" s="58"/>
     </row>
     <row r="764" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="72" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B764" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C764" s="73">
-        <v>2826</v>
+        <v>2828</v>
       </c>
       <c r="D764" s="74" t="s">
         <v>20</v>
@@ -18207,16 +18205,18 @@
       <c r="E764" s="48">
         <v>23.5</v>
       </c>
+      <c r="G764" s="55"/>
+      <c r="H764" s="56"/>
     </row>
     <row r="765" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="72" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B765" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C765" s="73">
-        <v>3058</v>
+        <v>2826</v>
       </c>
       <c r="D765" s="74" t="s">
         <v>20</v>
@@ -18227,13 +18227,13 @@
     </row>
     <row r="766" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="72" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B766" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C766" s="73">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="D766" s="74" t="s">
         <v>20</v>
@@ -18244,13 +18244,13 @@
     </row>
     <row r="767" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="72" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B767" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C767" s="73">
-        <v>2829</v>
+        <v>3059</v>
       </c>
       <c r="D767" s="74" t="s">
         <v>20</v>
@@ -18261,13 +18261,13 @@
     </row>
     <row r="768" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="72" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B768" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C768" s="73">
-        <v>4126</v>
+        <v>2829</v>
       </c>
       <c r="D768" s="74" t="s">
         <v>20</v>
@@ -18278,13 +18278,13 @@
     </row>
     <row r="769" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="72" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B769" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C769" s="73">
-        <v>2827</v>
+        <v>4126</v>
       </c>
       <c r="D769" s="74" t="s">
         <v>20</v>
@@ -18295,30 +18295,30 @@
     </row>
     <row r="770" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="72" t="s">
-        <v>1252</v>
+        <v>470</v>
       </c>
       <c r="B770" s="72" t="s">
-        <v>1206</v>
+        <v>145</v>
       </c>
       <c r="C770" s="73">
-        <v>3801</v>
+        <v>2827</v>
       </c>
       <c r="D770" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E770" s="48">
-        <v>25</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="771" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="72" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B771" s="72" t="s">
         <v>1206</v>
       </c>
       <c r="C771" s="73">
-        <v>3833</v>
+        <v>3801</v>
       </c>
       <c r="D771" s="74" t="s">
         <v>20</v>
@@ -18327,88 +18327,88 @@
         <v>25</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="72" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B772" s="72" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C772" s="73">
+        <v>3833</v>
+      </c>
+      <c r="D772" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E772" s="48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="773" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A773" s="72" t="s">
         <v>474</v>
-      </c>
-      <c r="B772" s="72" t="s">
-        <v>145</v>
-      </c>
-      <c r="C772" s="73">
-        <v>3897</v>
-      </c>
-      <c r="D772" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="E772" s="48">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="773" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A773" s="72" t="s">
-        <v>475</v>
       </c>
       <c r="B773" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C773" s="73">
+        <v>3897</v>
+      </c>
+      <c r="D773" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="E773" s="48">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="774" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A774" s="72" t="s">
+        <v>475</v>
+      </c>
+      <c r="B774" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C774" s="73">
         <v>3764</v>
       </c>
-      <c r="D773" s="74" t="s">
+      <c r="D774" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="E773" s="48">
+      <c r="E774" s="48">
         <v>78</v>
       </c>
     </row>
-    <row r="774" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A774" s="96"/>
-      <c r="B774" s="96"/>
-      <c r="C774" s="97"/>
-      <c r="D774" s="96"/>
-      <c r="E774" s="98"/>
-    </row>
     <row r="775" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A775" s="108" t="s">
+      <c r="A775" s="96"/>
+      <c r="B775" s="96"/>
+      <c r="C775" s="97"/>
+      <c r="D775" s="96"/>
+      <c r="E775" s="98"/>
+    </row>
+    <row r="776" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A776" s="130" t="s">
         <v>1287</v>
       </c>
-      <c r="B775" s="109"/>
-      <c r="C775" s="109"/>
-      <c r="D775" s="109"/>
-      <c r="E775" s="110"/>
-    </row>
-    <row r="776" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A776" s="66" t="s">
+      <c r="B776" s="131"/>
+      <c r="C776" s="131"/>
+      <c r="D776" s="131"/>
+      <c r="E776" s="132"/>
+    </row>
+    <row r="777" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A777" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B776" s="66" t="s">
+      <c r="B777" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="C776" s="66" t="s">
+      <c r="C777" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D776" s="66" t="s">
+      <c r="D777" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E776" s="47" t="s">
+      <c r="E777" s="47" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="777" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A777" s="72" t="s">
-        <v>425</v>
-      </c>
-      <c r="B777" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C777" s="73">
-        <v>3438</v>
-      </c>
-      <c r="D777" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E777" s="48">
-        <v>228</v>
       </c>
     </row>
     <row r="778" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -18416,33 +18416,33 @@
         <v>425</v>
       </c>
       <c r="B778" s="72" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="C778" s="73">
-        <v>3434</v>
+        <v>3438</v>
       </c>
       <c r="D778" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E778" s="48">
-        <v>76</v>
+        <v>228</v>
       </c>
     </row>
     <row r="779" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A779" s="72" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B779" s="72" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="C779" s="73">
-        <v>3443</v>
+        <v>3434</v>
       </c>
       <c r="D779" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E779" s="48">
-        <v>228</v>
+        <v>76</v>
       </c>
     </row>
     <row r="780" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -18450,67 +18450,67 @@
         <v>426</v>
       </c>
       <c r="B780" s="72" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="C780" s="73">
-        <v>3019</v>
+        <v>3443</v>
       </c>
       <c r="D780" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E780" s="48">
-        <v>76</v>
+        <v>228</v>
       </c>
     </row>
     <row r="781" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="72" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B781" s="72" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="C781" s="73">
-        <v>4489</v>
+        <v>3019</v>
       </c>
       <c r="D781" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E781" s="48">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="782" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="782" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="72" t="s">
         <v>427</v>
       </c>
       <c r="B782" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="C782" s="73">
+        <v>4489</v>
+      </c>
+      <c r="D782" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E782" s="48">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="783" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A783" s="72" t="s">
+        <v>427</v>
+      </c>
+      <c r="B783" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C782" s="73">
+      <c r="C783" s="73">
         <v>4490</v>
       </c>
-      <c r="D782" s="74" t="s">
+      <c r="D783" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="E782" s="48">
+      <c r="E783" s="48">
         <v>76</v>
-      </c>
-    </row>
-    <row r="783" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A783" s="72" t="s">
-        <v>428</v>
-      </c>
-      <c r="B783" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C783" s="73">
-        <v>3476</v>
-      </c>
-      <c r="D783" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E783" s="48">
-        <v>228</v>
       </c>
     </row>
     <row r="784" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -18518,84 +18518,84 @@
         <v>428</v>
       </c>
       <c r="B784" s="72" t="s">
+        <v>120</v>
+      </c>
+      <c r="C784" s="73">
+        <v>3476</v>
+      </c>
+      <c r="D784" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E784" s="48">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="785" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A785" s="72" t="s">
+        <v>428</v>
+      </c>
+      <c r="B785" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C784" s="73">
+      <c r="C785" s="73">
         <v>3477</v>
       </c>
-      <c r="D784" s="74" t="s">
+      <c r="D785" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="E784" s="48">
+      <c r="E785" s="48">
         <v>76</v>
-      </c>
-    </row>
-    <row r="785" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A785" s="72" t="s">
-        <v>1312</v>
-      </c>
-      <c r="B785" s="72" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C785" s="73">
-        <v>4344</v>
-      </c>
-      <c r="D785" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E785" s="48">
-        <v>328</v>
       </c>
     </row>
     <row r="786" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A786" s="72" t="s">
-        <v>429</v>
+        <v>1312</v>
       </c>
       <c r="B786" s="72" t="s">
-        <v>18</v>
+        <v>1154</v>
       </c>
       <c r="C786" s="73">
-        <v>3123</v>
+        <v>4344</v>
       </c>
       <c r="D786" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E786" s="48">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="787" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="787" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A787" s="72" t="s">
         <v>429</v>
       </c>
       <c r="B787" s="72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C787" s="73">
-        <v>2674</v>
+        <v>3123</v>
       </c>
       <c r="D787" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E787" s="48">
-        <v>60.5</v>
+        <v>121</v>
       </c>
     </row>
     <row r="788" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A788" s="72" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B788" s="72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C788" s="73">
-        <v>3719</v>
+        <v>2674</v>
       </c>
       <c r="D788" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E788" s="48">
-        <v>138</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="789" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -18603,33 +18603,33 @@
         <v>430</v>
       </c>
       <c r="B789" s="72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C789" s="73">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="D789" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E789" s="48">
-        <v>69</v>
+        <v>138</v>
       </c>
     </row>
     <row r="790" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="72" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B790" s="72" t="s">
-        <v>1124</v>
+        <v>19</v>
       </c>
       <c r="C790" s="73">
-        <v>3765</v>
+        <v>3720</v>
       </c>
       <c r="D790" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E790" s="48">
-        <v>138</v>
+        <v>69</v>
       </c>
     </row>
     <row r="791" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -18637,67 +18637,67 @@
         <v>431</v>
       </c>
       <c r="B791" s="72" t="s">
-        <v>19</v>
+        <v>1124</v>
       </c>
       <c r="C791" s="73">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="D791" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E791" s="48">
-        <v>69</v>
+        <v>138</v>
       </c>
     </row>
     <row r="792" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B792" s="72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C792" s="73">
-        <v>3126</v>
+        <v>3766</v>
       </c>
       <c r="D792" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E792" s="48">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="793" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="793" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="72" t="s">
         <v>432</v>
       </c>
       <c r="B793" s="72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C793" s="73">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="D793" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E793" s="48">
-        <v>60.5</v>
+        <v>121</v>
       </c>
     </row>
     <row r="794" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="72" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B794" s="72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C794" s="73">
-        <v>3435</v>
+        <v>3127</v>
       </c>
       <c r="D794" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E794" s="48">
-        <v>121</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="795" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -18705,33 +18705,33 @@
         <v>433</v>
       </c>
       <c r="B795" s="72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C795" s="73">
-        <v>3436</v>
+        <v>3435</v>
       </c>
       <c r="D795" s="74" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="E795" s="48">
-        <v>60.5</v>
+        <v>121</v>
       </c>
     </row>
     <row r="796" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="72" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B796" s="72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C796" s="73">
-        <v>3128</v>
+        <v>3436</v>
       </c>
       <c r="D796" s="74" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E796" s="48">
-        <v>121</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="797" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -18739,33 +18739,33 @@
         <v>434</v>
       </c>
       <c r="B797" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C797" s="73">
+        <v>3128</v>
+      </c>
+      <c r="D797" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E797" s="48">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="798" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A798" s="72" t="s">
+        <v>434</v>
+      </c>
+      <c r="B798" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C797" s="73">
+      <c r="C798" s="73">
         <v>3129</v>
       </c>
-      <c r="D797" s="74" t="s">
+      <c r="D798" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="E797" s="48">
+      <c r="E798" s="48">
         <v>60.5</v>
-      </c>
-    </row>
-    <row r="798" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A798" s="72" t="s">
-        <v>435</v>
-      </c>
-      <c r="B798" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="C798" s="73">
-        <v>4158</v>
-      </c>
-      <c r="D798" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E798" s="48">
-        <v>121</v>
       </c>
     </row>
     <row r="799" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -18773,33 +18773,33 @@
         <v>435</v>
       </c>
       <c r="B799" s="72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C799" s="73">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="D799" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E799" s="48">
-        <v>60.5</v>
+        <v>121</v>
       </c>
     </row>
     <row r="800" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="72" t="s">
-        <v>1325</v>
+        <v>435</v>
       </c>
       <c r="B800" s="72" t="s">
-        <v>1124</v>
+        <v>19</v>
       </c>
       <c r="C800" s="73">
-        <v>4561</v>
+        <v>4159</v>
       </c>
       <c r="D800" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E800" s="48">
-        <v>138</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="801" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -18807,33 +18807,33 @@
         <v>1325</v>
       </c>
       <c r="B801" s="72" t="s">
-        <v>1326</v>
+        <v>1124</v>
       </c>
       <c r="C801" s="73">
-        <v>4562</v>
+        <v>4561</v>
       </c>
       <c r="D801" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E801" s="48">
-        <v>69</v>
+        <v>138</v>
       </c>
     </row>
     <row r="802" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="72" t="s">
-        <v>436</v>
+        <v>1325</v>
       </c>
       <c r="B802" s="72" t="s">
-        <v>18</v>
+        <v>1326</v>
       </c>
       <c r="C802" s="73">
-        <v>3124</v>
+        <v>4562</v>
       </c>
       <c r="D802" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E802" s="48">
-        <v>161</v>
+        <v>69</v>
       </c>
     </row>
     <row r="803" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -18841,33 +18841,33 @@
         <v>436</v>
       </c>
       <c r="B803" s="72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C803" s="73">
-        <v>2824</v>
+        <v>3124</v>
       </c>
       <c r="D803" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E803" s="48">
-        <v>80.5</v>
+        <v>161</v>
       </c>
     </row>
     <row r="804" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="72" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B804" s="72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C804" s="73">
-        <v>3130</v>
+        <v>2824</v>
       </c>
       <c r="D804" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E804" s="48">
-        <v>138</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="805" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -18875,44 +18875,44 @@
         <v>437</v>
       </c>
       <c r="B805" s="72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C805" s="73">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="D805" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E805" s="48">
-        <v>69</v>
+        <v>138</v>
       </c>
     </row>
     <row r="806" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="72" t="s">
-        <v>1199</v>
+        <v>437</v>
       </c>
       <c r="B806" s="72" t="s">
-        <v>1154</v>
+        <v>19</v>
       </c>
       <c r="C806" s="73">
-        <v>4346</v>
+        <v>3131</v>
       </c>
       <c r="D806" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E806" s="48">
-        <v>328</v>
+        <v>69</v>
       </c>
     </row>
     <row r="807" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="72" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B807" s="72" t="s">
         <v>1154</v>
       </c>
       <c r="C807" s="73">
-        <v>4345</v>
+        <v>4346</v>
       </c>
       <c r="D807" s="74" t="s">
         <v>15</v>
@@ -18923,370 +18923,370 @@
     </row>
     <row r="808" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="72" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B808" s="72" t="s">
-        <v>1130</v>
+        <v>1154</v>
       </c>
       <c r="C808" s="73">
-        <v>4347</v>
+        <v>4345</v>
       </c>
       <c r="D808" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E808" s="48">
-        <v>274</v>
+        <v>328</v>
       </c>
     </row>
     <row r="809" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="72" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B809" s="72" t="s">
-        <v>1154</v>
+        <v>1130</v>
       </c>
       <c r="C809" s="73">
-        <v>4446</v>
+        <v>4347</v>
       </c>
       <c r="D809" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E809" s="48">
-        <v>325</v>
+        <v>274</v>
       </c>
     </row>
     <row r="810" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="72" t="s">
-        <v>438</v>
+        <v>1202</v>
       </c>
       <c r="B810" s="72" t="s">
-        <v>78</v>
+        <v>1154</v>
       </c>
       <c r="C810" s="73">
-        <v>4476</v>
+        <v>4446</v>
       </c>
       <c r="D810" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E810" s="48">
-        <v>30</v>
+        <v>325</v>
       </c>
     </row>
     <row r="811" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="72" t="s">
-        <v>1203</v>
+        <v>438</v>
       </c>
       <c r="B811" s="72" t="s">
-        <v>1154</v>
+        <v>78</v>
       </c>
       <c r="C811" s="73">
-        <v>4348</v>
+        <v>4476</v>
       </c>
       <c r="D811" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E811" s="48">
-        <v>328</v>
+        <v>30</v>
       </c>
     </row>
     <row r="812" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="72" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B812" s="72" t="s">
-        <v>1205</v>
+        <v>1154</v>
       </c>
       <c r="C812" s="73">
-        <v>4456</v>
+        <v>4348</v>
       </c>
       <c r="D812" s="74" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="E812" s="48">
-        <v>69</v>
+        <v>328</v>
       </c>
     </row>
     <row r="813" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="72" t="s">
-        <v>444</v>
+        <v>1204</v>
       </c>
       <c r="B813" s="72" t="s">
-        <v>110</v>
+        <v>1205</v>
       </c>
       <c r="C813" s="73">
-        <v>4051</v>
+        <v>4456</v>
       </c>
       <c r="D813" s="74" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E813" s="48">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="814" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="72" t="s">
-        <v>1313</v>
+        <v>444</v>
       </c>
       <c r="B814" s="72" t="s">
-        <v>1149</v>
+        <v>110</v>
       </c>
       <c r="C814" s="73">
-        <v>4408</v>
+        <v>4051</v>
       </c>
       <c r="D814" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E814" s="48">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="815" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="72" t="s">
-        <v>1211</v>
+        <v>1313</v>
       </c>
       <c r="B815" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C815" s="73">
-        <v>4341</v>
+        <v>4408</v>
       </c>
       <c r="D815" s="74" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E815" s="48">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="816" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="72" t="s">
-        <v>448</v>
+        <v>1211</v>
       </c>
       <c r="B816" s="72" t="s">
-        <v>145</v>
+        <v>1149</v>
       </c>
       <c r="C816" s="73">
-        <v>4265</v>
+        <v>4341</v>
       </c>
       <c r="D816" s="74" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E816" s="48">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="817" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="72" t="s">
-        <v>1212</v>
+        <v>448</v>
       </c>
       <c r="B817" s="72" t="s">
-        <v>1149</v>
+        <v>145</v>
       </c>
       <c r="C817" s="73">
-        <v>4266</v>
+        <v>4265</v>
       </c>
       <c r="D817" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E817" s="48">
-        <v>81.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="818" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="72" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B818" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C818" s="73">
-        <v>4269</v>
+        <v>4266</v>
       </c>
       <c r="D818" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E818" s="48">
-        <v>87.5</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="819" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="72" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B819" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C819" s="73">
-        <v>4273</v>
+        <v>4269</v>
       </c>
       <c r="D819" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E819" s="48">
-        <v>94</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="820" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="72" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B820" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C820" s="73">
-        <v>4405</v>
+        <v>4273</v>
       </c>
       <c r="D820" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E820" s="48">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="821" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="72" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B821" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C821" s="73">
-        <v>4406</v>
+        <v>4405</v>
       </c>
       <c r="D821" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E821" s="48">
-        <v>130</v>
+        <v>78</v>
       </c>
     </row>
     <row r="822" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="72" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B822" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C822" s="73">
-        <v>4267</v>
+        <v>4406</v>
       </c>
       <c r="D822" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E822" s="48">
-        <v>81.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="823" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="72" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B823" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C823" s="73">
-        <v>4271</v>
+        <v>4267</v>
       </c>
       <c r="D823" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E823" s="48">
-        <v>87.5</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="824" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="72" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B824" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C824" s="73">
-        <v>4276</v>
+        <v>4271</v>
       </c>
       <c r="D824" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E824" s="48">
-        <v>119</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="825" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="72" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B825" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C825" s="73">
-        <v>4342</v>
+        <v>4276</v>
       </c>
       <c r="D825" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E825" s="48">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="826" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="72" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B826" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C826" s="73">
-        <v>4398</v>
+        <v>4342</v>
       </c>
       <c r="D826" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E826" s="48">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="827" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="72" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B827" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C827" s="73">
-        <v>4270</v>
+        <v>4398</v>
       </c>
       <c r="D827" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E827" s="48">
-        <v>87.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="828" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="72" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B828" s="72" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="C828" s="73">
-        <v>4275</v>
+        <v>4270</v>
       </c>
       <c r="D828" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E828" s="48">
-        <v>54</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="829" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="72" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B829" s="72" t="s">
         <v>1145</v>
       </c>
       <c r="C829" s="73">
-        <v>4274</v>
+        <v>4275</v>
       </c>
       <c r="D829" s="74" t="s">
         <v>20</v>
@@ -19297,64 +19297,64 @@
     </row>
     <row r="830" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="72" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B830" s="72" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="C830" s="73">
-        <v>4399</v>
+        <v>4274</v>
       </c>
       <c r="D830" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E830" s="48">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="831" spans="1:5" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="831" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="72" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B831" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C831" s="73">
-        <v>4404</v>
+        <v>4399</v>
       </c>
       <c r="D831" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E831" s="48">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="832" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="832" spans="1:5" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A832" s="72" t="s">
-        <v>449</v>
+        <v>1226</v>
       </c>
       <c r="B832" s="72" t="s">
-        <v>145</v>
+        <v>1149</v>
       </c>
       <c r="C832" s="73">
-        <v>4262</v>
+        <v>4404</v>
       </c>
       <c r="D832" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E832" s="48">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="833" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="833" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A833" s="72" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B833" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C833" s="73">
-        <v>4263</v>
+        <v>4262</v>
       </c>
       <c r="D833" s="74" t="s">
         <v>20</v>
@@ -19365,13 +19365,13 @@
     </row>
     <row r="834" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="72" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B834" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C834" s="73">
-        <v>4264</v>
+        <v>4263</v>
       </c>
       <c r="D834" s="74" t="s">
         <v>20</v>
@@ -19382,87 +19382,87 @@
     </row>
     <row r="835" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="72" t="s">
-        <v>1227</v>
+        <v>451</v>
       </c>
       <c r="B835" s="72" t="s">
-        <v>1149</v>
+        <v>145</v>
       </c>
       <c r="C835" s="73">
-        <v>4407</v>
+        <v>4264</v>
       </c>
       <c r="D835" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E835" s="48">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="836" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="72" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B836" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C836" s="73">
-        <v>4397</v>
+        <v>4407</v>
       </c>
       <c r="D836" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E836" s="48">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="837" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A837" s="72" t="s">
-        <v>452</v>
+        <v>1228</v>
       </c>
       <c r="B837" s="72" t="s">
-        <v>145</v>
+        <v>1149</v>
       </c>
       <c r="C837" s="73">
-        <v>4343</v>
+        <v>4397</v>
       </c>
       <c r="D837" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E837" s="48">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="838" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A838" s="72" t="s">
-        <v>1229</v>
+        <v>452</v>
       </c>
       <c r="B838" s="72" t="s">
-        <v>1149</v>
+        <v>145</v>
       </c>
       <c r="C838" s="73">
-        <v>4268</v>
+        <v>4343</v>
       </c>
       <c r="D838" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E838" s="48">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="839" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A839" s="72" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B839" s="72" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C839" s="73">
+        <v>4268</v>
+      </c>
+      <c r="D839" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E839" s="48">
         <v>81.5</v>
-      </c>
-    </row>
-    <row r="839" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A839" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B839" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C839" s="70">
-        <v>2833</v>
-      </c>
-      <c r="D839" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E839" s="40">
-        <v>81</v>
       </c>
     </row>
     <row r="840" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -19470,101 +19470,101 @@
         <v>61</v>
       </c>
       <c r="B840" s="69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C840" s="70">
-        <v>3125</v>
+        <v>2833</v>
       </c>
       <c r="D840" s="69" t="s">
         <v>49</v>
       </c>
       <c r="E840" s="40">
-        <v>162</v>
+        <v>81</v>
       </c>
     </row>
     <row r="841" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A841" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B841" s="69" t="s">
         <v>18</v>
       </c>
       <c r="C841" s="70">
+        <v>3125</v>
+      </c>
+      <c r="D841" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E841" s="40">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="842" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A842" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="B842" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C842" s="70">
         <v>3752</v>
       </c>
-      <c r="D841" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E841" s="40">
+      <c r="D842" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E842" s="40">
         <v>166</v>
       </c>
     </row>
-    <row r="842" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A842" s="72" t="s">
+    <row r="843" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A843" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="B842" s="72" t="s">
+      <c r="B843" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C842" s="73">
+      <c r="C843" s="73">
         <v>3753</v>
       </c>
-      <c r="D842" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E842" s="50">
+      <c r="D843" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E843" s="50">
         <v>83</v>
-      </c>
-    </row>
-    <row r="843" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A843" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B843" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C843" s="70">
-        <v>2511</v>
-      </c>
-      <c r="D843" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E843" s="40">
-        <v>61</v>
       </c>
     </row>
     <row r="844" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A844" s="69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B844" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C844" s="70">
-        <v>4311</v>
+        <v>2511</v>
       </c>
       <c r="D844" s="69" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E844" s="40">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="845" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A845" s="69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B845" s="69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C845" s="70">
-        <v>4046</v>
+        <v>4311</v>
       </c>
       <c r="D845" s="69" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E845" s="40">
-        <v>166</v>
+        <v>65</v>
       </c>
     </row>
     <row r="846" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -19572,44 +19572,44 @@
         <v>67</v>
       </c>
       <c r="B846" s="69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C846" s="70">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="D846" s="69" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="E846" s="40">
-        <v>83</v>
+        <v>166</v>
       </c>
     </row>
     <row r="847" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A847" s="69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B847" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C847" s="70">
-        <v>4312</v>
+        <v>4047</v>
       </c>
       <c r="D847" s="69" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E847" s="40">
-        <v>65</v>
+        <v>83</v>
       </c>
     </row>
     <row r="848" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A848" s="69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B848" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C848" s="70">
-        <v>4310</v>
+        <v>4312</v>
       </c>
       <c r="D848" s="69" t="s">
         <v>20</v>
@@ -19619,71 +19619,71 @@
       </c>
     </row>
     <row r="849" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A849" s="72" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B849" s="72" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C849" s="73">
-        <v>4074</v>
-      </c>
-      <c r="D849" s="74" t="s">
+      <c r="A849" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B849" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C849" s="70">
+        <v>4310</v>
+      </c>
+      <c r="D849" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E849" s="48">
-        <v>27</v>
+      <c r="E849" s="40">
+        <v>65</v>
       </c>
     </row>
     <row r="850" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A850" s="72" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B850" s="72" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C850" s="73">
-        <v>4076</v>
+        <v>4074</v>
       </c>
       <c r="D850" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E850" s="48">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="851" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A851" s="72" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B851" s="72" t="s">
-        <v>1205</v>
+        <v>1233</v>
       </c>
       <c r="C851" s="73">
-        <v>4133</v>
+        <v>4076</v>
       </c>
       <c r="D851" s="74" t="s">
         <v>453</v>
       </c>
       <c r="E851" s="48">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="852" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A852" s="72" t="s">
-        <v>455</v>
+        <v>1234</v>
       </c>
       <c r="B852" s="72" t="s">
-        <v>120</v>
+        <v>1205</v>
       </c>
       <c r="C852" s="73">
-        <v>3068</v>
+        <v>4133</v>
       </c>
       <c r="D852" s="74" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="E852" s="48">
-        <v>372</v>
+        <v>72</v>
       </c>
     </row>
     <row r="853" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -19691,50 +19691,50 @@
         <v>455</v>
       </c>
       <c r="B853" s="72" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="C853" s="73">
-        <v>3087</v>
+        <v>3068</v>
       </c>
       <c r="D853" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E853" s="48">
-        <v>124</v>
+        <v>372</v>
       </c>
     </row>
     <row r="854" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A854" s="72" t="s">
-        <v>1324</v>
+        <v>455</v>
       </c>
       <c r="B854" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C854" s="73">
-        <v>4560</v>
+        <v>3087</v>
       </c>
       <c r="D854" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E854" s="48">
-        <v>195</v>
+        <v>124</v>
       </c>
     </row>
     <row r="855" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A855" s="72" t="s">
-        <v>456</v>
+        <v>1324</v>
       </c>
       <c r="B855" s="72" t="s">
-        <v>1130</v>
+        <v>19</v>
       </c>
       <c r="C855" s="73">
-        <v>4531</v>
+        <v>4560</v>
       </c>
       <c r="D855" s="74" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E855" s="48">
-        <v>880</v>
+        <v>195</v>
       </c>
     </row>
     <row r="856" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -19742,81 +19742,81 @@
         <v>456</v>
       </c>
       <c r="B856" s="72" t="s">
-        <v>78</v>
+        <v>1130</v>
       </c>
       <c r="C856" s="73">
-        <v>4532</v>
+        <v>4531</v>
       </c>
       <c r="D856" s="74" t="s">
         <v>34</v>
       </c>
       <c r="E856" s="48">
-        <v>88</v>
+        <v>880</v>
       </c>
     </row>
     <row r="857" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="72" t="s">
-        <v>1323</v>
+        <v>456</v>
       </c>
       <c r="B857" s="72" t="s">
-        <v>1164</v>
+        <v>78</v>
       </c>
       <c r="C857" s="73">
-        <v>4559</v>
+        <v>4532</v>
       </c>
       <c r="D857" s="74" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E857" s="48">
-        <v>210</v>
+        <v>88</v>
       </c>
     </row>
     <row r="858" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A858" s="72" t="s">
-        <v>457</v>
+        <v>1323</v>
       </c>
       <c r="B858" s="72" t="s">
-        <v>145</v>
+        <v>1164</v>
       </c>
       <c r="C858" s="73">
-        <v>4493</v>
+        <v>4559</v>
       </c>
       <c r="D858" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E858" s="48">
-        <v>83</v>
+        <v>210</v>
       </c>
     </row>
     <row r="859" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="72" t="s">
-        <v>1236</v>
+        <v>457</v>
       </c>
       <c r="B859" s="72" t="s">
-        <v>1237</v>
+        <v>145</v>
       </c>
       <c r="C859" s="73">
-        <v>4102</v>
+        <v>4493</v>
       </c>
       <c r="D859" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E859" s="48">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="860" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="72" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B860" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C860" s="73">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="D860" s="74" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E860" s="48">
         <v>77</v>
@@ -19824,13 +19824,13 @@
     </row>
     <row r="861" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="72" t="s">
-        <v>1314</v>
+        <v>1238</v>
       </c>
       <c r="B861" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C861" s="73">
-        <v>4547</v>
+        <v>4103</v>
       </c>
       <c r="D861" s="74" t="s">
         <v>160</v>
@@ -19841,13 +19841,13 @@
     </row>
     <row r="862" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="72" t="s">
-        <v>1239</v>
+        <v>1314</v>
       </c>
       <c r="B862" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C862" s="73">
-        <v>4104</v>
+        <v>4547</v>
       </c>
       <c r="D862" s="74" t="s">
         <v>160</v>
@@ -19858,13 +19858,13 @@
     </row>
     <row r="863" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="72" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B863" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C863" s="73">
-        <v>4101</v>
+        <v>4104</v>
       </c>
       <c r="D863" s="74" t="s">
         <v>160</v>
@@ -19875,13 +19875,13 @@
     </row>
     <row r="864" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="72" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B864" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C864" s="73">
-        <v>4105</v>
+        <v>4101</v>
       </c>
       <c r="D864" s="74" t="s">
         <v>160</v>
@@ -19890,69 +19890,69 @@
         <v>77</v>
       </c>
     </row>
-    <row r="865" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="72" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B865" s="72" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="C865" s="73">
-        <v>3705</v>
+        <v>4105</v>
       </c>
       <c r="D865" s="74" t="s">
         <v>160</v>
       </c>
       <c r="E865" s="48">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="866" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A866" s="72" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B866" s="72" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C866" s="73">
+        <v>3705</v>
+      </c>
+      <c r="D866" s="74" t="s">
+        <v>160</v>
+      </c>
+      <c r="E866" s="48">
         <v>123.5</v>
-      </c>
-    </row>
-    <row r="866" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A866" s="72" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B866" s="72" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C866" s="73">
-        <v>3823</v>
-      </c>
-      <c r="D866" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E866" s="48">
-        <v>77</v>
       </c>
     </row>
     <row r="867" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="72" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B867" s="72" t="s">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="C867" s="73">
-        <v>4308</v>
+        <v>3823</v>
       </c>
       <c r="D867" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E867" s="48">
-        <v>68.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="868" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="72" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B868" s="72" t="s">
         <v>1246</v>
       </c>
       <c r="C868" s="73">
-        <v>4309</v>
+        <v>4308</v>
       </c>
       <c r="D868" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E868" s="48">
         <v>68.5</v>
@@ -19960,36 +19960,36 @@
     </row>
     <row r="869" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="72" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B869" s="72" t="s">
-        <v>1149</v>
+        <v>1246</v>
       </c>
       <c r="C869" s="73">
-        <v>4412</v>
+        <v>4309</v>
       </c>
       <c r="D869" s="74" t="s">
         <v>453</v>
       </c>
       <c r="E869" s="48">
-        <v>71.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="870" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="72" t="s">
-        <v>459</v>
+        <v>1248</v>
       </c>
       <c r="B870" s="72" t="s">
-        <v>33</v>
+        <v>1149</v>
       </c>
       <c r="C870" s="73">
-        <v>4413</v>
+        <v>4412</v>
       </c>
       <c r="D870" s="74" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="E870" s="48">
-        <v>496</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="871" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -19997,33 +19997,33 @@
         <v>459</v>
       </c>
       <c r="B871" s="72" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C871" s="73">
-        <v>4414</v>
+        <v>4413</v>
       </c>
       <c r="D871" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E871" s="48">
-        <v>101</v>
+        <v>496</v>
       </c>
     </row>
     <row r="872" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A872" s="72" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B872" s="72" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C872" s="73">
-        <v>4415</v>
+        <v>4414</v>
       </c>
       <c r="D872" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E872" s="48">
-        <v>414</v>
+        <v>101</v>
       </c>
     </row>
     <row r="873" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20031,64 +20031,64 @@
         <v>460</v>
       </c>
       <c r="B873" s="72" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C873" s="73">
-        <v>4416</v>
+        <v>4415</v>
       </c>
       <c r="D873" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E873" s="48">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="874" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="874" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="72" t="s">
-        <v>1254</v>
+        <v>460</v>
       </c>
       <c r="B874" s="72" t="s">
-        <v>1255</v>
+        <v>19</v>
       </c>
       <c r="C874" s="73">
-        <v>4475</v>
+        <v>4416</v>
       </c>
       <c r="D874" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E874" s="48">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="875" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A875" s="72" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B875" s="72" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C875" s="73">
+        <v>4475</v>
+      </c>
+      <c r="D875" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E875" s="48">
         <v>8</v>
-      </c>
-    </row>
-    <row r="875" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A875" s="72" t="s">
-        <v>1256</v>
-      </c>
-      <c r="B875" s="72" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C875" s="73">
-        <v>4354</v>
-      </c>
-      <c r="D875" s="74" t="s">
-        <v>412</v>
-      </c>
-      <c r="E875" s="48">
-        <v>74</v>
       </c>
     </row>
     <row r="876" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="72" t="s">
-        <v>1335</v>
+        <v>1256</v>
       </c>
       <c r="B876" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C876" s="73">
-        <v>4445</v>
+        <v>4354</v>
       </c>
       <c r="D876" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E876" s="48">
         <v>74</v>
@@ -20096,16 +20096,16 @@
     </row>
     <row r="877" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="72" t="s">
-        <v>1258</v>
+        <v>1335</v>
       </c>
       <c r="B877" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C877" s="73">
-        <v>4353</v>
+        <v>4445</v>
       </c>
       <c r="D877" s="74" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E877" s="48">
         <v>74</v>
@@ -20113,13 +20113,13 @@
     </row>
     <row r="878" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="72" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B878" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C878" s="73">
-        <v>4350</v>
+        <v>4353</v>
       </c>
       <c r="D878" s="74" t="s">
         <v>50</v>
@@ -20130,13 +20130,13 @@
     </row>
     <row r="879" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="72" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B879" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C879" s="73">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="D879" s="74" t="s">
         <v>50</v>
@@ -20147,13 +20147,13 @@
     </row>
     <row r="880" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="72" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B880" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C880" s="73">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="D880" s="74" t="s">
         <v>50</v>
@@ -20164,13 +20164,13 @@
     </row>
     <row r="881" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="72" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B881" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C881" s="73">
-        <v>4351</v>
+        <v>4349</v>
       </c>
       <c r="D881" s="74" t="s">
         <v>50</v>
@@ -20180,82 +20180,82 @@
       </c>
     </row>
     <row r="882" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A882" s="96" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B882" s="96" t="s">
+      <c r="A882" s="72" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B882" s="72" t="s">
         <v>1257</v>
       </c>
-      <c r="C882" s="97">
-        <v>4581</v>
-      </c>
-      <c r="D882" s="96" t="s">
-        <v>15</v>
+      <c r="C882" s="73">
+        <v>4351</v>
+      </c>
+      <c r="D882" s="74" t="s">
+        <v>50</v>
       </c>
       <c r="E882" s="48">
         <v>74</v>
       </c>
     </row>
     <row r="883" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A883" s="80" t="s">
+      <c r="A883" s="96" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B883" s="96" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C883" s="97">
+        <v>4581</v>
+      </c>
+      <c r="D883" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="E883" s="48">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="884" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A884" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="B883" s="80" t="s">
+      <c r="B884" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="C883" s="81">
+      <c r="C884" s="81">
         <v>4096</v>
       </c>
-      <c r="D883" s="80" t="s">
-        <v>49</v>
-      </c>
-      <c r="E883" s="42">
+      <c r="D884" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="E884" s="42">
         <v>79</v>
-      </c>
-    </row>
-    <row r="884" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A884" s="72" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B884" s="72" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C884" s="73">
-        <v>4123</v>
-      </c>
-      <c r="D884" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E884" s="48">
-        <v>60</v>
       </c>
     </row>
     <row r="885" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A885" s="72" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B885" s="72" t="s">
-        <v>1237</v>
+        <v>1274</v>
       </c>
       <c r="C885" s="73">
-        <v>4306</v>
+        <v>4123</v>
       </c>
       <c r="D885" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E885" s="48">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="886" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="72" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B886" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C886" s="73">
-        <v>4307</v>
+        <v>4306</v>
       </c>
       <c r="D886" s="74" t="s">
         <v>453</v>
@@ -20266,19 +20266,19 @@
     </row>
     <row r="887" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A887" s="72" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B887" s="72" t="s">
-        <v>1278</v>
+        <v>1237</v>
       </c>
       <c r="C887" s="73">
-        <v>2659</v>
-      </c>
-      <c r="D887" s="72" t="s">
-        <v>160</v>
-      </c>
-      <c r="E887" s="50">
-        <v>27.5</v>
+        <v>4307</v>
+      </c>
+      <c r="D887" s="74" t="s">
+        <v>453</v>
+      </c>
+      <c r="E887" s="48">
+        <v>81</v>
       </c>
     </row>
     <row r="888" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20286,41 +20286,51 @@
         <v>1277</v>
       </c>
       <c r="B888" s="72" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C888" s="73">
-        <v>2621</v>
+        <v>2659</v>
       </c>
       <c r="D888" s="72" t="s">
         <v>160</v>
       </c>
       <c r="E888" s="50">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="889" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="72" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="B889" s="72" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C889" s="73">
-        <v>3656</v>
+        <v>2621</v>
       </c>
       <c r="D889" s="72" t="s">
         <v>160</v>
       </c>
       <c r="E889" s="50">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="890" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A890" s="72" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B890" s="72" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C890" s="73">
+        <v>3656</v>
+      </c>
+      <c r="D890" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="E890" s="50">
         <v>27</v>
       </c>
-    </row>
-    <row r="890" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A890" s="99"/>
-      <c r="B890" s="99"/>
-      <c r="C890" s="99"/>
-      <c r="D890" s="99"/>
-      <c r="E890" s="100"/>
     </row>
     <row r="891" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A891" s="99"/>
@@ -20336,271 +20346,277 @@
       <c r="D892" s="99"/>
       <c r="E892" s="100"/>
     </row>
-    <row r="893" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A893" s="121" t="s">
+    <row r="893" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A893" s="99"/>
+      <c r="B893" s="99"/>
+      <c r="C893" s="99"/>
+      <c r="D893" s="99"/>
+      <c r="E893" s="100"/>
+    </row>
+    <row r="894" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A894" s="102" t="s">
         <v>1288</v>
       </c>
-      <c r="B893" s="122"/>
-      <c r="C893" s="122"/>
-      <c r="D893" s="122"/>
-      <c r="E893" s="123"/>
-    </row>
-    <row r="894" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A894" s="87" t="s">
+      <c r="B894" s="103"/>
+      <c r="C894" s="103"/>
+      <c r="D894" s="103"/>
+      <c r="E894" s="104"/>
+    </row>
+    <row r="895" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A895" s="87" t="s">
         <v>1291</v>
       </c>
-      <c r="B894" s="87" t="s">
+      <c r="B895" s="87" t="s">
         <v>1289</v>
       </c>
-      <c r="C894" s="88">
+      <c r="C895" s="88">
         <v>3460</v>
       </c>
-      <c r="D894" s="89" t="s">
+      <c r="D895" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E894" s="63">
+      <c r="E895" s="63">
         <v>90</v>
-      </c>
-    </row>
-    <row r="895" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A895" s="72" t="s">
-        <v>1290</v>
-      </c>
-      <c r="B895" s="72" t="s">
-        <v>1289</v>
-      </c>
-      <c r="C895" s="73">
-        <v>3459</v>
-      </c>
-      <c r="D895" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E895" s="48">
-        <v>45</v>
       </c>
     </row>
     <row r="896" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="72" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B896" s="72" t="s">
         <v>1289</v>
       </c>
       <c r="C896" s="73">
-        <v>3803</v>
+        <v>3459</v>
       </c>
       <c r="D896" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E896" s="48">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="897" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="72" t="s">
-        <v>478</v>
+        <v>1292</v>
       </c>
       <c r="B897" s="72" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="C897" s="73">
-        <v>3425</v>
+        <v>3803</v>
       </c>
       <c r="D897" s="74" t="s">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="E897" s="48">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="898" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="72" t="s">
-        <v>1295</v>
+        <v>478</v>
       </c>
       <c r="B898" s="72" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C898" s="73">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="D898" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E898" s="48">
-        <v>252</v>
+        <v>27</v>
       </c>
     </row>
     <row r="899" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="72" t="s">
-        <v>479</v>
+        <v>1295</v>
       </c>
       <c r="B899" s="72" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C899" s="73">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="D899" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E899" s="48">
-        <v>57</v>
+        <v>252</v>
       </c>
     </row>
     <row r="900" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="72" t="s">
-        <v>1296</v>
+        <v>479</v>
       </c>
       <c r="B900" s="72" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C900" s="73">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="D900" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E900" s="48">
-        <v>540</v>
+        <v>57</v>
       </c>
     </row>
     <row r="901" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="72" t="s">
-        <v>480</v>
+        <v>1296</v>
       </c>
       <c r="B901" s="72" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C901" s="73">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="D901" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E901" s="48">
-        <v>70</v>
+        <v>540</v>
       </c>
     </row>
     <row r="902" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="72" t="s">
-        <v>1297</v>
+        <v>480</v>
       </c>
       <c r="B902" s="72" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C902" s="73">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="D902" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E902" s="48">
-        <v>660</v>
+        <v>70</v>
       </c>
     </row>
     <row r="903" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="72" t="s">
-        <v>481</v>
+        <v>1297</v>
       </c>
       <c r="B903" s="72" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C903" s="73">
-        <v>3913</v>
+        <v>3430</v>
       </c>
       <c r="D903" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E903" s="48">
-        <v>62.5</v>
+        <v>660</v>
       </c>
     </row>
     <row r="904" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="72" t="s">
-        <v>1298</v>
+        <v>481</v>
       </c>
       <c r="B904" s="72" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C904" s="73">
-        <v>3872</v>
+        <v>3913</v>
       </c>
       <c r="D904" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E904" s="48">
-        <v>582</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="905" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="72" t="s">
-        <v>482</v>
+        <v>1298</v>
       </c>
       <c r="B905" s="72" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C905" s="73">
-        <v>3422</v>
+        <v>3872</v>
       </c>
       <c r="D905" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E905" s="48">
-        <v>18</v>
+        <v>582</v>
       </c>
     </row>
     <row r="906" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="72" t="s">
+        <v>482</v>
+      </c>
+      <c r="B906" s="72" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C906" s="73">
+        <v>3422</v>
+      </c>
+      <c r="D906" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="E906" s="48">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="907" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A907" s="72" t="s">
         <v>1299</v>
       </c>
-      <c r="B906" s="72" t="s">
+      <c r="B907" s="72" t="s">
         <v>1293</v>
       </c>
-      <c r="C906" s="73">
+      <c r="C907" s="73">
         <v>3423</v>
       </c>
-      <c r="D906" s="74" t="s">
+      <c r="D907" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="E906" s="48">
+      <c r="E907" s="48">
         <v>168</v>
       </c>
     </row>
-    <row r="907" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A907" s="83" t="s">
+    <row r="908" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A908" s="83" t="s">
         <v>483</v>
       </c>
-      <c r="B907" s="83" t="s">
+      <c r="B908" s="83" t="s">
         <v>1300</v>
       </c>
-      <c r="C907" s="84">
+      <c r="C908" s="84">
         <v>3431</v>
       </c>
-      <c r="D907" s="74" t="s">
+      <c r="D908" s="74" t="s">
         <v>412</v>
       </c>
-      <c r="E907" s="48">
+      <c r="E908" s="48">
         <v>105</v>
       </c>
     </row>
-    <row r="908" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A908" s="90" t="s">
+    <row r="909" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A909" s="90" t="s">
         <v>483</v>
       </c>
-      <c r="B908" s="90" t="s">
+      <c r="B909" s="90" t="s">
         <v>1293</v>
       </c>
-      <c r="C908" s="91">
+      <c r="C909" s="91">
         <v>3432</v>
       </c>
-      <c r="D908" s="92" t="s">
+      <c r="D909" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="E908" s="48">
+      <c r="E909" s="48">
         <v>996</v>
       </c>
     </row>
-    <row r="909" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="910" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="911" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="912" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
@@ -20609,29 +20625,24 @@
     <row r="915" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="916" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="917" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
-    <row r="919" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A919" s="64" t="s">
+    <row r="918" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
+    <row r="920" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A920" s="64" t="s">
         <v>386</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A893:E893"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A287:E287"/>
+    <mergeCell ref="A738:E738"/>
     <mergeCell ref="A598:E598"/>
-    <mergeCell ref="A717:E717"/>
-    <mergeCell ref="A738:E738"/>
-    <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A560:E560"/>
-    <mergeCell ref="A716:E716"/>
-    <mergeCell ref="A288:E288"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A776:E776"/>
+    <mergeCell ref="A730:E730"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A750:E750"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A538:E538"/>
     <mergeCell ref="A8:E8"/>
@@ -20643,16 +20654,22 @@
     <mergeCell ref="A381:E381"/>
     <mergeCell ref="A140:E140"/>
     <mergeCell ref="A215:E215"/>
-    <mergeCell ref="A737:E737"/>
-    <mergeCell ref="A597:E597"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A775:E775"/>
-    <mergeCell ref="A729:E729"/>
-    <mergeCell ref="A748:E748"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
+    <mergeCell ref="A894:E894"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A287:E287"/>
+    <mergeCell ref="A599:E599"/>
+    <mergeCell ref="A718:E718"/>
+    <mergeCell ref="A739:E739"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A560:E560"/>
+    <mergeCell ref="A717:E717"/>
+    <mergeCell ref="A288:E288"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20692,78 +20709,78 @@
       <c r="A2" s="148" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="139"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="138"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="150" t="s">
+      <c r="A3" s="137" t="s">
         <v>485</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="139"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="138"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="149" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="139"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="138"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="137" t="s">
         <v>487</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="139"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="138"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="135"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="139"/>
+      <c r="B6" s="134"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="138"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="135"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="139"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="138"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="139"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="138"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="139"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="138"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="140" t="s">
+      <c r="A10" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="120"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22486,19 +22503,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="134"/>
-      <c r="B112" s="135"/>
-      <c r="C112" s="136"/>
-      <c r="D112" s="137"/>
+      <c r="A112" s="133"/>
+      <c r="B112" s="134"/>
+      <c r="C112" s="135"/>
+      <c r="D112" s="136"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="149" t="s">
+      <c r="A113" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="112"/>
-      <c r="C113" s="112"/>
-      <c r="D113" s="120"/>
+      <c r="B113" s="119"/>
+      <c r="C113" s="119"/>
+      <c r="D113" s="127"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22791,19 +22808,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="134"/>
-      <c r="B131" s="135"/>
-      <c r="C131" s="136"/>
-      <c r="D131" s="137"/>
+      <c r="A131" s="133"/>
+      <c r="B131" s="134"/>
+      <c r="C131" s="135"/>
+      <c r="D131" s="136"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="149" t="s">
+      <c r="A132" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="112"/>
-      <c r="C132" s="112"/>
-      <c r="D132" s="120"/>
+      <c r="B132" s="119"/>
+      <c r="C132" s="119"/>
+      <c r="D132" s="127"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22977,19 +22994,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="134"/>
-      <c r="B143" s="135"/>
-      <c r="C143" s="136"/>
-      <c r="D143" s="137"/>
+      <c r="A143" s="133"/>
+      <c r="B143" s="134"/>
+      <c r="C143" s="135"/>
+      <c r="D143" s="136"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="149" t="s">
+      <c r="A144" s="140" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="112"/>
-      <c r="C144" s="112"/>
-      <c r="D144" s="120"/>
+      <c r="B144" s="119"/>
+      <c r="C144" s="119"/>
+      <c r="D144" s="127"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23622,19 +23639,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="134"/>
-      <c r="B182" s="135"/>
-      <c r="C182" s="136"/>
-      <c r="D182" s="137"/>
+      <c r="A182" s="133"/>
+      <c r="B182" s="134"/>
+      <c r="C182" s="135"/>
+      <c r="D182" s="136"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="133" t="s">
+      <c r="A183" s="139" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="112"/>
-      <c r="C183" s="112"/>
-      <c r="D183" s="112"/>
+      <c r="B183" s="119"/>
+      <c r="C183" s="119"/>
+      <c r="D183" s="119"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24496,19 +24513,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="134"/>
-      <c r="B241" s="135"/>
-      <c r="C241" s="136"/>
-      <c r="D241" s="137"/>
+      <c r="A241" s="133"/>
+      <c r="B241" s="134"/>
+      <c r="C241" s="135"/>
+      <c r="D241" s="136"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="133" t="s">
+      <c r="A242" s="139" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="112"/>
-      <c r="C242" s="112"/>
-      <c r="D242" s="112"/>
+      <c r="B242" s="119"/>
+      <c r="C242" s="119"/>
+      <c r="D242" s="119"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25729,21 +25746,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="134"/>
-      <c r="B324" s="135"/>
-      <c r="C324" s="136"/>
-      <c r="D324" s="137"/>
+      <c r="A324" s="133"/>
+      <c r="B324" s="134"/>
+      <c r="C324" s="135"/>
+      <c r="D324" s="136"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="133" t="s">
+      <c r="A325" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="112"/>
-      <c r="C325" s="112"/>
-      <c r="D325" s="112"/>
+      <c r="B325" s="119"/>
+      <c r="C325" s="119"/>
+      <c r="D325" s="119"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26240,19 +26257,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="134"/>
-      <c r="B355" s="135"/>
-      <c r="C355" s="136"/>
-      <c r="D355" s="137"/>
+      <c r="A355" s="133"/>
+      <c r="B355" s="134"/>
+      <c r="C355" s="135"/>
+      <c r="D355" s="136"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="133" t="s">
+      <c r="A356" s="139" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="112"/>
-      <c r="C356" s="112"/>
-      <c r="D356" s="112"/>
+      <c r="B356" s="119"/>
+      <c r="C356" s="119"/>
+      <c r="D356" s="119"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28007,19 +28024,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="134"/>
-      <c r="B460" s="135"/>
-      <c r="C460" s="136"/>
-      <c r="D460" s="137"/>
+      <c r="A460" s="133"/>
+      <c r="B460" s="134"/>
+      <c r="C460" s="135"/>
+      <c r="D460" s="136"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="133" t="s">
+      <c r="A461" s="139" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="112"/>
-      <c r="C461" s="112"/>
-      <c r="D461" s="112"/>
+      <c r="B461" s="119"/>
+      <c r="C461" s="119"/>
+      <c r="D461" s="119"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28312,19 +28329,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="134"/>
-      <c r="B479" s="135"/>
-      <c r="C479" s="136"/>
-      <c r="D479" s="137"/>
+      <c r="A479" s="133"/>
+      <c r="B479" s="134"/>
+      <c r="C479" s="135"/>
+      <c r="D479" s="136"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="133" t="s">
+      <c r="A480" s="139" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="112"/>
-      <c r="C480" s="112"/>
-      <c r="D480" s="112"/>
+      <c r="B480" s="119"/>
+      <c r="C480" s="119"/>
+      <c r="D480" s="119"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28753,19 +28770,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="134"/>
-      <c r="B506" s="135"/>
-      <c r="C506" s="136"/>
-      <c r="D506" s="137"/>
+      <c r="A506" s="133"/>
+      <c r="B506" s="134"/>
+      <c r="C506" s="135"/>
+      <c r="D506" s="136"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="133" t="s">
+      <c r="A507" s="139" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="112"/>
-      <c r="C507" s="112"/>
-      <c r="D507" s="112"/>
+      <c r="B507" s="119"/>
+      <c r="C507" s="119"/>
+      <c r="D507" s="119"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30280,19 +30297,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="134"/>
-      <c r="B597" s="135"/>
-      <c r="C597" s="136"/>
-      <c r="D597" s="137"/>
+      <c r="A597" s="133"/>
+      <c r="B597" s="134"/>
+      <c r="C597" s="135"/>
+      <c r="D597" s="136"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="133" t="s">
+      <c r="A598" s="139" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="112"/>
-      <c r="C598" s="112"/>
-      <c r="D598" s="112"/>
+      <c r="B598" s="119"/>
+      <c r="C598" s="119"/>
+      <c r="D598" s="119"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30432,20 +30449,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="134"/>
-      <c r="B607" s="135"/>
-      <c r="C607" s="136"/>
-      <c r="D607" s="137"/>
+      <c r="A607" s="133"/>
+      <c r="B607" s="134"/>
+      <c r="C607" s="135"/>
+      <c r="D607" s="136"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="133" t="s">
+      <c r="A608" s="139" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="112"/>
-      <c r="C608" s="112"/>
-      <c r="D608" s="112"/>
+      <c r="B608" s="119"/>
+      <c r="C608" s="119"/>
+      <c r="D608" s="119"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30534,19 +30551,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="134"/>
-      <c r="B614" s="135"/>
-      <c r="C614" s="136"/>
-      <c r="D614" s="137"/>
+      <c r="A614" s="133"/>
+      <c r="B614" s="134"/>
+      <c r="C614" s="135"/>
+      <c r="D614" s="136"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="133" t="s">
+      <c r="A615" s="139" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="112"/>
-      <c r="C615" s="112"/>
-      <c r="D615" s="112"/>
+      <c r="B615" s="119"/>
+      <c r="C615" s="119"/>
+      <c r="D615" s="119"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31911,25 +31928,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31946,6 +31944,25 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D192A961-F9B8-402F-87D4-FDE104B3ACB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1200D0D6-6773-4E14-A109-9148AB7D06F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5116,6 +5116,51 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5133,12 +5178,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5148,43 +5187,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5199,14 +5202,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5227,10 +5227,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5552,83 +5552,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="126"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="128"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="111"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="128"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="111"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="128"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="128"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="108"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="111"/>
+      <c r="A6" s="127"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="128"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="114"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="125"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="117"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="122" t="s">
+      <c r="A9" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="120"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -7314,20 +7314,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="121"/>
-      <c r="B109" s="109"/>
-      <c r="C109" s="109"/>
-      <c r="D109" s="110"/>
-      <c r="E109" s="117"/>
+      <c r="A109" s="102"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="103"/>
+      <c r="D109" s="104"/>
+      <c r="E109" s="105"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="122" t="s">
+      <c r="A110" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="119"/>
-      <c r="C110" s="119"/>
-      <c r="D110" s="119"/>
-      <c r="E110" s="120"/>
+      <c r="B110" s="112"/>
+      <c r="C110" s="112"/>
+      <c r="D110" s="112"/>
+      <c r="E110" s="113"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7619,20 +7619,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="121"/>
-      <c r="B128" s="109"/>
-      <c r="C128" s="109"/>
-      <c r="D128" s="110"/>
-      <c r="E128" s="117"/>
+      <c r="A128" s="102"/>
+      <c r="B128" s="103"/>
+      <c r="C128" s="103"/>
+      <c r="D128" s="104"/>
+      <c r="E128" s="105"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="122" t="s">
+      <c r="A129" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="119"/>
-      <c r="C129" s="119"/>
-      <c r="D129" s="119"/>
-      <c r="E129" s="120"/>
+      <c r="B129" s="112"/>
+      <c r="C129" s="112"/>
+      <c r="D129" s="112"/>
+      <c r="E129" s="113"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7788,20 +7788,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="121"/>
-      <c r="B139" s="109"/>
-      <c r="C139" s="109"/>
-      <c r="D139" s="110"/>
-      <c r="E139" s="117"/>
+      <c r="A139" s="102"/>
+      <c r="B139" s="103"/>
+      <c r="C139" s="103"/>
+      <c r="D139" s="104"/>
+      <c r="E139" s="105"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="126" t="s">
+      <c r="A140" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="119"/>
-      <c r="C140" s="119"/>
-      <c r="D140" s="119"/>
-      <c r="E140" s="127"/>
+      <c r="B140" s="112"/>
+      <c r="C140" s="112"/>
+      <c r="D140" s="112"/>
+      <c r="E140" s="120"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -9045,20 +9045,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="121"/>
-      <c r="B214" s="109"/>
-      <c r="C214" s="109"/>
-      <c r="D214" s="110"/>
-      <c r="E214" s="117"/>
+      <c r="A214" s="102"/>
+      <c r="B214" s="103"/>
+      <c r="C214" s="103"/>
+      <c r="D214" s="104"/>
+      <c r="E214" s="105"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="122" t="s">
+      <c r="A215" s="118" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="119"/>
-      <c r="C215" s="119"/>
-      <c r="D215" s="119"/>
-      <c r="E215" s="120"/>
+      <c r="B215" s="112"/>
+      <c r="C215" s="112"/>
+      <c r="D215" s="112"/>
+      <c r="E215" s="113"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -9769,7 +9769,7 @@
         <v>49</v>
       </c>
       <c r="E257" s="40">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="258" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -9786,7 +9786,7 @@
         <v>49</v>
       </c>
       <c r="E258" s="40">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="259" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10266,20 +10266,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="116"/>
-      <c r="B287" s="109"/>
-      <c r="C287" s="109"/>
-      <c r="D287" s="110"/>
-      <c r="E287" s="117"/>
+      <c r="A287" s="114"/>
+      <c r="B287" s="103"/>
+      <c r="C287" s="103"/>
+      <c r="D287" s="104"/>
+      <c r="E287" s="105"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="122" t="s">
+      <c r="A288" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="119"/>
-      <c r="C288" s="119"/>
-      <c r="D288" s="119"/>
-      <c r="E288" s="120"/>
+      <c r="B288" s="112"/>
+      <c r="C288" s="112"/>
+      <c r="D288" s="112"/>
+      <c r="E288" s="113"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -11844,20 +11844,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="116"/>
-      <c r="B381" s="109"/>
-      <c r="C381" s="109"/>
-      <c r="D381" s="110"/>
-      <c r="E381" s="117"/>
+      <c r="A381" s="114"/>
+      <c r="B381" s="103"/>
+      <c r="C381" s="103"/>
+      <c r="D381" s="104"/>
+      <c r="E381" s="105"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="118" t="s">
+      <c r="A382" s="111" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="119"/>
-      <c r="C382" s="119"/>
-      <c r="D382" s="119"/>
-      <c r="E382" s="120"/>
+      <c r="B382" s="112"/>
+      <c r="C382" s="112"/>
+      <c r="D382" s="112"/>
+      <c r="E382" s="113"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12511,13 +12511,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="118" t="s">
+      <c r="A422" s="111" t="s">
         <v>1302</v>
       </c>
-      <c r="B422" s="119"/>
-      <c r="C422" s="119"/>
-      <c r="D422" s="119"/>
-      <c r="E422" s="120"/>
+      <c r="B422" s="112"/>
+      <c r="C422" s="112"/>
+      <c r="D422" s="112"/>
+      <c r="E422" s="113"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -14454,20 +14454,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="116"/>
-      <c r="B537" s="109"/>
-      <c r="C537" s="109"/>
-      <c r="D537" s="110"/>
-      <c r="E537" s="117"/>
+      <c r="A537" s="114"/>
+      <c r="B537" s="103"/>
+      <c r="C537" s="103"/>
+      <c r="D537" s="104"/>
+      <c r="E537" s="105"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="118" t="s">
+      <c r="A538" s="111" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="119"/>
-      <c r="C538" s="119"/>
-      <c r="D538" s="119"/>
-      <c r="E538" s="120"/>
+      <c r="B538" s="112"/>
+      <c r="C538" s="112"/>
+      <c r="D538" s="112"/>
+      <c r="E538" s="113"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14825,20 +14825,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="116"/>
-      <c r="B560" s="109"/>
-      <c r="C560" s="109"/>
-      <c r="D560" s="110"/>
-      <c r="E560" s="117"/>
+      <c r="A560" s="114"/>
+      <c r="B560" s="103"/>
+      <c r="C560" s="103"/>
+      <c r="D560" s="104"/>
+      <c r="E560" s="105"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="118" t="s">
+      <c r="A561" s="111" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="119"/>
-      <c r="C561" s="119"/>
-      <c r="D561" s="119"/>
-      <c r="E561" s="120"/>
+      <c r="B561" s="112"/>
+      <c r="C561" s="112"/>
+      <c r="D561" s="112"/>
+      <c r="E561" s="113"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15451,20 +15451,20 @@
       </c>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="128"/>
-      <c r="B598" s="129"/>
-      <c r="C598" s="129"/>
-      <c r="D598" s="129"/>
-      <c r="E598" s="129"/>
+      <c r="A598" s="106"/>
+      <c r="B598" s="107"/>
+      <c r="C598" s="107"/>
+      <c r="D598" s="107"/>
+      <c r="E598" s="107"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A599" s="118" t="s">
+      <c r="A599" s="111" t="s">
         <v>370</v>
       </c>
-      <c r="B599" s="119"/>
-      <c r="C599" s="119"/>
-      <c r="D599" s="119"/>
-      <c r="E599" s="120"/>
+      <c r="B599" s="112"/>
+      <c r="C599" s="112"/>
+      <c r="D599" s="112"/>
+      <c r="E599" s="113"/>
     </row>
     <row r="600" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="66" t="s">
@@ -16739,7 +16739,7 @@
         <v>34</v>
       </c>
       <c r="E674" s="40">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="675" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16756,7 +16756,7 @@
         <v>20</v>
       </c>
       <c r="E675" s="40">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="676" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16773,7 +16773,7 @@
         <v>34</v>
       </c>
       <c r="E676" s="40">
-        <v>220</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="677" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16790,7 +16790,7 @@
         <v>20</v>
       </c>
       <c r="E677" s="40">
-        <v>46</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="678" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17457,20 +17457,20 @@
       </c>
     </row>
     <row r="717" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="116"/>
-      <c r="B717" s="109"/>
-      <c r="C717" s="109"/>
-      <c r="D717" s="110"/>
-      <c r="E717" s="117"/>
+      <c r="A717" s="114"/>
+      <c r="B717" s="103"/>
+      <c r="C717" s="103"/>
+      <c r="D717" s="104"/>
+      <c r="E717" s="105"/>
     </row>
     <row r="718" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A718" s="118" t="s">
+      <c r="A718" s="111" t="s">
         <v>420</v>
       </c>
-      <c r="B718" s="119"/>
-      <c r="C718" s="119"/>
-      <c r="D718" s="119"/>
-      <c r="E718" s="120"/>
+      <c r="B718" s="112"/>
+      <c r="C718" s="112"/>
+      <c r="D718" s="112"/>
+      <c r="E718" s="113"/>
     </row>
     <row r="719" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="66" t="s">
@@ -17648,13 +17648,13 @@
       <c r="E729" s="61"/>
     </row>
     <row r="730" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A730" s="118" t="s">
+      <c r="A730" s="111" t="s">
         <v>1303</v>
       </c>
-      <c r="B730" s="119"/>
-      <c r="C730" s="119"/>
-      <c r="D730" s="119"/>
-      <c r="E730" s="120"/>
+      <c r="B730" s="112"/>
+      <c r="C730" s="112"/>
+      <c r="D730" s="112"/>
+      <c r="E730" s="113"/>
     </row>
     <row r="731" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="72" t="s">
@@ -17776,20 +17776,20 @@
       </c>
     </row>
     <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="121"/>
-      <c r="B738" s="109"/>
-      <c r="C738" s="109"/>
-      <c r="D738" s="110"/>
-      <c r="E738" s="117"/>
+      <c r="A738" s="102"/>
+      <c r="B738" s="103"/>
+      <c r="C738" s="103"/>
+      <c r="D738" s="104"/>
+      <c r="E738" s="105"/>
     </row>
     <row r="739" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A739" s="118" t="s">
+      <c r="A739" s="111" t="s">
         <v>421</v>
       </c>
-      <c r="B739" s="119"/>
-      <c r="C739" s="119"/>
-      <c r="D739" s="119"/>
-      <c r="E739" s="120"/>
+      <c r="B739" s="112"/>
+      <c r="C739" s="112"/>
+      <c r="D739" s="112"/>
+      <c r="E739" s="113"/>
     </row>
     <row r="740" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="66" t="s">
@@ -17943,20 +17943,20 @@
       </c>
     </row>
     <row r="749" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="121"/>
-      <c r="B749" s="109"/>
-      <c r="C749" s="109"/>
-      <c r="D749" s="110"/>
-      <c r="E749" s="117"/>
+      <c r="A749" s="102"/>
+      <c r="B749" s="103"/>
+      <c r="C749" s="103"/>
+      <c r="D749" s="104"/>
+      <c r="E749" s="105"/>
     </row>
     <row r="750" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A750" s="118" t="s">
+      <c r="A750" s="111" t="s">
         <v>1301</v>
       </c>
-      <c r="B750" s="119"/>
-      <c r="C750" s="119"/>
-      <c r="D750" s="119"/>
-      <c r="E750" s="120"/>
+      <c r="B750" s="112"/>
+      <c r="C750" s="112"/>
+      <c r="D750" s="112"/>
+      <c r="E750" s="113"/>
     </row>
     <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="66" t="s">
@@ -18386,13 +18386,13 @@
       <c r="E775" s="98"/>
     </row>
     <row r="776" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A776" s="130" t="s">
+      <c r="A776" s="108" t="s">
         <v>1287</v>
       </c>
-      <c r="B776" s="131"/>
-      <c r="C776" s="131"/>
-      <c r="D776" s="131"/>
-      <c r="E776" s="132"/>
+      <c r="B776" s="109"/>
+      <c r="C776" s="109"/>
+      <c r="D776" s="109"/>
+      <c r="E776" s="110"/>
     </row>
     <row r="777" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="66" t="s">
@@ -20354,13 +20354,13 @@
       <c r="E893" s="100"/>
     </row>
     <row r="894" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A894" s="102" t="s">
+      <c r="A894" s="121" t="s">
         <v>1288</v>
       </c>
-      <c r="B894" s="103"/>
-      <c r="C894" s="103"/>
-      <c r="D894" s="103"/>
-      <c r="E894" s="104"/>
+      <c r="B894" s="122"/>
+      <c r="C894" s="122"/>
+      <c r="D894" s="122"/>
+      <c r="E894" s="123"/>
     </row>
     <row r="895" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="87" t="s">
@@ -20633,27 +20633,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A738:E738"/>
-    <mergeCell ref="A598:E598"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A776:E776"/>
-    <mergeCell ref="A730:E730"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A750:E750"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A538:E538"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A422:E422"/>
-    <mergeCell ref="A382:E382"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A381:E381"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A215:E215"/>
     <mergeCell ref="A894:E894"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
@@ -20670,6 +20649,27 @@
     <mergeCell ref="A560:E560"/>
     <mergeCell ref="A717:E717"/>
     <mergeCell ref="A288:E288"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A538:E538"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A422:E422"/>
+    <mergeCell ref="A382:E382"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A215:E215"/>
+    <mergeCell ref="A738:E738"/>
+    <mergeCell ref="A598:E598"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A776:E776"/>
+    <mergeCell ref="A730:E730"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A750:E750"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20709,78 +20709,78 @@
       <c r="A2" s="148" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="138"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="139"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="150" t="s">
         <v>485</v>
       </c>
-      <c r="B3" s="134"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="138"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="139"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="149" t="s">
+      <c r="A4" s="138" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="138"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="139"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="150" t="s">
         <v>487</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="138"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="139"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="134"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="138"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="139"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="134"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="138"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="139"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="138"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="139"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="138"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="139"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="150" t="s">
+      <c r="A10" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22503,19 +22503,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="133"/>
-      <c r="B112" s="134"/>
-      <c r="C112" s="135"/>
-      <c r="D112" s="136"/>
+      <c r="A112" s="134"/>
+      <c r="B112" s="135"/>
+      <c r="C112" s="136"/>
+      <c r="D112" s="137"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="140" t="s">
+      <c r="A113" s="149" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="119"/>
-      <c r="C113" s="119"/>
-      <c r="D113" s="127"/>
+      <c r="B113" s="112"/>
+      <c r="C113" s="112"/>
+      <c r="D113" s="120"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22808,19 +22808,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="133"/>
-      <c r="B131" s="134"/>
-      <c r="C131" s="135"/>
-      <c r="D131" s="136"/>
+      <c r="A131" s="134"/>
+      <c r="B131" s="135"/>
+      <c r="C131" s="136"/>
+      <c r="D131" s="137"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="140" t="s">
+      <c r="A132" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="119"/>
-      <c r="C132" s="119"/>
-      <c r="D132" s="127"/>
+      <c r="B132" s="112"/>
+      <c r="C132" s="112"/>
+      <c r="D132" s="120"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22994,19 +22994,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="133"/>
-      <c r="B143" s="134"/>
-      <c r="C143" s="135"/>
-      <c r="D143" s="136"/>
+      <c r="A143" s="134"/>
+      <c r="B143" s="135"/>
+      <c r="C143" s="136"/>
+      <c r="D143" s="137"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="140" t="s">
+      <c r="A144" s="149" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="119"/>
-      <c r="C144" s="119"/>
-      <c r="D144" s="127"/>
+      <c r="B144" s="112"/>
+      <c r="C144" s="112"/>
+      <c r="D144" s="120"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23639,19 +23639,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="133"/>
-      <c r="B182" s="134"/>
-      <c r="C182" s="135"/>
-      <c r="D182" s="136"/>
+      <c r="A182" s="134"/>
+      <c r="B182" s="135"/>
+      <c r="C182" s="136"/>
+      <c r="D182" s="137"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="139" t="s">
+      <c r="A183" s="133" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="119"/>
-      <c r="C183" s="119"/>
-      <c r="D183" s="119"/>
+      <c r="B183" s="112"/>
+      <c r="C183" s="112"/>
+      <c r="D183" s="112"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24513,19 +24513,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="133"/>
-      <c r="B241" s="134"/>
-      <c r="C241" s="135"/>
-      <c r="D241" s="136"/>
+      <c r="A241" s="134"/>
+      <c r="B241" s="135"/>
+      <c r="C241" s="136"/>
+      <c r="D241" s="137"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="139" t="s">
+      <c r="A242" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="119"/>
-      <c r="C242" s="119"/>
-      <c r="D242" s="119"/>
+      <c r="B242" s="112"/>
+      <c r="C242" s="112"/>
+      <c r="D242" s="112"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25746,21 +25746,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="133"/>
-      <c r="B324" s="134"/>
-      <c r="C324" s="135"/>
-      <c r="D324" s="136"/>
+      <c r="A324" s="134"/>
+      <c r="B324" s="135"/>
+      <c r="C324" s="136"/>
+      <c r="D324" s="137"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="139" t="s">
+      <c r="A325" s="133" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="119"/>
-      <c r="C325" s="119"/>
-      <c r="D325" s="119"/>
+      <c r="B325" s="112"/>
+      <c r="C325" s="112"/>
+      <c r="D325" s="112"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26257,19 +26257,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="133"/>
-      <c r="B355" s="134"/>
-      <c r="C355" s="135"/>
-      <c r="D355" s="136"/>
+      <c r="A355" s="134"/>
+      <c r="B355" s="135"/>
+      <c r="C355" s="136"/>
+      <c r="D355" s="137"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="139" t="s">
+      <c r="A356" s="133" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="119"/>
-      <c r="C356" s="119"/>
-      <c r="D356" s="119"/>
+      <c r="B356" s="112"/>
+      <c r="C356" s="112"/>
+      <c r="D356" s="112"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28024,19 +28024,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="133"/>
-      <c r="B460" s="134"/>
-      <c r="C460" s="135"/>
-      <c r="D460" s="136"/>
+      <c r="A460" s="134"/>
+      <c r="B460" s="135"/>
+      <c r="C460" s="136"/>
+      <c r="D460" s="137"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="139" t="s">
+      <c r="A461" s="133" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="119"/>
-      <c r="C461" s="119"/>
-      <c r="D461" s="119"/>
+      <c r="B461" s="112"/>
+      <c r="C461" s="112"/>
+      <c r="D461" s="112"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28329,19 +28329,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="133"/>
-      <c r="B479" s="134"/>
-      <c r="C479" s="135"/>
-      <c r="D479" s="136"/>
+      <c r="A479" s="134"/>
+      <c r="B479" s="135"/>
+      <c r="C479" s="136"/>
+      <c r="D479" s="137"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="139" t="s">
+      <c r="A480" s="133" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="119"/>
-      <c r="C480" s="119"/>
-      <c r="D480" s="119"/>
+      <c r="B480" s="112"/>
+      <c r="C480" s="112"/>
+      <c r="D480" s="112"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28770,19 +28770,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="133"/>
-      <c r="B506" s="134"/>
-      <c r="C506" s="135"/>
-      <c r="D506" s="136"/>
+      <c r="A506" s="134"/>
+      <c r="B506" s="135"/>
+      <c r="C506" s="136"/>
+      <c r="D506" s="137"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="139" t="s">
+      <c r="A507" s="133" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="119"/>
-      <c r="C507" s="119"/>
-      <c r="D507" s="119"/>
+      <c r="B507" s="112"/>
+      <c r="C507" s="112"/>
+      <c r="D507" s="112"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30297,19 +30297,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="133"/>
-      <c r="B597" s="134"/>
-      <c r="C597" s="135"/>
-      <c r="D597" s="136"/>
+      <c r="A597" s="134"/>
+      <c r="B597" s="135"/>
+      <c r="C597" s="136"/>
+      <c r="D597" s="137"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="139" t="s">
+      <c r="A598" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="119"/>
-      <c r="C598" s="119"/>
-      <c r="D598" s="119"/>
+      <c r="B598" s="112"/>
+      <c r="C598" s="112"/>
+      <c r="D598" s="112"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30449,20 +30449,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="133"/>
-      <c r="B607" s="134"/>
-      <c r="C607" s="135"/>
-      <c r="D607" s="136"/>
+      <c r="A607" s="134"/>
+      <c r="B607" s="135"/>
+      <c r="C607" s="136"/>
+      <c r="D607" s="137"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="139" t="s">
+      <c r="A608" s="133" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="119"/>
-      <c r="C608" s="119"/>
-      <c r="D608" s="119"/>
+      <c r="B608" s="112"/>
+      <c r="C608" s="112"/>
+      <c r="D608" s="112"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30551,19 +30551,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="133"/>
-      <c r="B614" s="134"/>
-      <c r="C614" s="135"/>
-      <c r="D614" s="136"/>
+      <c r="A614" s="134"/>
+      <c r="B614" s="135"/>
+      <c r="C614" s="136"/>
+      <c r="D614" s="137"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="139" t="s">
+      <c r="A615" s="133" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="119"/>
-      <c r="C615" s="119"/>
-      <c r="D615" s="119"/>
+      <c r="B615" s="112"/>
+      <c r="C615" s="112"/>
+      <c r="D615" s="112"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31928,6 +31928,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31944,25 +31963,6 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1200D0D6-6773-4E14-A109-9148AB7D06F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF4CA18-AA4C-4FE6-8A79-5A794BC65EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5116,51 +5116,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5178,6 +5133,12 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5187,7 +5148,43 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5202,11 +5199,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5227,10 +5227,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5552,83 +5552,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="126"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="128"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127" t="s">
+      <c r="A3" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="128"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127" t="s">
+      <c r="A4" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="128"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="111"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="128"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="128"/>
+      <c r="A6" s="108"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="132"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="117"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="125"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="120"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -7314,20 +7314,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="102"/>
-      <c r="B109" s="103"/>
-      <c r="C109" s="103"/>
-      <c r="D109" s="104"/>
-      <c r="E109" s="105"/>
+      <c r="A109" s="121"/>
+      <c r="B109" s="109"/>
+      <c r="C109" s="109"/>
+      <c r="D109" s="110"/>
+      <c r="E109" s="117"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="118" t="s">
+      <c r="A110" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="112"/>
-      <c r="C110" s="112"/>
-      <c r="D110" s="112"/>
-      <c r="E110" s="113"/>
+      <c r="B110" s="119"/>
+      <c r="C110" s="119"/>
+      <c r="D110" s="119"/>
+      <c r="E110" s="120"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7619,20 +7619,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="102"/>
-      <c r="B128" s="103"/>
-      <c r="C128" s="103"/>
-      <c r="D128" s="104"/>
-      <c r="E128" s="105"/>
+      <c r="A128" s="121"/>
+      <c r="B128" s="109"/>
+      <c r="C128" s="109"/>
+      <c r="D128" s="110"/>
+      <c r="E128" s="117"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="118" t="s">
+      <c r="A129" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="112"/>
-      <c r="C129" s="112"/>
-      <c r="D129" s="112"/>
-      <c r="E129" s="113"/>
+      <c r="B129" s="119"/>
+      <c r="C129" s="119"/>
+      <c r="D129" s="119"/>
+      <c r="E129" s="120"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7788,20 +7788,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="102"/>
-      <c r="B139" s="103"/>
-      <c r="C139" s="103"/>
-      <c r="D139" s="104"/>
-      <c r="E139" s="105"/>
+      <c r="A139" s="121"/>
+      <c r="B139" s="109"/>
+      <c r="C139" s="109"/>
+      <c r="D139" s="110"/>
+      <c r="E139" s="117"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="119" t="s">
+      <c r="A140" s="126" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="112"/>
-      <c r="C140" s="112"/>
-      <c r="D140" s="112"/>
-      <c r="E140" s="120"/>
+      <c r="B140" s="119"/>
+      <c r="C140" s="119"/>
+      <c r="D140" s="119"/>
+      <c r="E140" s="127"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -8599,7 +8599,7 @@
         <v>49</v>
       </c>
       <c r="E187" s="40">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -9045,20 +9045,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="102"/>
-      <c r="B214" s="103"/>
-      <c r="C214" s="103"/>
-      <c r="D214" s="104"/>
-      <c r="E214" s="105"/>
+      <c r="A214" s="121"/>
+      <c r="B214" s="109"/>
+      <c r="C214" s="109"/>
+      <c r="D214" s="110"/>
+      <c r="E214" s="117"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="118" t="s">
+      <c r="A215" s="122" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="112"/>
-      <c r="C215" s="112"/>
-      <c r="D215" s="112"/>
-      <c r="E215" s="113"/>
+      <c r="B215" s="119"/>
+      <c r="C215" s="119"/>
+      <c r="D215" s="119"/>
+      <c r="E215" s="120"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -10266,20 +10266,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="114"/>
-      <c r="B287" s="103"/>
-      <c r="C287" s="103"/>
-      <c r="D287" s="104"/>
-      <c r="E287" s="105"/>
+      <c r="A287" s="116"/>
+      <c r="B287" s="109"/>
+      <c r="C287" s="109"/>
+      <c r="D287" s="110"/>
+      <c r="E287" s="117"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="118" t="s">
+      <c r="A288" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="112"/>
-      <c r="C288" s="112"/>
-      <c r="D288" s="112"/>
-      <c r="E288" s="113"/>
+      <c r="B288" s="119"/>
+      <c r="C288" s="119"/>
+      <c r="D288" s="119"/>
+      <c r="E288" s="120"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -11844,20 +11844,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="114"/>
-      <c r="B381" s="103"/>
-      <c r="C381" s="103"/>
-      <c r="D381" s="104"/>
-      <c r="E381" s="105"/>
+      <c r="A381" s="116"/>
+      <c r="B381" s="109"/>
+      <c r="C381" s="109"/>
+      <c r="D381" s="110"/>
+      <c r="E381" s="117"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="111" t="s">
+      <c r="A382" s="118" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="112"/>
-      <c r="C382" s="112"/>
-      <c r="D382" s="112"/>
-      <c r="E382" s="113"/>
+      <c r="B382" s="119"/>
+      <c r="C382" s="119"/>
+      <c r="D382" s="119"/>
+      <c r="E382" s="120"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12511,13 +12511,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="111" t="s">
+      <c r="A422" s="118" t="s">
         <v>1302</v>
       </c>
-      <c r="B422" s="112"/>
-      <c r="C422" s="112"/>
-      <c r="D422" s="112"/>
-      <c r="E422" s="113"/>
+      <c r="B422" s="119"/>
+      <c r="C422" s="119"/>
+      <c r="D422" s="119"/>
+      <c r="E422" s="120"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -14454,20 +14454,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="114"/>
-      <c r="B537" s="103"/>
-      <c r="C537" s="103"/>
-      <c r="D537" s="104"/>
-      <c r="E537" s="105"/>
+      <c r="A537" s="116"/>
+      <c r="B537" s="109"/>
+      <c r="C537" s="109"/>
+      <c r="D537" s="110"/>
+      <c r="E537" s="117"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="111" t="s">
+      <c r="A538" s="118" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="112"/>
-      <c r="C538" s="112"/>
-      <c r="D538" s="112"/>
-      <c r="E538" s="113"/>
+      <c r="B538" s="119"/>
+      <c r="C538" s="119"/>
+      <c r="D538" s="119"/>
+      <c r="E538" s="120"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14825,20 +14825,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="114"/>
-      <c r="B560" s="103"/>
-      <c r="C560" s="103"/>
-      <c r="D560" s="104"/>
-      <c r="E560" s="105"/>
+      <c r="A560" s="116"/>
+      <c r="B560" s="109"/>
+      <c r="C560" s="109"/>
+      <c r="D560" s="110"/>
+      <c r="E560" s="117"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="111" t="s">
+      <c r="A561" s="118" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="112"/>
-      <c r="C561" s="112"/>
-      <c r="D561" s="112"/>
-      <c r="E561" s="113"/>
+      <c r="B561" s="119"/>
+      <c r="C561" s="119"/>
+      <c r="D561" s="119"/>
+      <c r="E561" s="120"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15451,20 +15451,20 @@
       </c>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="106"/>
-      <c r="B598" s="107"/>
-      <c r="C598" s="107"/>
-      <c r="D598" s="107"/>
-      <c r="E598" s="107"/>
+      <c r="A598" s="128"/>
+      <c r="B598" s="129"/>
+      <c r="C598" s="129"/>
+      <c r="D598" s="129"/>
+      <c r="E598" s="129"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A599" s="111" t="s">
+      <c r="A599" s="118" t="s">
         <v>370</v>
       </c>
-      <c r="B599" s="112"/>
-      <c r="C599" s="112"/>
-      <c r="D599" s="112"/>
-      <c r="E599" s="113"/>
+      <c r="B599" s="119"/>
+      <c r="C599" s="119"/>
+      <c r="D599" s="119"/>
+      <c r="E599" s="120"/>
     </row>
     <row r="600" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="66" t="s">
@@ -17457,20 +17457,20 @@
       </c>
     </row>
     <row r="717" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="114"/>
-      <c r="B717" s="103"/>
-      <c r="C717" s="103"/>
-      <c r="D717" s="104"/>
-      <c r="E717" s="105"/>
+      <c r="A717" s="116"/>
+      <c r="B717" s="109"/>
+      <c r="C717" s="109"/>
+      <c r="D717" s="110"/>
+      <c r="E717" s="117"/>
     </row>
     <row r="718" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A718" s="111" t="s">
+      <c r="A718" s="118" t="s">
         <v>420</v>
       </c>
-      <c r="B718" s="112"/>
-      <c r="C718" s="112"/>
-      <c r="D718" s="112"/>
-      <c r="E718" s="113"/>
+      <c r="B718" s="119"/>
+      <c r="C718" s="119"/>
+      <c r="D718" s="119"/>
+      <c r="E718" s="120"/>
     </row>
     <row r="719" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="66" t="s">
@@ -17648,13 +17648,13 @@
       <c r="E729" s="61"/>
     </row>
     <row r="730" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A730" s="111" t="s">
+      <c r="A730" s="118" t="s">
         <v>1303</v>
       </c>
-      <c r="B730" s="112"/>
-      <c r="C730" s="112"/>
-      <c r="D730" s="112"/>
-      <c r="E730" s="113"/>
+      <c r="B730" s="119"/>
+      <c r="C730" s="119"/>
+      <c r="D730" s="119"/>
+      <c r="E730" s="120"/>
     </row>
     <row r="731" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="72" t="s">
@@ -17776,20 +17776,20 @@
       </c>
     </row>
     <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="102"/>
-      <c r="B738" s="103"/>
-      <c r="C738" s="103"/>
-      <c r="D738" s="104"/>
-      <c r="E738" s="105"/>
+      <c r="A738" s="121"/>
+      <c r="B738" s="109"/>
+      <c r="C738" s="109"/>
+      <c r="D738" s="110"/>
+      <c r="E738" s="117"/>
     </row>
     <row r="739" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A739" s="111" t="s">
+      <c r="A739" s="118" t="s">
         <v>421</v>
       </c>
-      <c r="B739" s="112"/>
-      <c r="C739" s="112"/>
-      <c r="D739" s="112"/>
-      <c r="E739" s="113"/>
+      <c r="B739" s="119"/>
+      <c r="C739" s="119"/>
+      <c r="D739" s="119"/>
+      <c r="E739" s="120"/>
     </row>
     <row r="740" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="66" t="s">
@@ -17943,20 +17943,20 @@
       </c>
     </row>
     <row r="749" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="102"/>
-      <c r="B749" s="103"/>
-      <c r="C749" s="103"/>
-      <c r="D749" s="104"/>
-      <c r="E749" s="105"/>
+      <c r="A749" s="121"/>
+      <c r="B749" s="109"/>
+      <c r="C749" s="109"/>
+      <c r="D749" s="110"/>
+      <c r="E749" s="117"/>
     </row>
     <row r="750" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A750" s="111" t="s">
+      <c r="A750" s="118" t="s">
         <v>1301</v>
       </c>
-      <c r="B750" s="112"/>
-      <c r="C750" s="112"/>
-      <c r="D750" s="112"/>
-      <c r="E750" s="113"/>
+      <c r="B750" s="119"/>
+      <c r="C750" s="119"/>
+      <c r="D750" s="119"/>
+      <c r="E750" s="120"/>
     </row>
     <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="66" t="s">
@@ -18386,13 +18386,13 @@
       <c r="E775" s="98"/>
     </row>
     <row r="776" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A776" s="108" t="s">
+      <c r="A776" s="130" t="s">
         <v>1287</v>
       </c>
-      <c r="B776" s="109"/>
-      <c r="C776" s="109"/>
-      <c r="D776" s="109"/>
-      <c r="E776" s="110"/>
+      <c r="B776" s="131"/>
+      <c r="C776" s="131"/>
+      <c r="D776" s="131"/>
+      <c r="E776" s="132"/>
     </row>
     <row r="777" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="66" t="s">
@@ -20354,13 +20354,13 @@
       <c r="E893" s="100"/>
     </row>
     <row r="894" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A894" s="121" t="s">
+      <c r="A894" s="102" t="s">
         <v>1288</v>
       </c>
-      <c r="B894" s="122"/>
-      <c r="C894" s="122"/>
-      <c r="D894" s="122"/>
-      <c r="E894" s="123"/>
+      <c r="B894" s="103"/>
+      <c r="C894" s="103"/>
+      <c r="D894" s="103"/>
+      <c r="E894" s="104"/>
     </row>
     <row r="895" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="87" t="s">
@@ -20633,6 +20633,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A738:E738"/>
+    <mergeCell ref="A598:E598"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A776:E776"/>
+    <mergeCell ref="A730:E730"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A750:E750"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A538:E538"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A422:E422"/>
+    <mergeCell ref="A382:E382"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A215:E215"/>
     <mergeCell ref="A894:E894"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
@@ -20649,27 +20670,6 @@
     <mergeCell ref="A560:E560"/>
     <mergeCell ref="A717:E717"/>
     <mergeCell ref="A288:E288"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A538:E538"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A422:E422"/>
-    <mergeCell ref="A382:E382"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A381:E381"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A215:E215"/>
-    <mergeCell ref="A738:E738"/>
-    <mergeCell ref="A598:E598"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A776:E776"/>
-    <mergeCell ref="A730:E730"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A750:E750"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20709,78 +20709,78 @@
       <c r="A2" s="148" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="139"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="138"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="150" t="s">
+      <c r="A3" s="137" t="s">
         <v>485</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="139"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="138"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="149" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="139"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="138"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="137" t="s">
         <v>487</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="139"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="138"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="135"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="139"/>
+      <c r="B6" s="134"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="138"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="135"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="139"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="138"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="139"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="138"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="139"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="138"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="140" t="s">
+      <c r="A10" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="120"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22503,19 +22503,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="134"/>
-      <c r="B112" s="135"/>
-      <c r="C112" s="136"/>
-      <c r="D112" s="137"/>
+      <c r="A112" s="133"/>
+      <c r="B112" s="134"/>
+      <c r="C112" s="135"/>
+      <c r="D112" s="136"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="149" t="s">
+      <c r="A113" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="112"/>
-      <c r="C113" s="112"/>
-      <c r="D113" s="120"/>
+      <c r="B113" s="119"/>
+      <c r="C113" s="119"/>
+      <c r="D113" s="127"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22808,19 +22808,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="134"/>
-      <c r="B131" s="135"/>
-      <c r="C131" s="136"/>
-      <c r="D131" s="137"/>
+      <c r="A131" s="133"/>
+      <c r="B131" s="134"/>
+      <c r="C131" s="135"/>
+      <c r="D131" s="136"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="149" t="s">
+      <c r="A132" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="112"/>
-      <c r="C132" s="112"/>
-      <c r="D132" s="120"/>
+      <c r="B132" s="119"/>
+      <c r="C132" s="119"/>
+      <c r="D132" s="127"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22994,19 +22994,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="134"/>
-      <c r="B143" s="135"/>
-      <c r="C143" s="136"/>
-      <c r="D143" s="137"/>
+      <c r="A143" s="133"/>
+      <c r="B143" s="134"/>
+      <c r="C143" s="135"/>
+      <c r="D143" s="136"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="149" t="s">
+      <c r="A144" s="140" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="112"/>
-      <c r="C144" s="112"/>
-      <c r="D144" s="120"/>
+      <c r="B144" s="119"/>
+      <c r="C144" s="119"/>
+      <c r="D144" s="127"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23639,19 +23639,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="134"/>
-      <c r="B182" s="135"/>
-      <c r="C182" s="136"/>
-      <c r="D182" s="137"/>
+      <c r="A182" s="133"/>
+      <c r="B182" s="134"/>
+      <c r="C182" s="135"/>
+      <c r="D182" s="136"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="133" t="s">
+      <c r="A183" s="139" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="112"/>
-      <c r="C183" s="112"/>
-      <c r="D183" s="112"/>
+      <c r="B183" s="119"/>
+      <c r="C183" s="119"/>
+      <c r="D183" s="119"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24513,19 +24513,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="134"/>
-      <c r="B241" s="135"/>
-      <c r="C241" s="136"/>
-      <c r="D241" s="137"/>
+      <c r="A241" s="133"/>
+      <c r="B241" s="134"/>
+      <c r="C241" s="135"/>
+      <c r="D241" s="136"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="133" t="s">
+      <c r="A242" s="139" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="112"/>
-      <c r="C242" s="112"/>
-      <c r="D242" s="112"/>
+      <c r="B242" s="119"/>
+      <c r="C242" s="119"/>
+      <c r="D242" s="119"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25746,21 +25746,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="134"/>
-      <c r="B324" s="135"/>
-      <c r="C324" s="136"/>
-      <c r="D324" s="137"/>
+      <c r="A324" s="133"/>
+      <c r="B324" s="134"/>
+      <c r="C324" s="135"/>
+      <c r="D324" s="136"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="133" t="s">
+      <c r="A325" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="112"/>
-      <c r="C325" s="112"/>
-      <c r="D325" s="112"/>
+      <c r="B325" s="119"/>
+      <c r="C325" s="119"/>
+      <c r="D325" s="119"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26257,19 +26257,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="134"/>
-      <c r="B355" s="135"/>
-      <c r="C355" s="136"/>
-      <c r="D355" s="137"/>
+      <c r="A355" s="133"/>
+      <c r="B355" s="134"/>
+      <c r="C355" s="135"/>
+      <c r="D355" s="136"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="133" t="s">
+      <c r="A356" s="139" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="112"/>
-      <c r="C356" s="112"/>
-      <c r="D356" s="112"/>
+      <c r="B356" s="119"/>
+      <c r="C356" s="119"/>
+      <c r="D356" s="119"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28024,19 +28024,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="134"/>
-      <c r="B460" s="135"/>
-      <c r="C460" s="136"/>
-      <c r="D460" s="137"/>
+      <c r="A460" s="133"/>
+      <c r="B460" s="134"/>
+      <c r="C460" s="135"/>
+      <c r="D460" s="136"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="133" t="s">
+      <c r="A461" s="139" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="112"/>
-      <c r="C461" s="112"/>
-      <c r="D461" s="112"/>
+      <c r="B461" s="119"/>
+      <c r="C461" s="119"/>
+      <c r="D461" s="119"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28329,19 +28329,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="134"/>
-      <c r="B479" s="135"/>
-      <c r="C479" s="136"/>
-      <c r="D479" s="137"/>
+      <c r="A479" s="133"/>
+      <c r="B479" s="134"/>
+      <c r="C479" s="135"/>
+      <c r="D479" s="136"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="133" t="s">
+      <c r="A480" s="139" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="112"/>
-      <c r="C480" s="112"/>
-      <c r="D480" s="112"/>
+      <c r="B480" s="119"/>
+      <c r="C480" s="119"/>
+      <c r="D480" s="119"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28770,19 +28770,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="134"/>
-      <c r="B506" s="135"/>
-      <c r="C506" s="136"/>
-      <c r="D506" s="137"/>
+      <c r="A506" s="133"/>
+      <c r="B506" s="134"/>
+      <c r="C506" s="135"/>
+      <c r="D506" s="136"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="133" t="s">
+      <c r="A507" s="139" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="112"/>
-      <c r="C507" s="112"/>
-      <c r="D507" s="112"/>
+      <c r="B507" s="119"/>
+      <c r="C507" s="119"/>
+      <c r="D507" s="119"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30297,19 +30297,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="134"/>
-      <c r="B597" s="135"/>
-      <c r="C597" s="136"/>
-      <c r="D597" s="137"/>
+      <c r="A597" s="133"/>
+      <c r="B597" s="134"/>
+      <c r="C597" s="135"/>
+      <c r="D597" s="136"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="133" t="s">
+      <c r="A598" s="139" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="112"/>
-      <c r="C598" s="112"/>
-      <c r="D598" s="112"/>
+      <c r="B598" s="119"/>
+      <c r="C598" s="119"/>
+      <c r="D598" s="119"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30449,20 +30449,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="134"/>
-      <c r="B607" s="135"/>
-      <c r="C607" s="136"/>
-      <c r="D607" s="137"/>
+      <c r="A607" s="133"/>
+      <c r="B607" s="134"/>
+      <c r="C607" s="135"/>
+      <c r="D607" s="136"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="133" t="s">
+      <c r="A608" s="139" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="112"/>
-      <c r="C608" s="112"/>
-      <c r="D608" s="112"/>
+      <c r="B608" s="119"/>
+      <c r="C608" s="119"/>
+      <c r="D608" s="119"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30551,19 +30551,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="134"/>
-      <c r="B614" s="135"/>
-      <c r="C614" s="136"/>
-      <c r="D614" s="137"/>
+      <c r="A614" s="133"/>
+      <c r="B614" s="134"/>
+      <c r="C614" s="135"/>
+      <c r="D614" s="136"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="133" t="s">
+      <c r="A615" s="139" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="112"/>
-      <c r="C615" s="112"/>
-      <c r="D615" s="112"/>
+      <c r="B615" s="119"/>
+      <c r="C615" s="119"/>
+      <c r="D615" s="119"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31928,25 +31928,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31963,6 +31944,25 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF4CA18-AA4C-4FE6-8A79-5A794BC65EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9D2AA2-CBA8-4EC8-B42D-D03CF6AD9BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5116,6 +5116,51 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5133,12 +5178,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5148,43 +5187,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5199,14 +5202,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5227,10 +5227,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5552,83 +5552,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="126"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="128"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="111"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="128"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="111"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="128"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="128"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="108"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="111"/>
+      <c r="A6" s="127"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="128"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="114"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="125"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="117"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="122" t="s">
+      <c r="A9" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="120"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -7314,20 +7314,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="121"/>
-      <c r="B109" s="109"/>
-      <c r="C109" s="109"/>
-      <c r="D109" s="110"/>
-      <c r="E109" s="117"/>
+      <c r="A109" s="102"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="103"/>
+      <c r="D109" s="104"/>
+      <c r="E109" s="105"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="122" t="s">
+      <c r="A110" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="119"/>
-      <c r="C110" s="119"/>
-      <c r="D110" s="119"/>
-      <c r="E110" s="120"/>
+      <c r="B110" s="112"/>
+      <c r="C110" s="112"/>
+      <c r="D110" s="112"/>
+      <c r="E110" s="113"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7619,20 +7619,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="121"/>
-      <c r="B128" s="109"/>
-      <c r="C128" s="109"/>
-      <c r="D128" s="110"/>
-      <c r="E128" s="117"/>
+      <c r="A128" s="102"/>
+      <c r="B128" s="103"/>
+      <c r="C128" s="103"/>
+      <c r="D128" s="104"/>
+      <c r="E128" s="105"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="122" t="s">
+      <c r="A129" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="119"/>
-      <c r="C129" s="119"/>
-      <c r="D129" s="119"/>
-      <c r="E129" s="120"/>
+      <c r="B129" s="112"/>
+      <c r="C129" s="112"/>
+      <c r="D129" s="112"/>
+      <c r="E129" s="113"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7788,20 +7788,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="121"/>
-      <c r="B139" s="109"/>
-      <c r="C139" s="109"/>
-      <c r="D139" s="110"/>
-      <c r="E139" s="117"/>
+      <c r="A139" s="102"/>
+      <c r="B139" s="103"/>
+      <c r="C139" s="103"/>
+      <c r="D139" s="104"/>
+      <c r="E139" s="105"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="126" t="s">
+      <c r="A140" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="119"/>
-      <c r="C140" s="119"/>
-      <c r="D140" s="119"/>
-      <c r="E140" s="127"/>
+      <c r="B140" s="112"/>
+      <c r="C140" s="112"/>
+      <c r="D140" s="112"/>
+      <c r="E140" s="120"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -9045,20 +9045,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="121"/>
-      <c r="B214" s="109"/>
-      <c r="C214" s="109"/>
-      <c r="D214" s="110"/>
-      <c r="E214" s="117"/>
+      <c r="A214" s="102"/>
+      <c r="B214" s="103"/>
+      <c r="C214" s="103"/>
+      <c r="D214" s="104"/>
+      <c r="E214" s="105"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="122" t="s">
+      <c r="A215" s="118" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="119"/>
-      <c r="C215" s="119"/>
-      <c r="D215" s="119"/>
-      <c r="E215" s="120"/>
+      <c r="B215" s="112"/>
+      <c r="C215" s="112"/>
+      <c r="D215" s="112"/>
+      <c r="E215" s="113"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -10266,20 +10266,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="116"/>
-      <c r="B287" s="109"/>
-      <c r="C287" s="109"/>
-      <c r="D287" s="110"/>
-      <c r="E287" s="117"/>
+      <c r="A287" s="114"/>
+      <c r="B287" s="103"/>
+      <c r="C287" s="103"/>
+      <c r="D287" s="104"/>
+      <c r="E287" s="105"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="122" t="s">
+      <c r="A288" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="119"/>
-      <c r="C288" s="119"/>
-      <c r="D288" s="119"/>
-      <c r="E288" s="120"/>
+      <c r="B288" s="112"/>
+      <c r="C288" s="112"/>
+      <c r="D288" s="112"/>
+      <c r="E288" s="113"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -11844,20 +11844,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="116"/>
-      <c r="B381" s="109"/>
-      <c r="C381" s="109"/>
-      <c r="D381" s="110"/>
-      <c r="E381" s="117"/>
+      <c r="A381" s="114"/>
+      <c r="B381" s="103"/>
+      <c r="C381" s="103"/>
+      <c r="D381" s="104"/>
+      <c r="E381" s="105"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="118" t="s">
+      <c r="A382" s="111" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="119"/>
-      <c r="C382" s="119"/>
-      <c r="D382" s="119"/>
-      <c r="E382" s="120"/>
+      <c r="B382" s="112"/>
+      <c r="C382" s="112"/>
+      <c r="D382" s="112"/>
+      <c r="E382" s="113"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12511,13 +12511,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="118" t="s">
+      <c r="A422" s="111" t="s">
         <v>1302</v>
       </c>
-      <c r="B422" s="119"/>
-      <c r="C422" s="119"/>
-      <c r="D422" s="119"/>
-      <c r="E422" s="120"/>
+      <c r="B422" s="112"/>
+      <c r="C422" s="112"/>
+      <c r="D422" s="112"/>
+      <c r="E422" s="113"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -13039,7 +13039,7 @@
         <v>84</v>
       </c>
       <c r="E453" s="40">
-        <v>105</v>
+        <v>125</v>
       </c>
     </row>
     <row r="454" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -14454,20 +14454,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="116"/>
-      <c r="B537" s="109"/>
-      <c r="C537" s="109"/>
-      <c r="D537" s="110"/>
-      <c r="E537" s="117"/>
+      <c r="A537" s="114"/>
+      <c r="B537" s="103"/>
+      <c r="C537" s="103"/>
+      <c r="D537" s="104"/>
+      <c r="E537" s="105"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="118" t="s">
+      <c r="A538" s="111" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="119"/>
-      <c r="C538" s="119"/>
-      <c r="D538" s="119"/>
-      <c r="E538" s="120"/>
+      <c r="B538" s="112"/>
+      <c r="C538" s="112"/>
+      <c r="D538" s="112"/>
+      <c r="E538" s="113"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14719,7 +14719,7 @@
         <v>15</v>
       </c>
       <c r="E553" s="40">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="554" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -14736,7 +14736,7 @@
         <v>20</v>
       </c>
       <c r="E554" s="40">
-        <v>212.5</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="555" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -14825,20 +14825,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="116"/>
-      <c r="B560" s="109"/>
-      <c r="C560" s="109"/>
-      <c r="D560" s="110"/>
-      <c r="E560" s="117"/>
+      <c r="A560" s="114"/>
+      <c r="B560" s="103"/>
+      <c r="C560" s="103"/>
+      <c r="D560" s="104"/>
+      <c r="E560" s="105"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="118" t="s">
+      <c r="A561" s="111" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="119"/>
-      <c r="C561" s="119"/>
-      <c r="D561" s="119"/>
-      <c r="E561" s="120"/>
+      <c r="B561" s="112"/>
+      <c r="C561" s="112"/>
+      <c r="D561" s="112"/>
+      <c r="E561" s="113"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15158,7 +15158,7 @@
         <v>20</v>
       </c>
       <c r="E580" s="50">
-        <v>147.5</v>
+        <v>152.5</v>
       </c>
     </row>
     <row r="581" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -15175,7 +15175,7 @@
         <v>15</v>
       </c>
       <c r="E581" s="50">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="582" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -15451,20 +15451,20 @@
       </c>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="128"/>
-      <c r="B598" s="129"/>
-      <c r="C598" s="129"/>
-      <c r="D598" s="129"/>
-      <c r="E598" s="129"/>
+      <c r="A598" s="106"/>
+      <c r="B598" s="107"/>
+      <c r="C598" s="107"/>
+      <c r="D598" s="107"/>
+      <c r="E598" s="107"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A599" s="118" t="s">
+      <c r="A599" s="111" t="s">
         <v>370</v>
       </c>
-      <c r="B599" s="119"/>
-      <c r="C599" s="119"/>
-      <c r="D599" s="119"/>
-      <c r="E599" s="120"/>
+      <c r="B599" s="112"/>
+      <c r="C599" s="112"/>
+      <c r="D599" s="112"/>
+      <c r="E599" s="113"/>
     </row>
     <row r="600" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="66" t="s">
@@ -16739,7 +16739,7 @@
         <v>34</v>
       </c>
       <c r="E674" s="40">
-        <v>275</v>
+        <v>255</v>
       </c>
     </row>
     <row r="675" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -16756,7 +16756,7 @@
         <v>20</v>
       </c>
       <c r="E675" s="40">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="676" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -17457,20 +17457,20 @@
       </c>
     </row>
     <row r="717" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="116"/>
-      <c r="B717" s="109"/>
-      <c r="C717" s="109"/>
-      <c r="D717" s="110"/>
-      <c r="E717" s="117"/>
+      <c r="A717" s="114"/>
+      <c r="B717" s="103"/>
+      <c r="C717" s="103"/>
+      <c r="D717" s="104"/>
+      <c r="E717" s="105"/>
     </row>
     <row r="718" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A718" s="118" t="s">
+      <c r="A718" s="111" t="s">
         <v>420</v>
       </c>
-      <c r="B718" s="119"/>
-      <c r="C718" s="119"/>
-      <c r="D718" s="119"/>
-      <c r="E718" s="120"/>
+      <c r="B718" s="112"/>
+      <c r="C718" s="112"/>
+      <c r="D718" s="112"/>
+      <c r="E718" s="113"/>
     </row>
     <row r="719" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="66" t="s">
@@ -17648,13 +17648,13 @@
       <c r="E729" s="61"/>
     </row>
     <row r="730" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A730" s="118" t="s">
+      <c r="A730" s="111" t="s">
         <v>1303</v>
       </c>
-      <c r="B730" s="119"/>
-      <c r="C730" s="119"/>
-      <c r="D730" s="119"/>
-      <c r="E730" s="120"/>
+      <c r="B730" s="112"/>
+      <c r="C730" s="112"/>
+      <c r="D730" s="112"/>
+      <c r="E730" s="113"/>
     </row>
     <row r="731" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="72" t="s">
@@ -17776,20 +17776,20 @@
       </c>
     </row>
     <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="121"/>
-      <c r="B738" s="109"/>
-      <c r="C738" s="109"/>
-      <c r="D738" s="110"/>
-      <c r="E738" s="117"/>
+      <c r="A738" s="102"/>
+      <c r="B738" s="103"/>
+      <c r="C738" s="103"/>
+      <c r="D738" s="104"/>
+      <c r="E738" s="105"/>
     </row>
     <row r="739" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A739" s="118" t="s">
+      <c r="A739" s="111" t="s">
         <v>421</v>
       </c>
-      <c r="B739" s="119"/>
-      <c r="C739" s="119"/>
-      <c r="D739" s="119"/>
-      <c r="E739" s="120"/>
+      <c r="B739" s="112"/>
+      <c r="C739" s="112"/>
+      <c r="D739" s="112"/>
+      <c r="E739" s="113"/>
     </row>
     <row r="740" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="66" t="s">
@@ -17943,20 +17943,20 @@
       </c>
     </row>
     <row r="749" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="121"/>
-      <c r="B749" s="109"/>
-      <c r="C749" s="109"/>
-      <c r="D749" s="110"/>
-      <c r="E749" s="117"/>
+      <c r="A749" s="102"/>
+      <c r="B749" s="103"/>
+      <c r="C749" s="103"/>
+      <c r="D749" s="104"/>
+      <c r="E749" s="105"/>
     </row>
     <row r="750" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A750" s="118" t="s">
+      <c r="A750" s="111" t="s">
         <v>1301</v>
       </c>
-      <c r="B750" s="119"/>
-      <c r="C750" s="119"/>
-      <c r="D750" s="119"/>
-      <c r="E750" s="120"/>
+      <c r="B750" s="112"/>
+      <c r="C750" s="112"/>
+      <c r="D750" s="112"/>
+      <c r="E750" s="113"/>
     </row>
     <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="66" t="s">
@@ -18386,13 +18386,13 @@
       <c r="E775" s="98"/>
     </row>
     <row r="776" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A776" s="130" t="s">
+      <c r="A776" s="108" t="s">
         <v>1287</v>
       </c>
-      <c r="B776" s="131"/>
-      <c r="C776" s="131"/>
-      <c r="D776" s="131"/>
-      <c r="E776" s="132"/>
+      <c r="B776" s="109"/>
+      <c r="C776" s="109"/>
+      <c r="D776" s="109"/>
+      <c r="E776" s="110"/>
     </row>
     <row r="777" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="66" t="s">
@@ -20354,13 +20354,13 @@
       <c r="E893" s="100"/>
     </row>
     <row r="894" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A894" s="102" t="s">
+      <c r="A894" s="121" t="s">
         <v>1288</v>
       </c>
-      <c r="B894" s="103"/>
-      <c r="C894" s="103"/>
-      <c r="D894" s="103"/>
-      <c r="E894" s="104"/>
+      <c r="B894" s="122"/>
+      <c r="C894" s="122"/>
+      <c r="D894" s="122"/>
+      <c r="E894" s="123"/>
     </row>
     <row r="895" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="87" t="s">
@@ -20633,27 +20633,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A738:E738"/>
-    <mergeCell ref="A598:E598"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A776:E776"/>
-    <mergeCell ref="A730:E730"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A750:E750"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A538:E538"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A422:E422"/>
-    <mergeCell ref="A382:E382"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A381:E381"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A215:E215"/>
     <mergeCell ref="A894:E894"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
@@ -20670,6 +20649,27 @@
     <mergeCell ref="A560:E560"/>
     <mergeCell ref="A717:E717"/>
     <mergeCell ref="A288:E288"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A538:E538"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A422:E422"/>
+    <mergeCell ref="A382:E382"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A215:E215"/>
+    <mergeCell ref="A738:E738"/>
+    <mergeCell ref="A598:E598"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A776:E776"/>
+    <mergeCell ref="A730:E730"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A750:E750"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20709,78 +20709,78 @@
       <c r="A2" s="148" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="138"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="139"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="150" t="s">
         <v>485</v>
       </c>
-      <c r="B3" s="134"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="138"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="139"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="149" t="s">
+      <c r="A4" s="138" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="138"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="139"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="150" t="s">
         <v>487</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="138"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="139"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="134"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="138"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="139"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="134"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="138"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="139"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="138"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="139"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="138"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="139"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="150" t="s">
+      <c r="A10" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22503,19 +22503,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="133"/>
-      <c r="B112" s="134"/>
-      <c r="C112" s="135"/>
-      <c r="D112" s="136"/>
+      <c r="A112" s="134"/>
+      <c r="B112" s="135"/>
+      <c r="C112" s="136"/>
+      <c r="D112" s="137"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="140" t="s">
+      <c r="A113" s="149" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="119"/>
-      <c r="C113" s="119"/>
-      <c r="D113" s="127"/>
+      <c r="B113" s="112"/>
+      <c r="C113" s="112"/>
+      <c r="D113" s="120"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22808,19 +22808,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="133"/>
-      <c r="B131" s="134"/>
-      <c r="C131" s="135"/>
-      <c r="D131" s="136"/>
+      <c r="A131" s="134"/>
+      <c r="B131" s="135"/>
+      <c r="C131" s="136"/>
+      <c r="D131" s="137"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="140" t="s">
+      <c r="A132" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="119"/>
-      <c r="C132" s="119"/>
-      <c r="D132" s="127"/>
+      <c r="B132" s="112"/>
+      <c r="C132" s="112"/>
+      <c r="D132" s="120"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22994,19 +22994,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="133"/>
-      <c r="B143" s="134"/>
-      <c r="C143" s="135"/>
-      <c r="D143" s="136"/>
+      <c r="A143" s="134"/>
+      <c r="B143" s="135"/>
+      <c r="C143" s="136"/>
+      <c r="D143" s="137"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="140" t="s">
+      <c r="A144" s="149" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="119"/>
-      <c r="C144" s="119"/>
-      <c r="D144" s="127"/>
+      <c r="B144" s="112"/>
+      <c r="C144" s="112"/>
+      <c r="D144" s="120"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23639,19 +23639,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="133"/>
-      <c r="B182" s="134"/>
-      <c r="C182" s="135"/>
-      <c r="D182" s="136"/>
+      <c r="A182" s="134"/>
+      <c r="B182" s="135"/>
+      <c r="C182" s="136"/>
+      <c r="D182" s="137"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="139" t="s">
+      <c r="A183" s="133" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="119"/>
-      <c r="C183" s="119"/>
-      <c r="D183" s="119"/>
+      <c r="B183" s="112"/>
+      <c r="C183" s="112"/>
+      <c r="D183" s="112"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24513,19 +24513,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="133"/>
-      <c r="B241" s="134"/>
-      <c r="C241" s="135"/>
-      <c r="D241" s="136"/>
+      <c r="A241" s="134"/>
+      <c r="B241" s="135"/>
+      <c r="C241" s="136"/>
+      <c r="D241" s="137"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="139" t="s">
+      <c r="A242" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="119"/>
-      <c r="C242" s="119"/>
-      <c r="D242" s="119"/>
+      <c r="B242" s="112"/>
+      <c r="C242" s="112"/>
+      <c r="D242" s="112"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25746,21 +25746,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="133"/>
-      <c r="B324" s="134"/>
-      <c r="C324" s="135"/>
-      <c r="D324" s="136"/>
+      <c r="A324" s="134"/>
+      <c r="B324" s="135"/>
+      <c r="C324" s="136"/>
+      <c r="D324" s="137"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="139" t="s">
+      <c r="A325" s="133" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="119"/>
-      <c r="C325" s="119"/>
-      <c r="D325" s="119"/>
+      <c r="B325" s="112"/>
+      <c r="C325" s="112"/>
+      <c r="D325" s="112"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26257,19 +26257,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="133"/>
-      <c r="B355" s="134"/>
-      <c r="C355" s="135"/>
-      <c r="D355" s="136"/>
+      <c r="A355" s="134"/>
+      <c r="B355" s="135"/>
+      <c r="C355" s="136"/>
+      <c r="D355" s="137"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="139" t="s">
+      <c r="A356" s="133" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="119"/>
-      <c r="C356" s="119"/>
-      <c r="D356" s="119"/>
+      <c r="B356" s="112"/>
+      <c r="C356" s="112"/>
+      <c r="D356" s="112"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28024,19 +28024,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="133"/>
-      <c r="B460" s="134"/>
-      <c r="C460" s="135"/>
-      <c r="D460" s="136"/>
+      <c r="A460" s="134"/>
+      <c r="B460" s="135"/>
+      <c r="C460" s="136"/>
+      <c r="D460" s="137"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="139" t="s">
+      <c r="A461" s="133" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="119"/>
-      <c r="C461" s="119"/>
-      <c r="D461" s="119"/>
+      <c r="B461" s="112"/>
+      <c r="C461" s="112"/>
+      <c r="D461" s="112"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28329,19 +28329,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="133"/>
-      <c r="B479" s="134"/>
-      <c r="C479" s="135"/>
-      <c r="D479" s="136"/>
+      <c r="A479" s="134"/>
+      <c r="B479" s="135"/>
+      <c r="C479" s="136"/>
+      <c r="D479" s="137"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="139" t="s">
+      <c r="A480" s="133" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="119"/>
-      <c r="C480" s="119"/>
-      <c r="D480" s="119"/>
+      <c r="B480" s="112"/>
+      <c r="C480" s="112"/>
+      <c r="D480" s="112"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28770,19 +28770,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="133"/>
-      <c r="B506" s="134"/>
-      <c r="C506" s="135"/>
-      <c r="D506" s="136"/>
+      <c r="A506" s="134"/>
+      <c r="B506" s="135"/>
+      <c r="C506" s="136"/>
+      <c r="D506" s="137"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="139" t="s">
+      <c r="A507" s="133" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="119"/>
-      <c r="C507" s="119"/>
-      <c r="D507" s="119"/>
+      <c r="B507" s="112"/>
+      <c r="C507" s="112"/>
+      <c r="D507" s="112"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30297,19 +30297,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="133"/>
-      <c r="B597" s="134"/>
-      <c r="C597" s="135"/>
-      <c r="D597" s="136"/>
+      <c r="A597" s="134"/>
+      <c r="B597" s="135"/>
+      <c r="C597" s="136"/>
+      <c r="D597" s="137"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="139" t="s">
+      <c r="A598" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="119"/>
-      <c r="C598" s="119"/>
-      <c r="D598" s="119"/>
+      <c r="B598" s="112"/>
+      <c r="C598" s="112"/>
+      <c r="D598" s="112"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30449,20 +30449,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="133"/>
-      <c r="B607" s="134"/>
-      <c r="C607" s="135"/>
-      <c r="D607" s="136"/>
+      <c r="A607" s="134"/>
+      <c r="B607" s="135"/>
+      <c r="C607" s="136"/>
+      <c r="D607" s="137"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="139" t="s">
+      <c r="A608" s="133" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="119"/>
-      <c r="C608" s="119"/>
-      <c r="D608" s="119"/>
+      <c r="B608" s="112"/>
+      <c r="C608" s="112"/>
+      <c r="D608" s="112"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30551,19 +30551,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="133"/>
-      <c r="B614" s="134"/>
-      <c r="C614" s="135"/>
-      <c r="D614" s="136"/>
+      <c r="A614" s="134"/>
+      <c r="B614" s="135"/>
+      <c r="C614" s="136"/>
+      <c r="D614" s="137"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="139" t="s">
+      <c r="A615" s="133" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="119"/>
-      <c r="C615" s="119"/>
-      <c r="D615" s="119"/>
+      <c r="B615" s="112"/>
+      <c r="C615" s="112"/>
+      <c r="D615" s="112"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31928,6 +31928,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31944,25 +31963,6 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9D2AA2-CBA8-4EC8-B42D-D03CF6AD9BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E36288-30CA-47D6-85F5-EDA6E990FC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5116,51 +5116,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5178,6 +5133,12 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5187,7 +5148,43 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5202,11 +5199,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5227,10 +5227,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5552,83 +5552,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="126"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="128"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127" t="s">
+      <c r="A3" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="128"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127" t="s">
+      <c r="A4" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="128"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="111"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="128"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="128"/>
+      <c r="A6" s="108"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="132"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="117"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="125"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="120"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -6239,7 +6239,7 @@
         <v>34</v>
       </c>
       <c r="E45" s="49">
-        <v>550</v>
+        <v>490</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -6256,7 +6256,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="41">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7314,20 +7314,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="102"/>
-      <c r="B109" s="103"/>
-      <c r="C109" s="103"/>
-      <c r="D109" s="104"/>
-      <c r="E109" s="105"/>
+      <c r="A109" s="121"/>
+      <c r="B109" s="109"/>
+      <c r="C109" s="109"/>
+      <c r="D109" s="110"/>
+      <c r="E109" s="117"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="118" t="s">
+      <c r="A110" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="112"/>
-      <c r="C110" s="112"/>
-      <c r="D110" s="112"/>
-      <c r="E110" s="113"/>
+      <c r="B110" s="119"/>
+      <c r="C110" s="119"/>
+      <c r="D110" s="119"/>
+      <c r="E110" s="120"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7619,20 +7619,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="102"/>
-      <c r="B128" s="103"/>
-      <c r="C128" s="103"/>
-      <c r="D128" s="104"/>
-      <c r="E128" s="105"/>
+      <c r="A128" s="121"/>
+      <c r="B128" s="109"/>
+      <c r="C128" s="109"/>
+      <c r="D128" s="110"/>
+      <c r="E128" s="117"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="118" t="s">
+      <c r="A129" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="112"/>
-      <c r="C129" s="112"/>
-      <c r="D129" s="112"/>
-      <c r="E129" s="113"/>
+      <c r="B129" s="119"/>
+      <c r="C129" s="119"/>
+      <c r="D129" s="119"/>
+      <c r="E129" s="120"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7788,20 +7788,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="102"/>
-      <c r="B139" s="103"/>
-      <c r="C139" s="103"/>
-      <c r="D139" s="104"/>
-      <c r="E139" s="105"/>
+      <c r="A139" s="121"/>
+      <c r="B139" s="109"/>
+      <c r="C139" s="109"/>
+      <c r="D139" s="110"/>
+      <c r="E139" s="117"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="119" t="s">
+      <c r="A140" s="126" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="112"/>
-      <c r="C140" s="112"/>
-      <c r="D140" s="112"/>
-      <c r="E140" s="120"/>
+      <c r="B140" s="119"/>
+      <c r="C140" s="119"/>
+      <c r="D140" s="119"/>
+      <c r="E140" s="127"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -9045,20 +9045,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="102"/>
-      <c r="B214" s="103"/>
-      <c r="C214" s="103"/>
-      <c r="D214" s="104"/>
-      <c r="E214" s="105"/>
+      <c r="A214" s="121"/>
+      <c r="B214" s="109"/>
+      <c r="C214" s="109"/>
+      <c r="D214" s="110"/>
+      <c r="E214" s="117"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="118" t="s">
+      <c r="A215" s="122" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="112"/>
-      <c r="C215" s="112"/>
-      <c r="D215" s="112"/>
-      <c r="E215" s="113"/>
+      <c r="B215" s="119"/>
+      <c r="C215" s="119"/>
+      <c r="D215" s="119"/>
+      <c r="E215" s="120"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -10266,20 +10266,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="114"/>
-      <c r="B287" s="103"/>
-      <c r="C287" s="103"/>
-      <c r="D287" s="104"/>
-      <c r="E287" s="105"/>
+      <c r="A287" s="116"/>
+      <c r="B287" s="109"/>
+      <c r="C287" s="109"/>
+      <c r="D287" s="110"/>
+      <c r="E287" s="117"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="118" t="s">
+      <c r="A288" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="112"/>
-      <c r="C288" s="112"/>
-      <c r="D288" s="112"/>
-      <c r="E288" s="113"/>
+      <c r="B288" s="119"/>
+      <c r="C288" s="119"/>
+      <c r="D288" s="119"/>
+      <c r="E288" s="120"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -10548,7 +10548,7 @@
         <v>84</v>
       </c>
       <c r="E304" s="40">
-        <v>162.5</v>
+        <v>148</v>
       </c>
     </row>
     <row r="305" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10565,7 +10565,7 @@
         <v>84</v>
       </c>
       <c r="E305" s="40">
-        <v>295</v>
+        <v>268.5</v>
       </c>
     </row>
     <row r="306" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -10582,7 +10582,7 @@
         <v>84</v>
       </c>
       <c r="E306" s="40">
-        <v>34.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="307" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -10871,7 +10871,7 @@
         <v>34</v>
       </c>
       <c r="E323" s="40">
-        <v>420</v>
+        <v>356</v>
       </c>
     </row>
     <row r="324" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10888,7 +10888,7 @@
         <v>34</v>
       </c>
       <c r="E324" s="40">
-        <v>210</v>
+        <v>178</v>
       </c>
     </row>
     <row r="325" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10905,7 +10905,7 @@
         <v>20</v>
       </c>
       <c r="E325" s="40">
-        <v>44</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="326" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -11534,7 +11534,7 @@
         <v>84</v>
       </c>
       <c r="E362" s="40">
-        <v>199.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="363" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -11551,7 +11551,7 @@
         <v>34</v>
       </c>
       <c r="E363" s="40">
-        <v>399</v>
+        <v>375</v>
       </c>
     </row>
     <row r="364" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -11568,7 +11568,7 @@
         <v>49</v>
       </c>
       <c r="E364" s="50">
-        <v>46</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="365" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -11844,20 +11844,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="114"/>
-      <c r="B381" s="103"/>
-      <c r="C381" s="103"/>
-      <c r="D381" s="104"/>
-      <c r="E381" s="105"/>
+      <c r="A381" s="116"/>
+      <c r="B381" s="109"/>
+      <c r="C381" s="109"/>
+      <c r="D381" s="110"/>
+      <c r="E381" s="117"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="111" t="s">
+      <c r="A382" s="118" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="112"/>
-      <c r="C382" s="112"/>
-      <c r="D382" s="112"/>
-      <c r="E382" s="113"/>
+      <c r="B382" s="119"/>
+      <c r="C382" s="119"/>
+      <c r="D382" s="119"/>
+      <c r="E382" s="120"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12296,7 +12296,7 @@
         <v>84</v>
       </c>
       <c r="E408" s="40">
-        <v>190</v>
+        <v>209</v>
       </c>
     </row>
     <row r="409" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12511,13 +12511,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="111" t="s">
+      <c r="A422" s="118" t="s">
         <v>1302</v>
       </c>
-      <c r="B422" s="112"/>
-      <c r="C422" s="112"/>
-      <c r="D422" s="112"/>
-      <c r="E422" s="113"/>
+      <c r="B422" s="119"/>
+      <c r="C422" s="119"/>
+      <c r="D422" s="119"/>
+      <c r="E422" s="120"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -14454,20 +14454,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="114"/>
-      <c r="B537" s="103"/>
-      <c r="C537" s="103"/>
-      <c r="D537" s="104"/>
-      <c r="E537" s="105"/>
+      <c r="A537" s="116"/>
+      <c r="B537" s="109"/>
+      <c r="C537" s="109"/>
+      <c r="D537" s="110"/>
+      <c r="E537" s="117"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="111" t="s">
+      <c r="A538" s="118" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="112"/>
-      <c r="C538" s="112"/>
-      <c r="D538" s="112"/>
-      <c r="E538" s="113"/>
+      <c r="B538" s="119"/>
+      <c r="C538" s="119"/>
+      <c r="D538" s="119"/>
+      <c r="E538" s="120"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14825,20 +14825,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="114"/>
-      <c r="B560" s="103"/>
-      <c r="C560" s="103"/>
-      <c r="D560" s="104"/>
-      <c r="E560" s="105"/>
+      <c r="A560" s="116"/>
+      <c r="B560" s="109"/>
+      <c r="C560" s="109"/>
+      <c r="D560" s="110"/>
+      <c r="E560" s="117"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="111" t="s">
+      <c r="A561" s="118" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="112"/>
-      <c r="C561" s="112"/>
-      <c r="D561" s="112"/>
-      <c r="E561" s="113"/>
+      <c r="B561" s="119"/>
+      <c r="C561" s="119"/>
+      <c r="D561" s="119"/>
+      <c r="E561" s="120"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15451,20 +15451,20 @@
       </c>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="106"/>
-      <c r="B598" s="107"/>
-      <c r="C598" s="107"/>
-      <c r="D598" s="107"/>
-      <c r="E598" s="107"/>
+      <c r="A598" s="128"/>
+      <c r="B598" s="129"/>
+      <c r="C598" s="129"/>
+      <c r="D598" s="129"/>
+      <c r="E598" s="129"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A599" s="111" t="s">
+      <c r="A599" s="118" t="s">
         <v>370</v>
       </c>
-      <c r="B599" s="112"/>
-      <c r="C599" s="112"/>
-      <c r="D599" s="112"/>
-      <c r="E599" s="113"/>
+      <c r="B599" s="119"/>
+      <c r="C599" s="119"/>
+      <c r="D599" s="119"/>
+      <c r="E599" s="120"/>
     </row>
     <row r="600" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="66" t="s">
@@ -17457,20 +17457,20 @@
       </c>
     </row>
     <row r="717" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="114"/>
-      <c r="B717" s="103"/>
-      <c r="C717" s="103"/>
-      <c r="D717" s="104"/>
-      <c r="E717" s="105"/>
+      <c r="A717" s="116"/>
+      <c r="B717" s="109"/>
+      <c r="C717" s="109"/>
+      <c r="D717" s="110"/>
+      <c r="E717" s="117"/>
     </row>
     <row r="718" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A718" s="111" t="s">
+      <c r="A718" s="118" t="s">
         <v>420</v>
       </c>
-      <c r="B718" s="112"/>
-      <c r="C718" s="112"/>
-      <c r="D718" s="112"/>
-      <c r="E718" s="113"/>
+      <c r="B718" s="119"/>
+      <c r="C718" s="119"/>
+      <c r="D718" s="119"/>
+      <c r="E718" s="120"/>
     </row>
     <row r="719" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="66" t="s">
@@ -17648,13 +17648,13 @@
       <c r="E729" s="61"/>
     </row>
     <row r="730" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A730" s="111" t="s">
+      <c r="A730" s="118" t="s">
         <v>1303</v>
       </c>
-      <c r="B730" s="112"/>
-      <c r="C730" s="112"/>
-      <c r="D730" s="112"/>
-      <c r="E730" s="113"/>
+      <c r="B730" s="119"/>
+      <c r="C730" s="119"/>
+      <c r="D730" s="119"/>
+      <c r="E730" s="120"/>
     </row>
     <row r="731" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="72" t="s">
@@ -17776,20 +17776,20 @@
       </c>
     </row>
     <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="102"/>
-      <c r="B738" s="103"/>
-      <c r="C738" s="103"/>
-      <c r="D738" s="104"/>
-      <c r="E738" s="105"/>
+      <c r="A738" s="121"/>
+      <c r="B738" s="109"/>
+      <c r="C738" s="109"/>
+      <c r="D738" s="110"/>
+      <c r="E738" s="117"/>
     </row>
     <row r="739" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A739" s="111" t="s">
+      <c r="A739" s="118" t="s">
         <v>421</v>
       </c>
-      <c r="B739" s="112"/>
-      <c r="C739" s="112"/>
-      <c r="D739" s="112"/>
-      <c r="E739" s="113"/>
+      <c r="B739" s="119"/>
+      <c r="C739" s="119"/>
+      <c r="D739" s="119"/>
+      <c r="E739" s="120"/>
     </row>
     <row r="740" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="66" t="s">
@@ -17943,20 +17943,20 @@
       </c>
     </row>
     <row r="749" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="102"/>
-      <c r="B749" s="103"/>
-      <c r="C749" s="103"/>
-      <c r="D749" s="104"/>
-      <c r="E749" s="105"/>
+      <c r="A749" s="121"/>
+      <c r="B749" s="109"/>
+      <c r="C749" s="109"/>
+      <c r="D749" s="110"/>
+      <c r="E749" s="117"/>
     </row>
     <row r="750" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A750" s="111" t="s">
+      <c r="A750" s="118" t="s">
         <v>1301</v>
       </c>
-      <c r="B750" s="112"/>
-      <c r="C750" s="112"/>
-      <c r="D750" s="112"/>
-      <c r="E750" s="113"/>
+      <c r="B750" s="119"/>
+      <c r="C750" s="119"/>
+      <c r="D750" s="119"/>
+      <c r="E750" s="120"/>
     </row>
     <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="66" t="s">
@@ -18386,13 +18386,13 @@
       <c r="E775" s="98"/>
     </row>
     <row r="776" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A776" s="108" t="s">
+      <c r="A776" s="130" t="s">
         <v>1287</v>
       </c>
-      <c r="B776" s="109"/>
-      <c r="C776" s="109"/>
-      <c r="D776" s="109"/>
-      <c r="E776" s="110"/>
+      <c r="B776" s="131"/>
+      <c r="C776" s="131"/>
+      <c r="D776" s="131"/>
+      <c r="E776" s="132"/>
     </row>
     <row r="777" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="66" t="s">
@@ -20354,13 +20354,13 @@
       <c r="E893" s="100"/>
     </row>
     <row r="894" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A894" s="121" t="s">
+      <c r="A894" s="102" t="s">
         <v>1288</v>
       </c>
-      <c r="B894" s="122"/>
-      <c r="C894" s="122"/>
-      <c r="D894" s="122"/>
-      <c r="E894" s="123"/>
+      <c r="B894" s="103"/>
+      <c r="C894" s="103"/>
+      <c r="D894" s="103"/>
+      <c r="E894" s="104"/>
     </row>
     <row r="895" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="87" t="s">
@@ -20427,7 +20427,7 @@
         <v>412</v>
       </c>
       <c r="E898" s="48">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="899" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20444,7 +20444,7 @@
         <v>15</v>
       </c>
       <c r="E899" s="48">
-        <v>252</v>
+        <v>276</v>
       </c>
     </row>
     <row r="900" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20461,7 +20461,7 @@
         <v>412</v>
       </c>
       <c r="E900" s="48">
-        <v>57</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="901" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20478,7 +20478,7 @@
         <v>15</v>
       </c>
       <c r="E901" s="48">
-        <v>540</v>
+        <v>582</v>
       </c>
     </row>
     <row r="902" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20495,7 +20495,7 @@
         <v>412</v>
       </c>
       <c r="E902" s="48">
-        <v>70</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="903" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20512,7 +20512,7 @@
         <v>15</v>
       </c>
       <c r="E903" s="48">
-        <v>660</v>
+        <v>714.5</v>
       </c>
     </row>
     <row r="904" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20529,7 +20529,7 @@
         <v>412</v>
       </c>
       <c r="E904" s="48">
-        <v>62.5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="905" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20546,7 +20546,7 @@
         <v>15</v>
       </c>
       <c r="E905" s="48">
-        <v>582</v>
+        <v>636</v>
       </c>
     </row>
     <row r="906" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20563,7 +20563,7 @@
         <v>412</v>
       </c>
       <c r="E906" s="48">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="907" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20580,7 +20580,7 @@
         <v>15</v>
       </c>
       <c r="E907" s="48">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="908" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -20597,7 +20597,7 @@
         <v>412</v>
       </c>
       <c r="E908" s="48">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="909" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
@@ -20614,7 +20614,7 @@
         <v>15</v>
       </c>
       <c r="E909" s="48">
-        <v>996</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="910" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
@@ -20633,6 +20633,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A738:E738"/>
+    <mergeCell ref="A598:E598"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A776:E776"/>
+    <mergeCell ref="A730:E730"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A750:E750"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A538:E538"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A422:E422"/>
+    <mergeCell ref="A382:E382"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A215:E215"/>
     <mergeCell ref="A894:E894"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
@@ -20649,27 +20670,6 @@
     <mergeCell ref="A560:E560"/>
     <mergeCell ref="A717:E717"/>
     <mergeCell ref="A288:E288"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A538:E538"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A422:E422"/>
-    <mergeCell ref="A382:E382"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A381:E381"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A215:E215"/>
-    <mergeCell ref="A738:E738"/>
-    <mergeCell ref="A598:E598"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A776:E776"/>
-    <mergeCell ref="A730:E730"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A750:E750"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20709,78 +20709,78 @@
       <c r="A2" s="148" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="139"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="138"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="150" t="s">
+      <c r="A3" s="137" t="s">
         <v>485</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="139"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="138"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="149" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="139"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="138"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="137" t="s">
         <v>487</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="139"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="138"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="135"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="139"/>
+      <c r="B6" s="134"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="138"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="135"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="139"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="138"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="139"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="138"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="139"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="138"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="140" t="s">
+      <c r="A10" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="120"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22503,19 +22503,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="134"/>
-      <c r="B112" s="135"/>
-      <c r="C112" s="136"/>
-      <c r="D112" s="137"/>
+      <c r="A112" s="133"/>
+      <c r="B112" s="134"/>
+      <c r="C112" s="135"/>
+      <c r="D112" s="136"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="149" t="s">
+      <c r="A113" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="112"/>
-      <c r="C113" s="112"/>
-      <c r="D113" s="120"/>
+      <c r="B113" s="119"/>
+      <c r="C113" s="119"/>
+      <c r="D113" s="127"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22808,19 +22808,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="134"/>
-      <c r="B131" s="135"/>
-      <c r="C131" s="136"/>
-      <c r="D131" s="137"/>
+      <c r="A131" s="133"/>
+      <c r="B131" s="134"/>
+      <c r="C131" s="135"/>
+      <c r="D131" s="136"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="149" t="s">
+      <c r="A132" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="112"/>
-      <c r="C132" s="112"/>
-      <c r="D132" s="120"/>
+      <c r="B132" s="119"/>
+      <c r="C132" s="119"/>
+      <c r="D132" s="127"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22994,19 +22994,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="134"/>
-      <c r="B143" s="135"/>
-      <c r="C143" s="136"/>
-      <c r="D143" s="137"/>
+      <c r="A143" s="133"/>
+      <c r="B143" s="134"/>
+      <c r="C143" s="135"/>
+      <c r="D143" s="136"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="149" t="s">
+      <c r="A144" s="140" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="112"/>
-      <c r="C144" s="112"/>
-      <c r="D144" s="120"/>
+      <c r="B144" s="119"/>
+      <c r="C144" s="119"/>
+      <c r="D144" s="127"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23639,19 +23639,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="134"/>
-      <c r="B182" s="135"/>
-      <c r="C182" s="136"/>
-      <c r="D182" s="137"/>
+      <c r="A182" s="133"/>
+      <c r="B182" s="134"/>
+      <c r="C182" s="135"/>
+      <c r="D182" s="136"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="133" t="s">
+      <c r="A183" s="139" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="112"/>
-      <c r="C183" s="112"/>
-      <c r="D183" s="112"/>
+      <c r="B183" s="119"/>
+      <c r="C183" s="119"/>
+      <c r="D183" s="119"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24513,19 +24513,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="134"/>
-      <c r="B241" s="135"/>
-      <c r="C241" s="136"/>
-      <c r="D241" s="137"/>
+      <c r="A241" s="133"/>
+      <c r="B241" s="134"/>
+      <c r="C241" s="135"/>
+      <c r="D241" s="136"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="133" t="s">
+      <c r="A242" s="139" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="112"/>
-      <c r="C242" s="112"/>
-      <c r="D242" s="112"/>
+      <c r="B242" s="119"/>
+      <c r="C242" s="119"/>
+      <c r="D242" s="119"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25746,21 +25746,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="134"/>
-      <c r="B324" s="135"/>
-      <c r="C324" s="136"/>
-      <c r="D324" s="137"/>
+      <c r="A324" s="133"/>
+      <c r="B324" s="134"/>
+      <c r="C324" s="135"/>
+      <c r="D324" s="136"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="133" t="s">
+      <c r="A325" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="112"/>
-      <c r="C325" s="112"/>
-      <c r="D325" s="112"/>
+      <c r="B325" s="119"/>
+      <c r="C325" s="119"/>
+      <c r="D325" s="119"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26257,19 +26257,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="134"/>
-      <c r="B355" s="135"/>
-      <c r="C355" s="136"/>
-      <c r="D355" s="137"/>
+      <c r="A355" s="133"/>
+      <c r="B355" s="134"/>
+      <c r="C355" s="135"/>
+      <c r="D355" s="136"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="133" t="s">
+      <c r="A356" s="139" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="112"/>
-      <c r="C356" s="112"/>
-      <c r="D356" s="112"/>
+      <c r="B356" s="119"/>
+      <c r="C356" s="119"/>
+      <c r="D356" s="119"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28024,19 +28024,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="134"/>
-      <c r="B460" s="135"/>
-      <c r="C460" s="136"/>
-      <c r="D460" s="137"/>
+      <c r="A460" s="133"/>
+      <c r="B460" s="134"/>
+      <c r="C460" s="135"/>
+      <c r="D460" s="136"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="133" t="s">
+      <c r="A461" s="139" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="112"/>
-      <c r="C461" s="112"/>
-      <c r="D461" s="112"/>
+      <c r="B461" s="119"/>
+      <c r="C461" s="119"/>
+      <c r="D461" s="119"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28329,19 +28329,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="134"/>
-      <c r="B479" s="135"/>
-      <c r="C479" s="136"/>
-      <c r="D479" s="137"/>
+      <c r="A479" s="133"/>
+      <c r="B479" s="134"/>
+      <c r="C479" s="135"/>
+      <c r="D479" s="136"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="133" t="s">
+      <c r="A480" s="139" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="112"/>
-      <c r="C480" s="112"/>
-      <c r="D480" s="112"/>
+      <c r="B480" s="119"/>
+      <c r="C480" s="119"/>
+      <c r="D480" s="119"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28770,19 +28770,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="134"/>
-      <c r="B506" s="135"/>
-      <c r="C506" s="136"/>
-      <c r="D506" s="137"/>
+      <c r="A506" s="133"/>
+      <c r="B506" s="134"/>
+      <c r="C506" s="135"/>
+      <c r="D506" s="136"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="133" t="s">
+      <c r="A507" s="139" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="112"/>
-      <c r="C507" s="112"/>
-      <c r="D507" s="112"/>
+      <c r="B507" s="119"/>
+      <c r="C507" s="119"/>
+      <c r="D507" s="119"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30297,19 +30297,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="134"/>
-      <c r="B597" s="135"/>
-      <c r="C597" s="136"/>
-      <c r="D597" s="137"/>
+      <c r="A597" s="133"/>
+      <c r="B597" s="134"/>
+      <c r="C597" s="135"/>
+      <c r="D597" s="136"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="133" t="s">
+      <c r="A598" s="139" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="112"/>
-      <c r="C598" s="112"/>
-      <c r="D598" s="112"/>
+      <c r="B598" s="119"/>
+      <c r="C598" s="119"/>
+      <c r="D598" s="119"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30449,20 +30449,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="134"/>
-      <c r="B607" s="135"/>
-      <c r="C607" s="136"/>
-      <c r="D607" s="137"/>
+      <c r="A607" s="133"/>
+      <c r="B607" s="134"/>
+      <c r="C607" s="135"/>
+      <c r="D607" s="136"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="133" t="s">
+      <c r="A608" s="139" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="112"/>
-      <c r="C608" s="112"/>
-      <c r="D608" s="112"/>
+      <c r="B608" s="119"/>
+      <c r="C608" s="119"/>
+      <c r="D608" s="119"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30551,19 +30551,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="134"/>
-      <c r="B614" s="135"/>
-      <c r="C614" s="136"/>
-      <c r="D614" s="137"/>
+      <c r="A614" s="133"/>
+      <c r="B614" s="134"/>
+      <c r="C614" s="135"/>
+      <c r="D614" s="136"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="133" t="s">
+      <c r="A615" s="139" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="112"/>
-      <c r="C615" s="112"/>
-      <c r="D615" s="112"/>
+      <c r="B615" s="119"/>
+      <c r="C615" s="119"/>
+      <c r="D615" s="119"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31928,25 +31928,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31963,6 +31944,25 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E36288-30CA-47D6-85F5-EDA6E990FC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279FE750-8BE3-4D93-8D71-3BCC70793C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="LISTA DE PRODUTOS T" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PRODUTOS B'!$A$1:$E$909</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PRODUTOS B'!$A$1:$E$910</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4027" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4030" uniqueCount="1339">
   <si>
     <t xml:space="preserve">    Tabela de Produtos e Preços</t>
   </si>
@@ -4036,6 +4036,12 @@
   </si>
   <si>
     <t>MARSHMALLOW MIX FOFURAS-81274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOCE DE ABOBORA C/ COCO </t>
+  </si>
+  <si>
+    <t>12X400G</t>
   </si>
 </sst>
 </file>
@@ -5116,6 +5122,51 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5133,12 +5184,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5148,43 +5193,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5199,14 +5208,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5227,10 +5233,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5539,7 +5545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R920"/>
+  <dimension ref="A1:R921"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62.1640625" style="64" bestFit="1" customWidth="1"/>
@@ -5552,83 +5558,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="126"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="111"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="128"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="109"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="111"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="128"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="111"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="128"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="111"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="128"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="108"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="111"/>
+      <c r="A6" s="127"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="128"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="113" t="s">
+      <c r="A7" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="114"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="115"/>
+      <c r="B7" s="131"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="115" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="124"/>
-      <c r="E8" s="125"/>
+      <c r="B8" s="116"/>
+      <c r="C8" s="116"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="117"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="122" t="s">
+      <c r="A9" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="119"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="120"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -7314,20 +7320,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="121"/>
-      <c r="B109" s="109"/>
-      <c r="C109" s="109"/>
-      <c r="D109" s="110"/>
-      <c r="E109" s="117"/>
+      <c r="A109" s="102"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="103"/>
+      <c r="D109" s="104"/>
+      <c r="E109" s="105"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="122" t="s">
+      <c r="A110" s="118" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="119"/>
-      <c r="C110" s="119"/>
-      <c r="D110" s="119"/>
-      <c r="E110" s="120"/>
+      <c r="B110" s="112"/>
+      <c r="C110" s="112"/>
+      <c r="D110" s="112"/>
+      <c r="E110" s="113"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7619,20 +7625,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="121"/>
-      <c r="B128" s="109"/>
-      <c r="C128" s="109"/>
-      <c r="D128" s="110"/>
-      <c r="E128" s="117"/>
+      <c r="A128" s="102"/>
+      <c r="B128" s="103"/>
+      <c r="C128" s="103"/>
+      <c r="D128" s="104"/>
+      <c r="E128" s="105"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="122" t="s">
+      <c r="A129" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="119"/>
-      <c r="C129" s="119"/>
-      <c r="D129" s="119"/>
-      <c r="E129" s="120"/>
+      <c r="B129" s="112"/>
+      <c r="C129" s="112"/>
+      <c r="D129" s="112"/>
+      <c r="E129" s="113"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7699,7 +7705,7 @@
         <v>84</v>
       </c>
       <c r="E133" s="40">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7716,7 +7722,7 @@
         <v>84</v>
       </c>
       <c r="E134" s="40">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7733,7 +7739,7 @@
         <v>84</v>
       </c>
       <c r="E135" s="40">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7750,7 +7756,7 @@
         <v>84</v>
       </c>
       <c r="E136" s="40">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7767,7 +7773,7 @@
         <v>84</v>
       </c>
       <c r="E137" s="44">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -7784,24 +7790,24 @@
         <v>84</v>
       </c>
       <c r="E138" s="42">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="121"/>
-      <c r="B139" s="109"/>
-      <c r="C139" s="109"/>
-      <c r="D139" s="110"/>
-      <c r="E139" s="117"/>
+      <c r="A139" s="102"/>
+      <c r="B139" s="103"/>
+      <c r="C139" s="103"/>
+      <c r="D139" s="104"/>
+      <c r="E139" s="105"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="126" t="s">
+      <c r="A140" s="119" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="119"/>
-      <c r="C140" s="119"/>
-      <c r="D140" s="119"/>
-      <c r="E140" s="127"/>
+      <c r="B140" s="112"/>
+      <c r="C140" s="112"/>
+      <c r="D140" s="112"/>
+      <c r="E140" s="120"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -9045,20 +9051,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="121"/>
-      <c r="B214" s="109"/>
-      <c r="C214" s="109"/>
-      <c r="D214" s="110"/>
-      <c r="E214" s="117"/>
+      <c r="A214" s="102"/>
+      <c r="B214" s="103"/>
+      <c r="C214" s="103"/>
+      <c r="D214" s="104"/>
+      <c r="E214" s="105"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="122" t="s">
+      <c r="A215" s="118" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="119"/>
-      <c r="C215" s="119"/>
-      <c r="D215" s="119"/>
-      <c r="E215" s="120"/>
+      <c r="B215" s="112"/>
+      <c r="C215" s="112"/>
+      <c r="D215" s="112"/>
+      <c r="E215" s="113"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -9769,7 +9775,7 @@
         <v>49</v>
       </c>
       <c r="E257" s="40">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="258" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -9786,7 +9792,7 @@
         <v>49</v>
       </c>
       <c r="E258" s="40">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="259" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -10266,20 +10272,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="116"/>
-      <c r="B287" s="109"/>
-      <c r="C287" s="109"/>
-      <c r="D287" s="110"/>
-      <c r="E287" s="117"/>
+      <c r="A287" s="114"/>
+      <c r="B287" s="103"/>
+      <c r="C287" s="103"/>
+      <c r="D287" s="104"/>
+      <c r="E287" s="105"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="122" t="s">
+      <c r="A288" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="119"/>
-      <c r="C288" s="119"/>
-      <c r="D288" s="119"/>
-      <c r="E288" s="120"/>
+      <c r="B288" s="112"/>
+      <c r="C288" s="112"/>
+      <c r="D288" s="112"/>
+      <c r="E288" s="113"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -11844,20 +11850,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="116"/>
-      <c r="B381" s="109"/>
-      <c r="C381" s="109"/>
-      <c r="D381" s="110"/>
-      <c r="E381" s="117"/>
+      <c r="A381" s="114"/>
+      <c r="B381" s="103"/>
+      <c r="C381" s="103"/>
+      <c r="D381" s="104"/>
+      <c r="E381" s="105"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="118" t="s">
+      <c r="A382" s="111" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="119"/>
-      <c r="C382" s="119"/>
-      <c r="D382" s="119"/>
-      <c r="E382" s="120"/>
+      <c r="B382" s="112"/>
+      <c r="C382" s="112"/>
+      <c r="D382" s="112"/>
+      <c r="E382" s="113"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12511,13 +12517,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="118" t="s">
+      <c r="A422" s="111" t="s">
         <v>1302</v>
       </c>
-      <c r="B422" s="119"/>
-      <c r="C422" s="119"/>
-      <c r="D422" s="119"/>
-      <c r="E422" s="120"/>
+      <c r="B422" s="112"/>
+      <c r="C422" s="112"/>
+      <c r="D422" s="112"/>
+      <c r="E422" s="113"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -14454,20 +14460,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="116"/>
-      <c r="B537" s="109"/>
-      <c r="C537" s="109"/>
-      <c r="D537" s="110"/>
-      <c r="E537" s="117"/>
+      <c r="A537" s="114"/>
+      <c r="B537" s="103"/>
+      <c r="C537" s="103"/>
+      <c r="D537" s="104"/>
+      <c r="E537" s="105"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="118" t="s">
+      <c r="A538" s="111" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="119"/>
-      <c r="C538" s="119"/>
-      <c r="D538" s="119"/>
-      <c r="E538" s="120"/>
+      <c r="B538" s="112"/>
+      <c r="C538" s="112"/>
+      <c r="D538" s="112"/>
+      <c r="E538" s="113"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14498,7 +14504,7 @@
         <v>15</v>
       </c>
       <c r="E540" s="40">
-        <v>290</v>
+        <v>310</v>
       </c>
     </row>
     <row r="541" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -14825,20 +14831,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="116"/>
-      <c r="B560" s="109"/>
-      <c r="C560" s="109"/>
-      <c r="D560" s="110"/>
-      <c r="E560" s="117"/>
+      <c r="A560" s="114"/>
+      <c r="B560" s="103"/>
+      <c r="C560" s="103"/>
+      <c r="D560" s="104"/>
+      <c r="E560" s="105"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="118" t="s">
+      <c r="A561" s="111" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="119"/>
-      <c r="C561" s="119"/>
-      <c r="D561" s="119"/>
-      <c r="E561" s="120"/>
+      <c r="B561" s="112"/>
+      <c r="C561" s="112"/>
+      <c r="D561" s="112"/>
+      <c r="E561" s="113"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15189,10 +15195,10 @@
         <v>653</v>
       </c>
       <c r="D582" s="69" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E582" s="40">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="583" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -15206,10 +15212,10 @@
         <v>2484</v>
       </c>
       <c r="D583" s="69" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="E583" s="40">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="584" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -15451,20 +15457,20 @@
       </c>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="128"/>
-      <c r="B598" s="129"/>
-      <c r="C598" s="129"/>
-      <c r="D598" s="129"/>
-      <c r="E598" s="129"/>
+      <c r="A598" s="106"/>
+      <c r="B598" s="107"/>
+      <c r="C598" s="107"/>
+      <c r="D598" s="107"/>
+      <c r="E598" s="107"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A599" s="118" t="s">
+      <c r="A599" s="111" t="s">
         <v>370</v>
       </c>
-      <c r="B599" s="119"/>
-      <c r="C599" s="119"/>
-      <c r="D599" s="119"/>
-      <c r="E599" s="120"/>
+      <c r="B599" s="112"/>
+      <c r="C599" s="112"/>
+      <c r="D599" s="112"/>
+      <c r="E599" s="113"/>
     </row>
     <row r="600" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="66" t="s">
@@ -17457,20 +17463,20 @@
       </c>
     </row>
     <row r="717" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="116"/>
-      <c r="B717" s="109"/>
-      <c r="C717" s="109"/>
-      <c r="D717" s="110"/>
-      <c r="E717" s="117"/>
+      <c r="A717" s="114"/>
+      <c r="B717" s="103"/>
+      <c r="C717" s="103"/>
+      <c r="D717" s="104"/>
+      <c r="E717" s="105"/>
     </row>
     <row r="718" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A718" s="118" t="s">
+      <c r="A718" s="111" t="s">
         <v>420</v>
       </c>
-      <c r="B718" s="119"/>
-      <c r="C718" s="119"/>
-      <c r="D718" s="119"/>
-      <c r="E718" s="120"/>
+      <c r="B718" s="112"/>
+      <c r="C718" s="112"/>
+      <c r="D718" s="112"/>
+      <c r="E718" s="113"/>
     </row>
     <row r="719" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="66" t="s">
@@ -17648,13 +17654,13 @@
       <c r="E729" s="61"/>
     </row>
     <row r="730" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A730" s="118" t="s">
+      <c r="A730" s="111" t="s">
         <v>1303</v>
       </c>
-      <c r="B730" s="119"/>
-      <c r="C730" s="119"/>
-      <c r="D730" s="119"/>
-      <c r="E730" s="120"/>
+      <c r="B730" s="112"/>
+      <c r="C730" s="112"/>
+      <c r="D730" s="112"/>
+      <c r="E730" s="113"/>
     </row>
     <row r="731" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="72" t="s">
@@ -17776,20 +17782,20 @@
       </c>
     </row>
     <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="121"/>
-      <c r="B738" s="109"/>
-      <c r="C738" s="109"/>
-      <c r="D738" s="110"/>
-      <c r="E738" s="117"/>
+      <c r="A738" s="102"/>
+      <c r="B738" s="103"/>
+      <c r="C738" s="103"/>
+      <c r="D738" s="104"/>
+      <c r="E738" s="105"/>
     </row>
     <row r="739" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A739" s="118" t="s">
+      <c r="A739" s="111" t="s">
         <v>421</v>
       </c>
-      <c r="B739" s="119"/>
-      <c r="C739" s="119"/>
-      <c r="D739" s="119"/>
-      <c r="E739" s="120"/>
+      <c r="B739" s="112"/>
+      <c r="C739" s="112"/>
+      <c r="D739" s="112"/>
+      <c r="E739" s="113"/>
     </row>
     <row r="740" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="66" t="s">
@@ -17943,20 +17949,20 @@
       </c>
     </row>
     <row r="749" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="121"/>
-      <c r="B749" s="109"/>
-      <c r="C749" s="109"/>
-      <c r="D749" s="110"/>
-      <c r="E749" s="117"/>
+      <c r="A749" s="102"/>
+      <c r="B749" s="103"/>
+      <c r="C749" s="103"/>
+      <c r="D749" s="104"/>
+      <c r="E749" s="105"/>
     </row>
     <row r="750" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A750" s="118" t="s">
+      <c r="A750" s="111" t="s">
         <v>1301</v>
       </c>
-      <c r="B750" s="119"/>
-      <c r="C750" s="119"/>
-      <c r="D750" s="119"/>
-      <c r="E750" s="120"/>
+      <c r="B750" s="112"/>
+      <c r="C750" s="112"/>
+      <c r="D750" s="112"/>
+      <c r="E750" s="113"/>
     </row>
     <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="66" t="s">
@@ -18386,13 +18392,13 @@
       <c r="E775" s="98"/>
     </row>
     <row r="776" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A776" s="130" t="s">
+      <c r="A776" s="108" t="s">
         <v>1287</v>
       </c>
-      <c r="B776" s="131"/>
-      <c r="C776" s="131"/>
-      <c r="D776" s="131"/>
-      <c r="E776" s="132"/>
+      <c r="B776" s="109"/>
+      <c r="C776" s="109"/>
+      <c r="D776" s="109"/>
+      <c r="E776" s="110"/>
     </row>
     <row r="777" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="66" t="s">
@@ -19943,33 +19949,33 @@
     </row>
     <row r="868" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="72" t="s">
-        <v>1245</v>
+        <v>1337</v>
       </c>
       <c r="B868" s="72" t="s">
-        <v>1246</v>
+        <v>1338</v>
       </c>
       <c r="C868" s="73">
-        <v>4308</v>
+        <v>4583</v>
       </c>
       <c r="D868" s="74" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E868" s="48">
-        <v>68.5</v>
+        <v>144</v>
       </c>
     </row>
     <row r="869" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="72" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B869" s="72" t="s">
         <v>1246</v>
       </c>
       <c r="C869" s="73">
-        <v>4309</v>
+        <v>4308</v>
       </c>
       <c r="D869" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E869" s="48">
         <v>68.5</v>
@@ -19977,36 +19983,36 @@
     </row>
     <row r="870" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="72" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B870" s="72" t="s">
-        <v>1149</v>
+        <v>1246</v>
       </c>
       <c r="C870" s="73">
-        <v>4412</v>
+        <v>4309</v>
       </c>
       <c r="D870" s="74" t="s">
         <v>453</v>
       </c>
       <c r="E870" s="48">
-        <v>71.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="871" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A871" s="72" t="s">
-        <v>459</v>
+        <v>1248</v>
       </c>
       <c r="B871" s="72" t="s">
-        <v>33</v>
+        <v>1149</v>
       </c>
       <c r="C871" s="73">
-        <v>4413</v>
+        <v>4412</v>
       </c>
       <c r="D871" s="74" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="E871" s="48">
-        <v>496</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="872" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20014,33 +20020,33 @@
         <v>459</v>
       </c>
       <c r="B872" s="72" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C872" s="73">
-        <v>4414</v>
+        <v>4413</v>
       </c>
       <c r="D872" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E872" s="48">
-        <v>101</v>
+        <v>496</v>
       </c>
     </row>
     <row r="873" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A873" s="72" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B873" s="72" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C873" s="73">
-        <v>4415</v>
+        <v>4414</v>
       </c>
       <c r="D873" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E873" s="48">
-        <v>414</v>
+        <v>101</v>
       </c>
     </row>
     <row r="874" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20048,64 +20054,64 @@
         <v>460</v>
       </c>
       <c r="B874" s="72" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C874" s="73">
-        <v>4416</v>
+        <v>4415</v>
       </c>
       <c r="D874" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E874" s="48">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="875" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="875" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="72" t="s">
-        <v>1254</v>
+        <v>460</v>
       </c>
       <c r="B875" s="72" t="s">
-        <v>1255</v>
+        <v>19</v>
       </c>
       <c r="C875" s="73">
-        <v>4475</v>
+        <v>4416</v>
       </c>
       <c r="D875" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E875" s="48">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="876" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A876" s="72" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B876" s="72" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C876" s="73">
+        <v>4475</v>
+      </c>
+      <c r="D876" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E876" s="48">
         <v>8</v>
-      </c>
-    </row>
-    <row r="876" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A876" s="72" t="s">
-        <v>1256</v>
-      </c>
-      <c r="B876" s="72" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C876" s="73">
-        <v>4354</v>
-      </c>
-      <c r="D876" s="74" t="s">
-        <v>412</v>
-      </c>
-      <c r="E876" s="48">
-        <v>74</v>
       </c>
     </row>
     <row r="877" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="72" t="s">
-        <v>1335</v>
+        <v>1256</v>
       </c>
       <c r="B877" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C877" s="73">
-        <v>4445</v>
+        <v>4354</v>
       </c>
       <c r="D877" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E877" s="48">
         <v>74</v>
@@ -20113,16 +20119,16 @@
     </row>
     <row r="878" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="72" t="s">
-        <v>1258</v>
+        <v>1335</v>
       </c>
       <c r="B878" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C878" s="73">
-        <v>4353</v>
+        <v>4445</v>
       </c>
       <c r="D878" s="74" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E878" s="48">
         <v>74</v>
@@ -20130,13 +20136,13 @@
     </row>
     <row r="879" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="72" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B879" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C879" s="73">
-        <v>4350</v>
+        <v>4353</v>
       </c>
       <c r="D879" s="74" t="s">
         <v>50</v>
@@ -20147,13 +20153,13 @@
     </row>
     <row r="880" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="72" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B880" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C880" s="73">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="D880" s="74" t="s">
         <v>50</v>
@@ -20164,13 +20170,13 @@
     </row>
     <row r="881" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="72" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B881" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C881" s="73">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="D881" s="74" t="s">
         <v>50</v>
@@ -20181,13 +20187,13 @@
     </row>
     <row r="882" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A882" s="72" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B882" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C882" s="73">
-        <v>4351</v>
+        <v>4349</v>
       </c>
       <c r="D882" s="74" t="s">
         <v>50</v>
@@ -20197,82 +20203,82 @@
       </c>
     </row>
     <row r="883" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A883" s="96" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B883" s="96" t="s">
+      <c r="A883" s="72" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B883" s="72" t="s">
         <v>1257</v>
       </c>
-      <c r="C883" s="97">
-        <v>4581</v>
-      </c>
-      <c r="D883" s="96" t="s">
-        <v>15</v>
+      <c r="C883" s="73">
+        <v>4351</v>
+      </c>
+      <c r="D883" s="74" t="s">
+        <v>50</v>
       </c>
       <c r="E883" s="48">
         <v>74</v>
       </c>
     </row>
     <row r="884" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A884" s="80" t="s">
+      <c r="A884" s="96" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B884" s="96" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C884" s="97">
+        <v>4581</v>
+      </c>
+      <c r="D884" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="E884" s="48">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="885" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A885" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="B884" s="80" t="s">
+      <c r="B885" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="C884" s="81">
+      <c r="C885" s="81">
         <v>4096</v>
       </c>
-      <c r="D884" s="80" t="s">
-        <v>49</v>
-      </c>
-      <c r="E884" s="42">
+      <c r="D885" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="E885" s="42">
         <v>79</v>
-      </c>
-    </row>
-    <row r="885" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A885" s="72" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B885" s="72" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C885" s="73">
-        <v>4123</v>
-      </c>
-      <c r="D885" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E885" s="48">
-        <v>60</v>
       </c>
     </row>
     <row r="886" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="72" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B886" s="72" t="s">
-        <v>1237</v>
+        <v>1274</v>
       </c>
       <c r="C886" s="73">
-        <v>4306</v>
+        <v>4123</v>
       </c>
       <c r="D886" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E886" s="48">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="887" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A887" s="72" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B887" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C887" s="73">
-        <v>4307</v>
+        <v>4306</v>
       </c>
       <c r="D887" s="74" t="s">
         <v>453</v>
@@ -20283,19 +20289,19 @@
     </row>
     <row r="888" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A888" s="72" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B888" s="72" t="s">
-        <v>1278</v>
+        <v>1237</v>
       </c>
       <c r="C888" s="73">
-        <v>2659</v>
-      </c>
-      <c r="D888" s="72" t="s">
-        <v>160</v>
-      </c>
-      <c r="E888" s="50">
-        <v>27.5</v>
+        <v>4307</v>
+      </c>
+      <c r="D888" s="74" t="s">
+        <v>453</v>
+      </c>
+      <c r="E888" s="48">
+        <v>81</v>
       </c>
     </row>
     <row r="889" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -20303,41 +20309,51 @@
         <v>1277</v>
       </c>
       <c r="B889" s="72" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C889" s="73">
-        <v>2621</v>
+        <v>2659</v>
       </c>
       <c r="D889" s="72" t="s">
         <v>160</v>
       </c>
       <c r="E889" s="50">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="890" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A890" s="72" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="B890" s="72" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C890" s="73">
-        <v>3656</v>
+        <v>2621</v>
       </c>
       <c r="D890" s="72" t="s">
         <v>160</v>
       </c>
       <c r="E890" s="50">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="891" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A891" s="72" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B891" s="72" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C891" s="73">
+        <v>3656</v>
+      </c>
+      <c r="D891" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="E891" s="50">
         <v>27</v>
       </c>
-    </row>
-    <row r="891" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A891" s="99"/>
-      <c r="B891" s="99"/>
-      <c r="C891" s="99"/>
-      <c r="D891" s="99"/>
-      <c r="E891" s="100"/>
     </row>
     <row r="892" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A892" s="99"/>
@@ -20353,271 +20369,277 @@
       <c r="D893" s="99"/>
       <c r="E893" s="100"/>
     </row>
-    <row r="894" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A894" s="102" t="s">
+    <row r="894" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A894" s="99"/>
+      <c r="B894" s="99"/>
+      <c r="C894" s="99"/>
+      <c r="D894" s="99"/>
+      <c r="E894" s="100"/>
+    </row>
+    <row r="895" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A895" s="121" t="s">
         <v>1288</v>
       </c>
-      <c r="B894" s="103"/>
-      <c r="C894" s="103"/>
-      <c r="D894" s="103"/>
-      <c r="E894" s="104"/>
-    </row>
-    <row r="895" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A895" s="87" t="s">
+      <c r="B895" s="122"/>
+      <c r="C895" s="122"/>
+      <c r="D895" s="122"/>
+      <c r="E895" s="123"/>
+    </row>
+    <row r="896" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A896" s="87" t="s">
         <v>1291</v>
       </c>
-      <c r="B895" s="87" t="s">
+      <c r="B896" s="87" t="s">
         <v>1289</v>
       </c>
-      <c r="C895" s="88">
+      <c r="C896" s="88">
         <v>3460</v>
       </c>
-      <c r="D895" s="89" t="s">
+      <c r="D896" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E895" s="63">
+      <c r="E896" s="63">
         <v>90</v>
-      </c>
-    </row>
-    <row r="896" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A896" s="72" t="s">
-        <v>1290</v>
-      </c>
-      <c r="B896" s="72" t="s">
-        <v>1289</v>
-      </c>
-      <c r="C896" s="73">
-        <v>3459</v>
-      </c>
-      <c r="D896" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E896" s="48">
-        <v>45</v>
       </c>
     </row>
     <row r="897" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="72" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B897" s="72" t="s">
         <v>1289</v>
       </c>
       <c r="C897" s="73">
-        <v>3803</v>
+        <v>3459</v>
       </c>
       <c r="D897" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E897" s="48">
-        <v>23</v>
+        <v>45</v>
       </c>
     </row>
     <row r="898" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="72" t="s">
-        <v>478</v>
+        <v>1292</v>
       </c>
       <c r="B898" s="72" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="C898" s="73">
-        <v>3425</v>
+        <v>3803</v>
       </c>
       <c r="D898" s="74" t="s">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="E898" s="48">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="899" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="72" t="s">
-        <v>1295</v>
+        <v>478</v>
       </c>
       <c r="B899" s="72" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C899" s="73">
-        <v>3426</v>
+        <v>3425</v>
       </c>
       <c r="D899" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E899" s="48">
-        <v>276</v>
+        <v>29</v>
       </c>
     </row>
     <row r="900" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="72" t="s">
-        <v>479</v>
+        <v>1295</v>
       </c>
       <c r="B900" s="72" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C900" s="73">
-        <v>3427</v>
+        <v>3426</v>
       </c>
       <c r="D900" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E900" s="48">
-        <v>62.5</v>
+        <v>276</v>
       </c>
     </row>
     <row r="901" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="72" t="s">
-        <v>1296</v>
+        <v>479</v>
       </c>
       <c r="B901" s="72" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C901" s="73">
-        <v>3428</v>
+        <v>3427</v>
       </c>
       <c r="D901" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E901" s="48">
-        <v>582</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="902" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="72" t="s">
-        <v>480</v>
+        <v>1296</v>
       </c>
       <c r="B902" s="72" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C902" s="73">
-        <v>3429</v>
+        <v>3428</v>
       </c>
       <c r="D902" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E902" s="48">
-        <v>76.5</v>
+        <v>582</v>
       </c>
     </row>
     <row r="903" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="72" t="s">
-        <v>1297</v>
+        <v>480</v>
       </c>
       <c r="B903" s="72" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C903" s="73">
-        <v>3430</v>
+        <v>3429</v>
       </c>
       <c r="D903" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E903" s="48">
-        <v>714.5</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="904" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="72" t="s">
-        <v>481</v>
+        <v>1297</v>
       </c>
       <c r="B904" s="72" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C904" s="73">
-        <v>3913</v>
+        <v>3430</v>
       </c>
       <c r="D904" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E904" s="48">
-        <v>68</v>
+        <v>714.5</v>
       </c>
     </row>
     <row r="905" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="72" t="s">
-        <v>1298</v>
+        <v>481</v>
       </c>
       <c r="B905" s="72" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C905" s="73">
-        <v>3872</v>
+        <v>3913</v>
       </c>
       <c r="D905" s="74" t="s">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="E905" s="48">
-        <v>636</v>
+        <v>68</v>
       </c>
     </row>
     <row r="906" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="72" t="s">
-        <v>482</v>
+        <v>1298</v>
       </c>
       <c r="B906" s="72" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C906" s="73">
-        <v>3422</v>
+        <v>3872</v>
       </c>
       <c r="D906" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E906" s="48">
-        <v>20</v>
+        <v>636</v>
       </c>
     </row>
     <row r="907" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="72" t="s">
+        <v>482</v>
+      </c>
+      <c r="B907" s="72" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C907" s="73">
+        <v>3422</v>
+      </c>
+      <c r="D907" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="E907" s="48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="908" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A908" s="72" t="s">
         <v>1299</v>
       </c>
-      <c r="B907" s="72" t="s">
+      <c r="B908" s="72" t="s">
         <v>1293</v>
       </c>
-      <c r="C907" s="73">
+      <c r="C908" s="73">
         <v>3423</v>
       </c>
-      <c r="D907" s="74" t="s">
+      <c r="D908" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="E907" s="48">
+      <c r="E908" s="48">
         <v>186</v>
       </c>
     </row>
-    <row r="908" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A908" s="83" t="s">
+    <row r="909" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A909" s="83" t="s">
         <v>483</v>
       </c>
-      <c r="B908" s="83" t="s">
+      <c r="B909" s="83" t="s">
         <v>1300</v>
       </c>
-      <c r="C908" s="84">
+      <c r="C909" s="84">
         <v>3431</v>
       </c>
-      <c r="D908" s="74" t="s">
+      <c r="D909" s="74" t="s">
         <v>412</v>
       </c>
-      <c r="E908" s="48">
+      <c r="E909" s="48">
         <v>115</v>
       </c>
     </row>
-    <row r="909" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A909" s="90" t="s">
+    <row r="910" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A910" s="90" t="s">
         <v>483</v>
       </c>
-      <c r="B909" s="90" t="s">
+      <c r="B910" s="90" t="s">
         <v>1293</v>
       </c>
-      <c r="C909" s="91">
+      <c r="C910" s="91">
         <v>3432</v>
       </c>
-      <c r="D909" s="92" t="s">
+      <c r="D910" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="E909" s="48">
+      <c r="E910" s="48">
         <v>1068</v>
       </c>
     </row>
-    <row r="910" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="911" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="912" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="913" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
@@ -20626,35 +20648,15 @@
     <row r="916" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="917" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="918" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
-    <row r="920" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A920" s="64" t="s">
+    <row r="919" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
+    <row r="921" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A921" s="64" t="s">
         <v>386</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A738:E738"/>
-    <mergeCell ref="A598:E598"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A776:E776"/>
-    <mergeCell ref="A730:E730"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A750:E750"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A538:E538"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A422:E422"/>
-    <mergeCell ref="A382:E382"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A381:E381"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A215:E215"/>
-    <mergeCell ref="A894:E894"/>
+    <mergeCell ref="A895:E895"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A3:E3"/>
@@ -20670,6 +20672,27 @@
     <mergeCell ref="A560:E560"/>
     <mergeCell ref="A717:E717"/>
     <mergeCell ref="A288:E288"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A538:E538"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A422:E422"/>
+    <mergeCell ref="A382:E382"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A215:E215"/>
+    <mergeCell ref="A738:E738"/>
+    <mergeCell ref="A598:E598"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A776:E776"/>
+    <mergeCell ref="A730:E730"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A750:E750"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20709,78 +20732,78 @@
       <c r="A2" s="148" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="138"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="139"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="150" t="s">
         <v>485</v>
       </c>
-      <c r="B3" s="134"/>
-      <c r="C3" s="135"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="138"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="139"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="149" t="s">
+      <c r="A4" s="138" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="134"/>
-      <c r="C4" s="135"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="138"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="136"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="139"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="150" t="s">
         <v>487</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="138"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="139"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="134"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="138"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="139"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="134"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="138"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="139"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="138"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="139"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="134"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="138"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="136"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="139"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="150" t="s">
+      <c r="A10" s="140" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22503,19 +22526,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="133"/>
-      <c r="B112" s="134"/>
-      <c r="C112" s="135"/>
-      <c r="D112" s="136"/>
+      <c r="A112" s="134"/>
+      <c r="B112" s="135"/>
+      <c r="C112" s="136"/>
+      <c r="D112" s="137"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="140" t="s">
+      <c r="A113" s="149" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="119"/>
-      <c r="C113" s="119"/>
-      <c r="D113" s="127"/>
+      <c r="B113" s="112"/>
+      <c r="C113" s="112"/>
+      <c r="D113" s="120"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22808,19 +22831,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="133"/>
-      <c r="B131" s="134"/>
-      <c r="C131" s="135"/>
-      <c r="D131" s="136"/>
+      <c r="A131" s="134"/>
+      <c r="B131" s="135"/>
+      <c r="C131" s="136"/>
+      <c r="D131" s="137"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="140" t="s">
+      <c r="A132" s="149" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="119"/>
-      <c r="C132" s="119"/>
-      <c r="D132" s="127"/>
+      <c r="B132" s="112"/>
+      <c r="C132" s="112"/>
+      <c r="D132" s="120"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22994,19 +23017,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="133"/>
-      <c r="B143" s="134"/>
-      <c r="C143" s="135"/>
-      <c r="D143" s="136"/>
+      <c r="A143" s="134"/>
+      <c r="B143" s="135"/>
+      <c r="C143" s="136"/>
+      <c r="D143" s="137"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="140" t="s">
+      <c r="A144" s="149" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="119"/>
-      <c r="C144" s="119"/>
-      <c r="D144" s="127"/>
+      <c r="B144" s="112"/>
+      <c r="C144" s="112"/>
+      <c r="D144" s="120"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23639,19 +23662,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="133"/>
-      <c r="B182" s="134"/>
-      <c r="C182" s="135"/>
-      <c r="D182" s="136"/>
+      <c r="A182" s="134"/>
+      <c r="B182" s="135"/>
+      <c r="C182" s="136"/>
+      <c r="D182" s="137"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="139" t="s">
+      <c r="A183" s="133" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="119"/>
-      <c r="C183" s="119"/>
-      <c r="D183" s="119"/>
+      <c r="B183" s="112"/>
+      <c r="C183" s="112"/>
+      <c r="D183" s="112"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24513,19 +24536,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="133"/>
-      <c r="B241" s="134"/>
-      <c r="C241" s="135"/>
-      <c r="D241" s="136"/>
+      <c r="A241" s="134"/>
+      <c r="B241" s="135"/>
+      <c r="C241" s="136"/>
+      <c r="D241" s="137"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="139" t="s">
+      <c r="A242" s="133" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="119"/>
-      <c r="C242" s="119"/>
-      <c r="D242" s="119"/>
+      <c r="B242" s="112"/>
+      <c r="C242" s="112"/>
+      <c r="D242" s="112"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25746,21 +25769,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="133"/>
-      <c r="B324" s="134"/>
-      <c r="C324" s="135"/>
-      <c r="D324" s="136"/>
+      <c r="A324" s="134"/>
+      <c r="B324" s="135"/>
+      <c r="C324" s="136"/>
+      <c r="D324" s="137"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="139" t="s">
+      <c r="A325" s="133" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="119"/>
-      <c r="C325" s="119"/>
-      <c r="D325" s="119"/>
+      <c r="B325" s="112"/>
+      <c r="C325" s="112"/>
+      <c r="D325" s="112"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26257,19 +26280,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="133"/>
-      <c r="B355" s="134"/>
-      <c r="C355" s="135"/>
-      <c r="D355" s="136"/>
+      <c r="A355" s="134"/>
+      <c r="B355" s="135"/>
+      <c r="C355" s="136"/>
+      <c r="D355" s="137"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="139" t="s">
+      <c r="A356" s="133" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="119"/>
-      <c r="C356" s="119"/>
-      <c r="D356" s="119"/>
+      <c r="B356" s="112"/>
+      <c r="C356" s="112"/>
+      <c r="D356" s="112"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28024,19 +28047,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="133"/>
-      <c r="B460" s="134"/>
-      <c r="C460" s="135"/>
-      <c r="D460" s="136"/>
+      <c r="A460" s="134"/>
+      <c r="B460" s="135"/>
+      <c r="C460" s="136"/>
+      <c r="D460" s="137"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="139" t="s">
+      <c r="A461" s="133" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="119"/>
-      <c r="C461" s="119"/>
-      <c r="D461" s="119"/>
+      <c r="B461" s="112"/>
+      <c r="C461" s="112"/>
+      <c r="D461" s="112"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28329,19 +28352,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="133"/>
-      <c r="B479" s="134"/>
-      <c r="C479" s="135"/>
-      <c r="D479" s="136"/>
+      <c r="A479" s="134"/>
+      <c r="B479" s="135"/>
+      <c r="C479" s="136"/>
+      <c r="D479" s="137"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="139" t="s">
+      <c r="A480" s="133" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="119"/>
-      <c r="C480" s="119"/>
-      <c r="D480" s="119"/>
+      <c r="B480" s="112"/>
+      <c r="C480" s="112"/>
+      <c r="D480" s="112"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28770,19 +28793,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="133"/>
-      <c r="B506" s="134"/>
-      <c r="C506" s="135"/>
-      <c r="D506" s="136"/>
+      <c r="A506" s="134"/>
+      <c r="B506" s="135"/>
+      <c r="C506" s="136"/>
+      <c r="D506" s="137"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="139" t="s">
+      <c r="A507" s="133" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="119"/>
-      <c r="C507" s="119"/>
-      <c r="D507" s="119"/>
+      <c r="B507" s="112"/>
+      <c r="C507" s="112"/>
+      <c r="D507" s="112"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30297,19 +30320,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="133"/>
-      <c r="B597" s="134"/>
-      <c r="C597" s="135"/>
-      <c r="D597" s="136"/>
+      <c r="A597" s="134"/>
+      <c r="B597" s="135"/>
+      <c r="C597" s="136"/>
+      <c r="D597" s="137"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="139" t="s">
+      <c r="A598" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="119"/>
-      <c r="C598" s="119"/>
-      <c r="D598" s="119"/>
+      <c r="B598" s="112"/>
+      <c r="C598" s="112"/>
+      <c r="D598" s="112"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30449,20 +30472,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="133"/>
-      <c r="B607" s="134"/>
-      <c r="C607" s="135"/>
-      <c r="D607" s="136"/>
+      <c r="A607" s="134"/>
+      <c r="B607" s="135"/>
+      <c r="C607" s="136"/>
+      <c r="D607" s="137"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="139" t="s">
+      <c r="A608" s="133" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="119"/>
-      <c r="C608" s="119"/>
-      <c r="D608" s="119"/>
+      <c r="B608" s="112"/>
+      <c r="C608" s="112"/>
+      <c r="D608" s="112"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30551,19 +30574,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="133"/>
-      <c r="B614" s="134"/>
-      <c r="C614" s="135"/>
-      <c r="D614" s="136"/>
+      <c r="A614" s="134"/>
+      <c r="B614" s="135"/>
+      <c r="C614" s="136"/>
+      <c r="D614" s="137"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="139" t="s">
+      <c r="A615" s="133" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="119"/>
-      <c r="C615" s="119"/>
-      <c r="D615" s="119"/>
+      <c r="B615" s="112"/>
+      <c r="C615" s="112"/>
+      <c r="D615" s="112"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31928,6 +31951,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31944,25 +31986,6 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279FE750-8BE3-4D93-8D71-3BCC70793C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743A6F0F-78AD-43FE-8947-EEA0971B21F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5122,51 +5122,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5184,6 +5139,12 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5193,7 +5154,43 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5208,11 +5205,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5233,10 +5233,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5558,83 +5558,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="126"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="107"/>
     </row>
     <row r="2" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="128"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="127" t="s">
+      <c r="A3" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="103"/>
-      <c r="C3" s="103"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="128"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="127" t="s">
+      <c r="A4" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="103"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="128"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="111"/>
     </row>
     <row r="5" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="127" t="s">
+      <c r="A5" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="128"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="111"/>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="127"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="128"/>
+      <c r="A6" s="108"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111"/>
     </row>
     <row r="7" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="131"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="132"/>
+      <c r="B7" s="114"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115"/>
     </row>
     <row r="8" spans="1:5" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="117"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="125"/>
     </row>
     <row r="9" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="122" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="120"/>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66" t="s">
@@ -7320,20 +7320,20 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="102"/>
-      <c r="B109" s="103"/>
-      <c r="C109" s="103"/>
-      <c r="D109" s="104"/>
-      <c r="E109" s="105"/>
+      <c r="A109" s="121"/>
+      <c r="B109" s="109"/>
+      <c r="C109" s="109"/>
+      <c r="D109" s="110"/>
+      <c r="E109" s="117"/>
     </row>
     <row r="110" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="118" t="s">
+      <c r="A110" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="B110" s="112"/>
-      <c r="C110" s="112"/>
-      <c r="D110" s="112"/>
-      <c r="E110" s="113"/>
+      <c r="B110" s="119"/>
+      <c r="C110" s="119"/>
+      <c r="D110" s="119"/>
+      <c r="E110" s="120"/>
     </row>
     <row r="111" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="66" t="s">
@@ -7625,20 +7625,20 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="102"/>
-      <c r="B128" s="103"/>
-      <c r="C128" s="103"/>
-      <c r="D128" s="104"/>
-      <c r="E128" s="105"/>
+      <c r="A128" s="121"/>
+      <c r="B128" s="109"/>
+      <c r="C128" s="109"/>
+      <c r="D128" s="110"/>
+      <c r="E128" s="117"/>
     </row>
     <row r="129" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="118" t="s">
+      <c r="A129" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="B129" s="112"/>
-      <c r="C129" s="112"/>
-      <c r="D129" s="112"/>
-      <c r="E129" s="113"/>
+      <c r="B129" s="119"/>
+      <c r="C129" s="119"/>
+      <c r="D129" s="119"/>
+      <c r="E129" s="120"/>
     </row>
     <row r="130" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="66" t="s">
@@ -7794,20 +7794,20 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="102"/>
-      <c r="B139" s="103"/>
-      <c r="C139" s="103"/>
-      <c r="D139" s="104"/>
-      <c r="E139" s="105"/>
+      <c r="A139" s="121"/>
+      <c r="B139" s="109"/>
+      <c r="C139" s="109"/>
+      <c r="D139" s="110"/>
+      <c r="E139" s="117"/>
     </row>
     <row r="140" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="119" t="s">
+      <c r="A140" s="126" t="s">
         <v>106</v>
       </c>
-      <c r="B140" s="112"/>
-      <c r="C140" s="112"/>
-      <c r="D140" s="112"/>
-      <c r="E140" s="120"/>
+      <c r="B140" s="119"/>
+      <c r="C140" s="119"/>
+      <c r="D140" s="119"/>
+      <c r="E140" s="127"/>
     </row>
     <row r="141" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="66" t="s">
@@ -9051,20 +9051,20 @@
       </c>
     </row>
     <row r="214" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="102"/>
-      <c r="B214" s="103"/>
-      <c r="C214" s="103"/>
-      <c r="D214" s="104"/>
-      <c r="E214" s="105"/>
+      <c r="A214" s="121"/>
+      <c r="B214" s="109"/>
+      <c r="C214" s="109"/>
+      <c r="D214" s="110"/>
+      <c r="E214" s="117"/>
     </row>
     <row r="215" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="118" t="s">
+      <c r="A215" s="122" t="s">
         <v>148</v>
       </c>
-      <c r="B215" s="112"/>
-      <c r="C215" s="112"/>
-      <c r="D215" s="112"/>
-      <c r="E215" s="113"/>
+      <c r="B215" s="119"/>
+      <c r="C215" s="119"/>
+      <c r="D215" s="119"/>
+      <c r="E215" s="120"/>
     </row>
     <row r="216" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="66" t="s">
@@ -10272,20 +10272,20 @@
       </c>
     </row>
     <row r="287" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="114"/>
-      <c r="B287" s="103"/>
-      <c r="C287" s="103"/>
-      <c r="D287" s="104"/>
-      <c r="E287" s="105"/>
+      <c r="A287" s="116"/>
+      <c r="B287" s="109"/>
+      <c r="C287" s="109"/>
+      <c r="D287" s="110"/>
+      <c r="E287" s="117"/>
     </row>
     <row r="288" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="118" t="s">
+      <c r="A288" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="B288" s="112"/>
-      <c r="C288" s="112"/>
-      <c r="D288" s="112"/>
-      <c r="E288" s="113"/>
+      <c r="B288" s="119"/>
+      <c r="C288" s="119"/>
+      <c r="D288" s="119"/>
+      <c r="E288" s="120"/>
     </row>
     <row r="289" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="66" t="s">
@@ -11850,20 +11850,20 @@
       </c>
     </row>
     <row r="381" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="114"/>
-      <c r="B381" s="103"/>
-      <c r="C381" s="103"/>
-      <c r="D381" s="104"/>
-      <c r="E381" s="105"/>
+      <c r="A381" s="116"/>
+      <c r="B381" s="109"/>
+      <c r="C381" s="109"/>
+      <c r="D381" s="110"/>
+      <c r="E381" s="117"/>
     </row>
     <row r="382" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="111" t="s">
+      <c r="A382" s="118" t="s">
         <v>235</v>
       </c>
-      <c r="B382" s="112"/>
-      <c r="C382" s="112"/>
-      <c r="D382" s="112"/>
-      <c r="E382" s="113"/>
+      <c r="B382" s="119"/>
+      <c r="C382" s="119"/>
+      <c r="D382" s="119"/>
+      <c r="E382" s="120"/>
     </row>
     <row r="383" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="66" t="s">
@@ -12517,13 +12517,13 @@
       <c r="E421" s="61"/>
     </row>
     <row r="422" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A422" s="111" t="s">
+      <c r="A422" s="118" t="s">
         <v>1302</v>
       </c>
-      <c r="B422" s="112"/>
-      <c r="C422" s="112"/>
-      <c r="D422" s="112"/>
-      <c r="E422" s="113"/>
+      <c r="B422" s="119"/>
+      <c r="C422" s="119"/>
+      <c r="D422" s="119"/>
+      <c r="E422" s="120"/>
     </row>
     <row r="423" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="66" t="s">
@@ -14460,20 +14460,20 @@
       </c>
     </row>
     <row r="537" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A537" s="114"/>
-      <c r="B537" s="103"/>
-      <c r="C537" s="103"/>
-      <c r="D537" s="104"/>
-      <c r="E537" s="105"/>
+      <c r="A537" s="116"/>
+      <c r="B537" s="109"/>
+      <c r="C537" s="109"/>
+      <c r="D537" s="110"/>
+      <c r="E537" s="117"/>
     </row>
     <row r="538" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A538" s="111" t="s">
+      <c r="A538" s="118" t="s">
         <v>338</v>
       </c>
-      <c r="B538" s="112"/>
-      <c r="C538" s="112"/>
-      <c r="D538" s="112"/>
-      <c r="E538" s="113"/>
+      <c r="B538" s="119"/>
+      <c r="C538" s="119"/>
+      <c r="D538" s="119"/>
+      <c r="E538" s="120"/>
     </row>
     <row r="539" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="66" t="s">
@@ -14810,7 +14810,7 @@
         <v>50</v>
       </c>
       <c r="E558" s="44">
-        <v>240</v>
+        <v>420</v>
       </c>
     </row>
     <row r="559" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -14831,20 +14831,20 @@
       </c>
     </row>
     <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="114"/>
-      <c r="B560" s="103"/>
-      <c r="C560" s="103"/>
-      <c r="D560" s="104"/>
-      <c r="E560" s="105"/>
+      <c r="A560" s="116"/>
+      <c r="B560" s="109"/>
+      <c r="C560" s="109"/>
+      <c r="D560" s="110"/>
+      <c r="E560" s="117"/>
     </row>
     <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="111" t="s">
+      <c r="A561" s="118" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="112"/>
-      <c r="C561" s="112"/>
-      <c r="D561" s="112"/>
-      <c r="E561" s="113"/>
+      <c r="B561" s="119"/>
+      <c r="C561" s="119"/>
+      <c r="D561" s="119"/>
+      <c r="E561" s="120"/>
     </row>
     <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="66" t="s">
@@ -15457,20 +15457,20 @@
       </c>
     </row>
     <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="106"/>
-      <c r="B598" s="107"/>
-      <c r="C598" s="107"/>
-      <c r="D598" s="107"/>
-      <c r="E598" s="107"/>
+      <c r="A598" s="128"/>
+      <c r="B598" s="129"/>
+      <c r="C598" s="129"/>
+      <c r="D598" s="129"/>
+      <c r="E598" s="129"/>
     </row>
     <row r="599" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A599" s="111" t="s">
+      <c r="A599" s="118" t="s">
         <v>370</v>
       </c>
-      <c r="B599" s="112"/>
-      <c r="C599" s="112"/>
-      <c r="D599" s="112"/>
-      <c r="E599" s="113"/>
+      <c r="B599" s="119"/>
+      <c r="C599" s="119"/>
+      <c r="D599" s="119"/>
+      <c r="E599" s="120"/>
     </row>
     <row r="600" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="66" t="s">
@@ -17463,20 +17463,20 @@
       </c>
     </row>
     <row r="717" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="114"/>
-      <c r="B717" s="103"/>
-      <c r="C717" s="103"/>
-      <c r="D717" s="104"/>
-      <c r="E717" s="105"/>
+      <c r="A717" s="116"/>
+      <c r="B717" s="109"/>
+      <c r="C717" s="109"/>
+      <c r="D717" s="110"/>
+      <c r="E717" s="117"/>
     </row>
     <row r="718" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A718" s="111" t="s">
+      <c r="A718" s="118" t="s">
         <v>420</v>
       </c>
-      <c r="B718" s="112"/>
-      <c r="C718" s="112"/>
-      <c r="D718" s="112"/>
-      <c r="E718" s="113"/>
+      <c r="B718" s="119"/>
+      <c r="C718" s="119"/>
+      <c r="D718" s="119"/>
+      <c r="E718" s="120"/>
     </row>
     <row r="719" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="66" t="s">
@@ -17654,13 +17654,13 @@
       <c r="E729" s="61"/>
     </row>
     <row r="730" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A730" s="111" t="s">
+      <c r="A730" s="118" t="s">
         <v>1303</v>
       </c>
-      <c r="B730" s="112"/>
-      <c r="C730" s="112"/>
-      <c r="D730" s="112"/>
-      <c r="E730" s="113"/>
+      <c r="B730" s="119"/>
+      <c r="C730" s="119"/>
+      <c r="D730" s="119"/>
+      <c r="E730" s="120"/>
     </row>
     <row r="731" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="72" t="s">
@@ -17782,20 +17782,20 @@
       </c>
     </row>
     <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="102"/>
-      <c r="B738" s="103"/>
-      <c r="C738" s="103"/>
-      <c r="D738" s="104"/>
-      <c r="E738" s="105"/>
+      <c r="A738" s="121"/>
+      <c r="B738" s="109"/>
+      <c r="C738" s="109"/>
+      <c r="D738" s="110"/>
+      <c r="E738" s="117"/>
     </row>
     <row r="739" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A739" s="111" t="s">
+      <c r="A739" s="118" t="s">
         <v>421</v>
       </c>
-      <c r="B739" s="112"/>
-      <c r="C739" s="112"/>
-      <c r="D739" s="112"/>
-      <c r="E739" s="113"/>
+      <c r="B739" s="119"/>
+      <c r="C739" s="119"/>
+      <c r="D739" s="119"/>
+      <c r="E739" s="120"/>
     </row>
     <row r="740" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="66" t="s">
@@ -17949,20 +17949,20 @@
       </c>
     </row>
     <row r="749" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="102"/>
-      <c r="B749" s="103"/>
-      <c r="C749" s="103"/>
-      <c r="D749" s="104"/>
-      <c r="E749" s="105"/>
+      <c r="A749" s="121"/>
+      <c r="B749" s="109"/>
+      <c r="C749" s="109"/>
+      <c r="D749" s="110"/>
+      <c r="E749" s="117"/>
     </row>
     <row r="750" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A750" s="111" t="s">
+      <c r="A750" s="118" t="s">
         <v>1301</v>
       </c>
-      <c r="B750" s="112"/>
-      <c r="C750" s="112"/>
-      <c r="D750" s="112"/>
-      <c r="E750" s="113"/>
+      <c r="B750" s="119"/>
+      <c r="C750" s="119"/>
+      <c r="D750" s="119"/>
+      <c r="E750" s="120"/>
     </row>
     <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="66" t="s">
@@ -18392,13 +18392,13 @@
       <c r="E775" s="98"/>
     </row>
     <row r="776" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A776" s="108" t="s">
+      <c r="A776" s="130" t="s">
         <v>1287</v>
       </c>
-      <c r="B776" s="109"/>
-      <c r="C776" s="109"/>
-      <c r="D776" s="109"/>
-      <c r="E776" s="110"/>
+      <c r="B776" s="131"/>
+      <c r="C776" s="131"/>
+      <c r="D776" s="131"/>
+      <c r="E776" s="132"/>
     </row>
     <row r="777" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="66" t="s">
@@ -20377,13 +20377,13 @@
       <c r="E894" s="100"/>
     </row>
     <row r="895" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A895" s="121" t="s">
+      <c r="A895" s="102" t="s">
         <v>1288</v>
       </c>
-      <c r="B895" s="122"/>
-      <c r="C895" s="122"/>
-      <c r="D895" s="122"/>
-      <c r="E895" s="123"/>
+      <c r="B895" s="103"/>
+      <c r="C895" s="103"/>
+      <c r="D895" s="103"/>
+      <c r="E895" s="104"/>
     </row>
     <row r="896" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="87" t="s">
@@ -20656,6 +20656,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A738:E738"/>
+    <mergeCell ref="A598:E598"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A776:E776"/>
+    <mergeCell ref="A730:E730"/>
+    <mergeCell ref="A749:E749"/>
+    <mergeCell ref="A750:E750"/>
+    <mergeCell ref="A537:E537"/>
+    <mergeCell ref="A561:E561"/>
+    <mergeCell ref="A109:E109"/>
+    <mergeCell ref="A538:E538"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A129:E129"/>
+    <mergeCell ref="A422:E422"/>
+    <mergeCell ref="A382:E382"/>
+    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A381:E381"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A215:E215"/>
     <mergeCell ref="A895:E895"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
@@ -20672,27 +20693,6 @@
     <mergeCell ref="A560:E560"/>
     <mergeCell ref="A717:E717"/>
     <mergeCell ref="A288:E288"/>
-    <mergeCell ref="A109:E109"/>
-    <mergeCell ref="A538:E538"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A422:E422"/>
-    <mergeCell ref="A382:E382"/>
-    <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A381:E381"/>
-    <mergeCell ref="A140:E140"/>
-    <mergeCell ref="A215:E215"/>
-    <mergeCell ref="A738:E738"/>
-    <mergeCell ref="A598:E598"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A776:E776"/>
-    <mergeCell ref="A730:E730"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A750:E750"/>
-    <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20732,78 +20732,78 @@
       <c r="A2" s="148" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="139"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="138"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="150" t="s">
+      <c r="A3" s="137" t="s">
         <v>485</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="139"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="138"/>
     </row>
     <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="149" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="139"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="138"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="137" t="s">
         <v>487</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="139"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="138"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="144"/>
-      <c r="B6" s="135"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="139"/>
+      <c r="B6" s="134"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="138"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="147" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="135"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="139"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="138"/>
     </row>
     <row r="8" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="145" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="137"/>
-      <c r="E8" s="139"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="138"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="146"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="139"/>
+      <c r="B9" s="134"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="138"/>
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="140" t="s">
+      <c r="A10" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="120"/>
     </row>
     <row r="11" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
@@ -22526,19 +22526,19 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="134"/>
-      <c r="B112" s="135"/>
-      <c r="C112" s="136"/>
-      <c r="D112" s="137"/>
+      <c r="A112" s="133"/>
+      <c r="B112" s="134"/>
+      <c r="C112" s="135"/>
+      <c r="D112" s="136"/>
       <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="149" t="s">
+      <c r="A113" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="B113" s="112"/>
-      <c r="C113" s="112"/>
-      <c r="D113" s="120"/>
+      <c r="B113" s="119"/>
+      <c r="C113" s="119"/>
+      <c r="D113" s="127"/>
       <c r="E113" s="28"/>
     </row>
     <row r="114" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -22831,19 +22831,19 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="134"/>
-      <c r="B131" s="135"/>
-      <c r="C131" s="136"/>
-      <c r="D131" s="137"/>
+      <c r="A131" s="133"/>
+      <c r="B131" s="134"/>
+      <c r="C131" s="135"/>
+      <c r="D131" s="136"/>
       <c r="E131" s="25"/>
     </row>
     <row r="132" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="149" t="s">
+      <c r="A132" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="B132" s="112"/>
-      <c r="C132" s="112"/>
-      <c r="D132" s="120"/>
+      <c r="B132" s="119"/>
+      <c r="C132" s="119"/>
+      <c r="D132" s="127"/>
       <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23017,19 +23017,19 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="134"/>
-      <c r="B143" s="135"/>
-      <c r="C143" s="136"/>
-      <c r="D143" s="137"/>
+      <c r="A143" s="133"/>
+      <c r="B143" s="134"/>
+      <c r="C143" s="135"/>
+      <c r="D143" s="136"/>
       <c r="E143" s="25"/>
     </row>
     <row r="144" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="149" t="s">
+      <c r="A144" s="140" t="s">
         <v>106</v>
       </c>
-      <c r="B144" s="112"/>
-      <c r="C144" s="112"/>
-      <c r="D144" s="120"/>
+      <c r="B144" s="119"/>
+      <c r="C144" s="119"/>
+      <c r="D144" s="127"/>
       <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -23662,19 +23662,19 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="134"/>
-      <c r="B182" s="135"/>
-      <c r="C182" s="136"/>
-      <c r="D182" s="137"/>
+      <c r="A182" s="133"/>
+      <c r="B182" s="134"/>
+      <c r="C182" s="135"/>
+      <c r="D182" s="136"/>
       <c r="E182" s="25"/>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="133" t="s">
+      <c r="A183" s="139" t="s">
         <v>148</v>
       </c>
-      <c r="B183" s="112"/>
-      <c r="C183" s="112"/>
-      <c r="D183" s="112"/>
+      <c r="B183" s="119"/>
+      <c r="C183" s="119"/>
+      <c r="D183" s="119"/>
       <c r="E183" s="26"/>
     </row>
     <row r="184" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -24536,19 +24536,19 @@
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="134"/>
-      <c r="B241" s="135"/>
-      <c r="C241" s="136"/>
-      <c r="D241" s="137"/>
+      <c r="A241" s="133"/>
+      <c r="B241" s="134"/>
+      <c r="C241" s="135"/>
+      <c r="D241" s="136"/>
       <c r="E241" s="25"/>
     </row>
     <row r="242" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="133" t="s">
+      <c r="A242" s="139" t="s">
         <v>186</v>
       </c>
-      <c r="B242" s="112"/>
-      <c r="C242" s="112"/>
-      <c r="D242" s="112"/>
+      <c r="B242" s="119"/>
+      <c r="C242" s="119"/>
+      <c r="D242" s="119"/>
       <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -25769,21 +25769,21 @@
       </c>
     </row>
     <row r="324" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="134"/>
-      <c r="B324" s="135"/>
-      <c r="C324" s="136"/>
-      <c r="D324" s="137"/>
+      <c r="A324" s="133"/>
+      <c r="B324" s="134"/>
+      <c r="C324" s="135"/>
+      <c r="D324" s="136"/>
       <c r="E324" s="25"/>
       <c r="G324" s="30"/>
       <c r="H324" s="30"/>
     </row>
     <row r="325" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="133" t="s">
+      <c r="A325" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="B325" s="112"/>
-      <c r="C325" s="112"/>
-      <c r="D325" s="112"/>
+      <c r="B325" s="119"/>
+      <c r="C325" s="119"/>
+      <c r="D325" s="119"/>
       <c r="E325" s="28"/>
     </row>
     <row r="326" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -26280,19 +26280,19 @@
       </c>
     </row>
     <row r="355" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="134"/>
-      <c r="B355" s="135"/>
-      <c r="C355" s="136"/>
-      <c r="D355" s="137"/>
+      <c r="A355" s="133"/>
+      <c r="B355" s="134"/>
+      <c r="C355" s="135"/>
+      <c r="D355" s="136"/>
       <c r="E355" s="25"/>
     </row>
     <row r="356" spans="1:5" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="133" t="s">
+      <c r="A356" s="139" t="s">
         <v>261</v>
       </c>
-      <c r="B356" s="112"/>
-      <c r="C356" s="112"/>
-      <c r="D356" s="112"/>
+      <c r="B356" s="119"/>
+      <c r="C356" s="119"/>
+      <c r="D356" s="119"/>
       <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28047,19 +28047,19 @@
       </c>
     </row>
     <row r="460" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A460" s="134"/>
-      <c r="B460" s="135"/>
-      <c r="C460" s="136"/>
-      <c r="D460" s="137"/>
+      <c r="A460" s="133"/>
+      <c r="B460" s="134"/>
+      <c r="C460" s="135"/>
+      <c r="D460" s="136"/>
       <c r="E460" s="25"/>
     </row>
     <row r="461" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A461" s="133" t="s">
+      <c r="A461" s="139" t="s">
         <v>338</v>
       </c>
-      <c r="B461" s="112"/>
-      <c r="C461" s="112"/>
-      <c r="D461" s="112"/>
+      <c r="B461" s="119"/>
+      <c r="C461" s="119"/>
+      <c r="D461" s="119"/>
       <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28352,19 +28352,19 @@
       </c>
     </row>
     <row r="479" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="134"/>
-      <c r="B479" s="135"/>
-      <c r="C479" s="136"/>
-      <c r="D479" s="137"/>
+      <c r="A479" s="133"/>
+      <c r="B479" s="134"/>
+      <c r="C479" s="135"/>
+      <c r="D479" s="136"/>
       <c r="E479" s="25"/>
     </row>
     <row r="480" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="133" t="s">
+      <c r="A480" s="139" t="s">
         <v>353</v>
       </c>
-      <c r="B480" s="112"/>
-      <c r="C480" s="112"/>
-      <c r="D480" s="112"/>
+      <c r="B480" s="119"/>
+      <c r="C480" s="119"/>
+      <c r="D480" s="119"/>
       <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -28793,19 +28793,19 @@
       </c>
     </row>
     <row r="506" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="134"/>
-      <c r="B506" s="135"/>
-      <c r="C506" s="136"/>
-      <c r="D506" s="137"/>
+      <c r="A506" s="133"/>
+      <c r="B506" s="134"/>
+      <c r="C506" s="135"/>
+      <c r="D506" s="136"/>
       <c r="E506" s="25"/>
     </row>
     <row r="507" spans="1:5" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A507" s="133" t="s">
+      <c r="A507" s="139" t="s">
         <v>370</v>
       </c>
-      <c r="B507" s="112"/>
-      <c r="C507" s="112"/>
-      <c r="D507" s="112"/>
+      <c r="B507" s="119"/>
+      <c r="C507" s="119"/>
+      <c r="D507" s="119"/>
       <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30320,19 +30320,19 @@
       </c>
     </row>
     <row r="597" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A597" s="134"/>
-      <c r="B597" s="135"/>
-      <c r="C597" s="136"/>
-      <c r="D597" s="137"/>
+      <c r="A597" s="133"/>
+      <c r="B597" s="134"/>
+      <c r="C597" s="135"/>
+      <c r="D597" s="136"/>
       <c r="E597" s="25"/>
     </row>
     <row r="598" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="133" t="s">
+      <c r="A598" s="139" t="s">
         <v>420</v>
       </c>
-      <c r="B598" s="112"/>
-      <c r="C598" s="112"/>
-      <c r="D598" s="112"/>
+      <c r="B598" s="119"/>
+      <c r="C598" s="119"/>
+      <c r="D598" s="119"/>
       <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30472,20 +30472,20 @@
       </c>
     </row>
     <row r="607" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A607" s="134"/>
-      <c r="B607" s="135"/>
-      <c r="C607" s="136"/>
-      <c r="D607" s="137"/>
+      <c r="A607" s="133"/>
+      <c r="B607" s="134"/>
+      <c r="C607" s="135"/>
+      <c r="D607" s="136"/>
       <c r="E607" s="25"/>
       <c r="G607" s="29"/>
     </row>
     <row r="608" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A608" s="133" t="s">
+      <c r="A608" s="139" t="s">
         <v>421</v>
       </c>
-      <c r="B608" s="112"/>
-      <c r="C608" s="112"/>
-      <c r="D608" s="112"/>
+      <c r="B608" s="119"/>
+      <c r="C608" s="119"/>
+      <c r="D608" s="119"/>
       <c r="E608" s="27"/>
     </row>
     <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -30574,19 +30574,19 @@
       </c>
     </row>
     <row r="614" spans="1:5" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A614" s="134"/>
-      <c r="B614" s="135"/>
-      <c r="C614" s="136"/>
-      <c r="D614" s="137"/>
+      <c r="A614" s="133"/>
+      <c r="B614" s="134"/>
+      <c r="C614" s="135"/>
+      <c r="D614" s="136"/>
       <c r="E614" s="25"/>
     </row>
     <row r="615" spans="1:5" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A615" s="133" t="s">
+      <c r="A615" s="139" t="s">
         <v>422</v>
       </c>
-      <c r="B615" s="112"/>
-      <c r="C615" s="112"/>
-      <c r="D615" s="112"/>
+      <c r="B615" s="119"/>
+      <c r="C615" s="119"/>
+      <c r="D615" s="119"/>
       <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -31951,25 +31951,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A597:D597"/>
-    <mergeCell ref="A506:D506"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A598:D598"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A460:D460"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A615:D615"/>
     <mergeCell ref="A182:D182"/>
     <mergeCell ref="A480:D480"/>
@@ -31986,6 +31967,25 @@
     <mergeCell ref="A607:D607"/>
     <mergeCell ref="A608:D608"/>
     <mergeCell ref="A507:D507"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A460:D460"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E9"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A597:D597"/>
+    <mergeCell ref="A506:D506"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A598:D598"/>
+    <mergeCell ref="A132:D132"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" display="mailto:E-mailastralalimentos@gmail.com" xr:uid="{00000000-0004-0000-0100-000000000000}"/>

--- a/scripts/produtos.xlsx
+++ b/scripts/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ListProducts\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743A6F0F-78AD-43FE-8947-EEA0971B21F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C74711D-4892-4B24-B97F-D239B825C92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="LISTA DE PRODUTOS T" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PRODUTOS B'!$A$1:$E$910</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTA DE PRODUTOS B'!$A$1:$E$912</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4030" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4036" uniqueCount="1340">
   <si>
     <t xml:space="preserve">    Tabela de Produtos e Preços</t>
   </si>
@@ -4042,13 +4042,17 @@
   </si>
   <si>
     <t>12X400G</t>
+  </si>
+  <si>
+    <t>MORANGO CHIPS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="########0"/>
@@ -4815,7 +4819,7 @@
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -5239,6 +5243,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="8" fontId="19" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -5545,7 +5552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R921"/>
+  <dimension ref="A1:R923"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="62.1640625" style="64" bestFit="1" customWidth="1"/>
@@ -14679,220 +14686,220 @@
     </row>
     <row r="551" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="69" t="s">
-        <v>347</v>
+        <v>1339</v>
       </c>
       <c r="B551" s="69" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="C551" s="70">
-        <v>2756</v>
+        <v>4585</v>
       </c>
       <c r="D551" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E551" s="40">
-        <v>580</v>
+        <v>15</v>
+      </c>
+      <c r="E551" s="151">
+        <v>675</v>
       </c>
     </row>
     <row r="552" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="69" t="s">
-        <v>347</v>
+        <v>1339</v>
       </c>
       <c r="B552" s="69" t="s">
-        <v>19</v>
+        <v>1149</v>
       </c>
       <c r="C552" s="70">
-        <v>2757</v>
+        <v>4584</v>
       </c>
       <c r="D552" s="69" t="s">
-        <v>50</v>
-      </c>
-      <c r="E552" s="40">
-        <v>290</v>
+        <v>20</v>
+      </c>
+      <c r="E552" s="151">
+        <v>337.5</v>
       </c>
     </row>
     <row r="553" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="69" t="s">
-        <v>1147</v>
+        <v>347</v>
       </c>
       <c r="B553" s="69" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C553" s="70">
-        <v>4491</v>
+        <v>2756</v>
       </c>
       <c r="D553" s="69" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="E553" s="40">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="554" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="69" t="s">
-        <v>1147</v>
+        <v>347</v>
       </c>
       <c r="B554" s="69" t="s">
-        <v>1149</v>
+        <v>19</v>
       </c>
       <c r="C554" s="70">
-        <v>4492</v>
+        <v>2757</v>
       </c>
       <c r="D554" s="69" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E554" s="40">
-        <v>217.5</v>
+        <v>290</v>
       </c>
     </row>
     <row r="555" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="69" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B555" s="69" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C555" s="70">
+        <v>4491</v>
+      </c>
+      <c r="D555" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E555" s="40">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A556" s="69" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B556" s="69" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C556" s="70">
+        <v>4492</v>
+      </c>
+      <c r="D556" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E556" s="40">
+        <v>217.5</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A557" s="69" t="s">
         <v>348</v>
       </c>
-      <c r="B555" s="69" t="s">
+      <c r="B557" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C555" s="70">
+      <c r="C557" s="70">
         <v>2350</v>
       </c>
-      <c r="D555" s="69" t="s">
+      <c r="D557" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E555" s="40">
+      <c r="E557" s="40">
         <v>150</v>
       </c>
     </row>
-    <row r="556" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A556" s="69" t="s">
+    <row r="558" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A558" s="69" t="s">
         <v>349</v>
       </c>
-      <c r="B556" s="69" t="s">
+      <c r="B558" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C556" s="70">
+      <c r="C558" s="70">
         <v>2362</v>
       </c>
-      <c r="D556" s="69" t="s">
+      <c r="D558" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E556" s="40">
+      <c r="E558" s="40">
         <v>115</v>
       </c>
     </row>
-    <row r="557" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A557" s="75" t="s">
+    <row r="559" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A559" s="75" t="s">
         <v>350</v>
       </c>
-      <c r="B557" s="75" t="s">
+      <c r="B559" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="C557" s="76">
+      <c r="C559" s="76">
         <v>4403</v>
       </c>
-      <c r="D557" s="75" t="s">
+      <c r="D559" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="E557" s="44">
+      <c r="E559" s="44">
         <v>142</v>
       </c>
     </row>
-    <row r="558" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A558" s="75" t="s">
+    <row r="560" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A560" s="75" t="s">
         <v>351</v>
       </c>
-      <c r="B558" s="75" t="s">
+      <c r="B560" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="C558" s="76">
+      <c r="C560" s="76">
         <v>2406</v>
       </c>
-      <c r="D558" s="75" t="s">
+      <c r="D560" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="E558" s="44">
+      <c r="E560" s="44">
         <v>420</v>
       </c>
     </row>
-    <row r="559" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A559" s="80" t="s">
+    <row r="561" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A561" s="80" t="s">
         <v>352</v>
       </c>
-      <c r="B559" s="80" t="s">
+      <c r="B561" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="C559" s="81">
+      <c r="C561" s="81">
         <v>2229</v>
       </c>
-      <c r="D559" s="80" t="s">
+      <c r="D561" s="80" t="s">
         <v>50</v>
       </c>
-      <c r="E559" s="42">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="560" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A560" s="116"/>
-      <c r="B560" s="109"/>
-      <c r="C560" s="109"/>
-      <c r="D560" s="110"/>
-      <c r="E560" s="117"/>
-    </row>
-    <row r="561" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A561" s="118" t="s">
+      <c r="E561" s="42">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A562" s="116"/>
+      <c r="B562" s="109"/>
+      <c r="C562" s="109"/>
+      <c r="D562" s="110"/>
+      <c r="E562" s="117"/>
+    </row>
+    <row r="563" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A563" s="118" t="s">
         <v>353</v>
       </c>
-      <c r="B561" s="119"/>
-      <c r="C561" s="119"/>
-      <c r="D561" s="119"/>
-      <c r="E561" s="120"/>
-    </row>
-    <row r="562" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A562" s="66" t="s">
+      <c r="B563" s="119"/>
+      <c r="C563" s="119"/>
+      <c r="D563" s="119"/>
+      <c r="E563" s="120"/>
+    </row>
+    <row r="564" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A564" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B562" s="66"/>
-      <c r="C562" s="66" t="s">
+      <c r="B564" s="66"/>
+      <c r="C564" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D562" s="66" t="s">
+      <c r="D564" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E562" s="46" t="s">
+      <c r="E564" s="46" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="563" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A563" s="69" t="s">
-        <v>354</v>
-      </c>
-      <c r="B563" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="C563" s="70">
-        <v>189</v>
-      </c>
-      <c r="D563" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E563" s="40">
-        <v>140.5</v>
-      </c>
-    </row>
-    <row r="564" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A564" s="69" t="s">
-        <v>354</v>
-      </c>
-      <c r="B564" s="69" t="s">
-        <v>226</v>
-      </c>
-      <c r="C564" s="70">
-        <v>9</v>
-      </c>
-      <c r="D564" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E564" s="40">
-        <v>281</v>
       </c>
     </row>
     <row r="565" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -14900,407 +14907,407 @@
         <v>354</v>
       </c>
       <c r="B565" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C565" s="70">
+        <v>189</v>
+      </c>
+      <c r="D565" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E565" s="40">
+        <v>140.5</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A566" s="69" t="s">
+        <v>354</v>
+      </c>
+      <c r="B566" s="69" t="s">
+        <v>226</v>
+      </c>
+      <c r="C566" s="70">
+        <v>9</v>
+      </c>
+      <c r="D566" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E566" s="40">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A567" s="69" t="s">
+        <v>354</v>
+      </c>
+      <c r="B567" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C565" s="70">
+      <c r="C567" s="70">
         <v>2553</v>
       </c>
-      <c r="D565" s="69" t="s">
+      <c r="D567" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E565" s="40">
+      <c r="E567" s="40">
         <v>33</v>
-      </c>
-    </row>
-    <row r="566" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A566" s="69" t="s">
-        <v>355</v>
-      </c>
-      <c r="B566" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C566" s="70">
-        <v>521</v>
-      </c>
-      <c r="D566" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E566" s="40">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="567" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A567" s="69" t="s">
-        <v>355</v>
-      </c>
-      <c r="B567" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="C567" s="70">
-        <v>99</v>
-      </c>
-      <c r="D567" s="69" t="s">
-        <v>84</v>
-      </c>
-      <c r="E567" s="40">
-        <v>350</v>
       </c>
     </row>
     <row r="568" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="69" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B568" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C568" s="70">
-        <v>2613</v>
+        <v>521</v>
       </c>
       <c r="D568" s="69" t="s">
         <v>49</v>
       </c>
       <c r="E568" s="40">
-        <v>34.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="569" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="69" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B569" s="69" t="s">
         <v>33</v>
       </c>
       <c r="C569" s="70">
-        <v>3365</v>
+        <v>99</v>
       </c>
       <c r="D569" s="69" t="s">
         <v>84</v>
       </c>
       <c r="E569" s="40">
-        <v>162.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="570" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="69" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B570" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C570" s="70">
-        <v>2556</v>
+        <v>2613</v>
       </c>
       <c r="D570" s="69" t="s">
         <v>49</v>
       </c>
       <c r="E570" s="40">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="571" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="69" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B571" s="69" t="s">
         <v>33</v>
       </c>
       <c r="C571" s="70">
-        <v>2555</v>
+        <v>3365</v>
       </c>
       <c r="D571" s="69" t="s">
         <v>84</v>
       </c>
       <c r="E571" s="40">
-        <v>725</v>
+        <v>162.5</v>
       </c>
     </row>
     <row r="572" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="69" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B572" s="69" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C572" s="70">
-        <v>4045</v>
+        <v>2556</v>
       </c>
       <c r="D572" s="69" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E572" s="40">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="573" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="69" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B573" s="69" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C573" s="70">
-        <v>3669</v>
+        <v>2555</v>
       </c>
       <c r="D573" s="69" t="s">
         <v>84</v>
       </c>
       <c r="E573" s="40">
-        <v>44.5</v>
+        <v>725</v>
       </c>
     </row>
     <row r="574" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="69" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B574" s="69" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C574" s="70">
-        <v>38</v>
+        <v>4045</v>
       </c>
       <c r="D574" s="69" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E574" s="40">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="575" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="69" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B575" s="69" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="C575" s="70">
-        <v>2479</v>
+        <v>3669</v>
       </c>
       <c r="D575" s="69" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="E575" s="40">
-        <v>22</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="576" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="69" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B576" s="69" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C576" s="70">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="D576" s="69" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="E576" s="40">
-        <v>67</v>
+        <v>157</v>
       </c>
     </row>
     <row r="577" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="69" t="s">
+        <v>359</v>
+      </c>
+      <c r="B577" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="C577" s="70">
+        <v>2479</v>
+      </c>
+      <c r="D577" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E577" s="40">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A578" s="69" t="s">
         <v>360</v>
       </c>
-      <c r="B577" s="69" t="s">
+      <c r="B578" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C578" s="70">
+        <v>105</v>
+      </c>
+      <c r="D578" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="E578" s="40">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A579" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="B579" s="69" t="s">
         <v>151</v>
       </c>
-      <c r="C577" s="70">
+      <c r="C579" s="70">
         <v>212</v>
       </c>
-      <c r="D577" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E577" s="40">
+      <c r="D579" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E579" s="40">
         <v>201</v>
-      </c>
-    </row>
-    <row r="578" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A578" s="72" t="s">
-        <v>361</v>
-      </c>
-      <c r="B578" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="C578" s="73">
-        <v>2848</v>
-      </c>
-      <c r="D578" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="E578" s="50">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="579" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A579" s="72" t="s">
-        <v>361</v>
-      </c>
-      <c r="B579" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C579" s="73">
-        <v>2851</v>
-      </c>
-      <c r="D579" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E579" s="50">
-        <v>125</v>
       </c>
     </row>
     <row r="580" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="72" t="s">
-        <v>1150</v>
+        <v>361</v>
       </c>
       <c r="B580" s="72" t="s">
-        <v>1149</v>
+        <v>33</v>
       </c>
       <c r="C580" s="73">
-        <v>4202</v>
+        <v>2848</v>
       </c>
       <c r="D580" s="72" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="E580" s="50">
-        <v>152.5</v>
+        <v>615</v>
       </c>
     </row>
     <row r="581" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="72" t="s">
+        <v>361</v>
+      </c>
+      <c r="B581" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C581" s="73">
+        <v>2851</v>
+      </c>
+      <c r="D581" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E581" s="50">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="582" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A582" s="72" t="s">
         <v>1150</v>
       </c>
-      <c r="B581" s="72" t="s">
+      <c r="B582" s="72" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C582" s="73">
+        <v>4202</v>
+      </c>
+      <c r="D582" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E582" s="50">
+        <v>152.5</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A583" s="72" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B583" s="72" t="s">
         <v>1148</v>
       </c>
-      <c r="C581" s="73">
+      <c r="C583" s="73">
         <v>4201</v>
       </c>
-      <c r="D581" s="72" t="s">
+      <c r="D583" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="E581" s="50">
+      <c r="E583" s="50">
         <v>305</v>
       </c>
     </row>
-    <row r="582" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A582" s="69" t="s">
+    <row r="584" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A584" s="69" t="s">
         <v>362</v>
-      </c>
-      <c r="B582" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="C582" s="70">
-        <v>653</v>
-      </c>
-      <c r="D582" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E582" s="40">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="583" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A583" s="69" t="s">
-        <v>362</v>
-      </c>
-      <c r="B583" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C583" s="70">
-        <v>2484</v>
-      </c>
-      <c r="D583" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="E583" s="40">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="584" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A584" s="69" t="s">
-        <v>363</v>
       </c>
       <c r="B584" s="69" t="s">
         <v>33</v>
       </c>
       <c r="C584" s="70">
-        <v>3417</v>
+        <v>653</v>
       </c>
       <c r="D584" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E584" s="40">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="585" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="585" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="69" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B585" s="69" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C585" s="70">
-        <v>2716</v>
+        <v>2484</v>
       </c>
       <c r="D585" s="69" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="E585" s="40">
-        <v>317.5</v>
-      </c>
-    </row>
-    <row r="586" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="69" t="s">
         <v>363</v>
       </c>
       <c r="B586" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="C586" s="70">
+        <v>3417</v>
+      </c>
+      <c r="D586" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E586" s="40">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="587" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A587" s="69" t="s">
+        <v>363</v>
+      </c>
+      <c r="B587" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C587" s="70">
+        <v>2716</v>
+      </c>
+      <c r="D587" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="E587" s="40">
+        <v>317.5</v>
+      </c>
+    </row>
+    <row r="588" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A588" s="69" t="s">
+        <v>363</v>
+      </c>
+      <c r="B588" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C586" s="70">
+      <c r="C588" s="70">
         <v>2478</v>
       </c>
-      <c r="D586" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E586" s="40">
+      <c r="D588" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E588" s="40">
         <v>72</v>
-      </c>
-    </row>
-    <row r="587" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A587" s="72" t="s">
-        <v>364</v>
-      </c>
-      <c r="B587" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C587" s="73">
-        <v>2606</v>
-      </c>
-      <c r="D587" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="E587" s="50">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="588" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A588" s="72" t="s">
-        <v>364</v>
-      </c>
-      <c r="B588" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="C588" s="73">
-        <v>2338</v>
-      </c>
-      <c r="D588" s="72" t="s">
-        <v>34</v>
-      </c>
-      <c r="E588" s="50">
-        <v>600</v>
       </c>
     </row>
     <row r="589" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -15308,268 +15315,268 @@
         <v>364</v>
       </c>
       <c r="B589" s="72" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C589" s="73">
-        <v>2425</v>
+        <v>2606</v>
       </c>
       <c r="D589" s="72" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="E589" s="50">
-        <v>91</v>
+        <v>450</v>
       </c>
     </row>
     <row r="590" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="72" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B590" s="72" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C590" s="73">
-        <v>2579</v>
+        <v>2338</v>
       </c>
       <c r="D590" s="72" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E590" s="50">
-        <v>102</v>
+        <v>600</v>
       </c>
     </row>
     <row r="591" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="72" t="s">
+        <v>364</v>
+      </c>
+      <c r="B591" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="C591" s="73">
+        <v>2425</v>
+      </c>
+      <c r="D591" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E591" s="50">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="592" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A592" s="72" t="s">
+        <v>365</v>
+      </c>
+      <c r="B592" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C592" s="73">
+        <v>2579</v>
+      </c>
+      <c r="D592" s="72" t="s">
+        <v>84</v>
+      </c>
+      <c r="E592" s="50">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="593" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A593" s="72" t="s">
         <v>366</v>
       </c>
-      <c r="B591" s="72" t="s">
+      <c r="B593" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="C591" s="73">
+      <c r="C593" s="73">
         <v>2243</v>
       </c>
-      <c r="D591" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="E591" s="50">
+      <c r="D593" s="72" t="s">
+        <v>84</v>
+      </c>
+      <c r="E593" s="50">
         <v>500</v>
       </c>
     </row>
-    <row r="592" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A592" s="69" t="s">
-        <v>367</v>
-      </c>
-      <c r="B592" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="C592" s="70">
-        <v>4400</v>
-      </c>
-      <c r="D592" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E592" s="40">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="593" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A593" s="69" t="s">
-        <v>367</v>
-      </c>
-      <c r="B593" s="69">
-        <v>20</v>
-      </c>
-      <c r="C593" s="70">
-        <v>2680</v>
-      </c>
-      <c r="D593" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E593" s="40">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="594" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="69" t="s">
         <v>367</v>
       </c>
       <c r="B594" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="C594" s="70">
+        <v>4400</v>
+      </c>
+      <c r="D594" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E594" s="40">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="595" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A595" s="69" t="s">
+        <v>367</v>
+      </c>
+      <c r="B595" s="69">
+        <v>20</v>
+      </c>
+      <c r="C595" s="70">
+        <v>2680</v>
+      </c>
+      <c r="D595" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E595" s="40">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="596" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A596" s="69" t="s">
+        <v>367</v>
+      </c>
+      <c r="B596" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C594" s="70">
+      <c r="C596" s="70">
         <v>2676</v>
       </c>
-      <c r="D594" s="69" t="s">
-        <v>84</v>
-      </c>
-      <c r="E594" s="40">
+      <c r="D596" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="E596" s="40">
         <v>182</v>
       </c>
     </row>
-    <row r="595" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A595" s="69" t="s">
+    <row r="597" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A597" s="69" t="s">
         <v>368</v>
       </c>
-      <c r="B595" s="69" t="s">
+      <c r="B597" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="C595" s="70">
+      <c r="C597" s="70">
         <v>571</v>
       </c>
-      <c r="D595" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E595" s="40">
+      <c r="D597" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E597" s="40">
         <v>525</v>
       </c>
     </row>
-    <row r="596" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A596" s="75" t="s">
+    <row r="598" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A598" s="75" t="s">
         <v>368</v>
       </c>
-      <c r="B596" s="75" t="s">
+      <c r="B598" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="C596" s="76">
+      <c r="C598" s="76">
         <v>2245</v>
       </c>
-      <c r="D596" s="75" t="s">
+      <c r="D598" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E596" s="44">
+      <c r="E598" s="44">
         <v>107</v>
       </c>
     </row>
-    <row r="597" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A597" s="80" t="s">
+    <row r="599" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A599" s="80" t="s">
         <v>369</v>
       </c>
-      <c r="B597" s="80" t="s">
+      <c r="B599" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="C597" s="81">
+      <c r="C599" s="81">
         <v>3754</v>
       </c>
-      <c r="D597" s="80" t="s">
+      <c r="D599" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="E597" s="42">
+      <c r="E599" s="42">
         <v>450</v>
       </c>
     </row>
-    <row r="598" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A598" s="128"/>
-      <c r="B598" s="129"/>
-      <c r="C598" s="129"/>
-      <c r="D598" s="129"/>
-      <c r="E598" s="129"/>
-    </row>
-    <row r="599" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A599" s="118" t="s">
+    <row r="600" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A600" s="128"/>
+      <c r="B600" s="129"/>
+      <c r="C600" s="129"/>
+      <c r="D600" s="129"/>
+      <c r="E600" s="129"/>
+    </row>
+    <row r="601" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A601" s="118" t="s">
         <v>370</v>
       </c>
-      <c r="B599" s="119"/>
-      <c r="C599" s="119"/>
-      <c r="D599" s="119"/>
-      <c r="E599" s="120"/>
-    </row>
-    <row r="600" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A600" s="66" t="s">
+      <c r="B601" s="119"/>
+      <c r="C601" s="119"/>
+      <c r="D601" s="119"/>
+      <c r="E601" s="120"/>
+    </row>
+    <row r="602" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A602" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B600" s="66"/>
-      <c r="C600" s="66" t="s">
+      <c r="B602" s="66"/>
+      <c r="C602" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D600" s="66" t="s">
+      <c r="D602" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E600" s="46" t="s">
+      <c r="E602" s="46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="601" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A601" s="82" t="s">
+    <row r="603" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A603" s="82" t="s">
         <v>371</v>
       </c>
-      <c r="B601" s="82" t="s">
+      <c r="B603" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="C601" s="82">
+      <c r="C603" s="82">
         <v>4336</v>
       </c>
-      <c r="D601" s="82" t="s">
+      <c r="D603" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="E601" s="43">
+      <c r="E603" s="43">
         <v>329.5</v>
-      </c>
-    </row>
-    <row r="602" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A602" s="69" t="s">
-        <v>372</v>
-      </c>
-      <c r="B602" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C602" s="70">
-        <v>2618</v>
-      </c>
-      <c r="D602" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E602" s="40">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="603" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A603" s="69" t="s">
-        <v>372</v>
-      </c>
-      <c r="B603" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C603" s="70">
-        <v>2398</v>
-      </c>
-      <c r="D603" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="E603" s="40">
-        <v>124.5</v>
       </c>
     </row>
     <row r="604" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="69" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B604" s="69" t="s">
-        <v>1154</v>
+        <v>18</v>
       </c>
       <c r="C604" s="70">
-        <v>2297</v>
+        <v>2618</v>
       </c>
       <c r="D604" s="69" t="s">
-        <v>160</v>
+        <v>34</v>
       </c>
       <c r="E604" s="40">
-        <v>77.5</v>
+        <v>245</v>
       </c>
     </row>
     <row r="605" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="69" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B605" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C605" s="70">
-        <v>3653</v>
+        <v>2398</v>
       </c>
       <c r="D605" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E605" s="40">
-        <v>29</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="606" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -15577,149 +15584,149 @@
         <v>373</v>
       </c>
       <c r="B606" s="69" t="s">
-        <v>1175</v>
+        <v>1154</v>
       </c>
       <c r="C606" s="70">
-        <v>2339</v>
+        <v>2297</v>
       </c>
       <c r="D606" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E606" s="40">
-        <v>173</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="607" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="69" t="s">
-        <v>1151</v>
+        <v>373</v>
       </c>
       <c r="B607" s="69" t="s">
-        <v>1130</v>
+        <v>19</v>
       </c>
       <c r="C607" s="70">
-        <v>2223</v>
+        <v>3653</v>
       </c>
       <c r="D607" s="69" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E607" s="40">
-        <v>57.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="608" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="69" t="s">
-        <v>1151</v>
+        <v>373</v>
       </c>
       <c r="B608" s="69" t="s">
-        <v>1137</v>
+        <v>1175</v>
       </c>
       <c r="C608" s="70">
-        <v>3707</v>
+        <v>2339</v>
       </c>
       <c r="D608" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E608" s="40">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="609" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="69" t="s">
         <v>1151</v>
       </c>
       <c r="B609" s="69" t="s">
-        <v>33</v>
+        <v>1130</v>
       </c>
       <c r="C609" s="70">
-        <v>4090</v>
+        <v>2223</v>
       </c>
       <c r="D609" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E609" s="40">
-        <v>141.5</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="610" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="69" t="s">
-        <v>374</v>
+        <v>1151</v>
       </c>
       <c r="B610" s="69" t="s">
-        <v>19</v>
+        <v>1137</v>
       </c>
       <c r="C610" s="70">
-        <v>4279</v>
+        <v>3707</v>
       </c>
       <c r="D610" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E610" s="40">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="611" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="69" t="s">
-        <v>1307</v>
+        <v>1151</v>
       </c>
       <c r="B611" s="69" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="C611" s="70">
-        <v>2259</v>
+        <v>4090</v>
       </c>
       <c r="D611" s="69" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E611" s="40">
-        <v>15.5</v>
+        <v>141.5</v>
       </c>
     </row>
     <row r="612" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="69" t="s">
-        <v>1306</v>
+        <v>374</v>
       </c>
       <c r="B612" s="69" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="C612" s="70">
-        <v>3540</v>
+        <v>4279</v>
       </c>
       <c r="D612" s="69" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="E612" s="40">
-        <v>15.5</v>
+        <v>295</v>
       </c>
     </row>
     <row r="613" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="69" t="s">
-        <v>375</v>
+        <v>1307</v>
       </c>
       <c r="B613" s="69" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="C613" s="70">
-        <v>3541</v>
+        <v>2259</v>
       </c>
       <c r="D613" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E613" s="40">
-        <v>120</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="614" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="69" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B614" s="69" t="s">
         <v>110</v>
       </c>
       <c r="C614" s="70">
-        <v>2422</v>
+        <v>3540</v>
       </c>
       <c r="D614" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E614" s="40">
         <v>15.5</v>
@@ -15727,189 +15734,189 @@
     </row>
     <row r="615" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="69" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B615" s="69" t="s">
         <v>33</v>
       </c>
       <c r="C615" s="70">
-        <v>569</v>
+        <v>3541</v>
       </c>
       <c r="D615" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E615" s="40">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="616" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="69" t="s">
-        <v>377</v>
+        <v>1305</v>
       </c>
       <c r="B616" s="69" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="C616" s="70">
-        <v>282</v>
+        <v>2422</v>
       </c>
       <c r="D616" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E616" s="40">
-        <v>118</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="617" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="69" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B617" s="69" t="s">
         <v>33</v>
       </c>
       <c r="C617" s="70">
-        <v>2336</v>
+        <v>569</v>
       </c>
       <c r="D617" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E617" s="40">
-        <v>750</v>
+        <v>118</v>
       </c>
     </row>
     <row r="618" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="69" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B618" s="69" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="C618" s="70">
-        <v>2421</v>
+        <v>282</v>
       </c>
       <c r="D618" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E618" s="40">
-        <v>91</v>
+        <v>118</v>
       </c>
     </row>
     <row r="619" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="69" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B619" s="69" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C619" s="70">
-        <v>2568</v>
+        <v>2336</v>
       </c>
       <c r="D619" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E619" s="40">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="620" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="69" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B620" s="69" t="s">
         <v>110</v>
       </c>
       <c r="C620" s="70">
-        <v>3009</v>
+        <v>2421</v>
       </c>
       <c r="D620" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E620" s="40">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="621" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="621" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="69" t="s">
-        <v>1320</v>
+        <v>379</v>
       </c>
       <c r="B621" s="69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C621" s="70">
-        <v>2778</v>
+        <v>2568</v>
       </c>
       <c r="D621" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E621" s="40">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="622" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="69" t="s">
-        <v>1319</v>
+        <v>379</v>
       </c>
       <c r="B622" s="69" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C622" s="70">
-        <v>3106</v>
+        <v>3009</v>
       </c>
       <c r="D622" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E622" s="40">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="623" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A623" s="72" t="s">
-        <v>380</v>
-      </c>
-      <c r="B623" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="C623" s="73">
-        <v>3489</v>
-      </c>
-      <c r="D623" s="72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A623" s="69" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B623" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C623" s="70">
+        <v>2778</v>
+      </c>
+      <c r="D623" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="E623" s="50">
-        <v>700</v>
+      <c r="E623" s="40">
+        <v>180</v>
       </c>
     </row>
     <row r="624" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="69" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B624" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C624" s="70">
+        <v>3106</v>
+      </c>
+      <c r="D624" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E624" s="40">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A625" s="72" t="s">
         <v>380</v>
       </c>
-      <c r="B624" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C624" s="70">
-        <v>3696</v>
-      </c>
-      <c r="D624" s="69" t="s">
+      <c r="B625" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="C625" s="73">
+        <v>3489</v>
+      </c>
+      <c r="D625" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="E624" s="40">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="625" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A625" s="69" t="s">
-        <v>380</v>
-      </c>
-      <c r="B625" s="69" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C625" s="70">
-        <v>2783</v>
-      </c>
-      <c r="D625" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="E625" s="40">
-        <v>142</v>
+      <c r="E625" s="50">
+        <v>700</v>
       </c>
     </row>
     <row r="626" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -15917,231 +15924,231 @@
         <v>380</v>
       </c>
       <c r="B626" s="69" t="s">
-        <v>1152</v>
+        <v>18</v>
       </c>
       <c r="C626" s="70">
-        <v>3755</v>
+        <v>3696</v>
       </c>
       <c r="D626" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E626" s="40">
-        <v>85</v>
+        <v>280</v>
       </c>
     </row>
     <row r="627" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="69" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B627" s="69" t="s">
-        <v>18</v>
+        <v>1133</v>
       </c>
       <c r="C627" s="70">
-        <v>3486</v>
+        <v>2783</v>
       </c>
       <c r="D627" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E627" s="40">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="628" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="69" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B628" s="69" t="s">
-        <v>110</v>
+        <v>1152</v>
       </c>
       <c r="C628" s="70">
-        <v>3487</v>
+        <v>3755</v>
       </c>
       <c r="D628" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E628" s="40">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="629" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="69" t="s">
         <v>382</v>
       </c>
       <c r="B629" s="69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C629" s="70">
-        <v>4488</v>
+        <v>3486</v>
       </c>
       <c r="D629" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E629" s="40">
-        <v>272</v>
+        <v>540</v>
       </c>
     </row>
     <row r="630" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="69" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B630" s="69" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C630" s="70">
-        <v>4333</v>
+        <v>3487</v>
       </c>
       <c r="D630" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E630" s="40">
-        <v>259.5</v>
+        <v>163</v>
       </c>
     </row>
     <row r="631" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="69" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B631" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C631" s="70">
-        <v>4388</v>
+        <v>4488</v>
       </c>
       <c r="D631" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E631" s="40">
-        <v>145</v>
+        <v>272</v>
       </c>
     </row>
     <row r="632" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="69" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B632" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C632" s="70">
-        <v>4389</v>
+        <v>4333</v>
       </c>
       <c r="D632" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E632" s="40">
-        <v>102</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="633" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="69" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B633" s="69" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C633" s="70">
-        <v>3488</v>
+        <v>4388</v>
       </c>
       <c r="D633" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E633" s="40">
-        <v>220</v>
+        <v>145</v>
       </c>
     </row>
     <row r="634" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="69" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B634" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C634" s="70">
-        <v>3400</v>
+        <v>4389</v>
       </c>
       <c r="D634" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E634" s="40">
-        <v>57</v>
+        <v>102</v>
       </c>
     </row>
     <row r="635" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="69" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B635" s="69" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="C635" s="70">
-        <v>2257</v>
+        <v>3488</v>
       </c>
       <c r="D635" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E635" s="40">
-        <v>16</v>
+        <v>220</v>
       </c>
     </row>
     <row r="636" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="69" t="s">
+        <v>387</v>
+      </c>
+      <c r="B636" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C636" s="70">
+        <v>3400</v>
+      </c>
+      <c r="D636" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E636" s="40">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A637" s="69" t="s">
         <v>388</v>
       </c>
-      <c r="B636" s="69" t="s">
+      <c r="B637" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="C637" s="70">
+        <v>2257</v>
+      </c>
+      <c r="D637" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E637" s="40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A638" s="69" t="s">
+        <v>388</v>
+      </c>
+      <c r="B638" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="C636" s="70">
+      <c r="C638" s="70">
         <v>565</v>
       </c>
-      <c r="D636" s="69" t="s">
+      <c r="D638" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="E636" s="40">
+      <c r="E638" s="40">
         <v>123</v>
-      </c>
-    </row>
-    <row r="637" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A637" s="72" t="s">
-        <v>389</v>
-      </c>
-      <c r="B637" s="72" t="s">
-        <v>110</v>
-      </c>
-      <c r="C637" s="73">
-        <v>4474</v>
-      </c>
-      <c r="D637" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E637" s="50">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="638" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A638" s="72" t="s">
-        <v>390</v>
-      </c>
-      <c r="B638" s="72" t="s">
-        <v>110</v>
-      </c>
-      <c r="C638" s="73">
-        <v>4473</v>
-      </c>
-      <c r="D638" s="72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E638" s="50">
-        <v>39</v>
       </c>
     </row>
     <row r="639" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="72" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B639" s="72" t="s">
         <v>110</v>
       </c>
       <c r="C639" s="73">
-        <v>2658</v>
+        <v>4474</v>
       </c>
       <c r="D639" s="72" t="s">
         <v>20</v>
@@ -16152,13 +16159,13 @@
     </row>
     <row r="640" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="72" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B640" s="72" t="s">
         <v>110</v>
       </c>
       <c r="C640" s="73">
-        <v>2657</v>
+        <v>4473</v>
       </c>
       <c r="D640" s="72" t="s">
         <v>20</v>
@@ -16169,209 +16176,209 @@
     </row>
     <row r="641" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="72" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B641" s="72" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C641" s="73">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="D641" s="72" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E641" s="50">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="642" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="72" t="s">
+        <v>392</v>
+      </c>
+      <c r="B642" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="C642" s="73">
+        <v>2657</v>
+      </c>
+      <c r="D642" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E642" s="50">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="643" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A643" s="72" t="s">
+        <v>393</v>
+      </c>
+      <c r="B643" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C643" s="73">
+        <v>2657</v>
+      </c>
+      <c r="D643" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E643" s="50">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="644" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A644" s="72" t="s">
         <v>391</v>
       </c>
-      <c r="B642" s="72" t="s">
+      <c r="B644" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C642" s="73">
+      <c r="C644" s="73">
         <v>2658</v>
       </c>
-      <c r="D642" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E642" s="50">
+      <c r="D644" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E644" s="50">
         <v>65</v>
       </c>
-      <c r="F642" s="1" t="s">
+      <c r="F644" s="1" t="s">
         <v>386</v>
-      </c>
-    </row>
-    <row r="643" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A643" s="69" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B643" s="69" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C643" s="70">
-        <v>3537</v>
-      </c>
-      <c r="D643" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E643" s="40">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="644" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A644" s="69" t="s">
-        <v>394</v>
-      </c>
-      <c r="B644" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C644" s="70">
-        <v>2732</v>
-      </c>
-      <c r="D644" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E644" s="40">
-        <v>175</v>
       </c>
     </row>
     <row r="645" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="69" t="s">
-        <v>394</v>
+        <v>1153</v>
       </c>
       <c r="B645" s="69" t="s">
-        <v>19</v>
+        <v>1154</v>
       </c>
       <c r="C645" s="70">
-        <v>2733</v>
+        <v>3537</v>
       </c>
       <c r="D645" s="69" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E645" s="40">
-        <v>87.5</v>
+        <v>162</v>
       </c>
     </row>
     <row r="646" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="69" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B646" s="69" t="s">
         <v>18</v>
       </c>
       <c r="C646" s="70">
-        <v>2584</v>
+        <v>2732</v>
       </c>
       <c r="D646" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E646" s="40">
-        <v>205</v>
+        <v>175</v>
       </c>
     </row>
     <row r="647" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="69" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B647" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C647" s="70">
-        <v>2677</v>
+        <v>2733</v>
       </c>
       <c r="D647" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E647" s="40">
-        <v>104.5</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="648" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="69" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B648" s="69" t="s">
         <v>18</v>
       </c>
       <c r="C648" s="70">
-        <v>2495</v>
+        <v>2584</v>
       </c>
       <c r="D648" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E648" s="40">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="649" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="69" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B649" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C649" s="70">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="D649" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E649" s="40">
-        <v>100.5</v>
-      </c>
-    </row>
-    <row r="650" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+        <v>104.5</v>
+      </c>
+    </row>
+    <row r="650" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="69" t="s">
-        <v>1155</v>
+        <v>396</v>
       </c>
       <c r="B650" s="69" t="s">
-        <v>1130</v>
+        <v>18</v>
       </c>
       <c r="C650" s="70">
-        <v>4498</v>
+        <v>2495</v>
       </c>
       <c r="D650" s="69" t="s">
-        <v>177</v>
+        <v>15</v>
       </c>
       <c r="E650" s="40">
-        <v>240</v>
+        <v>197</v>
       </c>
     </row>
     <row r="651" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="69" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B651" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C651" s="70">
-        <v>4253</v>
+        <v>2678</v>
       </c>
       <c r="D651" s="69" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E651" s="40">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="652" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>100.5</v>
+      </c>
+    </row>
+    <row r="652" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="69" t="s">
-        <v>397</v>
+        <v>1155</v>
       </c>
       <c r="B652" s="69" t="s">
-        <v>18</v>
+        <v>1130</v>
       </c>
       <c r="C652" s="70">
-        <v>4500</v>
+        <v>4498</v>
       </c>
       <c r="D652" s="69" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="E652" s="40">
-        <v>224</v>
+        <v>240</v>
       </c>
     </row>
     <row r="653" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16379,16 +16386,16 @@
         <v>397</v>
       </c>
       <c r="B653" s="69" t="s">
-        <v>1156</v>
+        <v>19</v>
       </c>
       <c r="C653" s="70">
-        <v>4249</v>
+        <v>4253</v>
       </c>
       <c r="D653" s="69" t="s">
         <v>160</v>
       </c>
       <c r="E653" s="40">
-        <v>230</v>
+        <v>112</v>
       </c>
     </row>
     <row r="654" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16396,10 +16403,10 @@
         <v>397</v>
       </c>
       <c r="B654" s="69" t="s">
-        <v>1130</v>
+        <v>18</v>
       </c>
       <c r="C654" s="70">
-        <v>3724</v>
+        <v>4500</v>
       </c>
       <c r="D654" s="69" t="s">
         <v>160</v>
@@ -16410,47 +16417,47 @@
     </row>
     <row r="655" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="69" t="s">
-        <v>1157</v>
+        <v>397</v>
       </c>
       <c r="B655" s="69" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="C655" s="70">
-        <v>3736</v>
+        <v>4249</v>
       </c>
       <c r="D655" s="69" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E655" s="40">
-        <v>162</v>
+        <v>230</v>
       </c>
     </row>
     <row r="656" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="69" t="s">
-        <v>1158</v>
+        <v>397</v>
       </c>
       <c r="B656" s="69" t="s">
         <v>1130</v>
       </c>
       <c r="C656" s="70">
-        <v>4499</v>
+        <v>3724</v>
       </c>
       <c r="D656" s="69" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="E656" s="40">
-        <v>240</v>
+        <v>224</v>
       </c>
     </row>
     <row r="657" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="69" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B657" s="69" t="s">
         <v>1154</v>
       </c>
       <c r="C657" s="70">
-        <v>3536</v>
+        <v>3736</v>
       </c>
       <c r="D657" s="69" t="s">
         <v>15</v>
@@ -16461,87 +16468,87 @@
     </row>
     <row r="658" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="69" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B658" s="69" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C658" s="70">
+        <v>4499</v>
+      </c>
+      <c r="D658" s="69" t="s">
+        <v>177</v>
+      </c>
+      <c r="E658" s="40">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A659" s="69" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B659" s="69" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C659" s="70">
+        <v>3536</v>
+      </c>
+      <c r="D659" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E659" s="40">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A660" s="69" t="s">
         <v>398</v>
       </c>
-      <c r="B658" s="69" t="s">
+      <c r="B660" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C658" s="70">
+      <c r="C660" s="70">
         <v>2494</v>
       </c>
-      <c r="D658" s="69" t="s">
+      <c r="D660" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E658" s="40">
+      <c r="E660" s="40">
         <v>170</v>
       </c>
     </row>
-    <row r="659" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A659" s="72" t="s">
+    <row r="661" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A661" s="72" t="s">
         <v>398</v>
       </c>
-      <c r="B659" s="72" t="s">
+      <c r="B661" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C659" s="73">
+      <c r="C661" s="73">
         <v>2679</v>
       </c>
-      <c r="D659" s="72" t="s">
+      <c r="D661" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="E659" s="50">
+      <c r="E661" s="50">
         <v>87</v>
       </c>
     </row>
-    <row r="660" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A660" s="72" t="s">
+    <row r="662" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A662" s="72" t="s">
         <v>1160</v>
       </c>
-      <c r="B660" s="72" t="s">
+      <c r="B662" s="72" t="s">
         <v>1130</v>
       </c>
-      <c r="C660" s="73">
+      <c r="C662" s="73">
         <v>4497</v>
       </c>
-      <c r="D660" s="72" t="s">
+      <c r="D662" s="72" t="s">
         <v>177</v>
       </c>
-      <c r="E660" s="50">
+      <c r="E662" s="50">
         <v>240</v>
-      </c>
-    </row>
-    <row r="661" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A661" s="69" t="s">
-        <v>399</v>
-      </c>
-      <c r="B661" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C661" s="70">
-        <v>2493</v>
-      </c>
-      <c r="D661" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E661" s="40">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="662" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A662" s="69" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B662" s="69" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C662" s="70">
-        <v>3535</v>
-      </c>
-      <c r="D662" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E662" s="40">
-        <v>162</v>
       </c>
     </row>
     <row r="663" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16549,390 +16556,390 @@
         <v>399</v>
       </c>
       <c r="B663" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C663" s="70">
+        <v>2493</v>
+      </c>
+      <c r="D663" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E663" s="40">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="664" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A664" s="69" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B664" s="69" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C664" s="70">
+        <v>3535</v>
+      </c>
+      <c r="D664" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E664" s="40">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="665" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A665" s="69" t="s">
+        <v>399</v>
+      </c>
+      <c r="B665" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C663" s="70">
+      <c r="C665" s="70">
         <v>2498</v>
       </c>
-      <c r="D663" s="69" t="s">
+      <c r="D665" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E663" s="40">
+      <c r="E665" s="40">
         <v>87</v>
-      </c>
-    </row>
-    <row r="664" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A664" s="72" t="s">
-        <v>462</v>
-      </c>
-      <c r="B664" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C664" s="73">
-        <v>2806</v>
-      </c>
-      <c r="D664" s="74" t="s">
-        <v>160</v>
-      </c>
-      <c r="E664" s="48">
-        <v>472.5</v>
-      </c>
-    </row>
-    <row r="665" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A665" s="72" t="s">
-        <v>462</v>
-      </c>
-      <c r="B665" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C665" s="73">
-        <v>2807</v>
-      </c>
-      <c r="D665" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E665" s="48">
-        <v>159.5</v>
       </c>
     </row>
     <row r="666" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="72" t="s">
-        <v>1321</v>
+        <v>462</v>
       </c>
       <c r="B666" s="72" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="C666" s="73">
-        <v>4556</v>
+        <v>2806</v>
       </c>
       <c r="D666" s="74" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="E666" s="48">
-        <v>900</v>
+        <v>472.5</v>
       </c>
     </row>
     <row r="667" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="72" t="s">
-        <v>1321</v>
+        <v>462</v>
       </c>
       <c r="B667" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C667" s="73">
-        <v>4557</v>
+        <v>2807</v>
       </c>
       <c r="D667" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E667" s="48">
-        <v>182</v>
+        <v>159.5</v>
       </c>
     </row>
     <row r="668" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="72" t="s">
-        <v>400</v>
+        <v>1321</v>
       </c>
       <c r="B668" s="72" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C668" s="73">
-        <v>4018</v>
-      </c>
-      <c r="D668" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E668" s="50">
-        <v>230</v>
+        <v>4556</v>
+      </c>
+      <c r="D668" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="E668" s="48">
+        <v>900</v>
       </c>
     </row>
     <row r="669" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="72" t="s">
-        <v>400</v>
+        <v>1321</v>
       </c>
       <c r="B669" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C669" s="73">
-        <v>2652</v>
-      </c>
-      <c r="D669" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E669" s="50">
-        <v>117</v>
+        <v>4557</v>
+      </c>
+      <c r="D669" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E669" s="48">
+        <v>182</v>
       </c>
     </row>
     <row r="670" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="72" t="s">
-        <v>458</v>
+        <v>400</v>
       </c>
       <c r="B670" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C670" s="73">
-        <v>4049</v>
-      </c>
-      <c r="D670" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E670" s="48">
-        <v>210</v>
+        <v>4018</v>
+      </c>
+      <c r="D670" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E670" s="50">
+        <v>230</v>
       </c>
     </row>
     <row r="671" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="72" t="s">
-        <v>458</v>
+        <v>400</v>
       </c>
       <c r="B671" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C671" s="73">
+        <v>2652</v>
+      </c>
+      <c r="D671" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E671" s="50">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="672" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A672" s="72" t="s">
+        <v>458</v>
+      </c>
+      <c r="B672" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C672" s="73">
+        <v>4049</v>
+      </c>
+      <c r="D672" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E672" s="48">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A673" s="72" t="s">
+        <v>458</v>
+      </c>
+      <c r="B673" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C673" s="73">
         <v>3737</v>
       </c>
-      <c r="D671" s="74" t="s">
+      <c r="D673" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="E671" s="48">
+      <c r="E673" s="48">
         <v>107</v>
       </c>
     </row>
-    <row r="672" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A672" s="69" t="s">
+    <row r="674" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A674" s="69" t="s">
         <v>401</v>
       </c>
-      <c r="B672" s="69" t="s">
+      <c r="B674" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="C672" s="70">
+      <c r="C674" s="70">
         <v>4301</v>
       </c>
-      <c r="D672" s="69" t="s">
+      <c r="D674" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E672" s="40">
+      <c r="E674" s="40">
         <v>235</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A673" s="69" t="s">
+    <row r="675" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A675" s="69" t="s">
         <v>402</v>
-      </c>
-      <c r="B673" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C673" s="70">
-        <v>4334</v>
-      </c>
-      <c r="D673" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="E673" s="40">
-        <v>376.5</v>
-      </c>
-    </row>
-    <row r="674" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A674" s="69" t="s">
-        <v>403</v>
-      </c>
-      <c r="B674" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="C674" s="70">
-        <v>195</v>
-      </c>
-      <c r="D674" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E674" s="40">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="675" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A675" s="69" t="s">
-        <v>403</v>
       </c>
       <c r="B675" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C675" s="70">
-        <v>54</v>
+        <v>4334</v>
       </c>
       <c r="D675" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E675" s="40">
-        <v>53</v>
+        <v>376.5</v>
       </c>
     </row>
     <row r="676" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="69" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B676" s="69" t="s">
         <v>33</v>
       </c>
       <c r="C676" s="70">
-        <v>63</v>
+        <v>195</v>
       </c>
       <c r="D676" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E676" s="40">
-        <v>237.5</v>
+        <v>255</v>
       </c>
     </row>
     <row r="677" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="69" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B677" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C677" s="70">
-        <v>2483</v>
+        <v>54</v>
       </c>
       <c r="D677" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E677" s="40">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="678" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="69" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B678" s="69" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C678" s="70">
-        <v>2974</v>
+        <v>63</v>
       </c>
       <c r="D678" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E678" s="40">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="679" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>237.5</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" s="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="69" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B679" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C679" s="70">
-        <v>2831</v>
+        <v>2483</v>
       </c>
       <c r="D679" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E679" s="40">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="680" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="680" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="69" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B680" s="69" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="C680" s="70">
-        <v>4137</v>
+        <v>2974</v>
       </c>
       <c r="D680" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E680" s="40">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="681" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="69" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B681" s="69" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="C681" s="70">
-        <v>4380</v>
+        <v>2831</v>
       </c>
       <c r="D681" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E681" s="40">
-        <v>270</v>
+        <v>127</v>
       </c>
     </row>
     <row r="682" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="69" t="s">
-        <v>1333</v>
+        <v>406</v>
       </c>
       <c r="B682" s="69" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C682" s="70">
-        <v>4566</v>
+        <v>4137</v>
       </c>
       <c r="D682" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E682" s="40">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="683" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="69" t="s">
-        <v>1334</v>
+        <v>407</v>
       </c>
       <c r="B683" s="69" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C683" s="70">
-        <v>4567</v>
+        <v>4380</v>
       </c>
       <c r="D683" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E683" s="40">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="684" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="69" t="s">
-        <v>408</v>
+        <v>1333</v>
       </c>
       <c r="B684" s="69" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="C684" s="70">
-        <v>4204</v>
+        <v>4566</v>
       </c>
       <c r="D684" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E684" s="40">
-        <v>145.5</v>
-      </c>
-    </row>
-    <row r="685" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="69" t="s">
-        <v>408</v>
+        <v>1334</v>
       </c>
       <c r="B685" s="69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C685" s="70">
-        <v>4205</v>
+        <v>4567</v>
       </c>
       <c r="D685" s="69" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E685" s="40">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="686" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -16940,186 +16947,186 @@
         <v>408</v>
       </c>
       <c r="B686" s="69" t="s">
-        <v>33</v>
+        <v>319</v>
       </c>
       <c r="C686" s="70">
-        <v>4225</v>
+        <v>4204</v>
       </c>
       <c r="D686" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E686" s="40">
-        <v>900</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="687" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="69" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B687" s="69" t="s">
         <v>18</v>
       </c>
       <c r="C687" s="70">
-        <v>4378</v>
+        <v>4205</v>
       </c>
       <c r="D687" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E687" s="40">
-        <v>430</v>
+        <v>360</v>
       </c>
     </row>
     <row r="688" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="69" t="s">
+        <v>408</v>
+      </c>
+      <c r="B688" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="C688" s="70">
+        <v>4225</v>
+      </c>
+      <c r="D688" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E688" s="40">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="689" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A689" s="69" t="s">
         <v>409</v>
       </c>
-      <c r="B688" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="C688" s="70">
-        <v>4379</v>
-      </c>
-      <c r="D688" s="69" t="s">
+      <c r="B689" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C689" s="70">
+        <v>4378</v>
+      </c>
+      <c r="D689" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="E688" s="40">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="689" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A689" s="69" t="s">
-        <v>410</v>
-      </c>
-      <c r="B689" s="69" t="s">
-        <v>411</v>
-      </c>
-      <c r="C689" s="70">
-        <v>3524</v>
-      </c>
-      <c r="D689" s="69" t="s">
-        <v>412</v>
-      </c>
       <c r="E689" s="40">
-        <v>350</v>
+        <v>430</v>
       </c>
     </row>
     <row r="690" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="69" t="s">
+        <v>409</v>
+      </c>
+      <c r="B690" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="C690" s="70">
+        <v>4379</v>
+      </c>
+      <c r="D690" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E690" s="40">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="691" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A691" s="69" t="s">
         <v>410</v>
       </c>
-      <c r="B690" s="69" t="s">
-        <v>110</v>
-      </c>
-      <c r="C690" s="70">
-        <v>3523</v>
-      </c>
-      <c r="D690" s="69" t="s">
+      <c r="B691" s="69" t="s">
+        <v>411</v>
+      </c>
+      <c r="C691" s="70">
+        <v>3524</v>
+      </c>
+      <c r="D691" s="69" t="s">
         <v>412</v>
       </c>
-      <c r="E690" s="40">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="691" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A691" s="69" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B691" s="69" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C691" s="70">
-        <v>3521</v>
-      </c>
-      <c r="D691" s="69" t="s">
-        <v>15</v>
-      </c>
       <c r="E691" s="40">
-        <v>158</v>
+        <v>350</v>
       </c>
     </row>
     <row r="692" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="69" t="s">
+        <v>410</v>
+      </c>
+      <c r="B692" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="C692" s="70">
+        <v>3523</v>
+      </c>
+      <c r="D692" s="69" t="s">
+        <v>412</v>
+      </c>
+      <c r="E692" s="40">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A693" s="69" t="s">
         <v>1162</v>
       </c>
-      <c r="B692" s="69" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C692" s="70">
-        <v>3522</v>
-      </c>
-      <c r="D692" s="69" t="s">
+      <c r="B693" s="69" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C693" s="70">
+        <v>3521</v>
+      </c>
+      <c r="D693" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E692" s="40">
-        <v>216.5</v>
-      </c>
-    </row>
-    <row r="693" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A693" s="72" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B693" s="72" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C693" s="73">
-        <v>64</v>
-      </c>
-      <c r="D693" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="E693" s="50">
-        <v>132</v>
+      <c r="E693" s="40">
+        <v>158</v>
       </c>
     </row>
     <row r="694" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="69" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="B694" s="69" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C694" s="70">
-        <v>90</v>
+        <v>3522</v>
       </c>
       <c r="D694" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E694" s="40">
+        <v>216.5</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A695" s="72" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B695" s="72" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C695" s="73">
+        <v>64</v>
+      </c>
+      <c r="D695" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E695" s="50">
         <v>132</v>
-      </c>
-    </row>
-    <row r="695" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A695" s="69" t="s">
-        <v>413</v>
-      </c>
-      <c r="B695" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="C695" s="70">
-        <v>3637</v>
-      </c>
-      <c r="D695" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="E695" s="40">
-        <v>375</v>
       </c>
     </row>
     <row r="696" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="69" t="s">
-        <v>413</v>
+        <v>1167</v>
       </c>
       <c r="B696" s="69" t="s">
-        <v>18</v>
+        <v>1166</v>
       </c>
       <c r="C696" s="70">
-        <v>2805</v>
+        <v>90</v>
       </c>
       <c r="D696" s="69" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E696" s="40">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="697" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17127,231 +17134,231 @@
         <v>413</v>
       </c>
       <c r="B697" s="69" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="C697" s="70">
-        <v>2427</v>
+        <v>3637</v>
       </c>
       <c r="D697" s="69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E697" s="40">
-        <v>46</v>
+        <v>375</v>
       </c>
     </row>
     <row r="698" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="69" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B698" s="69" t="s">
         <v>18</v>
       </c>
       <c r="C698" s="70">
-        <v>3437</v>
+        <v>2805</v>
       </c>
       <c r="D698" s="69" t="s">
         <v>34</v>
       </c>
       <c r="E698" s="40">
-        <v>390</v>
+        <v>150</v>
       </c>
     </row>
     <row r="699" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="69" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B699" s="69" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C699" s="70">
-        <v>3396</v>
+        <v>2427</v>
       </c>
       <c r="D699" s="69" t="s">
         <v>20</v>
       </c>
       <c r="E699" s="40">
-        <v>197</v>
+        <v>46</v>
       </c>
     </row>
     <row r="700" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="69" t="s">
-        <v>1168</v>
+        <v>414</v>
       </c>
       <c r="B700" s="69" t="s">
-        <v>1169</v>
+        <v>18</v>
       </c>
       <c r="C700" s="70">
-        <v>3395</v>
+        <v>3437</v>
       </c>
       <c r="D700" s="69" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E700" s="40">
-        <v>54</v>
+        <v>390</v>
       </c>
     </row>
     <row r="701" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="69" t="s">
-        <v>1170</v>
+        <v>414</v>
       </c>
       <c r="B701" s="69" t="s">
-        <v>1169</v>
+        <v>19</v>
       </c>
       <c r="C701" s="70">
-        <v>3490</v>
+        <v>3396</v>
       </c>
       <c r="D701" s="69" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E701" s="40">
-        <v>169</v>
+        <v>197</v>
       </c>
     </row>
     <row r="702" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="69" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="B702" s="69" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="C702" s="70">
-        <v>458</v>
+        <v>3395</v>
       </c>
       <c r="D702" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E702" s="40">
-        <v>269.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="703" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="69" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="B703" s="69" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="C703" s="70">
-        <v>2641</v>
+        <v>3490</v>
       </c>
       <c r="D703" s="69" t="s">
         <v>15</v>
       </c>
       <c r="E703" s="40">
-        <v>222</v>
+        <v>169</v>
       </c>
     </row>
     <row r="704" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A704" s="75" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B704" s="75" t="s">
+      <c r="A704" s="69" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B704" s="69" t="s">
         <v>1172</v>
       </c>
-      <c r="C704" s="76">
-        <v>4293</v>
+      <c r="C704" s="70">
+        <v>458</v>
       </c>
       <c r="D704" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E704" s="44">
+      <c r="E704" s="40">
+        <v>269.5</v>
+      </c>
+    </row>
+    <row r="705" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A705" s="69" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B705" s="69" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C705" s="70">
+        <v>2641</v>
+      </c>
+      <c r="D705" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E705" s="40">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="706" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A706" s="75" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B706" s="75" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C706" s="76">
+        <v>4293</v>
+      </c>
+      <c r="D706" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E706" s="44">
         <v>210</v>
       </c>
     </row>
-    <row r="705" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A705" s="75" t="s">
+    <row r="707" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A707" s="75" t="s">
         <v>415</v>
       </c>
-      <c r="B705" s="75" t="s">
+      <c r="B707" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C705" s="76">
+      <c r="C707" s="76">
         <v>2396</v>
       </c>
-      <c r="D705" s="75" t="s">
+      <c r="D707" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="E705" s="44">
+      <c r="E707" s="44">
         <v>675</v>
-      </c>
-    </row>
-    <row r="706" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A706" s="80" t="s">
-        <v>415</v>
-      </c>
-      <c r="B706" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C706" s="81">
-        <v>2426</v>
-      </c>
-      <c r="D706" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="E706" s="42">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="707" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A707" s="80" t="s">
-        <v>416</v>
-      </c>
-      <c r="B707" s="80" t="s">
-        <v>110</v>
-      </c>
-      <c r="C707" s="81">
-        <v>4335</v>
-      </c>
-      <c r="D707" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="E707" s="42">
-        <v>424.5</v>
       </c>
     </row>
     <row r="708" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="80" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B708" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C708" s="81">
-        <v>4477</v>
+        <v>2426</v>
       </c>
       <c r="D708" s="80" t="s">
         <v>20</v>
       </c>
       <c r="E708" s="42">
-        <v>244.5</v>
+        <v>137</v>
       </c>
     </row>
     <row r="709" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="80" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B709" s="80" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="C709" s="81">
-        <v>4479</v>
+        <v>4335</v>
       </c>
       <c r="D709" s="80" t="s">
         <v>20</v>
       </c>
       <c r="E709" s="42">
-        <v>244.5</v>
+        <v>424.5</v>
       </c>
     </row>
     <row r="710" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="80" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B710" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C710" s="81">
-        <v>4478</v>
+        <v>4477</v>
       </c>
       <c r="D710" s="80" t="s">
         <v>20</v>
@@ -17361,37 +17368,37 @@
       </c>
     </row>
     <row r="711" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A711" s="72" t="s">
-        <v>1263</v>
-      </c>
-      <c r="B711" s="72" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C711" s="73">
-        <v>2646</v>
-      </c>
-      <c r="D711" s="72" t="s">
-        <v>177</v>
-      </c>
-      <c r="E711" s="50">
-        <v>50.5</v>
+      <c r="A711" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="B711" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C711" s="81">
+        <v>4479</v>
+      </c>
+      <c r="D711" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E711" s="42">
+        <v>244.5</v>
       </c>
     </row>
     <row r="712" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A712" s="72" t="s">
-        <v>1263</v>
-      </c>
-      <c r="B712" s="72" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C712" s="73">
-        <v>2645</v>
-      </c>
-      <c r="D712" s="72" t="s">
-        <v>177</v>
-      </c>
-      <c r="E712" s="50">
-        <v>78</v>
+      <c r="A712" s="80" t="s">
+        <v>419</v>
+      </c>
+      <c r="B712" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C712" s="81">
+        <v>4478</v>
+      </c>
+      <c r="D712" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E712" s="42">
+        <v>244.5</v>
       </c>
     </row>
     <row r="713" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17399,318 +17406,318 @@
         <v>1263</v>
       </c>
       <c r="B713" s="72" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C713" s="73">
-        <v>2638</v>
+        <v>2646</v>
       </c>
       <c r="D713" s="72" t="s">
         <v>177</v>
       </c>
       <c r="E713" s="50">
-        <v>65</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="714" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="72" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="B714" s="72" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="C714" s="73">
-        <v>4294</v>
+        <v>2645</v>
       </c>
       <c r="D714" s="72" t="s">
         <v>177</v>
       </c>
       <c r="E714" s="50">
-        <v>150</v>
+        <v>78</v>
       </c>
     </row>
     <row r="715" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="72" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="B715" s="72" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="C715" s="73">
-        <v>4314</v>
+        <v>2638</v>
       </c>
       <c r="D715" s="72" t="s">
-        <v>15</v>
+        <v>177</v>
       </c>
       <c r="E715" s="50">
-        <v>252</v>
+        <v>65</v>
       </c>
     </row>
     <row r="716" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="72" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B716" s="72" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C716" s="73">
+        <v>4294</v>
+      </c>
+      <c r="D716" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="E716" s="50">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="717" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A717" s="72" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B717" s="72" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C717" s="73">
+        <v>4314</v>
+      </c>
+      <c r="D717" s="72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E717" s="50">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="718" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A718" s="72" t="s">
         <v>1271</v>
       </c>
-      <c r="B716" s="72" t="s">
+      <c r="B718" s="72" t="s">
         <v>1272</v>
       </c>
-      <c r="C716" s="73">
+      <c r="C718" s="73">
         <v>4315</v>
       </c>
-      <c r="D716" s="72" t="s">
+      <c r="D718" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="E716" s="50">
+      <c r="E718" s="50">
         <v>450</v>
       </c>
     </row>
-    <row r="717" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A717" s="116"/>
-      <c r="B717" s="109"/>
-      <c r="C717" s="109"/>
-      <c r="D717" s="110"/>
-      <c r="E717" s="117"/>
-    </row>
-    <row r="718" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A718" s="118" t="s">
+    <row r="719" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A719" s="116"/>
+      <c r="B719" s="109"/>
+      <c r="C719" s="109"/>
+      <c r="D719" s="110"/>
+      <c r="E719" s="117"/>
+    </row>
+    <row r="720" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A720" s="118" t="s">
         <v>420</v>
       </c>
-      <c r="B718" s="119"/>
-      <c r="C718" s="119"/>
-      <c r="D718" s="119"/>
-      <c r="E718" s="120"/>
-    </row>
-    <row r="719" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A719" s="66" t="s">
+      <c r="B720" s="119"/>
+      <c r="C720" s="119"/>
+      <c r="D720" s="119"/>
+      <c r="E720" s="120"/>
+    </row>
+    <row r="721" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A721" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B719" s="66"/>
-      <c r="C719" s="66" t="s">
+      <c r="B721" s="66"/>
+      <c r="C721" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D719" s="66" t="s">
+      <c r="D721" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E719" s="46" t="s">
+      <c r="E721" s="46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="720" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A720" s="69" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B720" s="69" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C720" s="70">
-        <v>3402</v>
-      </c>
-      <c r="D720" s="69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E720" s="40">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="721" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A721" s="69" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B721" s="69" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C721" s="70">
-        <v>3401</v>
-      </c>
-      <c r="D721" s="69" t="s">
-        <v>177</v>
-      </c>
-      <c r="E721" s="40">
-        <v>66.5</v>
-      </c>
-    </row>
-    <row r="722" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="69" t="s">
         <v>1176</v>
       </c>
       <c r="B722" s="69" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C722" s="70">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="D722" s="69" t="s">
         <v>177</v>
       </c>
       <c r="E722" s="40">
-        <v>38.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="723" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="69" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="B723" s="69" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="C723" s="70">
-        <v>4032</v>
+        <v>3401</v>
       </c>
       <c r="D723" s="69" t="s">
         <v>177</v>
       </c>
       <c r="E723" s="40">
-        <v>57.5</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="724" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A724" s="69" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B724" s="75" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C724" s="76">
-        <v>4460</v>
+        <v>1176</v>
+      </c>
+      <c r="B724" s="69" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C724" s="70">
+        <v>3403</v>
       </c>
       <c r="D724" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="E724" s="44">
+      <c r="E724" s="40">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="725" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A725" s="69" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B725" s="69" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C725" s="70">
+        <v>4032</v>
+      </c>
+      <c r="D725" s="69" t="s">
+        <v>177</v>
+      </c>
+      <c r="E725" s="40">
         <v>57.5</v>
       </c>
     </row>
-    <row r="725" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A725" s="75" t="s">
+    <row r="726" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A726" s="69" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B726" s="75" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C726" s="76">
+        <v>4460</v>
+      </c>
+      <c r="D726" s="69" t="s">
+        <v>177</v>
+      </c>
+      <c r="E726" s="44">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="727" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A727" s="75" t="s">
         <v>1183</v>
       </c>
-      <c r="B725" s="75" t="s">
+      <c r="B727" s="75" t="s">
         <v>1184</v>
       </c>
-      <c r="C725" s="76">
+      <c r="C727" s="76">
         <v>4260</v>
       </c>
-      <c r="D725" s="75" t="s">
+      <c r="D727" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="E725" s="44">
+      <c r="E727" s="44">
         <v>58</v>
       </c>
     </row>
-    <row r="726" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A726" s="75" t="s">
+    <row r="728" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A728" s="75" t="s">
         <v>1185</v>
       </c>
-      <c r="B726" s="75" t="s">
+      <c r="B728" s="75" t="s">
         <v>1186</v>
       </c>
-      <c r="C726" s="76">
+      <c r="C728" s="76">
         <v>2551</v>
       </c>
-      <c r="D726" s="75" t="s">
+      <c r="D728" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="E726" s="44">
+      <c r="E728" s="44">
         <v>82</v>
       </c>
     </row>
-    <row r="727" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A727" s="80" t="s">
+    <row r="729" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A729" s="80" t="s">
         <v>1187</v>
       </c>
-      <c r="B727" s="80" t="s">
+      <c r="B729" s="80" t="s">
         <v>1188</v>
       </c>
-      <c r="C727" s="81">
+      <c r="C729" s="81">
         <v>2550</v>
       </c>
-      <c r="D727" s="80" t="s">
+      <c r="D729" s="80" t="s">
         <v>177</v>
       </c>
-      <c r="E727" s="42">
+      <c r="E729" s="42">
         <v>25.5</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A728" s="80" t="s">
+    <row r="730" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A730" s="80" t="s">
         <v>1189</v>
       </c>
-      <c r="B728" s="80" t="s">
+      <c r="B730" s="80" t="s">
         <v>1190</v>
       </c>
-      <c r="C728" s="81">
+      <c r="C730" s="81">
         <v>4383</v>
       </c>
-      <c r="D728" s="80" t="s">
+      <c r="D730" s="80" t="s">
         <v>177</v>
       </c>
-      <c r="E728" s="42">
+      <c r="E730" s="42">
         <v>53</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A729" s="85"/>
-      <c r="B729" s="85"/>
-      <c r="C729" s="86"/>
-      <c r="D729" s="85"/>
-      <c r="E729" s="61"/>
-    </row>
-    <row r="730" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A730" s="118" t="s">
+    <row r="731" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A731" s="85"/>
+      <c r="B731" s="85"/>
+      <c r="C731" s="86"/>
+      <c r="D731" s="85"/>
+      <c r="E731" s="61"/>
+    </row>
+    <row r="732" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A732" s="118" t="s">
         <v>1303</v>
       </c>
-      <c r="B730" s="119"/>
-      <c r="C730" s="119"/>
-      <c r="D730" s="119"/>
-      <c r="E730" s="120"/>
-    </row>
-    <row r="731" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A731" s="72" t="s">
-        <v>1283</v>
-      </c>
-      <c r="B731" s="72" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C731" s="73">
-        <v>3642</v>
-      </c>
-      <c r="D731" s="74" t="s">
-        <v>160</v>
-      </c>
-      <c r="E731" s="48">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="732" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A732" s="72" t="s">
-        <v>1283</v>
-      </c>
-      <c r="B732" s="72" t="s">
-        <v>1285</v>
-      </c>
-      <c r="C732" s="73">
-        <v>3644</v>
-      </c>
-      <c r="D732" s="74" t="s">
-        <v>160</v>
-      </c>
-      <c r="E732" s="49">
-        <v>84</v>
-      </c>
+      <c r="B732" s="119"/>
+      <c r="C732" s="119"/>
+      <c r="D732" s="119"/>
+      <c r="E732" s="120"/>
     </row>
     <row r="733" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A733" s="72" t="s">
         <v>1283</v>
       </c>
       <c r="B733" s="72" t="s">
-        <v>1250</v>
+        <v>1284</v>
       </c>
       <c r="C733" s="73">
-        <v>3641</v>
+        <v>3642</v>
       </c>
       <c r="D733" s="74" t="s">
         <v>160</v>
       </c>
       <c r="E733" s="48">
-        <v>84</v>
+        <v>162</v>
       </c>
     </row>
     <row r="734" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -17718,149 +17725,149 @@
         <v>1283</v>
       </c>
       <c r="B734" s="72" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C734" s="73">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="D734" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="E734" s="48">
-        <v>162</v>
+      <c r="E734" s="49">
+        <v>84</v>
       </c>
     </row>
     <row r="735" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A735" s="72" t="s">
-        <v>1249</v>
+        <v>1283</v>
       </c>
       <c r="B735" s="72" t="s">
-        <v>1172</v>
+        <v>1250</v>
       </c>
       <c r="C735" s="73">
-        <v>3852</v>
+        <v>3641</v>
       </c>
       <c r="D735" s="74" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E735" s="48">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="736" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="72" t="s">
-        <v>1249</v>
+        <v>1283</v>
       </c>
       <c r="B736" s="72" t="s">
-        <v>1250</v>
+        <v>1286</v>
       </c>
       <c r="C736" s="73">
-        <v>3647</v>
+        <v>3645</v>
       </c>
       <c r="D736" s="74" t="s">
         <v>160</v>
       </c>
       <c r="E736" s="48">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="737" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="737" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A737" s="72" t="s">
         <v>1249</v>
       </c>
       <c r="B737" s="72" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C737" s="73">
+        <v>3852</v>
+      </c>
+      <c r="D737" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E737" s="48">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="738" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A738" s="72" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B738" s="72" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C738" s="73">
+        <v>3647</v>
+      </c>
+      <c r="D738" s="74" t="s">
+        <v>160</v>
+      </c>
+      <c r="E738" s="48">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="739" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A739" s="72" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B739" s="72" t="s">
         <v>1251</v>
       </c>
-      <c r="C737" s="73">
+      <c r="C739" s="73">
         <v>3648</v>
       </c>
-      <c r="D737" s="74" t="s">
+      <c r="D739" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="E737" s="48">
+      <c r="E739" s="48">
         <v>33</v>
       </c>
     </row>
-    <row r="738" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A738" s="121"/>
-      <c r="B738" s="109"/>
-      <c r="C738" s="109"/>
-      <c r="D738" s="110"/>
-      <c r="E738" s="117"/>
-    </row>
-    <row r="739" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A739" s="118" t="s">
+    <row r="740" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A740" s="121"/>
+      <c r="B740" s="109"/>
+      <c r="C740" s="109"/>
+      <c r="D740" s="110"/>
+      <c r="E740" s="117"/>
+    </row>
+    <row r="741" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A741" s="118" t="s">
         <v>421</v>
       </c>
-      <c r="B739" s="119"/>
-      <c r="C739" s="119"/>
-      <c r="D739" s="119"/>
-      <c r="E739" s="120"/>
-    </row>
-    <row r="740" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A740" s="66" t="s">
+      <c r="B741" s="119"/>
+      <c r="C741" s="119"/>
+      <c r="D741" s="119"/>
+      <c r="E741" s="120"/>
+    </row>
+    <row r="742" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A742" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B740" s="66"/>
-      <c r="C740" s="66" t="s">
+      <c r="B742" s="66"/>
+      <c r="C742" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D740" s="66" t="s">
+      <c r="D742" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E740" s="46" t="s">
+      <c r="E742" s="46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="741" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A741" s="69" t="s">
+    <row r="743" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A743" s="69" t="s">
         <v>1191</v>
-      </c>
-      <c r="B741" s="69" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C741" s="70">
-        <v>3056</v>
-      </c>
-      <c r="D741" s="69" t="s">
-        <v>160</v>
-      </c>
-      <c r="E741" s="40">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="742" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A742" s="69" t="s">
-        <v>1191</v>
-      </c>
-      <c r="B742" s="69" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C742" s="70">
-        <v>3083</v>
-      </c>
-      <c r="D742" s="69" t="s">
-        <v>160</v>
-      </c>
-      <c r="E742" s="40">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="743" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A743" s="69" t="s">
-        <v>1192</v>
       </c>
       <c r="B743" s="69" t="s">
         <v>1130</v>
       </c>
       <c r="C743" s="70">
-        <v>2264</v>
+        <v>3056</v>
       </c>
       <c r="D743" s="69" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E743" s="40">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="744" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -17871,174 +17878,174 @@
         <v>1137</v>
       </c>
       <c r="C744" s="70">
+        <v>3083</v>
+      </c>
+      <c r="D744" s="69" t="s">
+        <v>160</v>
+      </c>
+      <c r="E744" s="40">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="745" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A745" s="69" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B745" s="69" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C745" s="70">
+        <v>2264</v>
+      </c>
+      <c r="D745" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E745" s="40">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="746" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A746" s="69" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B746" s="69" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C746" s="70">
         <v>2355</v>
       </c>
-      <c r="D744" s="69" t="s">
+      <c r="D746" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E744" s="40">
+      <c r="E746" s="40">
         <v>59</v>
       </c>
     </row>
-    <row r="745" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A745" s="75" t="s">
+    <row r="747" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A747" s="75" t="s">
         <v>1193</v>
       </c>
-      <c r="B745" s="75" t="s">
+      <c r="B747" s="75" t="s">
         <v>1130</v>
       </c>
-      <c r="C745" s="76">
+      <c r="C747" s="76">
         <v>573</v>
       </c>
-      <c r="D745" s="75" t="s">
+      <c r="D747" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="E745" s="44">
+      <c r="E747" s="44">
         <v>59</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A746" s="80" t="s">
+    <row r="748" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A748" s="80" t="s">
         <v>1194</v>
       </c>
-      <c r="B746" s="80" t="s">
+      <c r="B748" s="80" t="s">
         <v>1195</v>
       </c>
-      <c r="C746" s="81">
+      <c r="C748" s="81">
         <v>572</v>
       </c>
-      <c r="D746" s="80" t="s">
+      <c r="D748" s="80" t="s">
         <v>177</v>
       </c>
-      <c r="E746" s="42">
+      <c r="E748" s="42">
         <v>60</v>
       </c>
     </row>
-    <row r="747" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A747" s="65" t="s">
+    <row r="749" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A749" s="65" t="s">
         <v>1196</v>
       </c>
-      <c r="B747" s="65" t="s">
+      <c r="B749" s="65" t="s">
         <v>1154</v>
       </c>
-      <c r="C747" s="81">
+      <c r="C749" s="81">
         <v>4411</v>
       </c>
-      <c r="D747" s="80" t="s">
+      <c r="D749" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="E747" s="42">
+      <c r="E749" s="42">
         <v>93</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A748" s="65" t="s">
+    <row r="750" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A750" s="65" t="s">
         <v>1197</v>
       </c>
-      <c r="B748" s="65" t="s">
+      <c r="B750" s="65" t="s">
         <v>1198</v>
       </c>
-      <c r="C748" s="81">
+      <c r="C750" s="81">
         <v>4410</v>
       </c>
-      <c r="D748" s="80" t="s">
+      <c r="D750" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="E748" s="42">
+      <c r="E750" s="42">
         <v>95</v>
       </c>
     </row>
-    <row r="749" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A749" s="121"/>
-      <c r="B749" s="109"/>
-      <c r="C749" s="109"/>
-      <c r="D749" s="110"/>
-      <c r="E749" s="117"/>
-    </row>
-    <row r="750" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A750" s="118" t="s">
+    <row r="751" spans="1:5" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A751" s="121"/>
+      <c r="B751" s="109"/>
+      <c r="C751" s="109"/>
+      <c r="D751" s="110"/>
+      <c r="E751" s="117"/>
+    </row>
+    <row r="752" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A752" s="118" t="s">
         <v>1301</v>
       </c>
-      <c r="B750" s="119"/>
-      <c r="C750" s="119"/>
-      <c r="D750" s="119"/>
-      <c r="E750" s="120"/>
-    </row>
-    <row r="751" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A751" s="66" t="s">
+      <c r="B752" s="119"/>
+      <c r="C752" s="119"/>
+      <c r="D752" s="119"/>
+      <c r="E752" s="120"/>
+    </row>
+    <row r="753" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A753" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B751" s="66"/>
-      <c r="C751" s="66" t="s">
+      <c r="B753" s="66"/>
+      <c r="C753" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D751" s="66" t="s">
+      <c r="D753" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E751" s="47" t="s">
+      <c r="E753" s="47" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="752" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A752" s="82" t="s">
+    <row r="754" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A754" s="82" t="s">
         <v>1328</v>
       </c>
-      <c r="B752" s="82" t="s">
+      <c r="B754" s="82" t="s">
         <v>1329</v>
       </c>
-      <c r="C752" s="82">
+      <c r="C754" s="82">
         <v>4044</v>
       </c>
-      <c r="D752" s="101" t="s">
+      <c r="D754" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E752" s="61">
+      <c r="E754" s="61">
         <v>22</v>
-      </c>
-    </row>
-    <row r="753" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A753" s="72" t="s">
-        <v>439</v>
-      </c>
-      <c r="B753" s="72" t="s">
-        <v>145</v>
-      </c>
-      <c r="C753" s="73">
-        <v>4043</v>
-      </c>
-      <c r="D753" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E753" s="48">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="754" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A754" s="72" t="s">
-        <v>440</v>
-      </c>
-      <c r="B754" s="72" t="s">
-        <v>145</v>
-      </c>
-      <c r="C754" s="73">
-        <v>3531</v>
-      </c>
-      <c r="D754" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E754" s="48">
-        <v>63</v>
       </c>
     </row>
     <row r="755" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="72" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B755" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C755" s="73">
-        <v>3974</v>
+        <v>4043</v>
       </c>
       <c r="D755" s="74" t="s">
         <v>20</v>
@@ -18047,15 +18054,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="756" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="72" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B756" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C756" s="73">
-        <v>3530</v>
+        <v>3531</v>
       </c>
       <c r="D756" s="74" t="s">
         <v>20</v>
@@ -18064,66 +18071,66 @@
         <v>63</v>
       </c>
     </row>
-    <row r="757" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="72" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B757" s="72" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="C757" s="73">
-        <v>4282</v>
+        <v>3974</v>
       </c>
       <c r="D757" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E757" s="48">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="758" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="72" t="s">
-        <v>1207</v>
+        <v>442</v>
       </c>
       <c r="B758" s="72" t="s">
-        <v>1206</v>
+        <v>145</v>
       </c>
       <c r="C758" s="73">
-        <v>3870</v>
+        <v>3530</v>
       </c>
       <c r="D758" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E758" s="48">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="759" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="72" t="s">
-        <v>1208</v>
+        <v>443</v>
       </c>
       <c r="B759" s="72" t="s">
-        <v>1206</v>
+        <v>78</v>
       </c>
       <c r="C759" s="73">
-        <v>3701</v>
+        <v>4282</v>
       </c>
       <c r="D759" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E759" s="48">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="760" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="72" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B760" s="72" t="s">
         <v>1206</v>
       </c>
       <c r="C760" s="73">
-        <v>3800</v>
+        <v>3870</v>
       </c>
       <c r="D760" s="74" t="s">
         <v>20</v>
@@ -18132,97 +18139,83 @@
         <v>22</v>
       </c>
     </row>
-    <row r="761" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A761" s="72" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B761" s="72" t="s">
         <v>1206</v>
       </c>
       <c r="C761" s="73">
-        <v>3725</v>
+        <v>3701</v>
       </c>
       <c r="D761" s="74" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E761" s="48">
         <v>22</v>
       </c>
     </row>
-    <row r="762" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A762" s="72" t="s">
-        <v>1235</v>
+        <v>1209</v>
       </c>
       <c r="B762" s="72" t="s">
         <v>1206</v>
       </c>
       <c r="C762" s="73">
-        <v>3871</v>
+        <v>3800</v>
       </c>
       <c r="D762" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E762" s="48">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="763" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="763" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="72" t="s">
-        <v>463</v>
+        <v>1210</v>
       </c>
       <c r="B763" s="72" t="s">
-        <v>145</v>
+        <v>1206</v>
       </c>
       <c r="C763" s="73">
-        <v>2825</v>
+        <v>3725</v>
       </c>
       <c r="D763" s="74" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E763" s="48">
-        <v>23.5</v>
-      </c>
-      <c r="F763" s="54"/>
-      <c r="G763" s="54"/>
-      <c r="I763" s="57"/>
-      <c r="J763" s="58"/>
-      <c r="K763" s="60"/>
-      <c r="L763" s="59"/>
-      <c r="M763" s="59"/>
-      <c r="N763" s="59"/>
-      <c r="O763" s="59"/>
-      <c r="P763" s="59"/>
-      <c r="Q763" s="59"/>
-      <c r="R763" s="58"/>
-    </row>
-    <row r="764" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="764" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A764" s="72" t="s">
-        <v>464</v>
+        <v>1235</v>
       </c>
       <c r="B764" s="72" t="s">
-        <v>145</v>
+        <v>1206</v>
       </c>
       <c r="C764" s="73">
-        <v>2828</v>
+        <v>3871</v>
       </c>
       <c r="D764" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E764" s="48">
-        <v>23.5</v>
-      </c>
-      <c r="G764" s="55"/>
-      <c r="H764" s="56"/>
+        <v>27</v>
+      </c>
     </row>
     <row r="765" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="72" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B765" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C765" s="73">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="D765" s="74" t="s">
         <v>20</v>
@@ -18230,16 +18223,28 @@
       <c r="E765" s="48">
         <v>23.5</v>
       </c>
+      <c r="F765" s="54"/>
+      <c r="G765" s="54"/>
+      <c r="I765" s="57"/>
+      <c r="J765" s="58"/>
+      <c r="K765" s="60"/>
+      <c r="L765" s="59"/>
+      <c r="M765" s="59"/>
+      <c r="N765" s="59"/>
+      <c r="O765" s="59"/>
+      <c r="P765" s="59"/>
+      <c r="Q765" s="59"/>
+      <c r="R765" s="58"/>
     </row>
     <row r="766" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="72" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B766" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C766" s="73">
-        <v>3058</v>
+        <v>2828</v>
       </c>
       <c r="D766" s="74" t="s">
         <v>20</v>
@@ -18247,16 +18252,18 @@
       <c r="E766" s="48">
         <v>23.5</v>
       </c>
+      <c r="G766" s="55"/>
+      <c r="H766" s="56"/>
     </row>
     <row r="767" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="72" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B767" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C767" s="73">
-        <v>3059</v>
+        <v>2826</v>
       </c>
       <c r="D767" s="74" t="s">
         <v>20</v>
@@ -18267,13 +18274,13 @@
     </row>
     <row r="768" spans="1:18" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="72" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B768" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C768" s="73">
-        <v>2829</v>
+        <v>3058</v>
       </c>
       <c r="D768" s="74" t="s">
         <v>20</v>
@@ -18284,13 +18291,13 @@
     </row>
     <row r="769" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="72" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B769" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C769" s="73">
-        <v>4126</v>
+        <v>3059</v>
       </c>
       <c r="D769" s="74" t="s">
         <v>20</v>
@@ -18301,13 +18308,13 @@
     </row>
     <row r="770" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="72" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B770" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C770" s="73">
-        <v>2827</v>
+        <v>2829</v>
       </c>
       <c r="D770" s="74" t="s">
         <v>20</v>
@@ -18318,148 +18325,148 @@
     </row>
     <row r="771" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="72" t="s">
-        <v>1252</v>
+        <v>469</v>
       </c>
       <c r="B771" s="72" t="s">
-        <v>1206</v>
+        <v>145</v>
       </c>
       <c r="C771" s="73">
-        <v>3801</v>
+        <v>4126</v>
       </c>
       <c r="D771" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E771" s="48">
-        <v>25</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="772" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="72" t="s">
-        <v>1253</v>
+        <v>470</v>
       </c>
       <c r="B772" s="72" t="s">
-        <v>1206</v>
+        <v>145</v>
       </c>
       <c r="C772" s="73">
-        <v>3833</v>
+        <v>2827</v>
       </c>
       <c r="D772" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E772" s="48">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="773" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A773" s="72" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B773" s="72" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C773" s="73">
+        <v>3801</v>
+      </c>
+      <c r="D773" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E773" s="48">
         <v>25</v>
-      </c>
-    </row>
-    <row r="773" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A773" s="72" t="s">
-        <v>474</v>
-      </c>
-      <c r="B773" s="72" t="s">
-        <v>145</v>
-      </c>
-      <c r="C773" s="73">
-        <v>3897</v>
-      </c>
-      <c r="D773" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="E773" s="48">
-        <v>60</v>
       </c>
     </row>
     <row r="774" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="72" t="s">
-        <v>475</v>
+        <v>1253</v>
       </c>
       <c r="B774" s="72" t="s">
-        <v>145</v>
+        <v>1206</v>
       </c>
       <c r="C774" s="73">
-        <v>3764</v>
+        <v>3833</v>
       </c>
       <c r="D774" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E774" s="48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="775" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A775" s="72" t="s">
+        <v>474</v>
+      </c>
+      <c r="B775" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C775" s="73">
+        <v>3897</v>
+      </c>
+      <c r="D775" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="E775" s="48">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="776" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A776" s="72" t="s">
+        <v>475</v>
+      </c>
+      <c r="B776" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C776" s="73">
+        <v>3764</v>
+      </c>
+      <c r="D776" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E776" s="48">
         <v>78</v>
       </c>
     </row>
-    <row r="775" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A775" s="96"/>
-      <c r="B775" s="96"/>
-      <c r="C775" s="97"/>
-      <c r="D775" s="96"/>
-      <c r="E775" s="98"/>
-    </row>
-    <row r="776" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A776" s="130" t="s">
+    <row r="777" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A777" s="96"/>
+      <c r="B777" s="96"/>
+      <c r="C777" s="97"/>
+      <c r="D777" s="96"/>
+      <c r="E777" s="98"/>
+    </row>
+    <row r="778" spans="1:5" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A778" s="130" t="s">
         <v>1287</v>
       </c>
-      <c r="B776" s="131"/>
-      <c r="C776" s="131"/>
-      <c r="D776" s="131"/>
-      <c r="E776" s="132"/>
-    </row>
-    <row r="777" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A777" s="66" t="s">
+      <c r="B778" s="131"/>
+      <c r="C778" s="131"/>
+      <c r="D778" s="131"/>
+      <c r="E778" s="132"/>
+    </row>
+    <row r="779" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A779" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B777" s="66" t="s">
+      <c r="B779" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="C777" s="66" t="s">
+      <c r="C779" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="D777" s="66" t="s">
+      <c r="D779" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="E777" s="47" t="s">
+      <c r="E779" s="47" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="778" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A778" s="72" t="s">
-        <v>425</v>
-      </c>
-      <c r="B778" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C778" s="73">
-        <v>3438</v>
-      </c>
-      <c r="D778" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E778" s="48">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="779" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A779" s="72" t="s">
-        <v>425</v>
-      </c>
-      <c r="B779" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C779" s="73">
-        <v>3434</v>
-      </c>
-      <c r="D779" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E779" s="48">
-        <v>76</v>
       </c>
     </row>
     <row r="780" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A780" s="72" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B780" s="72" t="s">
         <v>120</v>
       </c>
       <c r="C780" s="73">
-        <v>3443</v>
+        <v>3438</v>
       </c>
       <c r="D780" s="74" t="s">
         <v>15</v>
@@ -18470,13 +18477,13 @@
     </row>
     <row r="781" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="72" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B781" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C781" s="73">
-        <v>3019</v>
+        <v>3434</v>
       </c>
       <c r="D781" s="74" t="s">
         <v>20</v>
@@ -18487,13 +18494,13 @@
     </row>
     <row r="782" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="72" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B782" s="72" t="s">
         <v>120</v>
       </c>
       <c r="C782" s="73">
-        <v>4489</v>
+        <v>3443</v>
       </c>
       <c r="D782" s="74" t="s">
         <v>15</v>
@@ -18502,15 +18509,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="783" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A783" s="72" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B783" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C783" s="73">
-        <v>4490</v>
+        <v>3019</v>
       </c>
       <c r="D783" s="74" t="s">
         <v>20</v>
@@ -18521,13 +18528,13 @@
     </row>
     <row r="784" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A784" s="72" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B784" s="72" t="s">
         <v>120</v>
       </c>
       <c r="C784" s="73">
-        <v>3476</v>
+        <v>4489</v>
       </c>
       <c r="D784" s="74" t="s">
         <v>15</v>
@@ -18536,15 +18543,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="785" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A785" s="72" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B785" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C785" s="73">
-        <v>3477</v>
+        <v>4490</v>
       </c>
       <c r="D785" s="74" t="s">
         <v>20</v>
@@ -18553,100 +18560,100 @@
         <v>76</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A786" s="72" t="s">
-        <v>1312</v>
+        <v>428</v>
       </c>
       <c r="B786" s="72" t="s">
-        <v>1154</v>
+        <v>120</v>
       </c>
       <c r="C786" s="73">
-        <v>4344</v>
+        <v>3476</v>
       </c>
       <c r="D786" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E786" s="48">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="787" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A787" s="72" t="s">
+        <v>428</v>
+      </c>
+      <c r="B787" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C787" s="73">
+        <v>3477</v>
+      </c>
+      <c r="D787" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E787" s="48">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="788" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A788" s="72" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B788" s="72" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C788" s="73">
+        <v>4344</v>
+      </c>
+      <c r="D788" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E788" s="48">
         <v>328</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A787" s="72" t="s">
+    <row r="789" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A789" s="72" t="s">
         <v>429</v>
-      </c>
-      <c r="B787" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="C787" s="73">
-        <v>3123</v>
-      </c>
-      <c r="D787" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E787" s="48">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="788" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A788" s="72" t="s">
-        <v>429</v>
-      </c>
-      <c r="B788" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C788" s="73">
-        <v>2674</v>
-      </c>
-      <c r="D788" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E788" s="48">
-        <v>60.5</v>
-      </c>
-    </row>
-    <row r="789" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A789" s="72" t="s">
-        <v>430</v>
       </c>
       <c r="B789" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C789" s="73">
-        <v>3719</v>
+        <v>3123</v>
       </c>
       <c r="D789" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E789" s="48">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="790" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="72" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B790" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C790" s="73">
-        <v>3720</v>
+        <v>2674</v>
       </c>
       <c r="D790" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E790" s="48">
-        <v>69</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="791" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A791" s="72" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B791" s="72" t="s">
-        <v>1124</v>
+        <v>18</v>
       </c>
       <c r="C791" s="73">
-        <v>3765</v>
+        <v>3719</v>
       </c>
       <c r="D791" s="74" t="s">
         <v>15</v>
@@ -18657,13 +18664,13 @@
     </row>
     <row r="792" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="72" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B792" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C792" s="73">
-        <v>3766</v>
+        <v>3720</v>
       </c>
       <c r="D792" s="74" t="s">
         <v>15</v>
@@ -18674,47 +18681,47 @@
     </row>
     <row r="793" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B793" s="72" t="s">
-        <v>18</v>
+        <v>1124</v>
       </c>
       <c r="C793" s="73">
-        <v>3126</v>
+        <v>3765</v>
       </c>
       <c r="D793" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E793" s="48">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="794" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="794" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B794" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C794" s="73">
-        <v>3127</v>
+        <v>3766</v>
       </c>
       <c r="D794" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E794" s="48">
-        <v>60.5</v>
-      </c>
-    </row>
-    <row r="795" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="795" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A795" s="72" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B795" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C795" s="73">
-        <v>3435</v>
+        <v>3126</v>
       </c>
       <c r="D795" s="74" t="s">
         <v>15</v>
@@ -18725,16 +18732,16 @@
     </row>
     <row r="796" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="72" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B796" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C796" s="73">
-        <v>3436</v>
+        <v>3127</v>
       </c>
       <c r="D796" s="74" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E796" s="48">
         <v>60.5</v>
@@ -18742,13 +18749,13 @@
     </row>
     <row r="797" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A797" s="72" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B797" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C797" s="73">
-        <v>3128</v>
+        <v>3435</v>
       </c>
       <c r="D797" s="74" t="s">
         <v>15</v>
@@ -18759,30 +18766,30 @@
     </row>
     <row r="798" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A798" s="72" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B798" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C798" s="73">
-        <v>3129</v>
+        <v>3436</v>
       </c>
       <c r="D798" s="74" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E798" s="48">
         <v>60.5</v>
       </c>
     </row>
-    <row r="799" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A799" s="72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B799" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C799" s="73">
-        <v>4158</v>
+        <v>3128</v>
       </c>
       <c r="D799" s="74" t="s">
         <v>15</v>
@@ -18791,15 +18798,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="800" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B800" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C800" s="73">
-        <v>4159</v>
+        <v>3129</v>
       </c>
       <c r="D800" s="74" t="s">
         <v>20</v>
@@ -18810,271 +18817,271 @@
     </row>
     <row r="801" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="72" t="s">
-        <v>1325</v>
+        <v>435</v>
       </c>
       <c r="B801" s="72" t="s">
-        <v>1124</v>
+        <v>18</v>
       </c>
       <c r="C801" s="73">
-        <v>4561</v>
+        <v>4158</v>
       </c>
       <c r="D801" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E801" s="48">
-        <v>138</v>
+        <v>121</v>
       </c>
     </row>
     <row r="802" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="72" t="s">
-        <v>1325</v>
+        <v>435</v>
       </c>
       <c r="B802" s="72" t="s">
-        <v>1326</v>
+        <v>19</v>
       </c>
       <c r="C802" s="73">
-        <v>4562</v>
+        <v>4159</v>
       </c>
       <c r="D802" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E802" s="48">
-        <v>69</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="803" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A803" s="72" t="s">
-        <v>436</v>
+        <v>1325</v>
       </c>
       <c r="B803" s="72" t="s">
-        <v>18</v>
+        <v>1124</v>
       </c>
       <c r="C803" s="73">
-        <v>3124</v>
+        <v>4561</v>
       </c>
       <c r="D803" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E803" s="48">
-        <v>161</v>
+        <v>138</v>
       </c>
     </row>
     <row r="804" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="72" t="s">
-        <v>436</v>
+        <v>1325</v>
       </c>
       <c r="B804" s="72" t="s">
-        <v>19</v>
+        <v>1326</v>
       </c>
       <c r="C804" s="73">
-        <v>2824</v>
+        <v>4562</v>
       </c>
       <c r="D804" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E804" s="48">
-        <v>80.5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="805" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A805" s="72" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B805" s="72" t="s">
         <v>18</v>
       </c>
       <c r="C805" s="73">
-        <v>3130</v>
+        <v>3124</v>
       </c>
       <c r="D805" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E805" s="48">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="806" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="72" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B806" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C806" s="73">
-        <v>3131</v>
+        <v>2824</v>
       </c>
       <c r="D806" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E806" s="48">
-        <v>69</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="807" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="72" t="s">
-        <v>1199</v>
+        <v>437</v>
       </c>
       <c r="B807" s="72" t="s">
-        <v>1154</v>
+        <v>18</v>
       </c>
       <c r="C807" s="73">
-        <v>4346</v>
+        <v>3130</v>
       </c>
       <c r="D807" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E807" s="48">
-        <v>328</v>
+        <v>138</v>
       </c>
     </row>
     <row r="808" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="72" t="s">
-        <v>1200</v>
+        <v>437</v>
       </c>
       <c r="B808" s="72" t="s">
-        <v>1154</v>
+        <v>19</v>
       </c>
       <c r="C808" s="73">
-        <v>4345</v>
+        <v>3131</v>
       </c>
       <c r="D808" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E808" s="48">
-        <v>328</v>
+        <v>69</v>
       </c>
     </row>
     <row r="809" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="72" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="B809" s="72" t="s">
-        <v>1130</v>
+        <v>1154</v>
       </c>
       <c r="C809" s="73">
-        <v>4347</v>
+        <v>4346</v>
       </c>
       <c r="D809" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E809" s="48">
-        <v>274</v>
+        <v>328</v>
       </c>
     </row>
     <row r="810" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="72" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B810" s="72" t="s">
         <v>1154</v>
       </c>
       <c r="C810" s="73">
-        <v>4446</v>
+        <v>4345</v>
       </c>
       <c r="D810" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E810" s="48">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="811" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="72" t="s">
-        <v>438</v>
+        <v>1201</v>
       </c>
       <c r="B811" s="72" t="s">
-        <v>78</v>
+        <v>1130</v>
       </c>
       <c r="C811" s="73">
-        <v>4476</v>
+        <v>4347</v>
       </c>
       <c r="D811" s="74" t="s">
-        <v>412</v>
+        <v>15</v>
       </c>
       <c r="E811" s="48">
-        <v>30</v>
+        <v>274</v>
       </c>
     </row>
     <row r="812" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="72" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B812" s="72" t="s">
         <v>1154</v>
       </c>
       <c r="C812" s="73">
-        <v>4348</v>
+        <v>4446</v>
       </c>
       <c r="D812" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E812" s="48">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="813" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="72" t="s">
-        <v>1204</v>
+        <v>438</v>
       </c>
       <c r="B813" s="72" t="s">
-        <v>1205</v>
+        <v>78</v>
       </c>
       <c r="C813" s="73">
-        <v>4456</v>
+        <v>4476</v>
       </c>
       <c r="D813" s="74" t="s">
-        <v>160</v>
+        <v>412</v>
       </c>
       <c r="E813" s="48">
-        <v>69</v>
+        <v>30</v>
       </c>
     </row>
     <row r="814" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="72" t="s">
-        <v>444</v>
+        <v>1203</v>
       </c>
       <c r="B814" s="72" t="s">
-        <v>110</v>
+        <v>1154</v>
       </c>
       <c r="C814" s="73">
-        <v>4051</v>
+        <v>4348</v>
       </c>
       <c r="D814" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E814" s="48">
-        <v>72</v>
+        <v>328</v>
       </c>
     </row>
     <row r="815" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="72" t="s">
-        <v>1313</v>
+        <v>1204</v>
       </c>
       <c r="B815" s="72" t="s">
-        <v>1149</v>
+        <v>1205</v>
       </c>
       <c r="C815" s="73">
-        <v>4408</v>
+        <v>4456</v>
       </c>
       <c r="D815" s="74" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E815" s="48">
-        <v>92</v>
+        <v>69</v>
       </c>
     </row>
     <row r="816" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="72" t="s">
-        <v>1211</v>
+        <v>444</v>
       </c>
       <c r="B816" s="72" t="s">
-        <v>1149</v>
+        <v>110</v>
       </c>
       <c r="C816" s="73">
-        <v>4341</v>
+        <v>4051</v>
       </c>
       <c r="D816" s="74" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="E816" s="48">
         <v>72</v>
@@ -19082,319 +19089,319 @@
     </row>
     <row r="817" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="72" t="s">
-        <v>448</v>
+        <v>1313</v>
       </c>
       <c r="B817" s="72" t="s">
-        <v>145</v>
+        <v>1149</v>
       </c>
       <c r="C817" s="73">
-        <v>4265</v>
+        <v>4408</v>
       </c>
       <c r="D817" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E817" s="48">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="818" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="72" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B818" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C818" s="73">
-        <v>4266</v>
+        <v>4341</v>
       </c>
       <c r="D818" s="74" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E818" s="48">
-        <v>81.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="819" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="72" t="s">
-        <v>1213</v>
+        <v>448</v>
       </c>
       <c r="B819" s="72" t="s">
-        <v>1149</v>
+        <v>145</v>
       </c>
       <c r="C819" s="73">
-        <v>4269</v>
+        <v>4265</v>
       </c>
       <c r="D819" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E819" s="48">
-        <v>87.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="820" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="72" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="B820" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C820" s="73">
-        <v>4273</v>
+        <v>4266</v>
       </c>
       <c r="D820" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E820" s="48">
-        <v>94</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="821" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="72" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B821" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C821" s="73">
-        <v>4405</v>
+        <v>4269</v>
       </c>
       <c r="D821" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E821" s="48">
-        <v>78</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="822" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="72" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B822" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C822" s="73">
-        <v>4406</v>
+        <v>4273</v>
       </c>
       <c r="D822" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E822" s="48">
-        <v>130</v>
+        <v>94</v>
       </c>
     </row>
     <row r="823" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="72" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B823" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C823" s="73">
-        <v>4267</v>
+        <v>4405</v>
       </c>
       <c r="D823" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E823" s="48">
-        <v>81.5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="824" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="72" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B824" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C824" s="73">
-        <v>4271</v>
+        <v>4406</v>
       </c>
       <c r="D824" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E824" s="48">
-        <v>87.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="825" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="72" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B825" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C825" s="73">
-        <v>4276</v>
+        <v>4267</v>
       </c>
       <c r="D825" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E825" s="48">
-        <v>119</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="826" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="72" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B826" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C826" s="73">
-        <v>4342</v>
+        <v>4271</v>
       </c>
       <c r="D826" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E826" s="48">
-        <v>114</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="827" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="72" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B827" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C827" s="73">
-        <v>4398</v>
+        <v>4276</v>
       </c>
       <c r="D827" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E827" s="48">
-        <v>84</v>
+        <v>119</v>
       </c>
     </row>
     <row r="828" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="72" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B828" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C828" s="73">
-        <v>4270</v>
+        <v>4342</v>
       </c>
       <c r="D828" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E828" s="48">
-        <v>87.5</v>
+        <v>114</v>
       </c>
     </row>
     <row r="829" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="72" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B829" s="72" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="C829" s="73">
-        <v>4275</v>
+        <v>4398</v>
       </c>
       <c r="D829" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E829" s="48">
-        <v>54</v>
+        <v>84</v>
       </c>
     </row>
     <row r="830" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="72" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B830" s="72" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="C830" s="73">
-        <v>4274</v>
+        <v>4270</v>
       </c>
       <c r="D830" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E830" s="48">
-        <v>54</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="831" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="72" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B831" s="72" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="C831" s="73">
-        <v>4399</v>
+        <v>4275</v>
       </c>
       <c r="D831" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E831" s="48">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="832" spans="1:5" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="832" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A832" s="72" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B832" s="72" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="C832" s="73">
-        <v>4404</v>
+        <v>4274</v>
       </c>
       <c r="D832" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E832" s="48">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="833" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="833" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A833" s="72" t="s">
-        <v>449</v>
+        <v>1225</v>
       </c>
       <c r="B833" s="72" t="s">
-        <v>145</v>
+        <v>1149</v>
       </c>
       <c r="C833" s="73">
-        <v>4262</v>
+        <v>4399</v>
       </c>
       <c r="D833" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E833" s="48">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="834" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="834" spans="1:5" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="72" t="s">
-        <v>450</v>
+        <v>1226</v>
       </c>
       <c r="B834" s="72" t="s">
-        <v>145</v>
+        <v>1149</v>
       </c>
       <c r="C834" s="73">
-        <v>4263</v>
+        <v>4404</v>
       </c>
       <c r="D834" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E834" s="48">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="835" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="835" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="72" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B835" s="72" t="s">
         <v>145</v>
       </c>
       <c r="C835" s="73">
-        <v>4264</v>
+        <v>4262</v>
       </c>
       <c r="D835" s="74" t="s">
         <v>20</v>
@@ -19405,458 +19412,458 @@
     </row>
     <row r="836" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="72" t="s">
-        <v>1227</v>
+        <v>450</v>
       </c>
       <c r="B836" s="72" t="s">
-        <v>1149</v>
+        <v>145</v>
       </c>
       <c r="C836" s="73">
-        <v>4407</v>
+        <v>4263</v>
       </c>
       <c r="D836" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E836" s="48">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="837" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A837" s="72" t="s">
-        <v>1228</v>
+        <v>451</v>
       </c>
       <c r="B837" s="72" t="s">
-        <v>1149</v>
+        <v>145</v>
       </c>
       <c r="C837" s="73">
-        <v>4397</v>
+        <v>4264</v>
       </c>
       <c r="D837" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E837" s="48">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="838" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A838" s="72" t="s">
-        <v>452</v>
+        <v>1227</v>
       </c>
       <c r="B838" s="72" t="s">
-        <v>145</v>
+        <v>1149</v>
       </c>
       <c r="C838" s="73">
-        <v>4343</v>
+        <v>4407</v>
       </c>
       <c r="D838" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E838" s="48">
-        <v>67</v>
+        <v>92</v>
       </c>
     </row>
     <row r="839" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A839" s="72" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B839" s="72" t="s">
         <v>1149</v>
       </c>
       <c r="C839" s="73">
-        <v>4268</v>
+        <v>4397</v>
       </c>
       <c r="D839" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E839" s="48">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="840" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A840" s="72" t="s">
+        <v>452</v>
+      </c>
+      <c r="B840" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C840" s="73">
+        <v>4343</v>
+      </c>
+      <c r="D840" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E840" s="48">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="841" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A841" s="72" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B841" s="72" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C841" s="73">
+        <v>4268</v>
+      </c>
+      <c r="D841" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E841" s="48">
         <v>81.5</v>
-      </c>
-    </row>
-    <row r="840" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A840" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B840" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C840" s="70">
-        <v>2833</v>
-      </c>
-      <c r="D840" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E840" s="40">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="841" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A841" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B841" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C841" s="70">
-        <v>3125</v>
-      </c>
-      <c r="D841" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E841" s="40">
-        <v>162</v>
       </c>
     </row>
     <row r="842" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A842" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B842" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C842" s="70">
+        <v>2833</v>
+      </c>
+      <c r="D842" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E842" s="40">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="843" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A843" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="B843" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C842" s="70">
-        <v>3752</v>
-      </c>
-      <c r="D842" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E842" s="40">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="843" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A843" s="72" t="s">
-        <v>62</v>
-      </c>
-      <c r="B843" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C843" s="73">
-        <v>3753</v>
-      </c>
-      <c r="D843" s="72" t="s">
-        <v>49</v>
-      </c>
-      <c r="E843" s="50">
-        <v>83</v>
+      <c r="C843" s="70">
+        <v>3125</v>
+      </c>
+      <c r="D843" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E843" s="40">
+        <v>162</v>
       </c>
     </row>
     <row r="844" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A844" s="69" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B844" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C844" s="70">
+        <v>3752</v>
+      </c>
+      <c r="D844" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E844" s="40">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="845" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A845" s="72" t="s">
+        <v>62</v>
+      </c>
+      <c r="B845" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="C844" s="70">
-        <v>2511</v>
-      </c>
-      <c r="D844" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="E844" s="40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="845" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A845" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="B845" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="C845" s="70">
-        <v>4311</v>
-      </c>
-      <c r="D845" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="E845" s="40">
-        <v>65</v>
+      <c r="C845" s="73">
+        <v>3753</v>
+      </c>
+      <c r="D845" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="E845" s="50">
+        <v>83</v>
       </c>
     </row>
     <row r="846" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A846" s="69" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B846" s="69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C846" s="70">
-        <v>4046</v>
+        <v>2511</v>
       </c>
       <c r="D846" s="69" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="E846" s="40">
-        <v>166</v>
+        <v>61</v>
       </c>
     </row>
     <row r="847" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A847" s="69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B847" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C847" s="70">
-        <v>4047</v>
+        <v>4311</v>
       </c>
       <c r="D847" s="69" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E847" s="40">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="848" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A848" s="69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B848" s="69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C848" s="70">
-        <v>4312</v>
+        <v>4046</v>
       </c>
       <c r="D848" s="69" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E848" s="40">
-        <v>65</v>
+        <v>166</v>
       </c>
     </row>
     <row r="849" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A849" s="69" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B849" s="69" t="s">
         <v>19</v>
       </c>
       <c r="C849" s="70">
+        <v>4047</v>
+      </c>
+      <c r="D849" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E849" s="40">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="850" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A850" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B850" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C850" s="70">
+        <v>4312</v>
+      </c>
+      <c r="D850" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E850" s="40">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="851" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A851" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B851" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C851" s="70">
         <v>4310</v>
       </c>
-      <c r="D849" s="69" t="s">
+      <c r="D851" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="E849" s="40">
+      <c r="E851" s="40">
         <v>65</v>
-      </c>
-    </row>
-    <row r="850" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A850" s="72" t="s">
-        <v>1230</v>
-      </c>
-      <c r="B850" s="72" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C850" s="73">
-        <v>4074</v>
-      </c>
-      <c r="D850" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E850" s="48">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="851" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A851" s="72" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B851" s="72" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C851" s="73">
-        <v>4076</v>
-      </c>
-      <c r="D851" s="74" t="s">
-        <v>453</v>
-      </c>
-      <c r="E851" s="48">
-        <v>24</v>
       </c>
     </row>
     <row r="852" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A852" s="72" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="B852" s="72" t="s">
-        <v>1205</v>
+        <v>1231</v>
       </c>
       <c r="C852" s="73">
-        <v>4133</v>
+        <v>4074</v>
       </c>
       <c r="D852" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E852" s="48">
-        <v>72</v>
+        <v>27</v>
       </c>
     </row>
     <row r="853" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A853" s="72" t="s">
-        <v>455</v>
+        <v>1232</v>
       </c>
       <c r="B853" s="72" t="s">
-        <v>120</v>
+        <v>1233</v>
       </c>
       <c r="C853" s="73">
-        <v>3068</v>
+        <v>4076</v>
       </c>
       <c r="D853" s="74" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="E853" s="48">
-        <v>372</v>
+        <v>24</v>
       </c>
     </row>
     <row r="854" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A854" s="72" t="s">
-        <v>455</v>
+        <v>1234</v>
       </c>
       <c r="B854" s="72" t="s">
-        <v>19</v>
+        <v>1205</v>
       </c>
       <c r="C854" s="73">
-        <v>3087</v>
+        <v>4133</v>
       </c>
       <c r="D854" s="74" t="s">
-        <v>15</v>
+        <v>453</v>
       </c>
       <c r="E854" s="48">
-        <v>124</v>
+        <v>72</v>
       </c>
     </row>
     <row r="855" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A855" s="72" t="s">
-        <v>1324</v>
+        <v>455</v>
       </c>
       <c r="B855" s="72" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="C855" s="73">
-        <v>4560</v>
+        <v>3068</v>
       </c>
       <c r="D855" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E855" s="48">
-        <v>195</v>
+        <v>372</v>
       </c>
     </row>
     <row r="856" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A856" s="72" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B856" s="72" t="s">
-        <v>1130</v>
+        <v>19</v>
       </c>
       <c r="C856" s="73">
-        <v>4531</v>
+        <v>3087</v>
       </c>
       <c r="D856" s="74" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E856" s="48">
-        <v>880</v>
+        <v>124</v>
       </c>
     </row>
     <row r="857" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="72" t="s">
-        <v>456</v>
+        <v>1324</v>
       </c>
       <c r="B857" s="72" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="C857" s="73">
-        <v>4532</v>
+        <v>4560</v>
       </c>
       <c r="D857" s="74" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E857" s="48">
-        <v>88</v>
+        <v>195</v>
       </c>
     </row>
     <row r="858" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A858" s="72" t="s">
-        <v>1323</v>
+        <v>456</v>
       </c>
       <c r="B858" s="72" t="s">
-        <v>1164</v>
+        <v>1130</v>
       </c>
       <c r="C858" s="73">
-        <v>4559</v>
+        <v>4531</v>
       </c>
       <c r="D858" s="74" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E858" s="48">
-        <v>210</v>
+        <v>880</v>
       </c>
     </row>
     <row r="859" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="72" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B859" s="72" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="C859" s="73">
-        <v>4493</v>
+        <v>4532</v>
       </c>
       <c r="D859" s="74" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E859" s="48">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="860" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="72" t="s">
-        <v>1236</v>
+        <v>1323</v>
       </c>
       <c r="B860" s="72" t="s">
-        <v>1237</v>
+        <v>1164</v>
       </c>
       <c r="C860" s="73">
-        <v>4102</v>
+        <v>4559</v>
       </c>
       <c r="D860" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E860" s="48">
-        <v>77</v>
+        <v>210</v>
       </c>
     </row>
     <row r="861" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="72" t="s">
-        <v>1238</v>
+        <v>457</v>
       </c>
       <c r="B861" s="72" t="s">
-        <v>1237</v>
+        <v>145</v>
       </c>
       <c r="C861" s="73">
-        <v>4103</v>
+        <v>4493</v>
       </c>
       <c r="D861" s="74" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E861" s="48">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="862" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="72" t="s">
-        <v>1314</v>
+        <v>1236</v>
       </c>
       <c r="B862" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C862" s="73">
-        <v>4547</v>
+        <v>4102</v>
       </c>
       <c r="D862" s="74" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E862" s="48">
         <v>77</v>
@@ -19864,13 +19871,13 @@
     </row>
     <row r="863" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="72" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B863" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C863" s="73">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="D863" s="74" t="s">
         <v>160</v>
@@ -19881,13 +19888,13 @@
     </row>
     <row r="864" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="72" t="s">
-        <v>1240</v>
+        <v>1314</v>
       </c>
       <c r="B864" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C864" s="73">
-        <v>4101</v>
+        <v>4547</v>
       </c>
       <c r="D864" s="74" t="s">
         <v>160</v>
@@ -19898,13 +19905,13 @@
     </row>
     <row r="865" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="72" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B865" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C865" s="73">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="D865" s="74" t="s">
         <v>160</v>
@@ -19913,239 +19920,239 @@
         <v>77</v>
       </c>
     </row>
-    <row r="866" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A866" s="72" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B866" s="72" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="C866" s="73">
-        <v>3705</v>
+        <v>4101</v>
       </c>
       <c r="D866" s="74" t="s">
         <v>160</v>
       </c>
       <c r="E866" s="48">
-        <v>123.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="867" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="72" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="B867" s="72" t="s">
         <v>1237</v>
       </c>
       <c r="C867" s="73">
-        <v>3823</v>
+        <v>4105</v>
       </c>
       <c r="D867" s="74" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E867" s="48">
         <v>77</v>
       </c>
     </row>
-    <row r="868" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="72" t="s">
-        <v>1337</v>
+        <v>1242</v>
       </c>
       <c r="B868" s="72" t="s">
-        <v>1338</v>
+        <v>1243</v>
       </c>
       <c r="C868" s="73">
-        <v>4583</v>
+        <v>3705</v>
       </c>
       <c r="D868" s="74" t="s">
         <v>160</v>
       </c>
       <c r="E868" s="48">
-        <v>144</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="869" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="72" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B869" s="72" t="s">
-        <v>1246</v>
+        <v>1237</v>
       </c>
       <c r="C869" s="73">
-        <v>4308</v>
+        <v>3823</v>
       </c>
       <c r="D869" s="74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E869" s="48">
-        <v>68.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="870" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="72" t="s">
-        <v>1247</v>
+        <v>1337</v>
       </c>
       <c r="B870" s="72" t="s">
-        <v>1246</v>
+        <v>1338</v>
       </c>
       <c r="C870" s="73">
-        <v>4309</v>
+        <v>4583</v>
       </c>
       <c r="D870" s="74" t="s">
-        <v>453</v>
+        <v>160</v>
       </c>
       <c r="E870" s="48">
-        <v>68.5</v>
+        <v>144</v>
       </c>
     </row>
     <row r="871" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A871" s="72" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="B871" s="72" t="s">
-        <v>1149</v>
+        <v>1246</v>
       </c>
       <c r="C871" s="73">
-        <v>4412</v>
+        <v>4308</v>
       </c>
       <c r="D871" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E871" s="48">
-        <v>71.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="872" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A872" s="72" t="s">
-        <v>459</v>
+        <v>1247</v>
       </c>
       <c r="B872" s="72" t="s">
-        <v>33</v>
+        <v>1246</v>
       </c>
       <c r="C872" s="73">
-        <v>4413</v>
+        <v>4309</v>
       </c>
       <c r="D872" s="74" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="E872" s="48">
-        <v>496</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="873" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A873" s="72" t="s">
-        <v>459</v>
+        <v>1248</v>
       </c>
       <c r="B873" s="72" t="s">
-        <v>19</v>
+        <v>1149</v>
       </c>
       <c r="C873" s="73">
-        <v>4414</v>
+        <v>4412</v>
       </c>
       <c r="D873" s="74" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="E873" s="48">
-        <v>101</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="874" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="72" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B874" s="72" t="s">
         <v>33</v>
       </c>
       <c r="C874" s="73">
-        <v>4415</v>
+        <v>4413</v>
       </c>
       <c r="D874" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E874" s="48">
-        <v>414</v>
+        <v>496</v>
       </c>
     </row>
     <row r="875" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="72" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B875" s="72" t="s">
         <v>19</v>
       </c>
       <c r="C875" s="73">
-        <v>4416</v>
+        <v>4414</v>
       </c>
       <c r="D875" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E875" s="48">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="876" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="876" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="72" t="s">
-        <v>1254</v>
+        <v>460</v>
       </c>
       <c r="B876" s="72" t="s">
-        <v>1255</v>
+        <v>33</v>
       </c>
       <c r="C876" s="73">
-        <v>4475</v>
+        <v>4415</v>
       </c>
       <c r="D876" s="74" t="s">
         <v>20</v>
       </c>
       <c r="E876" s="48">
-        <v>8</v>
+        <v>414</v>
       </c>
     </row>
     <row r="877" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="72" t="s">
-        <v>1256</v>
+        <v>460</v>
       </c>
       <c r="B877" s="72" t="s">
-        <v>1257</v>
+        <v>19</v>
       </c>
       <c r="C877" s="73">
-        <v>4354</v>
+        <v>4416</v>
       </c>
       <c r="D877" s="74" t="s">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="E877" s="48">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="878" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="878" spans="1:5" s="39" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="72" t="s">
-        <v>1335</v>
+        <v>1254</v>
       </c>
       <c r="B878" s="72" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C878" s="73">
-        <v>4445</v>
+        <v>4475</v>
       </c>
       <c r="D878" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E878" s="48">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="879" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="72" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B879" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C879" s="73">
-        <v>4353</v>
+        <v>4354</v>
       </c>
       <c r="D879" s="74" t="s">
-        <v>50</v>
+        <v>412</v>
       </c>
       <c r="E879" s="48">
         <v>74</v>
@@ -20153,16 +20160,16 @@
     </row>
     <row r="880" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="72" t="s">
-        <v>1259</v>
+        <v>1335</v>
       </c>
       <c r="B880" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C880" s="73">
-        <v>4350</v>
+        <v>4445</v>
       </c>
       <c r="D880" s="74" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E880" s="48">
         <v>74</v>
@@ -20170,13 +20177,13 @@
     </row>
     <row r="881" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="72" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B881" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C881" s="73">
-        <v>4352</v>
+        <v>4353</v>
       </c>
       <c r="D881" s="74" t="s">
         <v>50</v>
@@ -20187,13 +20194,13 @@
     </row>
     <row r="882" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A882" s="72" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="B882" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C882" s="73">
-        <v>4349</v>
+        <v>4350</v>
       </c>
       <c r="D882" s="74" t="s">
         <v>50</v>
@@ -20204,13 +20211,13 @@
     </row>
     <row r="883" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A883" s="72" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B883" s="72" t="s">
         <v>1257</v>
       </c>
       <c r="C883" s="73">
-        <v>4351</v>
+        <v>4352</v>
       </c>
       <c r="D883" s="74" t="s">
         <v>50</v>
@@ -20220,154 +20227,174 @@
       </c>
     </row>
     <row r="884" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A884" s="96" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B884" s="96" t="s">
+      <c r="A884" s="72" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B884" s="72" t="s">
         <v>1257</v>
       </c>
-      <c r="C884" s="97">
-        <v>4581</v>
-      </c>
-      <c r="D884" s="96" t="s">
-        <v>15</v>
+      <c r="C884" s="73">
+        <v>4349</v>
+      </c>
+      <c r="D884" s="74" t="s">
+        <v>50</v>
       </c>
       <c r="E884" s="48">
         <v>74</v>
       </c>
     </row>
     <row r="885" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A885" s="80" t="s">
+      <c r="A885" s="72" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B885" s="72" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C885" s="73">
+        <v>4351</v>
+      </c>
+      <c r="D885" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="E885" s="48">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="886" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A886" s="96" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B886" s="96" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C886" s="97">
+        <v>4581</v>
+      </c>
+      <c r="D886" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="E886" s="48">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="887" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A887" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="B885" s="80" t="s">
+      <c r="B887" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="C885" s="81">
+      <c r="C887" s="81">
         <v>4096</v>
       </c>
-      <c r="D885" s="80" t="s">
-        <v>49</v>
-      </c>
-      <c r="E885" s="42">
+      <c r="D887" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="E887" s="42">
         <v>79</v>
-      </c>
-    </row>
-    <row r="886" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A886" s="72" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B886" s="72" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C886" s="73">
-        <v>4123</v>
-      </c>
-      <c r="D886" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E886" s="48">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="887" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A887" s="72" t="s">
-        <v>1275</v>
-      </c>
-      <c r="B887" s="72" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C887" s="73">
-        <v>4306</v>
-      </c>
-      <c r="D887" s="74" t="s">
-        <v>453</v>
-      </c>
-      <c r="E887" s="48">
-        <v>81</v>
       </c>
     </row>
     <row r="888" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A888" s="72" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="B888" s="72" t="s">
-        <v>1237</v>
+        <v>1274</v>
       </c>
       <c r="C888" s="73">
-        <v>4307</v>
+        <v>4123</v>
       </c>
       <c r="D888" s="74" t="s">
-        <v>453</v>
+        <v>20</v>
       </c>
       <c r="E888" s="48">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="889" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="72" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B889" s="72" t="s">
-        <v>1278</v>
+        <v>1237</v>
       </c>
       <c r="C889" s="73">
-        <v>2659</v>
-      </c>
-      <c r="D889" s="72" t="s">
-        <v>160</v>
-      </c>
-      <c r="E889" s="50">
-        <v>27.5</v>
+        <v>4306</v>
+      </c>
+      <c r="D889" s="74" t="s">
+        <v>453</v>
+      </c>
+      <c r="E889" s="48">
+        <v>81</v>
       </c>
     </row>
     <row r="890" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A890" s="72" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B890" s="72" t="s">
-        <v>1279</v>
+        <v>1237</v>
       </c>
       <c r="C890" s="73">
-        <v>2621</v>
-      </c>
-      <c r="D890" s="72" t="s">
-        <v>160</v>
-      </c>
-      <c r="E890" s="50">
-        <v>24.5</v>
+        <v>4307</v>
+      </c>
+      <c r="D890" s="74" t="s">
+        <v>453</v>
+      </c>
+      <c r="E890" s="48">
+        <v>81</v>
       </c>
     </row>
     <row r="891" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A891" s="72" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="B891" s="72" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="C891" s="73">
-        <v>3656</v>
+        <v>2659</v>
       </c>
       <c r="D891" s="72" t="s">
         <v>160</v>
       </c>
       <c r="E891" s="50">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="892" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A892" s="72" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B892" s="72" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C892" s="73">
+        <v>2621</v>
+      </c>
+      <c r="D892" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="E892" s="50">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="893" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A893" s="72" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B893" s="72" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C893" s="73">
+        <v>3656</v>
+      </c>
+      <c r="D893" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="E893" s="50">
         <v>27</v>
       </c>
-    </row>
-    <row r="892" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A892" s="99"/>
-      <c r="B892" s="99"/>
-      <c r="C892" s="99"/>
-      <c r="D892" s="99"/>
-      <c r="E892" s="100"/>
-    </row>
-    <row r="893" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A893" s="99"/>
-      <c r="B893" s="99"/>
-      <c r="C893" s="99"/>
-      <c r="D893" s="99"/>
-      <c r="E893" s="100"/>
     </row>
     <row r="894" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="99"/>
@@ -20376,272 +20403,284 @@
       <c r="D894" s="99"/>
       <c r="E894" s="100"/>
     </row>
-    <row r="895" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A895" s="102" t="s">
+    <row r="895" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A895" s="99"/>
+      <c r="B895" s="99"/>
+      <c r="C895" s="99"/>
+      <c r="D895" s="99"/>
+      <c r="E895" s="100"/>
+    </row>
+    <row r="896" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A896" s="99"/>
+      <c r="B896" s="99"/>
+      <c r="C896" s="99"/>
+      <c r="D896" s="99"/>
+      <c r="E896" s="100"/>
+    </row>
+    <row r="897" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A897" s="102" t="s">
         <v>1288</v>
       </c>
-      <c r="B895" s="103"/>
-      <c r="C895" s="103"/>
-      <c r="D895" s="103"/>
-      <c r="E895" s="104"/>
-    </row>
-    <row r="896" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A896" s="87" t="s">
+      <c r="B897" s="103"/>
+      <c r="C897" s="103"/>
+      <c r="D897" s="103"/>
+      <c r="E897" s="104"/>
+    </row>
+    <row r="898" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A898" s="87" t="s">
         <v>1291</v>
       </c>
-      <c r="B896" s="87" t="s">
+      <c r="B898" s="87" t="s">
         <v>1289</v>
       </c>
-      <c r="C896" s="88">
+      <c r="C898" s="88">
         <v>3460</v>
       </c>
-      <c r="D896" s="89" t="s">
+      <c r="D898" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E896" s="63">
+      <c r="E898" s="63">
         <v>90</v>
-      </c>
-    </row>
-    <row r="897" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A897" s="72" t="s">
-        <v>1290</v>
-      </c>
-      <c r="B897" s="72" t="s">
-        <v>1289</v>
-      </c>
-      <c r="C897" s="73">
-        <v>3459</v>
-      </c>
-      <c r="D897" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E897" s="48">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="898" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A898" s="72" t="s">
-        <v>1292</v>
-      </c>
-      <c r="B898" s="72" t="s">
-        <v>1289</v>
-      </c>
-      <c r="C898" s="73">
-        <v>3803</v>
-      </c>
-      <c r="D898" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E898" s="48">
-        <v>23</v>
       </c>
     </row>
     <row r="899" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="72" t="s">
-        <v>478</v>
+        <v>1290</v>
       </c>
       <c r="B899" s="72" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="C899" s="73">
-        <v>3425</v>
+        <v>3459</v>
       </c>
       <c r="D899" s="74" t="s">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="E899" s="48">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="900" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="72" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="B900" s="72" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="C900" s="73">
-        <v>3426</v>
+        <v>3803</v>
       </c>
       <c r="D900" s="74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E900" s="48">
-        <v>276</v>
+        <v>23</v>
       </c>
     </row>
     <row r="901" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="72" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B901" s="72" t="s">
         <v>1294</v>
       </c>
       <c r="C901" s="73">
-        <v>3427</v>
+        <v>3425</v>
       </c>
       <c r="D901" s="74" t="s">
         <v>412</v>
       </c>
       <c r="E901" s="48">
-        <v>62.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="902" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="72" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B902" s="72" t="s">
         <v>1293</v>
       </c>
       <c r="C902" s="73">
-        <v>3428</v>
+        <v>3426</v>
       </c>
       <c r="D902" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E902" s="48">
-        <v>582</v>
+        <v>276</v>
       </c>
     </row>
     <row r="903" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="72" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B903" s="72" t="s">
         <v>1294</v>
       </c>
       <c r="C903" s="73">
-        <v>3429</v>
+        <v>3427</v>
       </c>
       <c r="D903" s="74" t="s">
         <v>412</v>
       </c>
       <c r="E903" s="48">
-        <v>76.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="904" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="72" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B904" s="72" t="s">
         <v>1293</v>
       </c>
       <c r="C904" s="73">
-        <v>3430</v>
+        <v>3428</v>
       </c>
       <c r="D904" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E904" s="48">
-        <v>714.5</v>
+        <v>582</v>
       </c>
     </row>
     <row r="905" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="72" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B905" s="72" t="s">
         <v>1294</v>
       </c>
       <c r="C905" s="73">
-        <v>3913</v>
+        <v>3429</v>
       </c>
       <c r="D905" s="74" t="s">
         <v>412</v>
       </c>
       <c r="E905" s="48">
-        <v>68</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="906" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="72" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B906" s="72" t="s">
         <v>1293</v>
       </c>
       <c r="C906" s="73">
-        <v>3872</v>
+        <v>3430</v>
       </c>
       <c r="D906" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E906" s="48">
-        <v>636</v>
+        <v>714.5</v>
       </c>
     </row>
     <row r="907" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="72" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B907" s="72" t="s">
         <v>1294</v>
       </c>
       <c r="C907" s="73">
-        <v>3422</v>
+        <v>3913</v>
       </c>
       <c r="D907" s="74" t="s">
         <v>412</v>
       </c>
       <c r="E907" s="48">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="908" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A908" s="72" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B908" s="72" t="s">
         <v>1293</v>
       </c>
       <c r="C908" s="73">
-        <v>3423</v>
+        <v>3872</v>
       </c>
       <c r="D908" s="74" t="s">
         <v>15</v>
       </c>
       <c r="E908" s="48">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="909" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A909" s="83" t="s">
-        <v>483</v>
-      </c>
-      <c r="B909" s="83" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C909" s="84">
-        <v>3431</v>
+        <v>636</v>
+      </c>
+    </row>
+    <row r="909" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A909" s="72" t="s">
+        <v>482</v>
+      </c>
+      <c r="B909" s="72" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C909" s="73">
+        <v>3422</v>
       </c>
       <c r="D909" s="74" t="s">
         <v>412</v>
       </c>
       <c r="E909" s="48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="910" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A910" s="72" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B910" s="72" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C910" s="73">
+        <v>3423</v>
+      </c>
+      <c r="D910" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E910" s="48">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="911" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A911" s="83" t="s">
+        <v>483</v>
+      </c>
+      <c r="B911" s="83" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C911" s="84">
+        <v>3431</v>
+      </c>
+      <c r="D911" s="74" t="s">
+        <v>412</v>
+      </c>
+      <c r="E911" s="48">
         <v>115</v>
       </c>
     </row>
-    <row r="910" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A910" s="90" t="s">
+    <row r="912" spans="1:5" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A912" s="90" t="s">
         <v>483</v>
       </c>
-      <c r="B910" s="90" t="s">
+      <c r="B912" s="90" t="s">
         <v>1293</v>
       </c>
-      <c r="C910" s="91">
+      <c r="C912" s="91">
         <v>3432</v>
       </c>
-      <c r="D910" s="92" t="s">
+      <c r="D912" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="E910" s="48">
+      <c r="E912" s="48">
         <v>1068</v>
       </c>
     </row>
-    <row r="911" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
-    <row r="912" spans="1:5" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="913" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="914" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="915" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
@@ -20649,23 +20688,25 @@
     <row r="917" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="918" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
     <row r="919" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
-    <row r="921" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A921" s="64" t="s">
+    <row r="920" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
+    <row r="921" spans="1:1" ht="15.75" x14ac:dyDescent="0.2"/>
+    <row r="923" spans="1:1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A923" s="64" t="s">
         <v>386</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A738:E738"/>
-    <mergeCell ref="A598:E598"/>
+    <mergeCell ref="A740:E740"/>
+    <mergeCell ref="A600:E600"/>
     <mergeCell ref="A214:E214"/>
     <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A776:E776"/>
-    <mergeCell ref="A730:E730"/>
-    <mergeCell ref="A749:E749"/>
-    <mergeCell ref="A750:E750"/>
+    <mergeCell ref="A778:E778"/>
+    <mergeCell ref="A732:E732"/>
+    <mergeCell ref="A751:E751"/>
+    <mergeCell ref="A752:E752"/>
     <mergeCell ref="A537:E537"/>
-    <mergeCell ref="A561:E561"/>
+    <mergeCell ref="A563:E563"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A538:E538"/>
     <mergeCell ref="A8:E8"/>
@@ -20677,7 +20718,7 @@
     <mergeCell ref="A381:E381"/>
     <mergeCell ref="A140:E140"/>
     <mergeCell ref="A215:E215"/>
-    <mergeCell ref="A895:E895"/>
+    <mergeCell ref="A897:E897"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A3:E3"/>
@@ -20686,12 +20727,12 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A287:E287"/>
-    <mergeCell ref="A599:E599"/>
-    <mergeCell ref="A718:E718"/>
-    <mergeCell ref="A739:E739"/>
+    <mergeCell ref="A601:E601"/>
+    <mergeCell ref="A720:E720"/>
+    <mergeCell ref="A741:E741"/>
     <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A560:E560"/>
-    <mergeCell ref="A717:E717"/>
+    <mergeCell ref="A562:E562"/>
+    <mergeCell ref="A719:E719"/>
     <mergeCell ref="A288:E288"/>
   </mergeCells>
   <hyperlinks>
